--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E99E0-14DB-46DE-947E-21895BFACF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCEA6A7-8CC4-439C-B14C-ED7227A42A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1089,9 +1089,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -2106,15 +2106,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2123,43 +2114,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2169,38 +2133,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2236,9 +2185,6 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2257,150 +2203,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2409,36 +2268,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2457,24 +2310,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2483,37 +2318,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2523,93 +2334,36 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2620,66 +2374,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2690,32 +2402,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2732,62 +2423,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2797,46 +2440,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2848,100 +2461,34 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2953,16 +2500,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2972,15 +2510,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2993,41 +2522,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3046,25 +2545,526 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3758,17 +3758,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M76"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="20.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.6</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3824,12 +3824,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3858,13 +3858,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="346">
+      <c r="B9" s="174">
         <f>Sheet2!Q14</f>
-        <v>80.09</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
@@ -3888,11 +3888,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="346">
+      <c r="B10" s="174">
         <f>Sheet2!Q15</f>
         <v>101.01</v>
       </c>
@@ -3918,11 +3918,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="346">
+      <c r="B11" s="174">
         <f>Sheet2!Q16</f>
         <v>120.92</v>
       </c>
@@ -3948,12 +3948,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4068,12 +4068,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -4133,12 +4133,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4189,12 +4189,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -4369,12 +4369,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -4408,12 +4408,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>71</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -4483,12 +4483,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -4611,12 +4611,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -4656,12 +4656,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>132</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>138</v>
       </c>
@@ -4701,12 +4701,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>140</v>
       </c>
@@ -4722,12 +4722,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>143</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>44</v>
       </c>
@@ -4805,12 +4805,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>152</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>155</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>155</v>
       </c>
@@ -4854,12 +4854,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>115</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>163</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>168</v>
       </c>
@@ -4981,327 +4981,327 @@
       <c r="A1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="342" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="6"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
+      <c r="H1" s="342"/>
+      <c r="I1" s="342"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="342" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="342" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
+      <c r="H3" s="342"/>
+      <c r="I3" s="342"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="342" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="7" t="s">
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="345">
         <v>22.7</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="342" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="7" t="s">
+      <c r="C6" s="342"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
+      <c r="F6" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="345">
         <v>50.2</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="342" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="7" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="342" t="s">
         <v>183</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="341">
         <v>46066</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="C8" s="342"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="342"/>
+      <c r="H8" s="342"/>
+      <c r="I8" s="342"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="343" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="C10" s="343"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="344"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="183" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="184"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="184" t="s">
         <v>188</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="P11" s="19" t="s">
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="P11" s="331" t="s">
         <v>189</v>
       </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="21"/>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
+      <c r="V11" s="332"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18" t="s">
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="18" t="s">
+      <c r="N12" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="P12" s="25" t="s">
+      <c r="P12" s="334" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="26" t="s">
+      <c r="R12" s="336"/>
+      <c r="S12" s="336"/>
+      <c r="T12" s="337" t="s">
         <v>199</v>
       </c>
-      <c r="U12" s="27" t="s">
+      <c r="U12" s="305" t="s">
         <v>200</v>
       </c>
-      <c r="V12" s="26"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="28" t="s">
+      <c r="V12" s="337"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="339" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="29">
+      <c r="A13" s="15">
         <v>80</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="15">
         <v>10</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="15">
         <v>1</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="16">
         <v>80.089508056640625</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="16">
         <v>1009.7550048828125</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="16">
         <v>0.53200346456088066</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="16">
         <v>0.52686382586796521</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="16">
         <v>5.3412013053894043</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="16">
         <v>9.155095100402832</v>
       </c>
       <c r="M13">
@@ -5312,51 +5312,51 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="32">
+      <c r="P13" s="335"/>
+      <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
       </c>
-      <c r="R13" s="32">
+      <c r="R13" s="17">
         <f>B17</f>
         <v>100</v>
       </c>
-      <c r="S13" s="32">
+      <c r="S13" s="17">
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="33"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="36"/>
+      <c r="T13" s="338"/>
+      <c r="U13" s="216"/>
+      <c r="V13" s="338"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="340"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="20">
         <v>80</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="20">
         <v>10</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="20">
         <v>1</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="21">
         <v>80.092048645019531</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="21">
         <v>1009.219970703125</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="21">
         <v>0.53090225072621677</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="21">
         <v>0.52605203254648436</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="21">
         <v>5.3462395668029785</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="21">
         <v>9.1747226715087891</v>
       </c>
       <c r="M14">
@@ -5367,68 +5367,67 @@
         <f t="shared" ref="N14:N51" si="0">ROUND(F14,4)</f>
         <v>0.53090000000000004</v>
       </c>
-      <c r="P14" s="39">
+      <c r="P14" s="22">
         <f>A14</f>
         <v>80</v>
       </c>
-      <c r="Q14" s="40">
-        <f>M14</f>
-        <v>80.09</v>
-      </c>
-      <c r="R14" s="40">
+      <c r="Q14" s="23">
+        <v>78</v>
+      </c>
+      <c r="R14" s="23">
         <f>M17</f>
         <v>80.06</v>
       </c>
-      <c r="S14" s="40">
+      <c r="S14" s="23">
         <f>M22</f>
         <v>79.8</v>
       </c>
-      <c r="T14" s="41">
+      <c r="T14" s="24">
         <f>ROUND(AVERAGE(Q14:S14),2)</f>
-        <v>79.98</v>
-      </c>
-      <c r="U14" s="42" t="str">
+        <v>79.290000000000006</v>
+      </c>
+      <c r="U14" s="25" t="str">
         <f>IF(AND(X14&lt;2), "Pass", "Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="44">
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="27">
         <f>ABS(P14-T14)</f>
-        <v>1.9999999999996021E-2</v>
-      </c>
-      <c r="Y14" s="45" t="s">
+        <v>0.70999999999999375</v>
+      </c>
+      <c r="Y14" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="46"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="37">
+      <c r="A15" s="20">
         <v>80</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="20">
         <v>10</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="20">
         <v>2</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="21">
         <v>80.040214538574219</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="21">
         <v>2009.4300537109375</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="21">
         <v>1.0568827061565376</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="21">
         <v>0.52425365436853733</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="21">
         <v>5.3467330932617188</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="21">
         <v>9.190093994140625</v>
       </c>
       <c r="M15">
@@ -5439,63 +5438,63 @@
         <f t="shared" si="0"/>
         <v>1.0569</v>
       </c>
-      <c r="P15" s="47">
+      <c r="P15" s="30">
         <f>A23</f>
         <v>100</v>
       </c>
-      <c r="Q15" s="48">
+      <c r="Q15" s="31">
         <f>M23</f>
         <v>101.01</v>
       </c>
-      <c r="R15" s="48">
+      <c r="R15" s="31">
         <f>M24</f>
         <v>101.08</v>
       </c>
-      <c r="S15" s="48">
+      <c r="S15" s="31">
         <f>M29</f>
         <v>101.05</v>
       </c>
-      <c r="T15" s="49">
+      <c r="T15" s="32">
         <f>ROUND(AVERAGE(Q15:S15),2)</f>
         <v>101.05</v>
       </c>
-      <c r="U15" s="50" t="str">
+      <c r="U15" s="14" t="str">
         <f t="shared" ref="U15:U17" si="2">IF(AND(X15&lt;2), "Pass", "Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="51">
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="33">
         <f t="shared" ref="X15:X17" si="3">ABS(P15-T15)</f>
         <v>1.0499999999999972</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="37">
+      <c r="A16" s="20">
         <v>80</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="20">
         <v>10</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="20">
         <v>3</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="21">
         <v>80.065841674804688</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="21">
         <v>3008.136962890625</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="21">
         <v>1.5836110227887408</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="21">
         <v>0.52529937371920676</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="21">
         <v>5.3418159484863281</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="21">
         <v>9.1636581420898438</v>
       </c>
       <c r="L16" t="s">
@@ -5509,63 +5508,63 @@
         <f t="shared" si="0"/>
         <v>1.5835999999999999</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="30">
         <f>A30</f>
         <v>120</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="31">
         <f>M30</f>
         <v>120.92</v>
       </c>
-      <c r="R16" s="48">
+      <c r="R16" s="31">
         <f>M34</f>
         <v>120.93</v>
       </c>
-      <c r="S16" s="48">
+      <c r="S16" s="31">
         <f>M42</f>
         <v>121.31</v>
       </c>
-      <c r="T16" s="49">
+      <c r="T16" s="32">
         <f>ROUND(AVERAGE(Q16:S16),2)</f>
         <v>121.05</v>
       </c>
-      <c r="U16" s="50" t="str">
+      <c r="U16" s="14" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="51">
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="33">
         <f t="shared" si="3"/>
         <v>1.0499999999999972</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37">
+      <c r="A17" s="20">
         <v>80</v>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="20">
         <v>100</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="20">
         <v>1</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="21">
         <v>80.063262939453125</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="21">
         <v>1007.7470092773438</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="21">
         <v>5.2957562539370615</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="21">
         <v>5.2550452653337141</v>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="21">
         <v>5.3355674743652344</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="21">
         <v>9.139195442199707</v>
       </c>
       <c r="M17">
@@ -5576,62 +5575,62 @@
         <f t="shared" si="0"/>
         <v>5.2957999999999998</v>
       </c>
-      <c r="P17" s="52">
+      <c r="P17" s="34">
         <f>A45</f>
         <v>140</v>
       </c>
-      <c r="Q17" s="53">
+      <c r="Q17" s="35">
         <f>M45</f>
         <v>141.65</v>
       </c>
-      <c r="R17" s="53">
+      <c r="R17" s="35">
         <f>M46</f>
         <v>141.59</v>
       </c>
-      <c r="S17" s="53" t="s">
+      <c r="S17" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="T17" s="54">
+      <c r="T17" s="36">
         <f>ROUND(AVERAGE(Q17:S17),2)</f>
         <v>141.62</v>
       </c>
-      <c r="U17" s="55" t="str">
+      <c r="U17" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="V17" s="56"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="57">
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="39">
         <f t="shared" si="3"/>
         <v>1.6200000000000045</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="37">
+      <c r="A18" s="20">
         <v>80</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="20">
         <v>100</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="20">
         <v>1</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="21">
         <v>80.060577392578125</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="21">
         <v>1007.7420043945313</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="21">
         <v>5.2999179850117768</v>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="21">
         <v>5.259200978481104</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="21">
         <v>5.338630199432373</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="21">
         <v>9.1521940231323242</v>
       </c>
       <c r="M18">
@@ -5642,44 +5641,44 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="58" t="s">
+      <c r="P18" s="325" t="s">
         <v>205</v>
       </c>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59"/>
-      <c r="U18" s="59"/>
-      <c r="V18" s="60"/>
-      <c r="W18" s="61"/>
-      <c r="X18" s="62"/>
+      <c r="Q18" s="326"/>
+      <c r="R18" s="326"/>
+      <c r="S18" s="326"/>
+      <c r="T18" s="326"/>
+      <c r="U18" s="326"/>
+      <c r="V18" s="327"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="41"/>
     </row>
     <row r="19" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="37">
+      <c r="A19" s="20">
         <v>80</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="20">
         <v>100</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="20">
         <v>1</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="21">
         <v>80.079856872558594</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="21">
         <v>1008.2249755859375</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="21">
         <v>5.3005181729636837</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="21">
         <v>5.257277470598992</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="21">
         <v>5.3371672630310059</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="21">
         <v>9.1413602828979492</v>
       </c>
       <c r="M19">
@@ -5690,40 +5689,40 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="63"/>
-      <c r="S19" s="63"/>
-      <c r="T19" s="63"/>
-      <c r="U19" s="63"/>
-      <c r="V19" s="63"/>
+      <c r="P19" s="289"/>
+      <c r="Q19" s="289"/>
+      <c r="R19" s="289"/>
+      <c r="S19" s="289"/>
+      <c r="T19" s="289"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="20">
         <v>80</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="20">
         <v>100</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="20">
         <v>1</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="21">
         <v>80.100906372070313</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="21">
         <v>1008.2150268554688</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="21">
         <v>5.3001849135215817</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="21">
         <v>5.2569983056369596</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="21">
         <v>5.3381953239440918</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="21">
         <v>9.1400852203369141</v>
       </c>
       <c r="M20">
@@ -5734,41 +5733,41 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="64" t="s">
+      <c r="P20" s="310" t="s">
         <v>206</v>
       </c>
-      <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="66"/>
+      <c r="Q20" s="311"/>
+      <c r="R20" s="311"/>
+      <c r="S20" s="311"/>
+      <c r="T20" s="311"/>
+      <c r="U20" s="313"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="37">
+      <c r="A21" s="20">
         <v>80</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="20">
         <v>100</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="20">
         <v>1</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="21">
         <v>80.100761413574219</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="21">
         <v>1007.7369995117188</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="21">
         <v>5.2970411482868647</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="21">
         <v>5.2563719954227377</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="21">
         <v>5.3356938362121582</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="21">
         <v>9.1300859451293945</v>
       </c>
       <c r="M21">
@@ -5779,50 +5778,50 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="67" t="s">
+      <c r="P21" s="328" t="s">
         <v>207</v>
       </c>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="69" t="s">
+      <c r="Q21" s="329"/>
+      <c r="R21" s="330" t="s">
         <v>208</v>
       </c>
-      <c r="S21" s="68"/>
-      <c r="T21" s="50" t="s">
+      <c r="S21" s="329"/>
+      <c r="T21" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="U21" s="70" t="s">
+      <c r="U21" s="43" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="37">
+      <c r="A22" s="20">
         <v>80</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="20">
         <v>350</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="20">
         <v>1</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="21">
         <v>79.800338745117188</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="21">
         <v>1008.2449951171875</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="21">
         <v>18.497443905428351</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="21">
         <v>18.346179691351473</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="21">
         <v>5.3167481422424316</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="21">
         <v>9.1354408264160156</v>
       </c>
-      <c r="J22" s="71" t="s">
+      <c r="J22" s="44" t="s">
         <v>210</v>
       </c>
       <c r="M22">
@@ -5833,51 +5832,51 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="72">
+      <c r="P22" s="316">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="74">
+      <c r="Q22" s="317"/>
+      <c r="R22" s="318">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="74"/>
-      <c r="T22" s="75">
+      <c r="S22" s="318"/>
+      <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
       </c>
-      <c r="U22" s="70" t="str">
+      <c r="U22" s="43" t="str">
         <f>IF(AND(T22&gt;10),"Fail", "Pass")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" s="37">
+      <c r="A23" s="20">
         <v>100</v>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="20">
         <v>10</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="20">
         <v>1</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="21">
         <v>101.01091766357422</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="21">
         <v>1009.7169799804688</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="21">
         <v>0.94919704534211358</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="21">
         <v>0.94006251703742083</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="21">
         <v>6.6159138679504395</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23" s="21">
         <v>9.1940040588378906</v>
       </c>
       <c r="M23">
@@ -5888,51 +5887,51 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="72">
+      <c r="P23" s="316">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="74">
+      <c r="Q23" s="317"/>
+      <c r="R23" s="318">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="74"/>
-      <c r="T23" s="75">
+      <c r="S23" s="318"/>
+      <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
       </c>
-      <c r="U23" s="70" t="str">
+      <c r="U23" s="43" t="str">
         <f t="shared" ref="U23:U24" si="4">IF(AND(T23&gt;10),"Fail", "Pass")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="37">
+      <c r="A24" s="20">
         <v>100</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="20">
         <v>100</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="20">
         <v>1</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="21">
         <v>101.07517242431641</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="21">
         <v>1008.2440185546875</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="21">
         <v>9.4794123764104956</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="21">
         <v>9.4019037013230804</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="21">
         <v>6.6090168952941895</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24" s="21">
         <v>9.1570568084716797</v>
       </c>
       <c r="M24">
@@ -5943,51 +5942,51 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="72">
+      <c r="P24" s="316">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="74">
+      <c r="Q24" s="317"/>
+      <c r="R24" s="318">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="74"/>
-      <c r="T24" s="75">
+      <c r="S24" s="318"/>
+      <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
       </c>
-      <c r="U24" s="70" t="str">
+      <c r="U24" s="43" t="str">
         <f t="shared" si="4"/>
         <v>Pass</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="37">
+      <c r="A25" s="20">
         <v>100</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="20">
         <v>100</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="20">
         <v>1</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="21">
         <v>101.1383056640625</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="21">
         <v>1007.718994140625</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="21">
         <v>9.4793492550394394</v>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="21">
         <v>9.4067381029410413</v>
       </c>
-      <c r="H25" s="38">
+      <c r="H25" s="21">
         <v>6.606837272644043</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="21">
         <v>9.1373414993286133</v>
       </c>
       <c r="M25">
@@ -5998,41 +5997,41 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="76" t="s">
+      <c r="P25" s="319" t="s">
         <v>211</v>
       </c>
-      <c r="Q25" s="77"/>
-      <c r="R25" s="77"/>
-      <c r="S25" s="77"/>
-      <c r="T25" s="77"/>
-      <c r="U25" s="78"/>
+      <c r="Q25" s="320"/>
+      <c r="R25" s="320"/>
+      <c r="S25" s="320"/>
+      <c r="T25" s="320"/>
+      <c r="U25" s="321"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="37">
+      <c r="A26" s="20">
         <v>100</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="20">
         <v>100</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="20">
         <v>1</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="21">
         <v>101.09636688232422</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="21">
         <v>1007.708984375</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="21">
         <v>9.473160151114703</v>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="21">
         <v>9.400688971548167</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="21">
         <v>6.605858325958252</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="21">
         <v>9.1417398452758789</v>
       </c>
       <c r="M26">
@@ -6045,31 +6044,31 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="37">
+      <c r="A27" s="20">
         <v>100</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="20">
         <v>100</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="20">
         <v>1</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="21">
         <v>101.13681793212891</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="21">
         <v>1007.7379760742188</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="21">
         <v>9.4782376769966046</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27" s="21">
         <v>9.4054598505999163</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27" s="21">
         <v>6.604067325592041</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27" s="21">
         <v>9.1277132034301758</v>
       </c>
       <c r="M27">
@@ -6080,113 +6079,113 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="79" t="s">
+      <c r="P27" s="322" t="s">
         <v>212</v>
       </c>
-      <c r="Q27" s="80"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="82" t="s">
+      <c r="Q27" s="323"/>
+      <c r="R27" s="324"/>
+      <c r="S27" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="T27" s="82">
+      <c r="T27" s="47">
         <f>A34</f>
         <v>120</v>
       </c>
-      <c r="U27" s="82" t="s">
+      <c r="U27" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="V27" s="82"/>
-      <c r="W27" s="82"/>
-      <c r="X27" s="83">
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="48">
         <f>C34</f>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" s="37">
+      <c r="A28" s="20">
         <v>100</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="20">
         <v>100</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="20">
         <v>1</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="21">
         <v>101.14177703857422</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="21">
         <v>1007.2310180664063</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="21">
         <v>9.4741797217353199</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28" s="21">
         <v>9.4061630565521828</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="21">
         <v>6.6096558570861816</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="21">
         <v>9.1467800140380859</v>
       </c>
       <c r="M28">
         <f t="shared" si="1"/>
         <v>101.14</v>
       </c>
-      <c r="N28" s="84">
+      <c r="N28" s="49">
         <f t="shared" si="0"/>
         <v>9.4741999999999997</v>
       </c>
-      <c r="P28" s="47" t="s">
+      <c r="P28" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="Q28" s="27" t="s">
+      <c r="Q28" s="305" t="s">
         <v>215</v>
       </c>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="50" t="s">
+      <c r="R28" s="305"/>
+      <c r="S28" s="305"/>
+      <c r="T28" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="U28" s="50" t="s">
+      <c r="U28" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="70" t="s">
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="43" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="37">
+      <c r="A29" s="20">
         <v>100</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="20">
         <v>350</v>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="20">
         <v>1</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="21">
         <v>101.04947662353516</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="21">
         <v>1007.7459716796875</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="21">
         <v>33.100879077426598</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="21">
         <v>32.846455820603495</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29" s="21">
         <v>6.5883312225341797</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="21">
         <v>9.0879783630371094</v>
       </c>
-      <c r="J29" s="71" t="s">
+      <c r="J29" s="44" t="s">
         <v>210</v>
       </c>
       <c r="M29">
@@ -6197,63 +6196,63 @@
         <f t="shared" si="0"/>
         <v>33.100900000000003</v>
       </c>
-      <c r="P29" s="85">
+      <c r="P29" s="50">
         <f>B31</f>
         <v>50</v>
       </c>
-      <c r="Q29" s="86">
+      <c r="Q29" s="51">
         <f>N31</f>
         <v>7.2830000000000004</v>
       </c>
-      <c r="R29" s="86">
+      <c r="R29" s="51">
         <f>N32</f>
         <v>7.2817999999999996</v>
       </c>
-      <c r="S29" s="86">
+      <c r="S29" s="51">
         <f>N33</f>
         <v>7.2878999999999996</v>
       </c>
-      <c r="T29" s="87">
+      <c r="T29" s="52">
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="88">
+      <c r="U29" s="306">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
-      <c r="V29" s="89"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="90" t="str">
+      <c r="V29" s="13"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="308" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="37">
+      <c r="A30" s="20">
         <v>120</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="20">
         <v>10</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="20">
         <v>1</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="21">
         <v>120.920051574707</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="21">
         <v>1010.7210083007813</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="21">
         <v>1.4566471992512735</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="21">
         <v>1.4411962209930553</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="21">
         <v>7.7191543579101563</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="21">
         <v>9.2275180816650391</v>
       </c>
       <c r="M30">
@@ -6264,57 +6263,57 @@
         <f t="shared" si="0"/>
         <v>1.4565999999999999</v>
       </c>
-      <c r="P30" s="85">
+      <c r="P30" s="50">
         <f>B34</f>
         <v>100</v>
       </c>
-      <c r="Q30" s="86">
+      <c r="Q30" s="51">
         <f>N34</f>
         <v>14.521599999999999</v>
       </c>
-      <c r="R30" s="86">
+      <c r="R30" s="51">
         <f>N35</f>
         <v>14.5259</v>
       </c>
-      <c r="S30" s="86">
+      <c r="S30" s="51">
         <f>N36</f>
         <v>14.532299999999999</v>
       </c>
-      <c r="T30" s="87">
+      <c r="T30" s="52">
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="88"/>
-      <c r="V30" s="89"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="90"/>
+      <c r="U30" s="306"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="308"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="37">
+      <c r="A31" s="20">
         <v>120</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="20">
         <v>50</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="20">
         <v>1</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="21">
         <v>120.863983154297</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="21">
         <v>1008.2349853515625</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="21">
         <v>7.2829630498192373</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31" s="21">
         <v>7.2234780893596051</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31" s="21">
         <v>7.7184734344482422</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31" s="21">
         <v>9.234339714050293</v>
       </c>
       <c r="M31">
@@ -6325,57 +6324,57 @@
         <f t="shared" si="0"/>
         <v>7.2830000000000004</v>
       </c>
-      <c r="P31" s="85">
+      <c r="P31" s="50">
         <f>B39</f>
         <v>200</v>
       </c>
-      <c r="Q31" s="86">
+      <c r="Q31" s="51">
         <f>N39</f>
         <v>29.085699999999999</v>
       </c>
-      <c r="R31" s="86">
+      <c r="R31" s="51">
         <f>N40</f>
         <v>29.1005</v>
       </c>
-      <c r="S31" s="86">
+      <c r="S31" s="51">
         <f>N41</f>
         <v>29.098600000000001</v>
       </c>
-      <c r="T31" s="87">
+      <c r="T31" s="52">
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="88"/>
-      <c r="V31" s="89"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="90"/>
+      <c r="U31" s="306"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="308"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="37">
+      <c r="A32" s="20">
         <v>120</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="20">
         <v>50</v>
       </c>
-      <c r="C32" s="37">
+      <c r="C32" s="20">
         <v>1</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="21">
         <v>120.841148376465</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="21">
         <v>1008.2349853515625</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="21">
         <v>7.2818477272882891</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32" s="21">
         <v>7.2223720166058412</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="21">
         <v>7.7171602249145508</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32" s="21">
         <v>9.2334108352661133</v>
       </c>
       <c r="M32">
@@ -6386,57 +6385,57 @@
         <f t="shared" si="0"/>
         <v>7.2817999999999996</v>
       </c>
-      <c r="P32" s="91">
+      <c r="P32" s="53">
         <f>B42</f>
         <v>350</v>
       </c>
-      <c r="Q32" s="92">
+      <c r="Q32" s="54">
         <f>N42</f>
         <v>50.905500000000004</v>
       </c>
-      <c r="R32" s="92">
+      <c r="R32" s="54">
         <f>N43</f>
         <v>50.876800000000003</v>
       </c>
-      <c r="S32" s="92">
+      <c r="S32" s="54">
         <f>N44</f>
         <v>50.917000000000002</v>
       </c>
-      <c r="T32" s="93">
+      <c r="T32" s="55">
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="94"/>
-      <c r="V32" s="95"/>
-      <c r="W32" s="35"/>
-      <c r="X32" s="96"/>
+      <c r="U32" s="307"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="309"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37">
+      <c r="A33" s="20">
         <v>120</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="20">
         <v>50</v>
       </c>
-      <c r="C33" s="37">
+      <c r="C33" s="20">
         <v>1</v>
       </c>
-      <c r="D33" s="38">
+      <c r="D33" s="21">
         <v>120.93138122558599</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="21">
         <v>1007.7150268554688</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="21">
         <v>7.2878875866153594</v>
       </c>
-      <c r="G33" s="38">
+      <c r="G33" s="21">
         <v>7.2320920836671272</v>
       </c>
-      <c r="H33" s="38">
+      <c r="H33" s="21">
         <v>7.716036319732666</v>
       </c>
-      <c r="I33" s="38">
+      <c r="I33" s="21">
         <v>9.214508056640625</v>
       </c>
       <c r="M33">
@@ -6447,44 +6446,44 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="97" t="s">
+      <c r="P33" s="210" t="s">
         <v>218</v>
       </c>
-      <c r="Q33" s="98"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="98"/>
-      <c r="T33" s="98"/>
-      <c r="U33" s="98"/>
-      <c r="V33" s="98"/>
-      <c r="W33" s="98"/>
-      <c r="X33" s="99"/>
+      <c r="Q33" s="211"/>
+      <c r="R33" s="211"/>
+      <c r="S33" s="211"/>
+      <c r="T33" s="211"/>
+      <c r="U33" s="211"/>
+      <c r="V33" s="211"/>
+      <c r="W33" s="211"/>
+      <c r="X33" s="212"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="37">
+      <c r="A34" s="20">
         <v>120</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="20">
         <v>100</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="20">
         <v>1</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="21">
         <v>120.926467895508</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="21">
         <v>1007.2459716796875</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="21">
         <v>14.521575312568471</v>
       </c>
-      <c r="G34" s="38">
+      <c r="G34" s="21">
         <v>14.417109488047878</v>
       </c>
-      <c r="H34" s="38">
+      <c r="H34" s="21">
         <v>7.7138433456420898</v>
       </c>
-      <c r="I34" s="38">
+      <c r="I34" s="21">
         <v>9.207493782043457</v>
       </c>
       <c r="M34">
@@ -6497,31 +6496,31 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="37">
+      <c r="A35" s="20">
         <v>120</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="20">
         <v>100</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="20">
         <v>1</v>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="21">
         <v>121.007217407227</v>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="21">
         <v>1007.2130126953125</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="21">
         <v>14.525865426092793</v>
       </c>
-      <c r="G35" s="38">
+      <c r="G35" s="21">
         <v>14.421840247584127</v>
       </c>
-      <c r="H35" s="38">
+      <c r="H35" s="21">
         <v>7.7140040397644043</v>
       </c>
-      <c r="I35" s="38">
+      <c r="I35" s="21">
         <v>9.1947765350341797</v>
       </c>
       <c r="M35">
@@ -6532,45 +6531,45 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="64" t="s">
+      <c r="P35" s="310" t="s">
         <v>219</v>
       </c>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="100"/>
-      <c r="W35" s="100"/>
-      <c r="X35" s="100"/>
-      <c r="Y35" s="66"/>
+      <c r="Q35" s="311"/>
+      <c r="R35" s="311"/>
+      <c r="S35" s="311"/>
+      <c r="T35" s="311"/>
+      <c r="U35" s="311"/>
+      <c r="V35" s="312"/>
+      <c r="W35" s="312"/>
+      <c r="X35" s="312"/>
+      <c r="Y35" s="313"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="37">
+      <c r="A36" s="20">
         <v>120</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="20">
         <v>100</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="20">
         <v>1</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="21">
         <v>121.04571533203099</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="21">
         <v>1008.2169799804688</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="21">
         <v>14.532316644185473</v>
       </c>
-      <c r="G36" s="38">
+      <c r="G36" s="21">
         <v>14.413877638188016</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="21">
         <v>7.7114577293395996</v>
       </c>
-      <c r="I36" s="38">
+      <c r="I36" s="21">
         <v>9.1793909072875977</v>
       </c>
       <c r="M36">
@@ -6581,55 +6580,55 @@
         <f t="shared" si="0"/>
         <v>14.532299999999999</v>
       </c>
-      <c r="P36" s="101" t="s">
+      <c r="P36" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="Q36" s="102" t="s">
+      <c r="Q36" s="314" t="s">
         <v>215</v>
       </c>
-      <c r="R36" s="102"/>
-      <c r="S36" s="102"/>
-      <c r="T36" s="102"/>
-      <c r="U36" s="103"/>
-      <c r="V36" s="95" t="s">
+      <c r="R36" s="314"/>
+      <c r="S36" s="314"/>
+      <c r="T36" s="314"/>
+      <c r="U36" s="315"/>
+      <c r="V36" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="W36" s="95" t="s">
+      <c r="W36" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="X36" s="32" t="s">
+      <c r="X36" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="Y36" s="104" t="s">
+      <c r="Y36" s="57" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="37">
+      <c r="A37" s="20">
         <v>120</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="20">
         <v>100</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="20">
         <v>1</v>
       </c>
-      <c r="D37" s="38">
+      <c r="D37" s="21">
         <v>121.06346130371099</v>
       </c>
-      <c r="E37" s="38">
+      <c r="E37" s="21">
         <v>1007.7479858398438</v>
       </c>
-      <c r="F37" s="38">
+      <c r="F37" s="21">
         <v>14.526018415178571</v>
       </c>
-      <c r="G37" s="38">
+      <c r="G37" s="21">
         <v>14.41433455489234</v>
       </c>
-      <c r="H37" s="38">
+      <c r="H37" s="21">
         <v>7.7135024070739746</v>
       </c>
-      <c r="I37" s="38">
+      <c r="I37" s="21">
         <v>9.1837491989135742</v>
       </c>
       <c r="M37">
@@ -6640,73 +6639,73 @@
         <f t="shared" si="0"/>
         <v>14.526</v>
       </c>
-      <c r="P37" s="105">
+      <c r="P37" s="58">
         <f>A18</f>
         <v>80</v>
       </c>
-      <c r="Q37" s="106">
+      <c r="Q37" s="59">
         <f>N17</f>
         <v>5.2957999999999998</v>
       </c>
-      <c r="R37" s="106">
+      <c r="R37" s="59">
         <f>N18</f>
         <v>5.2999000000000001</v>
       </c>
-      <c r="S37" s="106">
+      <c r="S37" s="59">
         <f>N19</f>
         <v>5.3005000000000004</v>
       </c>
-      <c r="T37" s="106">
+      <c r="T37" s="59">
         <f>N20</f>
         <v>5.3002000000000002</v>
       </c>
-      <c r="U37" s="107">
+      <c r="U37" s="60">
         <f>N21</f>
         <v>5.2969999999999997</v>
       </c>
-      <c r="V37" s="108">
+      <c r="V37" s="61">
         <f>ROUND(AVERAGE(Q37:U37),4)</f>
         <v>5.2987000000000002</v>
       </c>
-      <c r="W37" s="109">
+      <c r="W37" s="62">
         <f>ROUND(IF(V37&lt;&gt;"",STDEV(Q37:U37),""),4)</f>
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="X37" s="108">
+      <c r="X37" s="61">
         <f>ROUND(IF(W37&lt;&gt;"",PRODUCT(W37,POWER(V37,-1)),""),4)</f>
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="Y37" s="110" t="str">
+      <c r="Y37" s="63" t="str">
         <f>IF(X37&lt;0.05,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="37">
+      <c r="A38" s="20">
         <v>120</v>
       </c>
-      <c r="B38" s="37">
+      <c r="B38" s="20">
         <v>100</v>
       </c>
-      <c r="C38" s="37">
+      <c r="C38" s="20">
         <v>1</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="21">
         <v>121.10099029541</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="21">
         <v>1007.2310180664063</v>
       </c>
-      <c r="F38" s="38">
+      <c r="F38" s="21">
         <v>14.529267561007341</v>
       </c>
-      <c r="G38" s="38">
+      <c r="G38" s="21">
         <v>14.42496176877636</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="21">
         <v>7.7166938781738281</v>
       </c>
-      <c r="I38" s="38">
+      <c r="I38" s="21">
         <v>9.1889448165893555</v>
       </c>
       <c r="M38">
@@ -6717,73 +6716,73 @@
         <f t="shared" si="0"/>
         <v>14.529299999999999</v>
       </c>
-      <c r="P38" s="47">
+      <c r="P38" s="30">
         <f>A26</f>
         <v>100</v>
       </c>
-      <c r="Q38" s="111">
+      <c r="Q38" s="64">
         <f>N24</f>
         <v>9.4794</v>
       </c>
-      <c r="R38" s="111">
+      <c r="R38" s="64">
         <f>N25</f>
         <v>9.4793000000000003</v>
       </c>
-      <c r="S38" s="111">
+      <c r="S38" s="64">
         <f>N26</f>
         <v>9.4732000000000003</v>
       </c>
-      <c r="T38" s="111">
+      <c r="T38" s="64">
         <f>N27</f>
         <v>9.4781999999999993</v>
       </c>
-      <c r="U38" s="112">
+      <c r="U38" s="65">
         <f>N28</f>
         <v>9.4741999999999997</v>
       </c>
-      <c r="V38" s="113">
+      <c r="V38" s="66">
         <f t="shared" ref="V38:V40" si="5">ROUND(AVERAGE(Q38:U38),4)</f>
         <v>9.4769000000000005</v>
       </c>
-      <c r="W38" s="114">
+      <c r="W38" s="67">
         <f t="shared" ref="W38:W40" si="6">ROUND(IF(V38&lt;&gt;"",STDEV(Q38:U38),""),4)</f>
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="X38" s="108">
+      <c r="X38" s="61">
         <f t="shared" ref="X38:X40" si="7">ROUND(IF(W38&lt;&gt;"",PRODUCT(W38,POWER(V38,-1)),""),4)</f>
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="Y38" s="110" t="str">
+      <c r="Y38" s="63" t="str">
         <f t="shared" ref="Y38:Y40" si="8">IF(X38&lt;0.05,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="37">
+      <c r="A39" s="20">
         <v>120</v>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="20">
         <v>200</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="20">
         <v>1</v>
       </c>
-      <c r="D39" s="38">
+      <c r="D39" s="21">
         <v>121.024909973145</v>
       </c>
-      <c r="E39" s="38">
+      <c r="E39" s="21">
         <v>1007.708984375</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F39" s="21">
         <v>29.085711546888696</v>
       </c>
-      <c r="G39" s="38">
+      <c r="G39" s="21">
         <v>28.863205326045772</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="21">
         <v>7.7075557708740234</v>
       </c>
-      <c r="I39" s="38">
+      <c r="I39" s="21">
         <v>9.1689281463623047</v>
       </c>
       <c r="M39">
@@ -6794,73 +6793,73 @@
         <f t="shared" si="0"/>
         <v>29.085699999999999</v>
       </c>
-      <c r="P39" s="47">
+      <c r="P39" s="30">
         <f>A37</f>
         <v>120</v>
       </c>
-      <c r="Q39" s="111">
+      <c r="Q39" s="64">
         <f>N34</f>
         <v>14.521599999999999</v>
       </c>
-      <c r="R39" s="111">
+      <c r="R39" s="64">
         <f>N35</f>
         <v>14.5259</v>
       </c>
-      <c r="S39" s="111">
+      <c r="S39" s="64">
         <f>N36</f>
         <v>14.532299999999999</v>
       </c>
-      <c r="T39" s="111">
+      <c r="T39" s="64">
         <f>N37</f>
         <v>14.526</v>
       </c>
-      <c r="U39" s="112">
+      <c r="U39" s="65">
         <f>N38</f>
         <v>14.529299999999999</v>
       </c>
-      <c r="V39" s="113">
+      <c r="V39" s="66">
         <f t="shared" si="5"/>
         <v>14.526999999999999</v>
       </c>
-      <c r="W39" s="114">
+      <c r="W39" s="67">
         <f t="shared" si="6"/>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="X39" s="108">
+      <c r="X39" s="61">
         <f t="shared" si="7"/>
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="Y39" s="110" t="str">
+      <c r="Y39" s="63" t="str">
         <f t="shared" si="8"/>
         <v>Pass</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37">
+      <c r="A40" s="20">
         <v>120</v>
       </c>
-      <c r="B40" s="37">
+      <c r="B40" s="20">
         <v>200</v>
       </c>
-      <c r="C40" s="37">
+      <c r="C40" s="20">
         <v>1</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="21">
         <v>121.20184326171901</v>
       </c>
-      <c r="E40" s="38">
+      <c r="E40" s="21">
         <v>1007.7479858398438</v>
       </c>
-      <c r="F40" s="38">
+      <c r="F40" s="21">
         <v>29.100488366838299</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G40" s="21">
         <v>28.876750120251558</v>
       </c>
-      <c r="H40" s="38">
+      <c r="H40" s="21">
         <v>7.7061457633972168</v>
       </c>
-      <c r="I40" s="38">
+      <c r="I40" s="21">
         <v>9.1349763870239258</v>
       </c>
       <c r="M40">
@@ -6871,73 +6870,73 @@
         <f t="shared" si="0"/>
         <v>29.1005</v>
       </c>
-      <c r="P40" s="52">
+      <c r="P40" s="34">
         <f>A49</f>
         <v>140</v>
       </c>
-      <c r="Q40" s="115">
+      <c r="Q40" s="68">
         <f>N46</f>
         <v>20.186800000000002</v>
       </c>
-      <c r="R40" s="115">
+      <c r="R40" s="68">
         <f>N47</f>
         <v>20.193899999999999</v>
       </c>
-      <c r="S40" s="115">
+      <c r="S40" s="68">
         <f>N48</f>
         <v>20.188400000000001</v>
       </c>
-      <c r="T40" s="115">
+      <c r="T40" s="68">
         <f>N49</f>
         <v>20.187999999999999</v>
       </c>
-      <c r="U40" s="116">
+      <c r="U40" s="69">
         <f>N50</f>
         <v>20.197600000000001</v>
       </c>
-      <c r="V40" s="117">
+      <c r="V40" s="70">
         <f t="shared" si="5"/>
         <v>20.190899999999999</v>
       </c>
-      <c r="W40" s="118">
+      <c r="W40" s="71">
         <f t="shared" si="6"/>
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="X40" s="108">
+      <c r="X40" s="61">
         <f t="shared" si="7"/>
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="Y40" s="110" t="str">
+      <c r="Y40" s="63" t="str">
         <f t="shared" si="8"/>
         <v>Pass</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="37">
+      <c r="A41" s="20">
         <v>120</v>
       </c>
-      <c r="B41" s="37">
+      <c r="B41" s="20">
         <v>200</v>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="20">
         <v>1</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="21">
         <v>121.221961975098</v>
       </c>
-      <c r="E41" s="38">
+      <c r="E41" s="21">
         <v>1007.719970703125</v>
       </c>
-      <c r="F41" s="38">
+      <c r="F41" s="21">
         <v>29.098643938978967</v>
       </c>
-      <c r="G41" s="38">
+      <c r="G41" s="21">
         <v>28.875722614882321</v>
       </c>
-      <c r="H41" s="38">
+      <c r="H41" s="21">
         <v>7.7104229927062988</v>
       </c>
-      <c r="I41" s="38">
+      <c r="I41" s="21">
         <v>9.1468400955200195</v>
       </c>
       <c r="M41">
@@ -6948,48 +6947,48 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="97" t="s">
+      <c r="P41" s="210" t="s">
         <v>222</v>
       </c>
-      <c r="Q41" s="98"/>
-      <c r="R41" s="98"/>
-      <c r="S41" s="98"/>
-      <c r="T41" s="98"/>
-      <c r="U41" s="98"/>
-      <c r="V41" s="98"/>
-      <c r="W41" s="98"/>
-      <c r="X41" s="98"/>
-      <c r="Y41" s="99"/>
+      <c r="Q41" s="211"/>
+      <c r="R41" s="211"/>
+      <c r="S41" s="211"/>
+      <c r="T41" s="211"/>
+      <c r="U41" s="211"/>
+      <c r="V41" s="211"/>
+      <c r="W41" s="211"/>
+      <c r="X41" s="211"/>
+      <c r="Y41" s="212"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="37">
+      <c r="A42" s="20">
         <v>120</v>
       </c>
-      <c r="B42" s="37">
+      <c r="B42" s="20">
         <v>350</v>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="20">
         <v>1</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="21">
         <v>121.31259155273401</v>
       </c>
-      <c r="E42" s="38">
+      <c r="E42" s="21">
         <v>1007.7319946289063</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F42" s="21">
         <v>50.905511372973272</v>
       </c>
-      <c r="G42" s="38">
+      <c r="G42" s="21">
         <v>50.514927740651473</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="21">
         <v>7.6990723609924316</v>
       </c>
-      <c r="I42" s="38">
+      <c r="I42" s="21">
         <v>9.0919656753540039</v>
       </c>
-      <c r="J42" s="71" t="s">
+      <c r="J42" s="44" t="s">
         <v>210</v>
       </c>
       <c r="M42">
@@ -7002,31 +7001,31 @@
       </c>
     </row>
     <row r="43" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="37">
+      <c r="A43" s="20">
         <v>120</v>
       </c>
-      <c r="B43" s="37">
+      <c r="B43" s="20">
         <v>350</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="20">
         <v>1</v>
       </c>
-      <c r="D43" s="38">
+      <c r="D43" s="21">
         <v>121.38840484619099</v>
       </c>
-      <c r="E43" s="38">
+      <c r="E43" s="21">
         <v>1007.2109985351563</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="21">
         <v>50.876809336656443</v>
       </c>
-      <c r="G43" s="38">
+      <c r="G43" s="21">
         <v>50.51256514696081</v>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="21">
         <v>7.7000017166137695</v>
       </c>
-      <c r="I43" s="38">
+      <c r="I43" s="21">
         <v>9.0829200744628906</v>
       </c>
       <c r="M43">
@@ -7037,43 +7036,43 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="119" t="s">
+      <c r="P43" s="180" t="s">
         <v>223</v>
       </c>
-      <c r="Q43" s="120"/>
-      <c r="R43" s="121" t="s">
+      <c r="Q43" s="296"/>
+      <c r="R43" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="S43" s="122" t="s">
+      <c r="S43" s="73" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="37">
+      <c r="A44" s="20">
         <v>120</v>
       </c>
-      <c r="B44" s="37">
+      <c r="B44" s="20">
         <v>350</v>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="20">
         <v>1</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="21">
         <v>121.382972717285</v>
       </c>
-      <c r="E44" s="38">
+      <c r="E44" s="21">
         <v>1007.7130126953125</v>
       </c>
-      <c r="F44" s="38">
+      <c r="F44" s="21">
         <v>50.917005881627958</v>
       </c>
-      <c r="G44" s="38">
+      <c r="G44" s="21">
         <v>50.527289009149953</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="21">
         <v>7.6991653442382813</v>
       </c>
-      <c r="I44" s="38">
+      <c r="I44" s="21">
         <v>9.0808610916137695</v>
       </c>
       <c r="M44">
@@ -7084,48 +7083,48 @@
         <f t="shared" si="0"/>
         <v>50.917000000000002</v>
       </c>
-      <c r="P44" s="123" t="s">
+      <c r="P44" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="Q44" s="124">
+      <c r="Q44" s="75">
         <f>A46</f>
         <v>140</v>
       </c>
-      <c r="R44" s="125">
+      <c r="R44" s="76">
         <f>ROUND(I46,2)</f>
         <v>9.39</v>
       </c>
-      <c r="S44" s="126" t="str">
+      <c r="S44" s="77" t="str">
         <f>IF(AND(Q44&lt;=70,R44&gt;=1.5),"Pass",IF(AND(Q44&lt;=100,R44&gt;=2),"Pass",IF(AND(Q44&gt;100,R44&gt;=2.5),"Pass","Fail")))</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A45" s="37">
+      <c r="A45" s="20">
         <v>140</v>
       </c>
-      <c r="B45" s="37">
+      <c r="B45" s="20">
         <v>10</v>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="20">
         <v>1</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="21">
         <v>141.648361206055</v>
       </c>
-      <c r="E45" s="38">
+      <c r="E45" s="21">
         <v>1011.7529907226563</v>
       </c>
-      <c r="F45" s="38">
+      <c r="F45" s="21">
         <v>2.0245690308152113</v>
       </c>
-      <c r="G45" s="38">
+      <c r="G45" s="21">
         <v>2.0010506866481825</v>
       </c>
-      <c r="H45" s="38">
+      <c r="H45" s="21">
         <v>8.6313028335571289</v>
       </c>
-      <c r="I45" s="38">
+      <c r="I45" s="21">
         <v>9.3963460922241211</v>
       </c>
       <c r="M45">
@@ -7136,39 +7135,39 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="127" t="s">
+      <c r="P45" s="297" t="s">
         <v>224</v>
       </c>
-      <c r="Q45" s="128"/>
-      <c r="R45" s="128"/>
-      <c r="S45" s="129"/>
+      <c r="Q45" s="298"/>
+      <c r="R45" s="298"/>
+      <c r="S45" s="299"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A46" s="37">
+      <c r="A46" s="20">
         <v>140</v>
       </c>
-      <c r="B46" s="37">
+      <c r="B46" s="20">
         <v>100</v>
       </c>
-      <c r="C46" s="37">
+      <c r="C46" s="20">
         <v>1</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="21">
         <v>141.58995056152301</v>
       </c>
-      <c r="E46" s="38">
+      <c r="E46" s="21">
         <v>1007.7150268554688</v>
       </c>
-      <c r="F46" s="38">
+      <c r="F46" s="21">
         <v>20.186772927393733</v>
       </c>
-      <c r="G46" s="38">
+      <c r="G46" s="21">
         <v>20.032224618932357</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="21">
         <v>8.628443717956543</v>
       </c>
-      <c r="I46" s="38">
+      <c r="I46" s="21">
         <v>9.3948917388916016</v>
       </c>
       <c r="M46">
@@ -7179,37 +7178,37 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="127"/>
-      <c r="Q46" s="128"/>
-      <c r="R46" s="128"/>
-      <c r="S46" s="129"/>
+      <c r="P46" s="297"/>
+      <c r="Q46" s="298"/>
+      <c r="R46" s="298"/>
+      <c r="S46" s="299"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="37">
+      <c r="A47" s="20">
         <v>140</v>
       </c>
-      <c r="B47" s="37">
+      <c r="B47" s="20">
         <v>100</v>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="20">
         <v>1</v>
       </c>
-      <c r="D47" s="38">
+      <c r="D47" s="21">
         <v>141.63255310058599</v>
       </c>
-      <c r="E47" s="38">
+      <c r="E47" s="21">
         <v>1008.2260131835938</v>
       </c>
-      <c r="F47" s="38">
+      <c r="F47" s="21">
         <v>20.19393880778922</v>
       </c>
-      <c r="G47" s="38">
+      <c r="G47" s="21">
         <v>20.02917999347817</v>
       </c>
-      <c r="H47" s="38">
+      <c r="H47" s="21">
         <v>8.6284246444702148</v>
       </c>
-      <c r="I47" s="38">
+      <c r="I47" s="21">
         <v>9.3881053924560547</v>
       </c>
       <c r="M47">
@@ -7220,37 +7219,37 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="130"/>
-      <c r="Q47" s="131"/>
-      <c r="R47" s="131"/>
-      <c r="S47" s="132"/>
+      <c r="P47" s="229"/>
+      <c r="Q47" s="300"/>
+      <c r="R47" s="300"/>
+      <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A48" s="37">
+      <c r="A48" s="20">
         <v>140</v>
       </c>
-      <c r="B48" s="37">
+      <c r="B48" s="20">
         <v>100</v>
       </c>
-      <c r="C48" s="37">
+      <c r="C48" s="20">
         <v>1</v>
       </c>
-      <c r="D48" s="38">
+      <c r="D48" s="21">
         <v>141.65559387207</v>
       </c>
-      <c r="E48" s="38">
+      <c r="E48" s="21">
         <v>1007.7379760742188</v>
       </c>
-      <c r="F48" s="38">
+      <c r="F48" s="21">
         <v>20.188354171231378</v>
       </c>
-      <c r="G48" s="38">
+      <c r="G48" s="21">
         <v>20.033336821056547</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="21">
         <v>8.6275720596313477</v>
       </c>
-      <c r="I48" s="38">
+      <c r="I48" s="21">
         <v>9.3813076019287109</v>
       </c>
       <c r="M48">
@@ -7263,31 +7262,31 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="37">
+      <c r="A49" s="20">
         <v>140</v>
       </c>
-      <c r="B49" s="37">
+      <c r="B49" s="20">
         <v>100</v>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="20">
         <v>1</v>
       </c>
-      <c r="D49" s="38">
+      <c r="D49" s="21">
         <v>141.658935546875</v>
       </c>
-      <c r="E49" s="38">
+      <c r="E49" s="21">
         <v>1008.2160034179688</v>
       </c>
-      <c r="F49" s="38">
+      <c r="F49" s="21">
         <v>20.18804391364483</v>
       </c>
-      <c r="G49" s="38">
+      <c r="G49" s="21">
         <v>20.023532057240313</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="21">
         <v>8.6275978088378906</v>
       </c>
-      <c r="I49" s="38">
+      <c r="I49" s="21">
         <v>9.3808803558349609</v>
       </c>
       <c r="M49">
@@ -7300,31 +7299,31 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="37">
+      <c r="A50" s="20">
         <v>140</v>
       </c>
-      <c r="B50" s="37">
+      <c r="B50" s="20">
         <v>100</v>
       </c>
-      <c r="C50" s="37">
+      <c r="C50" s="20">
         <v>1</v>
       </c>
-      <c r="D50" s="38">
+      <c r="D50" s="21">
         <v>141.68133544921901</v>
       </c>
-      <c r="E50" s="38">
+      <c r="E50" s="21">
         <v>1008.2160034179688</v>
       </c>
-      <c r="F50" s="38">
+      <c r="F50" s="21">
         <v>20.197587009065511</v>
       </c>
-      <c r="G50" s="38">
+      <c r="G50" s="21">
         <v>20.032993576312808</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="21">
         <v>8.629054069519043</v>
       </c>
-      <c r="I50" s="38">
+      <c r="I50" s="21">
         <v>9.382777214050293</v>
       </c>
       <c r="M50">
@@ -7337,34 +7336,34 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="37">
+      <c r="A51" s="20">
         <v>140</v>
       </c>
-      <c r="B51" s="37">
+      <c r="B51" s="20">
         <v>280</v>
       </c>
-      <c r="C51" s="37">
+      <c r="C51" s="20">
         <v>1</v>
       </c>
-      <c r="D51" s="38">
+      <c r="D51" s="21">
         <v>141.58903503418</v>
       </c>
-      <c r="E51" s="38">
+      <c r="E51" s="21">
         <v>1007.2210083007813</v>
       </c>
-      <c r="F51" s="38">
+      <c r="F51" s="21">
         <v>56.592802537521912</v>
       </c>
-      <c r="G51" s="38">
+      <c r="G51" s="21">
         <v>56.187078334976626</v>
       </c>
-      <c r="H51" s="38">
+      <c r="H51" s="21">
         <v>8.6159791946411133</v>
       </c>
-      <c r="I51" s="38">
+      <c r="I51" s="21">
         <v>9.3486919403076172</v>
       </c>
-      <c r="J51" s="71" t="s">
+      <c r="J51" s="44" t="s">
         <v>210</v>
       </c>
       <c r="M51">
@@ -7377,132 +7376,132 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="133"/>
-      <c r="B52" s="134"/>
-      <c r="C52" s="134"/>
-      <c r="D52" s="135"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
-      <c r="I52" s="136"/>
-      <c r="J52" s="135"/>
+      <c r="A52" s="78"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="80"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="80"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="133"/>
-      <c r="B53" s="134"/>
-      <c r="C53" s="134"/>
-      <c r="D53" s="135"/>
-      <c r="E53" s="135"/>
-      <c r="F53" s="135"/>
-      <c r="G53" s="135"/>
-      <c r="H53" s="135"/>
-      <c r="I53" s="136"/>
-      <c r="J53" s="135"/>
+      <c r="A53" s="78"/>
+      <c r="B53" s="79"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="80"/>
+      <c r="F53" s="80"/>
+      <c r="G53" s="80"/>
+      <c r="H53" s="80"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="80"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="133"/>
-      <c r="B54" s="134"/>
-      <c r="C54" s="134"/>
-      <c r="D54" s="135"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="135"/>
-      <c r="H54" s="135"/>
-      <c r="I54" s="136"/>
-      <c r="J54" s="135"/>
+      <c r="A54" s="78"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="80"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="133"/>
-      <c r="B55" s="134"/>
-      <c r="C55" s="134"/>
-      <c r="D55" s="135"/>
-      <c r="E55" s="135"/>
-      <c r="F55" s="135"/>
-      <c r="G55" s="135"/>
-      <c r="H55" s="135"/>
-      <c r="I55" s="136"/>
-      <c r="J55" s="135"/>
+      <c r="A55" s="78"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="80"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="80"/>
     </row>
     <row r="56" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="133"/>
-      <c r="B56" s="134"/>
-      <c r="C56" s="134"/>
-      <c r="D56" s="135"/>
-      <c r="E56" s="135"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="135"/>
-      <c r="H56" s="135"/>
-      <c r="I56" s="136"/>
-      <c r="J56" s="135"/>
+      <c r="A56" s="78"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="301" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="138"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="138"/>
-      <c r="E57" s="138"/>
-      <c r="F57" s="138"/>
-      <c r="G57" s="138"/>
-      <c r="H57" s="138"/>
-      <c r="I57" s="139"/>
-      <c r="J57" s="135"/>
+      <c r="B57" s="302"/>
+      <c r="C57" s="302"/>
+      <c r="D57" s="302"/>
+      <c r="E57" s="302"/>
+      <c r="F57" s="302"/>
+      <c r="G57" s="302"/>
+      <c r="H57" s="302"/>
+      <c r="I57" s="303"/>
+      <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="140"/>
-      <c r="B58" s="141" t="s">
+      <c r="A58" s="82"/>
+      <c r="B58" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="C58" s="142"/>
-      <c r="D58" s="142" t="s">
+      <c r="C58" s="84"/>
+      <c r="D58" s="84" t="s">
         <v>227</v>
       </c>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142" t="s">
+      <c r="E58" s="84"/>
+      <c r="F58" s="84"/>
+      <c r="G58" s="84" t="s">
         <v>228</v>
       </c>
-      <c r="H58" s="142" t="s">
+      <c r="H58" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="I58" s="143"/>
+      <c r="I58" s="85"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="144"/>
-      <c r="B59" s="145" t="s">
+      <c r="A59" s="86"/>
+      <c r="B59" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="C59" s="145" t="s">
+      <c r="C59" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="D59" s="145" t="s">
+      <c r="D59" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="E59" s="145" t="s">
+      <c r="E59" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="F59" s="145" t="s">
+      <c r="F59" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="G59" s="145" t="s">
+      <c r="G59" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="H59" s="146" t="s">
+      <c r="H59" s="291" t="s">
         <v>236</v>
       </c>
-      <c r="I59" s="147"/>
+      <c r="I59" s="292"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="144"/>
-      <c r="B60" s="3">
+      <c r="A60" s="86"/>
+      <c r="B60" s="2">
         <v>120</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="2">
         <v>100</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="2" t="s">
         <v>237</v>
       </c>
       <c r="E60">
@@ -7511,111 +7510,111 @@
       <c r="F60" t="s">
         <v>84</v>
       </c>
-      <c r="H60" s="148">
+      <c r="H60" s="304">
         <v>18.12</v>
       </c>
-      <c r="I60" s="148"/>
+      <c r="I60" s="304"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="144"/>
+      <c r="A61" s="86"/>
       <c r="F61" t="s">
         <v>86</v>
       </c>
-      <c r="H61" s="149">
+      <c r="H61" s="287">
         <v>19.98</v>
       </c>
-      <c r="I61" s="149"/>
+      <c r="I61" s="287"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="144"/>
+      <c r="A62" s="86"/>
       <c r="F62" t="s">
         <v>89</v>
       </c>
-      <c r="H62" s="149">
+      <c r="H62" s="287">
         <v>18.7</v>
       </c>
-      <c r="I62" s="149"/>
-      <c r="J62" s="150"/>
-      <c r="K62" s="150"/>
+      <c r="I62" s="287"/>
+      <c r="J62" s="88"/>
+      <c r="K62" s="88"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="144"/>
+      <c r="A63" s="86"/>
       <c r="F63" t="s">
         <v>238</v>
       </c>
-      <c r="H63" s="149">
+      <c r="H63" s="287">
         <v>17.62</v>
       </c>
-      <c r="I63" s="149"/>
-      <c r="J63" s="150"/>
-      <c r="K63" s="150"/>
+      <c r="I63" s="287"/>
+      <c r="J63" s="88"/>
+      <c r="K63" s="88"/>
     </row>
     <row r="64" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="144"/>
+      <c r="A64" s="86"/>
       <c r="F64" t="s">
         <v>239</v>
       </c>
-      <c r="H64" s="151">
+      <c r="H64" s="290">
         <v>18.79</v>
       </c>
-      <c r="I64" s="151"/>
-      <c r="J64" s="150"/>
-      <c r="K64" s="150"/>
+      <c r="I64" s="290"/>
+      <c r="J64" s="88"/>
+      <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="144"/>
-      <c r="B65" s="152" t="s">
+      <c r="A65" s="86"/>
+      <c r="B65" s="277" t="s">
         <v>240</v>
       </c>
-      <c r="C65" s="153"/>
-      <c r="D65" s="154">
+      <c r="C65" s="278"/>
+      <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="155">
+      <c r="H65" s="294">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="156"/>
-      <c r="J65" s="157">
+      <c r="I65" s="295"/>
+      <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
       </c>
-      <c r="K65" s="157">
+      <c r="K65" s="92">
         <f>ABS(H65-D65)/D65*100</f>
         <v>2.7977839335179997</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="144"/>
-      <c r="G66" s="158" t="s">
+      <c r="A66" s="86"/>
+      <c r="G66" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H66" s="159" t="str">
+      <c r="H66" s="242" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="160"/>
-      <c r="J66" s="150"/>
-      <c r="K66" s="150"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="I66" s="244"/>
+      <c r="J66" s="88"/>
+      <c r="K66" s="88"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A67" s="144"/>
-      <c r="H67" s="161"/>
-      <c r="I67" s="162"/>
-      <c r="J67" s="150"/>
-      <c r="K67" s="150"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="A67" s="86"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="93"/>
+      <c r="J67" s="88"/>
+      <c r="K67" s="88"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A68" s="144"/>
-      <c r="B68" s="71" t="s">
+      <c r="A68" s="86"/>
+      <c r="B68" s="44" t="s">
         <v>226</v>
       </c>
       <c r="D68" t="s">
@@ -7627,52 +7626,52 @@
       <c r="H68" t="s">
         <v>242</v>
       </c>
-      <c r="I68" s="163"/>
-      <c r="J68" s="150"/>
-      <c r="K68" s="150"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="161"/>
+      <c r="I68" s="94"/>
+      <c r="J68" s="88"/>
+      <c r="K68" s="88"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="42"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A69" s="144"/>
-      <c r="B69" s="145" t="s">
+      <c r="A69" s="86"/>
+      <c r="B69" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="C69" s="145" t="s">
+      <c r="C69" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="145" t="s">
+      <c r="D69" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="E69" s="145" t="s">
+      <c r="E69" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="F69" s="145" t="s">
+      <c r="F69" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="G69" s="145" t="s">
+      <c r="G69" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="H69" s="146" t="s">
+      <c r="H69" s="291" t="s">
         <v>236</v>
       </c>
-      <c r="I69" s="147"/>
-      <c r="P69" s="164"/>
-      <c r="Q69" s="164"/>
-      <c r="R69" s="63"/>
-      <c r="S69" s="63"/>
+      <c r="I69" s="292"/>
+      <c r="P69" s="288"/>
+      <c r="Q69" s="288"/>
+      <c r="R69" s="289"/>
+      <c r="S69" s="289"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A70" s="144"/>
-      <c r="B70" s="3">
+      <c r="A70" s="86"/>
+      <c r="B70" s="2">
         <v>120</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="2">
         <v>100</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>237</v>
       </c>
       <c r="E70">
@@ -7681,592 +7680,592 @@
       <c r="F70" t="s">
         <v>84</v>
       </c>
-      <c r="H70" s="165">
+      <c r="H70" s="293">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="165"/>
-      <c r="P70" s="164"/>
-      <c r="Q70" s="164"/>
-      <c r="R70" s="63"/>
-      <c r="S70" s="63"/>
+      <c r="I70" s="293"/>
+      <c r="P70" s="288"/>
+      <c r="Q70" s="288"/>
+      <c r="R70" s="289"/>
+      <c r="S70" s="289"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A71" s="144"/>
+      <c r="A71" s="86"/>
       <c r="F71" t="s">
         <v>86</v>
       </c>
-      <c r="H71" s="149">
+      <c r="H71" s="287">
         <v>11.78</v>
       </c>
-      <c r="I71" s="149"/>
-      <c r="P71" s="164"/>
-      <c r="Q71" s="164"/>
-      <c r="R71" s="63"/>
-      <c r="S71" s="63"/>
+      <c r="I71" s="287"/>
+      <c r="P71" s="288"/>
+      <c r="Q71" s="288"/>
+      <c r="R71" s="289"/>
+      <c r="S71" s="289"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A72" s="144"/>
+      <c r="A72" s="86"/>
       <c r="F72" t="s">
         <v>89</v>
       </c>
-      <c r="H72" s="149">
+      <c r="H72" s="287">
         <v>12.39</v>
       </c>
-      <c r="I72" s="149"/>
-      <c r="P72" s="164"/>
-      <c r="Q72" s="164"/>
-      <c r="R72" s="63"/>
-      <c r="S72" s="63"/>
+      <c r="I72" s="287"/>
+      <c r="P72" s="288"/>
+      <c r="Q72" s="288"/>
+      <c r="R72" s="289"/>
+      <c r="S72" s="289"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A73" s="144"/>
+      <c r="A73" s="86"/>
       <c r="F73" t="s">
         <v>238</v>
       </c>
-      <c r="H73" s="149">
+      <c r="H73" s="287">
         <v>11.21</v>
       </c>
-      <c r="I73" s="149"/>
-      <c r="J73" s="150"/>
-      <c r="K73" s="150"/>
-      <c r="P73" s="164"/>
-      <c r="Q73" s="164"/>
-      <c r="R73" s="63"/>
-      <c r="S73" s="63"/>
+      <c r="I73" s="287"/>
+      <c r="J73" s="88"/>
+      <c r="K73" s="88"/>
+      <c r="P73" s="288"/>
+      <c r="Q73" s="288"/>
+      <c r="R73" s="289"/>
+      <c r="S73" s="289"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="144"/>
+      <c r="A74" s="86"/>
       <c r="F74" t="s">
         <v>239</v>
       </c>
-      <c r="H74" s="151">
+      <c r="H74" s="290">
         <v>12.75</v>
       </c>
-      <c r="I74" s="151"/>
-      <c r="J74" s="166">
+      <c r="I74" s="290"/>
+      <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
       </c>
-      <c r="K74" s="157">
+      <c r="K74" s="92">
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="164"/>
-      <c r="Q74" s="164"/>
-      <c r="R74" s="63"/>
-      <c r="S74" s="63"/>
+      <c r="P74" s="288"/>
+      <c r="Q74" s="288"/>
+      <c r="R74" s="289"/>
+      <c r="S74" s="289"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="167"/>
-      <c r="B75" s="152" t="s">
+      <c r="A75" s="96"/>
+      <c r="B75" s="277" t="s">
         <v>240</v>
       </c>
-      <c r="C75" s="153"/>
-      <c r="D75" s="154">
+      <c r="C75" s="278"/>
+      <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
-      <c r="E75" s="168"/>
-      <c r="F75" s="168"/>
-      <c r="G75" s="168"/>
-      <c r="H75" s="169">
+      <c r="E75" s="97"/>
+      <c r="F75" s="97"/>
+      <c r="G75" s="97"/>
+      <c r="H75" s="279">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="170"/>
-      <c r="J75" s="171"/>
-      <c r="K75" s="171"/>
+      <c r="I75" s="280"/>
+      <c r="J75" s="98"/>
+      <c r="K75" s="98"/>
     </row>
     <row r="76" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G76" s="172" t="s">
+      <c r="G76" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="H76" s="119" t="str">
+      <c r="H76" s="180" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="173"/>
+      <c r="I76" s="182"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="174" t="s">
+      <c r="A77" s="281" t="s">
         <v>243</v>
       </c>
-      <c r="B77" s="175"/>
-      <c r="C77" s="175"/>
-      <c r="D77" s="175"/>
-      <c r="E77" s="175"/>
-      <c r="F77" s="175"/>
-      <c r="G77" s="175"/>
-      <c r="H77" s="175"/>
-      <c r="I77" s="176"/>
+      <c r="B77" s="282"/>
+      <c r="C77" s="282"/>
+      <c r="D77" s="282"/>
+      <c r="E77" s="282"/>
+      <c r="F77" s="282"/>
+      <c r="G77" s="282"/>
+      <c r="H77" s="282"/>
+      <c r="I77" s="283"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G78" s="18"/>
-      <c r="H78" s="177"/>
-      <c r="I78" s="177"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="100"/>
+      <c r="I78" s="100"/>
     </row>
     <row r="79" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G79" s="18"/>
-      <c r="H79" s="177"/>
-      <c r="I79" s="177"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="100"/>
+      <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="119" t="s">
+      <c r="A80" s="180" t="s">
         <v>244</v>
       </c>
-      <c r="B80" s="178"/>
-      <c r="C80" s="178"/>
-      <c r="D80" s="82" t="s">
+      <c r="B80" s="181"/>
+      <c r="C80" s="181"/>
+      <c r="D80" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="E80" s="83" t="s">
+      <c r="E80" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="G80" s="150"/>
-      <c r="H80" s="150"/>
-      <c r="I80" s="150"/>
-      <c r="J80" s="150"/>
-      <c r="K80" s="150"/>
+      <c r="G80" s="88"/>
+      <c r="H80" s="88"/>
+      <c r="I80" s="88"/>
+      <c r="J80" s="88"/>
+      <c r="K80" s="88"/>
     </row>
     <row r="81" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="179" t="s">
+      <c r="A81" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B81" s="180" t="s">
+      <c r="B81" s="284" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="181"/>
-      <c r="D81" s="182" t="s">
+      <c r="C81" s="285"/>
+      <c r="D81" s="102" t="s">
         <v>247</v>
       </c>
-      <c r="E81" s="183">
+      <c r="E81" s="103">
         <f t="array" ref="E81">INDEX($J$82:$J$84,MATCH(E80,$I$82:$I$84,0),0)</f>
         <v>0.5</v>
       </c>
-      <c r="G81" s="150"/>
-      <c r="H81" s="184"/>
-      <c r="I81" s="184"/>
-      <c r="J81" s="150"/>
-      <c r="K81" s="150"/>
+      <c r="G81" s="88"/>
+      <c r="H81" s="286"/>
+      <c r="I81" s="286"/>
+      <c r="J81" s="88"/>
+      <c r="K81" s="88"/>
     </row>
     <row r="82" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="185">
+      <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="186">
+      <c r="B82" s="268">
         <v>15</v>
       </c>
-      <c r="C82" s="186"/>
-      <c r="D82" s="187" t="s">
+      <c r="C82" s="268"/>
+      <c r="D82" s="269" t="s">
         <v>248</v>
       </c>
-      <c r="E82" s="188"/>
-      <c r="G82" s="150"/>
-      <c r="H82" s="189"/>
-      <c r="I82" s="190" t="s">
+      <c r="E82" s="106"/>
+      <c r="G82" s="88"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="108" t="s">
         <v>249</v>
       </c>
-      <c r="J82" s="191">
+      <c r="J82" s="109">
         <v>0.42</v>
       </c>
-      <c r="K82" s="150"/>
+      <c r="K82" s="88"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="B83" s="192" t="s">
+      <c r="B83" s="272" t="s">
         <v>251</v>
       </c>
-      <c r="C83" s="193"/>
-      <c r="D83" s="194"/>
-      <c r="E83" s="195" t="s">
+      <c r="C83" s="263"/>
+      <c r="D83" s="270"/>
+      <c r="E83" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="F83" s="196" t="s">
+      <c r="F83" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="G83" s="150"/>
-      <c r="H83" s="189"/>
-      <c r="I83" s="190" t="s">
+      <c r="G83" s="88"/>
+      <c r="H83" s="107"/>
+      <c r="I83" s="108" t="s">
         <v>246</v>
       </c>
-      <c r="J83" s="191">
+      <c r="J83" s="109">
         <v>0.5</v>
       </c>
-      <c r="K83" s="150"/>
+      <c r="K83" s="88"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" s="85">
+      <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="197">
+      <c r="B84" s="273">
         <v>2.8</v>
       </c>
-      <c r="C84" s="197"/>
-      <c r="D84" s="194"/>
-      <c r="E84" s="198">
+      <c r="C84" s="273"/>
+      <c r="D84" s="270"/>
+      <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
       </c>
-      <c r="F84" s="70" t="str">
+      <c r="F84" s="43" t="str">
         <f>IF(E84&lt;(A84+G84),"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="G84" s="150">
+      <c r="G84" s="88">
         <f>IF(A84&lt;1,0.5,IF(AND(A84&gt;=1,A84&lt;=2),(A84/2),IF(A84&gt;2,1)))</f>
         <v>0.625</v>
       </c>
-      <c r="H84" s="150"/>
-      <c r="I84" s="199" t="s">
+      <c r="H84" s="88"/>
+      <c r="I84" s="112" t="s">
         <v>253</v>
       </c>
-      <c r="J84" s="191">
+      <c r="J84" s="109">
         <v>0.5</v>
       </c>
-      <c r="K84" s="150"/>
+      <c r="K84" s="88"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A85" s="85">
+      <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="200">
+      <c r="B85" s="274">
         <v>5</v>
       </c>
-      <c r="C85" s="201"/>
-      <c r="D85" s="194"/>
-      <c r="E85" s="198">
+      <c r="C85" s="275"/>
+      <c r="D85" s="270"/>
+      <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
       </c>
-      <c r="F85" s="70" t="str">
+      <c r="F85" s="43" t="str">
         <f t="shared" ref="F85:F86" si="9">IF(E85&lt;(A85+G85),"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="G85" s="150">
+      <c r="G85" s="88">
         <f t="shared" ref="G85:G86" si="10">IF(A85&lt;1,0.5,IF(AND(A85&gt;=1,A85&lt;=2),(A85/2),IF(A85&gt;2,1)))</f>
         <v>1</v>
       </c>
-      <c r="H85" s="150"/>
-      <c r="I85" s="150"/>
-      <c r="J85" s="150"/>
-      <c r="K85" s="150"/>
+      <c r="H85" s="88"/>
+      <c r="I85" s="88"/>
+      <c r="J85" s="88"/>
+      <c r="K85" s="88"/>
     </row>
     <row r="86" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="202">
+      <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="203">
+      <c r="B86" s="276">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="203"/>
-      <c r="D86" s="204"/>
-      <c r="E86" s="205">
+      <c r="C86" s="276"/>
+      <c r="D86" s="271"/>
+      <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="F86" s="206" t="str">
+      <c r="F86" s="116" t="str">
         <f t="shared" si="9"/>
         <v>Pass</v>
       </c>
-      <c r="G86" s="150">
+      <c r="G86" s="88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H86" s="150"/>
-      <c r="I86" s="150"/>
-      <c r="J86" s="150"/>
-      <c r="K86" s="150"/>
+      <c r="H86" s="88"/>
+      <c r="I86" s="88"/>
+      <c r="J86" s="88"/>
+      <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="207" t="s">
+      <c r="A87" s="254" t="s">
         <v>254</v>
       </c>
-      <c r="B87" s="208"/>
-      <c r="C87" s="208"/>
-      <c r="D87" s="208"/>
-      <c r="E87" s="208"/>
-      <c r="F87" s="209"/>
-      <c r="G87" s="150"/>
-      <c r="H87" s="150"/>
-      <c r="I87" s="150"/>
-      <c r="J87" s="150"/>
-      <c r="K87" s="150"/>
+      <c r="B87" s="255"/>
+      <c r="C87" s="255"/>
+      <c r="D87" s="255"/>
+      <c r="E87" s="255"/>
+      <c r="F87" s="256"/>
+      <c r="G87" s="88"/>
+      <c r="H87" s="88"/>
+      <c r="I87" s="88"/>
+      <c r="J87" s="88"/>
+      <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="210"/>
-      <c r="B88" s="211"/>
-      <c r="C88" s="211"/>
-      <c r="D88" s="211"/>
-      <c r="E88" s="211"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="150"/>
-      <c r="H88" s="150"/>
-      <c r="I88" s="150"/>
-      <c r="J88" s="150"/>
-      <c r="K88" s="150"/>
+      <c r="A88" s="257"/>
+      <c r="B88" s="258"/>
+      <c r="C88" s="258"/>
+      <c r="D88" s="258"/>
+      <c r="E88" s="258"/>
+      <c r="F88" s="259"/>
+      <c r="G88" s="88"/>
+      <c r="H88" s="88"/>
+      <c r="I88" s="88"/>
+      <c r="J88" s="88"/>
+      <c r="K88" s="88"/>
     </row>
     <row r="89" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="213" t="s">
+      <c r="A90" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B90" s="82" t="s">
+      <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="178" t="s">
+      <c r="C90" s="181" t="s">
         <v>255</v>
       </c>
-      <c r="D90" s="178"/>
-      <c r="E90" s="173"/>
+      <c r="D90" s="181"/>
+      <c r="E90" s="182"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="214">
+      <c r="A91" s="118">
         <v>120</v>
       </c>
-      <c r="B91" s="37">
+      <c r="B91" s="20">
         <v>200</v>
       </c>
-      <c r="C91" s="215" t="s">
+      <c r="C91" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="D91" s="216">
+      <c r="D91" s="260">
         <v>107</v>
       </c>
-      <c r="E91" s="217"/>
-      <c r="F91" s="218" t="s">
+      <c r="E91" s="261"/>
+      <c r="F91" s="120" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="219" t="s">
+      <c r="A92" s="262" t="s">
         <v>256</v>
       </c>
-      <c r="B92" s="193"/>
-      <c r="C92" s="220">
+      <c r="B92" s="263"/>
+      <c r="C92" s="264">
         <v>3</v>
       </c>
-      <c r="D92" s="220"/>
-      <c r="E92" s="220"/>
-      <c r="F92" s="221" t="str">
+      <c r="D92" s="264"/>
+      <c r="E92" s="264"/>
+      <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="222" t="s">
+      <c r="A93" s="265" t="s">
         <v>257</v>
       </c>
-      <c r="B93" s="223"/>
-      <c r="C93" s="223"/>
-      <c r="D93" s="223"/>
-      <c r="E93" s="224"/>
+      <c r="B93" s="266"/>
+      <c r="C93" s="266"/>
+      <c r="D93" s="266"/>
+      <c r="E93" s="267"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="225"/>
-      <c r="B94" s="226"/>
-      <c r="C94" s="227"/>
-      <c r="D94" s="227"/>
-      <c r="E94" s="228"/>
+      <c r="A94" s="122"/>
+      <c r="B94" s="123"/>
+      <c r="C94" s="124"/>
+      <c r="D94" s="124"/>
+      <c r="E94" s="125"/>
     </row>
     <row r="95" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="213" t="s">
+      <c r="A95" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B95" s="229" t="s">
+      <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="159" t="s">
+      <c r="C95" s="242" t="s">
         <v>258</v>
       </c>
-      <c r="D95" s="230"/>
-      <c r="E95" s="160"/>
+      <c r="D95" s="243"/>
+      <c r="E95" s="244"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="214">
+      <c r="A96" s="118">
         <v>140</v>
       </c>
-      <c r="B96" s="37">
+      <c r="B96" s="20">
         <v>65</v>
       </c>
-      <c r="C96" s="231" t="s">
+      <c r="C96" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="D96" s="232">
+      <c r="D96" s="245">
         <v>3691</v>
       </c>
-      <c r="E96" s="233"/>
-      <c r="F96" s="218" t="s">
+      <c r="E96" s="246"/>
+      <c r="F96" s="120" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="234" t="s">
+      <c r="A97" s="247" t="s">
         <v>256</v>
       </c>
-      <c r="B97" s="235"/>
-      <c r="C97" s="236">
+      <c r="B97" s="248"/>
+      <c r="C97" s="249">
         <v>6.25</v>
       </c>
-      <c r="D97" s="236"/>
-      <c r="E97" s="236"/>
-      <c r="F97" s="221" t="str">
+      <c r="D97" s="249"/>
+      <c r="E97" s="249"/>
+      <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="237" t="s">
+      <c r="A98" s="250" t="s">
         <v>259</v>
       </c>
-      <c r="B98" s="238"/>
-      <c r="C98" s="238"/>
-      <c r="D98" s="238"/>
-      <c r="E98" s="239"/>
+      <c r="B98" s="251"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
+      <c r="E98" s="252"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="240"/>
-      <c r="B99" s="241"/>
-      <c r="C99" s="241"/>
-      <c r="D99" s="241"/>
-      <c r="E99" s="242"/>
+      <c r="A99" s="225"/>
+      <c r="B99" s="253"/>
+      <c r="C99" s="253"/>
+      <c r="D99" s="253"/>
+      <c r="E99" s="226"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="243"/>
-      <c r="B100" s="243"/>
-      <c r="C100" s="243"/>
-      <c r="D100" s="243"/>
-      <c r="E100" s="243"/>
+      <c r="A100" s="128"/>
+      <c r="B100" s="128"/>
+      <c r="C100" s="128"/>
+      <c r="D100" s="128"/>
+      <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="159" t="s">
+      <c r="A101" s="242" t="s">
         <v>260</v>
       </c>
-      <c r="B101" s="230"/>
-      <c r="C101" s="230"/>
-      <c r="D101" s="230"/>
-      <c r="E101" s="230"/>
-      <c r="F101" s="230"/>
-      <c r="G101" s="230"/>
-      <c r="H101" s="230"/>
-      <c r="I101" s="230"/>
-      <c r="J101" s="160"/>
+      <c r="B101" s="243"/>
+      <c r="C101" s="243"/>
+      <c r="D101" s="243"/>
+      <c r="E101" s="243"/>
+      <c r="F101" s="243"/>
+      <c r="G101" s="243"/>
+      <c r="H101" s="243"/>
+      <c r="I101" s="243"/>
+      <c r="J101" s="244"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="244" t="s">
+      <c r="A102" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="B102" s="245" t="s">
+      <c r="B102" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="C102" s="126" t="s">
+      <c r="C102" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="D102" s="142"/>
-      <c r="E102" s="244" t="s">
+      <c r="D102" s="84"/>
+      <c r="E102" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="F102" s="245">
+      <c r="F102" s="90">
         <v>500</v>
       </c>
-      <c r="G102" s="246" t="s">
+      <c r="G102" s="129" t="s">
         <v>263</v>
       </c>
-      <c r="H102" s="247"/>
-      <c r="I102" s="248"/>
-      <c r="J102" s="249"/>
+      <c r="H102" s="130"/>
+      <c r="I102" s="219"/>
+      <c r="J102" s="220"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="250">
+      <c r="A103" s="131">
         <v>140</v>
       </c>
-      <c r="B103" s="251">
+      <c r="B103" s="132">
         <v>100</v>
       </c>
-      <c r="C103" s="252">
+      <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="253"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="254" t="s">
+      <c r="D103" s="221"/>
+      <c r="E103" s="222"/>
+      <c r="F103" s="222"/>
+      <c r="G103" s="223" t="s">
         <v>264</v>
       </c>
-      <c r="H103" s="255"/>
-      <c r="I103" s="256" t="s">
+      <c r="H103" s="224"/>
+      <c r="I103" s="227" t="s">
         <v>265</v>
       </c>
-      <c r="J103" s="257"/>
-      <c r="K103" s="258" t="s">
+      <c r="J103" s="228"/>
+      <c r="K103" s="231" t="s">
         <v>63</v>
       </c>
-      <c r="L103" s="259"/>
+      <c r="L103" s="232"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="260" t="s">
+      <c r="A104" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="B104" s="261" t="s">
+      <c r="B104" s="134" t="s">
         <v>266</v>
       </c>
-      <c r="C104" s="262" t="s">
+      <c r="C104" s="135" t="s">
         <v>267</v>
       </c>
-      <c r="D104" s="262" t="s">
+      <c r="D104" s="135" t="s">
         <v>268</v>
       </c>
-      <c r="E104" s="263" t="s">
+      <c r="E104" s="136" t="s">
         <v>269</v>
       </c>
-      <c r="F104" s="262" t="s">
+      <c r="F104" s="135" t="s">
         <v>270</v>
       </c>
-      <c r="G104" s="240"/>
-      <c r="H104" s="242"/>
-      <c r="I104" s="130"/>
-      <c r="J104" s="132"/>
-      <c r="K104" s="264"/>
-      <c r="L104" s="265"/>
+      <c r="G104" s="225"/>
+      <c r="H104" s="226"/>
+      <c r="I104" s="229"/>
+      <c r="J104" s="230"/>
+      <c r="K104" s="233"/>
+      <c r="L104" s="234"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="266"/>
-      <c r="B105" s="267"/>
-      <c r="C105" s="268"/>
-      <c r="D105" s="268"/>
-      <c r="E105" s="269"/>
-      <c r="F105" s="270" t="s">
+      <c r="A105" s="194"/>
+      <c r="B105" s="138"/>
+      <c r="C105" s="139"/>
+      <c r="D105" s="139"/>
+      <c r="E105" s="140"/>
+      <c r="F105" s="141" t="s">
         <v>159</v>
       </c>
-      <c r="G105" s="271">
+      <c r="G105" s="236">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="272"/>
-      <c r="I105" s="273">
+      <c r="H105" s="237"/>
+      <c r="I105" s="238">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="274"/>
-      <c r="K105" s="275" t="str">
+      <c r="J105" s="239"/>
+      <c r="K105" s="240" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="276"/>
+      <c r="L105" s="241"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="97" t="s">
+      <c r="A106" s="210" t="s">
         <v>271</v>
       </c>
-      <c r="B106" s="98"/>
-      <c r="C106" s="98"/>
-      <c r="D106" s="98"/>
-      <c r="E106" s="98"/>
-      <c r="F106" s="98"/>
-      <c r="G106" s="98"/>
-      <c r="H106" s="98"/>
-      <c r="I106" s="98"/>
-      <c r="J106" s="98"/>
-      <c r="K106" s="98"/>
-      <c r="L106" s="99"/>
+      <c r="B106" s="211"/>
+      <c r="C106" s="211"/>
+      <c r="D106" s="211"/>
+      <c r="E106" s="211"/>
+      <c r="F106" s="211"/>
+      <c r="G106" s="211"/>
+      <c r="H106" s="211"/>
+      <c r="I106" s="211"/>
+      <c r="J106" s="211"/>
+      <c r="K106" s="211"/>
+      <c r="L106" s="212"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -8275,743 +8274,743 @@
     </row>
     <row r="109" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="213" t="s">
+      <c r="A110" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B110" s="82" t="s">
+      <c r="B110" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C110" s="82" t="s">
+      <c r="C110" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="D110" s="83" t="s">
+      <c r="D110" s="48" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="277">
+      <c r="A111" s="142">
         <v>140</v>
       </c>
-      <c r="B111" s="278">
+      <c r="B111" s="114">
         <v>50</v>
       </c>
-      <c r="C111" s="278">
+      <c r="C111" s="114">
         <v>2</v>
       </c>
-      <c r="D111" s="279">
+      <c r="D111" s="143">
         <v>25000</v>
       </c>
-      <c r="I111" s="150"/>
+      <c r="I111" s="88"/>
     </row>
     <row r="112" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="280"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="162"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="150"/>
+      <c r="A112" s="137"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="93"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="281" t="s">
+      <c r="A113" s="213" t="s">
         <v>115</v>
       </c>
-      <c r="B113" s="282"/>
-      <c r="C113" s="282"/>
-      <c r="D113" s="282"/>
-      <c r="E113" s="282" t="s">
+      <c r="B113" s="214"/>
+      <c r="C113" s="214"/>
+      <c r="D113" s="214"/>
+      <c r="E113" s="214" t="s">
         <v>275</v>
       </c>
-      <c r="F113" s="282"/>
-      <c r="G113" s="282" t="s">
+      <c r="F113" s="214"/>
+      <c r="G113" s="214" t="s">
         <v>276</v>
       </c>
-      <c r="H113" s="282" t="s">
+      <c r="H113" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="I113" s="283" t="s">
+      <c r="I113" s="217" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="284"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="34"/>
-      <c r="D114" s="34"/>
-      <c r="E114" s="34"/>
-      <c r="F114" s="34"/>
-      <c r="G114" s="34"/>
-      <c r="H114" s="34"/>
-      <c r="I114" s="285"/>
+      <c r="A114" s="215"/>
+      <c r="B114" s="216"/>
+      <c r="C114" s="216"/>
+      <c r="D114" s="216"/>
+      <c r="E114" s="216"/>
+      <c r="F114" s="216"/>
+      <c r="G114" s="216"/>
+      <c r="H114" s="216"/>
+      <c r="I114" s="218"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="286" t="s">
+      <c r="A115" s="205" t="s">
         <v>278</v>
       </c>
-      <c r="B115" s="287"/>
-      <c r="C115" s="287"/>
-      <c r="D115" s="287"/>
-      <c r="E115" s="288">
+      <c r="B115" s="206"/>
+      <c r="C115" s="206"/>
+      <c r="D115" s="206"/>
+      <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
-      <c r="F115" s="289" t="s">
+      <c r="F115" s="145" t="s">
         <v>159</v>
       </c>
-      <c r="G115" s="290">
+      <c r="G115" s="146">
         <f>ROUND((E115*D111)/(60*B111),3)</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="H115" s="291" t="str">
+      <c r="H115" s="147" t="str">
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="292" t="s">
+      <c r="I115" s="207" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="293" t="s">
+      <c r="A116" s="201" t="s">
         <v>280</v>
       </c>
-      <c r="B116" s="294"/>
-      <c r="C116" s="294"/>
-      <c r="D116" s="294"/>
-      <c r="E116" s="295">
+      <c r="B116" s="202"/>
+      <c r="C116" s="202"/>
+      <c r="D116" s="202"/>
+      <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="F116" s="296" t="s">
+      <c r="F116" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G116" s="75">
+      <c r="G116" s="45">
         <f>ROUND((E116*D111)/(60*B111),3)</f>
         <v>0.36699999999999999</v>
       </c>
-      <c r="H116" s="297" t="str">
+      <c r="H116" s="149" t="str">
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="298"/>
+      <c r="I116" s="208"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="293" t="s">
+      <c r="A117" s="201" t="s">
         <v>281</v>
       </c>
-      <c r="B117" s="294"/>
-      <c r="C117" s="294"/>
-      <c r="D117" s="294"/>
-      <c r="E117" s="295">
+      <c r="B117" s="202"/>
+      <c r="C117" s="202"/>
+      <c r="D117" s="202"/>
+      <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F117" s="296" t="s">
+      <c r="F117" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G117" s="75">
+      <c r="G117" s="45">
         <f>ROUND((E117*D111)/(60*B111),3)</f>
         <v>0.28299999999999997</v>
       </c>
-      <c r="H117" s="297" t="str">
+      <c r="H117" s="149" t="str">
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="298"/>
+      <c r="I117" s="208"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="293" t="s">
+      <c r="A118" s="201" t="s">
         <v>282</v>
       </c>
-      <c r="B118" s="294"/>
-      <c r="C118" s="294"/>
-      <c r="D118" s="294"/>
-      <c r="E118" s="295">
+      <c r="B118" s="202"/>
+      <c r="C118" s="202"/>
+      <c r="D118" s="202"/>
+      <c r="E118" s="148">
         <v>0.04</v>
       </c>
-      <c r="F118" s="296" t="s">
+      <c r="F118" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G118" s="75">
+      <c r="G118" s="45">
         <f>ROUND((E118*D111)/(60*B111),3)</f>
         <v>0.33300000000000002</v>
       </c>
-      <c r="H118" s="297" t="str">
+      <c r="H118" s="149" t="str">
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="298"/>
+      <c r="I118" s="208"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="299" t="s">
+      <c r="A119" s="203" t="s">
         <v>283</v>
       </c>
-      <c r="B119" s="300"/>
-      <c r="C119" s="300"/>
-      <c r="D119" s="300"/>
-      <c r="E119" s="301">
+      <c r="B119" s="204"/>
+      <c r="C119" s="204"/>
+      <c r="D119" s="204"/>
+      <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F119" s="302" t="s">
+      <c r="F119" s="151" t="s">
         <v>159</v>
       </c>
-      <c r="G119" s="303">
+      <c r="G119" s="152">
         <f>ROUND((E119*D111)/(60*B111),3)</f>
         <v>0.26700000000000002</v>
       </c>
-      <c r="H119" s="304" t="str">
+      <c r="H119" s="153" t="str">
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="305"/>
+      <c r="I119" s="209"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="306" t="s">
+      <c r="A120" s="196" t="s">
         <v>284</v>
       </c>
-      <c r="B120" s="307"/>
-      <c r="C120" s="307"/>
-      <c r="D120" s="307"/>
-      <c r="E120" s="308">
+      <c r="B120" s="197"/>
+      <c r="C120" s="197"/>
+      <c r="D120" s="197"/>
+      <c r="E120" s="154">
         <v>0.106</v>
       </c>
-      <c r="F120" s="309" t="s">
+      <c r="F120" s="155" t="s">
         <v>159</v>
       </c>
-      <c r="G120" s="310">
+      <c r="G120" s="156">
         <f>ROUND((E120*D111)/(60*B111),3)</f>
         <v>0.88300000000000001</v>
       </c>
-      <c r="H120" s="311" t="str">
+      <c r="H120" s="157" t="str">
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="312" t="s">
+      <c r="I120" s="198" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="293" t="s">
+      <c r="A121" s="201" t="s">
         <v>286</v>
       </c>
-      <c r="B121" s="294"/>
-      <c r="C121" s="294"/>
-      <c r="D121" s="294"/>
-      <c r="E121" s="295">
+      <c r="B121" s="202"/>
+      <c r="C121" s="202"/>
+      <c r="D121" s="202"/>
+      <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="F121" s="296" t="s">
+      <c r="F121" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G121" s="75">
+      <c r="G121" s="45">
         <f>ROUND((E121*D111)/(60*B111),3)</f>
         <v>0.317</v>
       </c>
-      <c r="H121" s="297" t="str">
+      <c r="H121" s="149" t="str">
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="313"/>
+      <c r="I121" s="199"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="293" t="s">
+      <c r="A122" s="201" t="s">
         <v>287</v>
       </c>
-      <c r="B122" s="294"/>
-      <c r="C122" s="294"/>
-      <c r="D122" s="294"/>
-      <c r="E122" s="295">
+      <c r="B122" s="202"/>
+      <c r="C122" s="202"/>
+      <c r="D122" s="202"/>
+      <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F122" s="296" t="s">
+      <c r="F122" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G122" s="75">
+      <c r="G122" s="45">
         <f>ROUND((E122*D111)/(60*B111),3)</f>
         <v>0.35</v>
       </c>
-      <c r="H122" s="297" t="str">
+      <c r="H122" s="149" t="str">
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="313"/>
+      <c r="I122" s="199"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="293" t="s">
+      <c r="A123" s="201" t="s">
         <v>288</v>
       </c>
-      <c r="B123" s="294"/>
-      <c r="C123" s="294"/>
-      <c r="D123" s="294"/>
-      <c r="E123" s="295">
+      <c r="B123" s="202"/>
+      <c r="C123" s="202"/>
+      <c r="D123" s="202"/>
+      <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
-      <c r="F123" s="296" t="s">
+      <c r="F123" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G123" s="75">
+      <c r="G123" s="45">
         <f>ROUND((E123*D111)/(60*B111),3)</f>
         <v>0.2</v>
       </c>
-      <c r="H123" s="297" t="str">
+      <c r="H123" s="149" t="str">
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="313"/>
+      <c r="I123" s="199"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="299" t="s">
+      <c r="A124" s="203" t="s">
         <v>289</v>
       </c>
-      <c r="B124" s="300"/>
-      <c r="C124" s="300"/>
-      <c r="D124" s="300"/>
-      <c r="E124" s="301"/>
-      <c r="F124" s="302" t="s">
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+      <c r="D124" s="204"/>
+      <c r="E124" s="150"/>
+      <c r="F124" s="151" t="s">
         <v>159</v>
       </c>
-      <c r="G124" s="303" t="s">
+      <c r="G124" s="152" t="s">
         <v>290</v>
       </c>
-      <c r="H124" s="304" t="s">
+      <c r="H124" s="153" t="s">
         <v>290</v>
       </c>
-      <c r="I124" s="314"/>
+      <c r="I124" s="200"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H125" s="150"/>
-      <c r="I125" s="150"/>
+      <c r="H125" s="88"/>
+      <c r="I125" s="88"/>
     </row>
     <row r="126" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="315" t="s">
+      <c r="A126" s="158" t="s">
         <v>291</v>
       </c>
-      <c r="C126" s="316" t="s">
+      <c r="C126" s="159" t="s">
         <v>292</v>
       </c>
-      <c r="D126" s="317"/>
-      <c r="E126" s="317"/>
-      <c r="F126" s="317"/>
-      <c r="G126" s="318"/>
-      <c r="H126" s="150"/>
-      <c r="I126" s="150"/>
+      <c r="D126" s="160"/>
+      <c r="E126" s="160"/>
+      <c r="F126" s="160"/>
+      <c r="G126" s="161"/>
+      <c r="H126" s="88"/>
+      <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="119" t="s">
+      <c r="A127" s="180" t="s">
         <v>293</v>
       </c>
-      <c r="B127" s="178"/>
-      <c r="C127" s="178"/>
-      <c r="D127" s="178"/>
-      <c r="E127" s="178"/>
-      <c r="F127" s="178"/>
-      <c r="G127" s="173"/>
-      <c r="H127" s="171"/>
-      <c r="I127" s="171"/>
-      <c r="J127" s="171"/>
-      <c r="K127" s="171"/>
-      <c r="L127" s="171"/>
-      <c r="M127" s="171"/>
-      <c r="N127" s="171"/>
-      <c r="O127" s="171"/>
+      <c r="B127" s="181"/>
+      <c r="C127" s="181"/>
+      <c r="D127" s="181"/>
+      <c r="E127" s="181"/>
+      <c r="F127" s="181"/>
+      <c r="G127" s="182"/>
+      <c r="H127" s="98"/>
+      <c r="I127" s="98"/>
+      <c r="J127" s="98"/>
+      <c r="K127" s="98"/>
+      <c r="L127" s="98"/>
+      <c r="M127" s="98"/>
+      <c r="N127" s="98"/>
+      <c r="O127" s="98"/>
     </row>
     <row r="128" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="172" t="s">
+      <c r="A128" s="99" t="s">
         <v>294</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="183" t="s">
         <v>295</v>
       </c>
-      <c r="C128" s="16"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="319" t="s">
+      <c r="C128" s="184"/>
+      <c r="D128" s="184"/>
+      <c r="E128" s="185"/>
+      <c r="F128" s="162" t="s">
         <v>296</v>
       </c>
-      <c r="G128" s="320" t="s">
+      <c r="G128" s="163" t="s">
         <v>200</v>
       </c>
-      <c r="H128" s="150"/>
-      <c r="I128" s="150"/>
-      <c r="J128" s="150"/>
-      <c r="K128" s="171"/>
-      <c r="L128" s="171"/>
-      <c r="M128" s="171"/>
-      <c r="N128" s="171"/>
-      <c r="O128" s="171"/>
+      <c r="H128" s="88"/>
+      <c r="I128" s="88"/>
+      <c r="J128" s="88"/>
+      <c r="K128" s="98"/>
+      <c r="L128" s="98"/>
+      <c r="M128" s="98"/>
+      <c r="N128" s="98"/>
+      <c r="O128" s="98"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A129" s="213">
+      <c r="A129" s="117">
         <v>15</v>
       </c>
-      <c r="B129" s="82" t="s">
+      <c r="B129" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="C129" s="321"/>
-      <c r="D129" s="322" t="s">
+      <c r="C129" s="105"/>
+      <c r="D129" s="164" t="s">
         <v>298</v>
       </c>
-      <c r="E129" s="321"/>
-      <c r="F129" s="82" t="e">
+      <c r="E129" s="105"/>
+      <c r="F129" s="47" t="e">
         <f>ROUND(DEGREES(H129),2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G129" s="196" t="e">
+      <c r="G129" s="110" t="e">
         <f>IF(I129&lt;2,"Pass","Fail")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H129" s="150" t="e">
+      <c r="H129" s="88" t="e">
         <f>ROUND(ACOS(C129/E129),4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I129" s="150" t="e">
+      <c r="I129" s="88" t="e">
         <f>ABS(A129-F129)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J129" s="150"/>
-      <c r="K129" s="171"/>
-      <c r="L129" s="171"/>
-      <c r="M129" s="171"/>
-      <c r="N129" s="171"/>
-      <c r="O129" s="171"/>
+      <c r="J129" s="88"/>
+      <c r="K129" s="98"/>
+      <c r="L129" s="98"/>
+      <c r="M129" s="98"/>
+      <c r="N129" s="98"/>
+      <c r="O129" s="98"/>
     </row>
     <row r="130" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="179">
+      <c r="A130" s="101">
         <v>15</v>
       </c>
-      <c r="B130" s="182" t="s">
+      <c r="B130" s="102" t="s">
         <v>299</v>
       </c>
-      <c r="C130" s="278"/>
-      <c r="D130" s="323" t="s">
+      <c r="C130" s="114"/>
+      <c r="D130" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="E130" s="278"/>
-      <c r="F130" s="182" t="e">
+      <c r="E130" s="114"/>
+      <c r="F130" s="102" t="e">
         <f>ROUND(DEGREES(H130),2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G130" s="206" t="e">
+      <c r="G130" s="116" t="e">
         <f>IF(I130&lt;2,"Pass","Fail")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H130" s="150" t="e">
+      <c r="H130" s="88" t="e">
         <f>ROUND(ACOS(C130/E130),4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I130" s="150" t="e">
+      <c r="I130" s="88" t="e">
         <f>ABS(A130-F130)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J130" s="150"/>
-      <c r="K130" s="171"/>
-      <c r="L130" s="171"/>
-      <c r="M130" s="171"/>
-      <c r="N130" s="171"/>
-      <c r="O130" s="171"/>
+      <c r="J130" s="88"/>
+      <c r="K130" s="98"/>
+      <c r="L130" s="98"/>
+      <c r="M130" s="98"/>
+      <c r="N130" s="98"/>
+      <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="324" t="s">
+      <c r="A131" s="186" t="s">
         <v>301</v>
       </c>
-      <c r="B131" s="325"/>
-      <c r="C131" s="325"/>
-      <c r="D131" s="325"/>
-      <c r="E131" s="325"/>
-      <c r="F131" s="325"/>
-      <c r="G131" s="326"/>
-      <c r="H131" s="150"/>
-      <c r="I131" s="150"/>
-      <c r="J131" s="150"/>
-      <c r="K131" s="171"/>
-      <c r="L131" s="171"/>
-      <c r="M131" s="171"/>
-      <c r="N131" s="171"/>
-      <c r="O131" s="171"/>
+      <c r="B131" s="176"/>
+      <c r="C131" s="176"/>
+      <c r="D131" s="176"/>
+      <c r="E131" s="176"/>
+      <c r="F131" s="176"/>
+      <c r="G131" s="177"/>
+      <c r="H131" s="88"/>
+      <c r="I131" s="88"/>
+      <c r="J131" s="88"/>
+      <c r="K131" s="98"/>
+      <c r="L131" s="98"/>
+      <c r="M131" s="98"/>
+      <c r="N131" s="98"/>
+      <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="327" t="s">
+      <c r="A132" s="187" t="s">
         <v>302</v>
       </c>
-      <c r="B132" s="328"/>
-      <c r="C132" s="328"/>
-      <c r="D132" s="328"/>
-      <c r="E132" s="328"/>
-      <c r="F132" s="328"/>
-      <c r="G132" s="329"/>
-      <c r="H132" s="150"/>
-      <c r="I132" s="150"/>
-      <c r="J132" s="150"/>
-      <c r="K132" s="171"/>
-      <c r="L132" s="171"/>
-      <c r="M132" s="171"/>
-      <c r="N132" s="171"/>
-      <c r="O132" s="171"/>
+      <c r="B132" s="188"/>
+      <c r="C132" s="188"/>
+      <c r="D132" s="188"/>
+      <c r="E132" s="188"/>
+      <c r="F132" s="188"/>
+      <c r="G132" s="189"/>
+      <c r="H132" s="88"/>
+      <c r="I132" s="88"/>
+      <c r="J132" s="88"/>
+      <c r="K132" s="98"/>
+      <c r="L132" s="98"/>
+      <c r="M132" s="98"/>
+      <c r="N132" s="98"/>
+      <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="330"/>
-      <c r="B133" s="331"/>
-      <c r="C133" s="331"/>
-      <c r="D133" s="331"/>
-      <c r="E133" s="331"/>
-      <c r="F133" s="331"/>
-      <c r="G133" s="332"/>
-      <c r="H133" s="171"/>
-      <c r="I133" s="171"/>
-      <c r="J133" s="171"/>
-      <c r="K133" s="171"/>
-      <c r="L133" s="171"/>
-      <c r="M133" s="171"/>
-      <c r="N133" s="171"/>
-      <c r="O133" s="171"/>
+      <c r="A133" s="190"/>
+      <c r="B133" s="191"/>
+      <c r="C133" s="191"/>
+      <c r="D133" s="191"/>
+      <c r="E133" s="191"/>
+      <c r="F133" s="191"/>
+      <c r="G133" s="192"/>
+      <c r="H133" s="98"/>
+      <c r="I133" s="98"/>
+      <c r="J133" s="98"/>
+      <c r="K133" s="98"/>
+      <c r="L133" s="98"/>
+      <c r="M133" s="98"/>
+      <c r="N133" s="98"/>
+      <c r="O133" s="98"/>
     </row>
     <row r="134" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H134" s="171"/>
-      <c r="I134" s="171"/>
-      <c r="J134" s="171"/>
-      <c r="K134" s="171"/>
-      <c r="L134" s="171"/>
-      <c r="M134" s="171"/>
-      <c r="N134" s="171"/>
-      <c r="O134" s="171"/>
+      <c r="H134" s="98"/>
+      <c r="I134" s="98"/>
+      <c r="J134" s="98"/>
+      <c r="K134" s="98"/>
+      <c r="L134" s="98"/>
+      <c r="M134" s="98"/>
+      <c r="N134" s="98"/>
+      <c r="O134" s="98"/>
     </row>
     <row r="135" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="333" t="s">
+      <c r="A135" s="166" t="s">
         <v>303</v>
       </c>
-      <c r="B135" s="246"/>
-      <c r="C135" s="246"/>
-      <c r="D135" s="334">
+      <c r="B135" s="129"/>
+      <c r="C135" s="129"/>
+      <c r="D135" s="167">
         <v>0</v>
       </c>
-      <c r="E135" s="335" t="s">
+      <c r="E135" s="168" t="s">
         <v>304</v>
       </c>
-      <c r="F135" s="336" t="str">
+      <c r="F135" s="169" t="str">
         <f>IF(D135&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I135" s="171"/>
-      <c r="J135" s="171"/>
-      <c r="K135" s="171"/>
-      <c r="L135" s="171"/>
-      <c r="M135" s="171"/>
-      <c r="N135" s="171"/>
-      <c r="O135" s="171"/>
+      <c r="I135" s="98"/>
+      <c r="J135" s="98"/>
+      <c r="K135" s="98"/>
+      <c r="L135" s="98"/>
+      <c r="M135" s="98"/>
+      <c r="N135" s="98"/>
+      <c r="O135" s="98"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H136" s="171"/>
-      <c r="I136" s="171"/>
-      <c r="J136" s="171"/>
-      <c r="K136" s="171"/>
-      <c r="L136" s="171"/>
-      <c r="M136" s="171"/>
-      <c r="N136" s="171"/>
-      <c r="O136" s="171"/>
+      <c r="H136" s="98"/>
+      <c r="I136" s="98"/>
+      <c r="J136" s="98"/>
+      <c r="K136" s="98"/>
+      <c r="L136" s="98"/>
+      <c r="M136" s="98"/>
+      <c r="N136" s="98"/>
+      <c r="O136" s="98"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H137" s="171"/>
-      <c r="I137" s="171"/>
-      <c r="J137" s="171"/>
-      <c r="K137" s="171"/>
-      <c r="L137" s="171"/>
-      <c r="M137" s="171"/>
-      <c r="N137" s="171"/>
-      <c r="O137" s="171"/>
+      <c r="H137" s="98"/>
+      <c r="I137" s="98"/>
+      <c r="J137" s="98"/>
+      <c r="K137" s="98"/>
+      <c r="L137" s="98"/>
+      <c r="M137" s="98"/>
+      <c r="N137" s="98"/>
+      <c r="O137" s="98"/>
     </row>
     <row r="138" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="71" t="s">
+      <c r="A138" s="44" t="s">
         <v>305</v>
       </c>
-      <c r="H138" s="171"/>
-      <c r="I138" s="171"/>
-      <c r="J138" s="171"/>
-      <c r="K138" s="171"/>
-      <c r="L138" s="171"/>
-      <c r="M138" s="171"/>
-      <c r="N138" s="171"/>
-      <c r="O138" s="171"/>
+      <c r="H138" s="98"/>
+      <c r="I138" s="98"/>
+      <c r="J138" s="98"/>
+      <c r="K138" s="98"/>
+      <c r="L138" s="98"/>
+      <c r="M138" s="98"/>
+      <c r="N138" s="98"/>
+      <c r="O138" s="98"/>
     </row>
     <row r="139" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="337" t="s">
+      <c r="A139" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="B139" s="321">
+      <c r="B139" s="105">
         <v>0</v>
       </c>
-      <c r="C139" s="321">
+      <c r="C139" s="105">
         <v>50</v>
       </c>
-      <c r="D139" s="321">
+      <c r="D139" s="105">
         <v>100</v>
       </c>
-      <c r="E139" s="321">
+      <c r="E139" s="105">
         <v>150</v>
       </c>
-      <c r="F139" s="338">
+      <c r="F139" s="171">
         <v>200</v>
       </c>
-      <c r="G139" s="339"/>
-      <c r="H139" s="171"/>
-      <c r="I139" s="171"/>
-      <c r="J139" s="171"/>
-      <c r="K139" s="171"/>
-      <c r="L139" s="171"/>
-      <c r="M139" s="171"/>
-      <c r="N139" s="171"/>
-      <c r="O139" s="171"/>
+      <c r="G139" s="172"/>
+      <c r="H139" s="98"/>
+      <c r="I139" s="98"/>
+      <c r="J139" s="98"/>
+      <c r="K139" s="98"/>
+      <c r="L139" s="98"/>
+      <c r="M139" s="98"/>
+      <c r="N139" s="98"/>
+      <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="340" t="s">
+      <c r="A140" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="37">
+      <c r="B140" s="20">
         <v>15.88</v>
       </c>
-      <c r="C140" s="37">
+      <c r="C140" s="20">
         <v>65.88</v>
       </c>
-      <c r="D140" s="37">
+      <c r="D140" s="20">
         <v>115.88</v>
       </c>
-      <c r="E140" s="37">
+      <c r="E140" s="20">
         <v>165.88</v>
       </c>
-      <c r="F140" s="37">
+      <c r="F140" s="20">
         <v>215.88</v>
       </c>
-      <c r="G140" s="37">
+      <c r="G140" s="20">
         <v>-117.68</v>
       </c>
-      <c r="H140" s="171"/>
-      <c r="I140" s="171"/>
-      <c r="J140" s="171"/>
-      <c r="K140" s="171"/>
-      <c r="L140" s="171"/>
-      <c r="M140" s="171"/>
-      <c r="N140" s="171"/>
-      <c r="O140" s="171"/>
+      <c r="H140" s="98"/>
+      <c r="I140" s="98"/>
+      <c r="J140" s="98"/>
+      <c r="K140" s="98"/>
+      <c r="L140" s="98"/>
+      <c r="M140" s="98"/>
+      <c r="N140" s="98"/>
+      <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="266"/>
-      <c r="B141" s="37">
+      <c r="A141" s="194"/>
+      <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
       </c>
-      <c r="C141" s="37">
+      <c r="C141" s="20">
         <f>ABS(B140-C140)</f>
         <v>49.999999999999993</v>
       </c>
-      <c r="D141" s="37">
+      <c r="D141" s="20">
         <f>ABS(B140-D140)</f>
         <v>100</v>
       </c>
-      <c r="E141" s="37">
+      <c r="E141" s="20">
         <f>ABS(B140-E140)</f>
         <v>150</v>
       </c>
-      <c r="F141" s="37">
+      <c r="F141" s="20">
         <f>ABS(B140-F140)</f>
         <v>200</v>
       </c>
-      <c r="G141" s="37">
+      <c r="G141" s="20">
         <f>ABS(B140-G140)</f>
         <v>133.56</v>
       </c>
-      <c r="H141" s="171"/>
-      <c r="I141" s="171"/>
-      <c r="J141" s="171"/>
-      <c r="K141" s="171"/>
-      <c r="L141" s="171"/>
-      <c r="M141" s="171"/>
-      <c r="N141" s="171"/>
-      <c r="O141" s="171"/>
+      <c r="H141" s="98"/>
+      <c r="I141" s="98"/>
+      <c r="J141" s="98"/>
+      <c r="K141" s="98"/>
+      <c r="L141" s="98"/>
+      <c r="M141" s="98"/>
+      <c r="N141" s="98"/>
+      <c r="O141" s="98"/>
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="167"/>
-      <c r="B142" s="341" t="s">
+      <c r="A142" s="96"/>
+      <c r="B142" s="195" t="s">
         <v>306</v>
       </c>
-      <c r="C142" s="342">
+      <c r="C142" s="173">
         <f>C139-C141</f>
         <v>0</v>
       </c>
-      <c r="D142" s="342">
+      <c r="D142" s="173">
         <f t="shared" ref="D142:G142" si="13">D139-D141</f>
         <v>0</v>
       </c>
-      <c r="E142" s="342">
+      <c r="E142" s="173">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F142" s="342">
+      <c r="F142" s="173">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G142" s="342">
+      <c r="G142" s="173">
         <f t="shared" si="13"/>
         <v>-133.56</v>
       </c>
-      <c r="H142" s="171"/>
-      <c r="I142" s="171"/>
-      <c r="J142" s="171"/>
-      <c r="K142" s="171"/>
-      <c r="L142" s="171"/>
-      <c r="M142" s="171"/>
-      <c r="N142" s="171"/>
-      <c r="O142" s="171"/>
+      <c r="H142" s="98"/>
+      <c r="I142" s="98"/>
+      <c r="J142" s="98"/>
+      <c r="K142" s="98"/>
+      <c r="L142" s="98"/>
+      <c r="M142" s="98"/>
+      <c r="N142" s="98"/>
+      <c r="O142" s="98"/>
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="167"/>
-      <c r="B143" s="341"/>
-      <c r="C143" s="37" t="str">
+      <c r="A143" s="96"/>
+      <c r="B143" s="195"/>
+      <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
       </c>
-      <c r="D143" s="37" t="str">
+      <c r="D143" s="20" t="str">
         <f t="shared" si="14"/>
         <v>Pass</v>
       </c>
-      <c r="E143" s="37" t="str">
+      <c r="E143" s="20" t="str">
         <f t="shared" si="14"/>
         <v>Pass</v>
       </c>
-      <c r="F143" s="37" t="str">
+      <c r="F143" s="20" t="str">
         <f>IF(F142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
       </c>
-      <c r="G143" s="296" t="str">
+      <c r="G143" s="6" t="str">
         <f>IF(G142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
       </c>
-      <c r="H143" s="171"/>
-      <c r="I143" s="171"/>
-      <c r="J143" s="171"/>
-      <c r="K143" s="171"/>
-      <c r="L143" s="171"/>
-      <c r="M143" s="171"/>
-      <c r="N143" s="171"/>
-      <c r="O143" s="171"/>
+      <c r="H143" s="98"/>
+      <c r="I143" s="98"/>
+      <c r="J143" s="98"/>
+      <c r="K143" s="98"/>
+      <c r="L143" s="98"/>
+      <c r="M143" s="98"/>
+      <c r="N143" s="98"/>
+      <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="343" t="s">
+      <c r="A144" s="175" t="s">
         <v>307</v>
       </c>
-      <c r="B144" s="325"/>
-      <c r="C144" s="325"/>
-      <c r="D144" s="325"/>
-      <c r="E144" s="325"/>
-      <c r="F144" s="325"/>
-      <c r="G144" s="326"/>
+      <c r="B144" s="176"/>
+      <c r="C144" s="176"/>
+      <c r="D144" s="176"/>
+      <c r="E144" s="176"/>
+      <c r="F144" s="176"/>
+      <c r="G144" s="177"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="343" t="s">
+      <c r="A145" s="175" t="s">
         <v>308</v>
       </c>
-      <c r="B145" s="344"/>
-      <c r="C145" s="344"/>
-      <c r="D145" s="344"/>
-      <c r="E145" s="344"/>
-      <c r="F145" s="344"/>
-      <c r="G145" s="345"/>
+      <c r="B145" s="178"/>
+      <c r="C145" s="178"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="179"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9027,26 +9026,107 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9062,107 +9142,26 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
   </mergeCells>
   <conditionalFormatting sqref="C142:G142">
     <cfRule type="cellIs" dxfId="40" priority="6" operator="greaterThan">
@@ -9178,19 +9177,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:F86">
+    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",F84)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="36" priority="19" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",F84)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",F84)))</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
+    <cfRule type="containsText" dxfId="35" priority="18" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",F92)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="34" priority="17" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",F92)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="18" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",F92)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
@@ -9228,11 +9227,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H66:I66">
+    <cfRule type="containsText" dxfId="25" priority="24" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",H66)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="24" priority="22" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",H66)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="24" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",H66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H75:I75">
@@ -9241,11 +9240,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H76:I76 H78:I79">
+    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",H76)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",H76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",H76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105:J105">
@@ -9264,11 +9263,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L105">
+    <cfRule type="containsText" dxfId="17" priority="14" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K105)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",K105)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",K105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q14:T14">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCEA6A7-8CC4-439C-B14C-ED7227A42A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF25B65D-8DB7-42C1-9160-09DFAF1D835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="306">
   <si>
     <t>TEST: RADIATION PROFILE WIDTH FOR CT SCAN</t>
   </si>
@@ -438,15 +438,6 @@
   </si>
   <si>
     <t>0.5</t>
-  </si>
-  <si>
-    <t>TEST: ALIGNMENT OF TABLE/GANTRY</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>±2.0</t>
   </si>
   <si>
     <t>TEST: TABLE POSITION</t>
@@ -2549,6 +2540,474 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2564,24 +3023,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2606,9 +3047,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2617,453 +3055,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4701,47 +4692,26 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F63" t="s">
         <v>3</v>
@@ -4764,7 +4734,7 @@
         <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E64" t="s">
         <v>26</v>
@@ -4787,7 +4757,7 @@
         <v>44</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
@@ -4807,7 +4777,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -4815,29 +4785,29 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C68" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C69" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
         <v>138</v>
@@ -4845,18 +4815,18 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -4864,16 +4834,16 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" t="s">
+        <v>158</v>
+      </c>
+      <c r="E74" t="s">
         <v>159</v>
-      </c>
-      <c r="C74" t="s">
-        <v>160</v>
-      </c>
-      <c r="D74" t="s">
-        <v>161</v>
-      </c>
-      <c r="E74" t="s">
-        <v>162</v>
       </c>
       <c r="F74" t="s">
         <v>4</v>
@@ -4890,19 +4860,19 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
         <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E75" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
@@ -4914,18 +4884,18 @@
         <v>138</v>
       </c>
       <c r="I75" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
         <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D76" t="s">
         <v>10</v>
@@ -4949,7 +4919,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M2 A5:M8 A4:H4 J4:M4 B3:M3 A12:M76 A9 C9:M9 A10 C10:M10 A11 C11:M11" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M2 A5:M8 A4:H4 J4:M4 B3:M3 A12:M57 A9 C9:M9 A10 C10:M10 A11 C11:M11 A61:M76" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4979,40 +4949,40 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" s="342" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" s="342"/>
-      <c r="D1" s="342"/>
-      <c r="E1" s="342"/>
-      <c r="F1" s="342"/>
-      <c r="G1" s="342"/>
-      <c r="H1" s="342"/>
-      <c r="I1" s="342"/>
+        <v>166</v>
+      </c>
+      <c r="B1" s="175" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
+      <c r="K1" s="177"/>
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="342" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="342"/>
-      <c r="D2" s="342"/>
-      <c r="E2" s="342"/>
-      <c r="F2" s="342"/>
-      <c r="G2" s="342"/>
-      <c r="H2" s="342"/>
-      <c r="I2" s="342"/>
+        <v>168</v>
+      </c>
+      <c r="B2" s="175" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5022,16 +4992,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="342" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="342"/>
-      <c r="D3" s="342"/>
-      <c r="E3" s="342"/>
-      <c r="F3" s="342"/>
-      <c r="G3" s="342"/>
-      <c r="H3" s="342"/>
-      <c r="I3" s="342"/>
+      <c r="B3" s="175" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5041,16 +5011,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="342"/>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
+        <v>171</v>
+      </c>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5060,22 +5030,22 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="342" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="342"/>
-      <c r="D5" s="342"/>
-      <c r="E5" s="342"/>
+        <v>172</v>
+      </c>
+      <c r="B5" s="175" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="345">
+        <v>174</v>
+      </c>
+      <c r="G5" s="176">
         <v>22.7</v>
       </c>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5085,22 +5055,22 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="342" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="342"/>
-      <c r="D6" s="342"/>
-      <c r="E6" s="342"/>
+        <v>175</v>
+      </c>
+      <c r="B6" s="175" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="175"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
       <c r="F6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="345">
+        <v>177</v>
+      </c>
+      <c r="G6" s="176">
         <v>50.2</v>
       </c>
-      <c r="H6" s="345"/>
-      <c r="I6" s="345"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5110,22 +5080,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="342" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
+        <v>178</v>
+      </c>
+      <c r="B7" s="175" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="175"/>
       <c r="F7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="342" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
+      <c r="G7" s="175" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="175"/>
+      <c r="I7" s="175"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5134,18 +5104,18 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" s="341">
+        <v>181</v>
+      </c>
+      <c r="B8" s="191">
         <v>46066</v>
       </c>
-      <c r="C8" s="342"/>
-      <c r="D8" s="342"/>
-      <c r="E8" s="342"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="175"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="342"/>
-      <c r="H8" s="342"/>
-      <c r="I8" s="342"/>
+      <c r="G8" s="175"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5154,14 +5124,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5170,18 +5140,18 @@
     </row>
     <row r="10" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="343" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="343"/>
-      <c r="D10" s="343"/>
-      <c r="E10" s="343"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="343"/>
-      <c r="H10" s="343"/>
-      <c r="I10" s="344"/>
+        <v>182</v>
+      </c>
+      <c r="B10" s="192" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5189,39 +5159,39 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="183" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="184" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="184"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="185"/>
+      <c r="A11" s="194" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="195"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="195" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="196"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="331" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q11" s="332"/>
-      <c r="R11" s="332"/>
-      <c r="S11" s="332"/>
-      <c r="T11" s="332"/>
-      <c r="U11" s="332"/>
-      <c r="V11" s="332"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
+      <c r="P11" s="179" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q11" s="180"/>
+      <c r="R11" s="180"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="180"/>
+      <c r="U11" s="180"/>
+      <c r="V11" s="180"/>
+      <c r="W11" s="180"/>
+      <c r="X11" s="181"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
@@ -5230,22 +5200,22 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>195</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -5254,26 +5224,26 @@
         <v>65</v>
       </c>
       <c r="N12" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="P12" s="182" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q12" s="184" t="s">
+        <v>195</v>
+      </c>
+      <c r="R12" s="184"/>
+      <c r="S12" s="184"/>
+      <c r="T12" s="185" t="s">
         <v>196</v>
       </c>
-      <c r="P12" s="334" t="s">
+      <c r="U12" s="187" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" s="336" t="s">
+      <c r="V12" s="185"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="189" t="s">
         <v>198</v>
-      </c>
-      <c r="R12" s="336"/>
-      <c r="S12" s="336"/>
-      <c r="T12" s="337" t="s">
-        <v>199</v>
-      </c>
-      <c r="U12" s="305" t="s">
-        <v>200</v>
-      </c>
-      <c r="V12" s="337"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="339" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -5312,7 +5282,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="335"/>
+      <c r="P13" s="183"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5325,11 +5295,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="338"/>
-      <c r="U13" s="216"/>
-      <c r="V13" s="338"/>
+      <c r="T13" s="186"/>
+      <c r="U13" s="188"/>
+      <c r="V13" s="186"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="340"/>
+      <c r="X13" s="190"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5397,7 +5367,7 @@
         <v>0.70999999999999375</v>
       </c>
       <c r="Y14" s="28" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29"/>
@@ -5498,7 +5468,7 @@
         <v>9.1636581420898438</v>
       </c>
       <c r="L16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
@@ -5588,7 +5558,7 @@
         <v>141.59</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="T17" s="36">
         <f>ROUND(AVERAGE(Q17:S17),2)</f>
@@ -5641,15 +5611,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="325" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q18" s="326"/>
-      <c r="R18" s="326"/>
-      <c r="S18" s="326"/>
-      <c r="T18" s="326"/>
-      <c r="U18" s="326"/>
-      <c r="V18" s="327"/>
+      <c r="P18" s="206" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q18" s="207"/>
+      <c r="R18" s="207"/>
+      <c r="S18" s="207"/>
+      <c r="T18" s="207"/>
+      <c r="U18" s="207"/>
+      <c r="V18" s="208"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5689,13 +5659,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="289"/>
-      <c r="Q19" s="289"/>
-      <c r="R19" s="289"/>
-      <c r="S19" s="289"/>
-      <c r="T19" s="289"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
+      <c r="P19" s="209"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5733,14 +5703,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="310" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q20" s="311"/>
-      <c r="R20" s="311"/>
-      <c r="S20" s="311"/>
-      <c r="T20" s="311"/>
-      <c r="U20" s="313"/>
+      <c r="P20" s="210" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q20" s="211"/>
+      <c r="R20" s="211"/>
+      <c r="S20" s="211"/>
+      <c r="T20" s="211"/>
+      <c r="U20" s="212"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5778,16 +5748,16 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="328" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q21" s="329"/>
-      <c r="R21" s="330" t="s">
-        <v>208</v>
-      </c>
-      <c r="S21" s="329"/>
+      <c r="P21" s="213" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q21" s="214"/>
+      <c r="R21" s="215" t="s">
+        <v>205</v>
+      </c>
+      <c r="S21" s="214"/>
       <c r="T21" s="14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U21" s="43" t="s">
         <v>63</v>
@@ -5822,7 +5792,7 @@
         <v>9.1354408264160156</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
@@ -5832,16 +5802,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="316">
+      <c r="P22" s="197">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="317"/>
-      <c r="R22" s="318">
+      <c r="Q22" s="198"/>
+      <c r="R22" s="199">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="318"/>
+      <c r="S22" s="199"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5887,16 +5857,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="316">
+      <c r="P23" s="197">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="317"/>
-      <c r="R23" s="318">
+      <c r="Q23" s="198"/>
+      <c r="R23" s="199">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="318"/>
+      <c r="S23" s="199"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -5942,16 +5912,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="316">
+      <c r="P24" s="197">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="317"/>
-      <c r="R24" s="318">
+      <c r="Q24" s="198"/>
+      <c r="R24" s="199">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="318"/>
+      <c r="S24" s="199"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -5997,14 +5967,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="319" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q25" s="320"/>
-      <c r="R25" s="320"/>
-      <c r="S25" s="320"/>
-      <c r="T25" s="320"/>
-      <c r="U25" s="321"/>
+      <c r="P25" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q25" s="201"/>
+      <c r="R25" s="201"/>
+      <c r="S25" s="201"/>
+      <c r="T25" s="201"/>
+      <c r="U25" s="202"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6079,20 +6049,20 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="322" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q27" s="323"/>
-      <c r="R27" s="324"/>
+      <c r="P27" s="203" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q27" s="204"/>
+      <c r="R27" s="205"/>
       <c r="S27" s="47" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="T27" s="47">
         <f>A34</f>
         <v>120</v>
       </c>
       <c r="U27" s="47" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="V27" s="47"/>
       <c r="W27" s="47"/>
@@ -6138,23 +6108,23 @@
         <v>9.4741999999999997</v>
       </c>
       <c r="P28" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q28" s="187" t="s">
+        <v>212</v>
+      </c>
+      <c r="R28" s="187"/>
+      <c r="S28" s="187"/>
+      <c r="T28" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="U28" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="Q28" s="305" t="s">
-        <v>215</v>
-      </c>
-      <c r="R28" s="305"/>
-      <c r="S28" s="305"/>
-      <c r="T28" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="U28" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
       <c r="X28" s="43" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -6186,7 +6156,7 @@
         <v>9.0879783630371094</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M29">
         <f t="shared" si="1"/>
@@ -6216,13 +6186,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="306">
+      <c r="U29" s="237">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="308" t="str">
+      <c r="X29" s="239" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6283,10 +6253,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="306"/>
+      <c r="U30" s="237"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="308"/>
+      <c r="X30" s="239"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6344,10 +6314,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="306"/>
+      <c r="U31" s="237"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="308"/>
+      <c r="X31" s="239"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6405,10 +6375,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="307"/>
+      <c r="U32" s="238"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="309"/>
+      <c r="X32" s="240"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6446,17 +6416,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="210" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q33" s="211"/>
-      <c r="R33" s="211"/>
-      <c r="S33" s="211"/>
-      <c r="T33" s="211"/>
-      <c r="U33" s="211"/>
-      <c r="V33" s="211"/>
-      <c r="W33" s="211"/>
-      <c r="X33" s="212"/>
+      <c r="P33" s="220" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q33" s="221"/>
+      <c r="R33" s="221"/>
+      <c r="S33" s="221"/>
+      <c r="T33" s="221"/>
+      <c r="U33" s="221"/>
+      <c r="V33" s="221"/>
+      <c r="W33" s="221"/>
+      <c r="X33" s="222"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6531,18 +6501,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="310" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q35" s="311"/>
-      <c r="R35" s="311"/>
-      <c r="S35" s="311"/>
-      <c r="T35" s="311"/>
-      <c r="U35" s="311"/>
-      <c r="V35" s="312"/>
-      <c r="W35" s="312"/>
-      <c r="X35" s="312"/>
-      <c r="Y35" s="313"/>
+      <c r="P35" s="210" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q35" s="211"/>
+      <c r="R35" s="211"/>
+      <c r="S35" s="211"/>
+      <c r="T35" s="211"/>
+      <c r="U35" s="211"/>
+      <c r="V35" s="241"/>
+      <c r="W35" s="241"/>
+      <c r="X35" s="241"/>
+      <c r="Y35" s="212"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6583,24 +6553,24 @@
       <c r="P36" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="Q36" s="314" t="s">
-        <v>215</v>
-      </c>
-      <c r="R36" s="314"/>
-      <c r="S36" s="314"/>
-      <c r="T36" s="314"/>
-      <c r="U36" s="315"/>
+      <c r="Q36" s="242" t="s">
+        <v>212</v>
+      </c>
+      <c r="R36" s="242"/>
+      <c r="S36" s="242"/>
+      <c r="T36" s="242"/>
+      <c r="U36" s="243"/>
       <c r="V36" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="W36" s="18" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="X36" s="17" t="s">
         <v>104</v>
       </c>
       <c r="Y36" s="57" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,18 +6917,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="210" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q41" s="211"/>
-      <c r="R41" s="211"/>
-      <c r="S41" s="211"/>
-      <c r="T41" s="211"/>
-      <c r="U41" s="211"/>
-      <c r="V41" s="211"/>
-      <c r="W41" s="211"/>
-      <c r="X41" s="211"/>
-      <c r="Y41" s="212"/>
+      <c r="P41" s="220" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q41" s="221"/>
+      <c r="R41" s="221"/>
+      <c r="S41" s="221"/>
+      <c r="T41" s="221"/>
+      <c r="U41" s="221"/>
+      <c r="V41" s="221"/>
+      <c r="W41" s="221"/>
+      <c r="X41" s="221"/>
+      <c r="Y41" s="222"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -6989,7 +6959,7 @@
         <v>9.0919656753540039</v>
       </c>
       <c r="J42" s="44" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M42">
         <f t="shared" si="1"/>
@@ -7036,15 +7006,15 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="180" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q43" s="296"/>
+      <c r="P43" s="223" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q43" s="224"/>
       <c r="R43" s="72" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="S43" s="73" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -7084,7 +7054,7 @@
         <v>50.917000000000002</v>
       </c>
       <c r="P44" s="74" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q44" s="75">
         <f>A46</f>
@@ -7135,12 +7105,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="297" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q45" s="298"/>
-      <c r="R45" s="298"/>
-      <c r="S45" s="299"/>
+      <c r="P45" s="225" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q45" s="226"/>
+      <c r="R45" s="226"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7178,10 +7148,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="297"/>
-      <c r="Q46" s="298"/>
-      <c r="R46" s="298"/>
-      <c r="S46" s="299"/>
+      <c r="P46" s="225"/>
+      <c r="Q46" s="226"/>
+      <c r="R46" s="226"/>
+      <c r="S46" s="227"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7219,9 +7189,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="229"/>
-      <c r="Q47" s="300"/>
-      <c r="R47" s="300"/>
+      <c r="P47" s="228"/>
+      <c r="Q47" s="229"/>
+      <c r="R47" s="229"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7364,7 +7334,7 @@
         <v>9.3486919403076172</v>
       </c>
       <c r="J51" s="44" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M51">
         <f t="shared" si="1"/>
@@ -7436,62 +7406,62 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="301" t="s">
-        <v>225</v>
-      </c>
-      <c r="B57" s="302"/>
-      <c r="C57" s="302"/>
-      <c r="D57" s="302"/>
-      <c r="E57" s="302"/>
-      <c r="F57" s="302"/>
-      <c r="G57" s="302"/>
-      <c r="H57" s="302"/>
-      <c r="I57" s="303"/>
+      <c r="A57" s="231" t="s">
+        <v>222</v>
+      </c>
+      <c r="B57" s="232"/>
+      <c r="C57" s="232"/>
+      <c r="D57" s="232"/>
+      <c r="E57" s="232"/>
+      <c r="F57" s="232"/>
+      <c r="G57" s="232"/>
+      <c r="H57" s="232"/>
+      <c r="I57" s="233"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="82"/>
       <c r="B58" s="83" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C58" s="84"/>
       <c r="D58" s="84" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E58" s="84"/>
       <c r="F58" s="84"/>
       <c r="G58" s="84" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H58" s="84" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I58" s="85"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="86"/>
       <c r="B59" s="87" t="s">
+        <v>227</v>
+      </c>
+      <c r="C59" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" s="87" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="C59" s="87" t="s">
+      <c r="F59" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="D59" s="87" t="s">
+      <c r="G59" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="E59" s="87" t="s">
+      <c r="H59" s="234" t="s">
         <v>233</v>
       </c>
-      <c r="F59" s="87" t="s">
-        <v>234</v>
-      </c>
-      <c r="G59" s="87" t="s">
-        <v>235</v>
-      </c>
-      <c r="H59" s="291" t="s">
-        <v>236</v>
-      </c>
-      <c r="I59" s="292"/>
+      <c r="I59" s="235"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7502,7 +7472,7 @@
         <v>100</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -7510,71 +7480,71 @@
       <c r="F60" t="s">
         <v>84</v>
       </c>
-      <c r="H60" s="304">
+      <c r="H60" s="236">
         <v>18.12</v>
       </c>
-      <c r="I60" s="304"/>
+      <c r="I60" s="236"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
         <v>86</v>
       </c>
-      <c r="H61" s="287">
+      <c r="H61" s="248">
         <v>19.98</v>
       </c>
-      <c r="I61" s="287"/>
+      <c r="I61" s="248"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
         <v>89</v>
       </c>
-      <c r="H62" s="287">
+      <c r="H62" s="248">
         <v>18.7</v>
       </c>
-      <c r="I62" s="287"/>
+      <c r="I62" s="248"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="86"/>
       <c r="F63" t="s">
-        <v>238</v>
-      </c>
-      <c r="H63" s="287">
+        <v>235</v>
+      </c>
+      <c r="H63" s="248">
         <v>17.62</v>
       </c>
-      <c r="I63" s="287"/>
+      <c r="I63" s="248"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
     <row r="64" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="86"/>
       <c r="F64" t="s">
-        <v>239</v>
-      </c>
-      <c r="H64" s="290">
+        <v>236</v>
+      </c>
+      <c r="H64" s="249">
         <v>18.79</v>
       </c>
-      <c r="I64" s="290"/>
+      <c r="I64" s="249"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="277" t="s">
-        <v>240</v>
-      </c>
-      <c r="C65" s="278"/>
+      <c r="B65" s="216" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" s="217"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="294">
+      <c r="H65" s="218">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="295"/>
+      <c r="I65" s="219"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7589,11 +7559,11 @@
       <c r="G66" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H66" s="242" t="str">
+      <c r="H66" s="244" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="244"/>
+      <c r="I66" s="245"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7615,16 +7585,16 @@
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="86"/>
       <c r="B68" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G68" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H68" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I68" s="94"/>
       <c r="J68" s="88"/>
@@ -7637,31 +7607,31 @@
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="86"/>
       <c r="B69" s="87" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" s="87" t="s">
+        <v>229</v>
+      </c>
+      <c r="E69" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="C69" s="87" t="s">
+      <c r="F69" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="87" t="s">
+      <c r="G69" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="E69" s="87" t="s">
+      <c r="H69" s="234" t="s">
         <v>233</v>
       </c>
-      <c r="F69" s="87" t="s">
-        <v>234</v>
-      </c>
-      <c r="G69" s="87" t="s">
-        <v>235</v>
-      </c>
-      <c r="H69" s="291" t="s">
-        <v>236</v>
-      </c>
-      <c r="I69" s="292"/>
-      <c r="P69" s="288"/>
-      <c r="Q69" s="288"/>
-      <c r="R69" s="289"/>
-      <c r="S69" s="289"/>
+      <c r="I69" s="235"/>
+      <c r="P69" s="246"/>
+      <c r="Q69" s="246"/>
+      <c r="R69" s="209"/>
+      <c r="S69" s="209"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7672,7 +7642,7 @@
         <v>100</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -7680,68 +7650,68 @@
       <c r="F70" t="s">
         <v>84</v>
       </c>
-      <c r="H70" s="293">
+      <c r="H70" s="247">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="293"/>
-      <c r="P70" s="288"/>
-      <c r="Q70" s="288"/>
-      <c r="R70" s="289"/>
-      <c r="S70" s="289"/>
+      <c r="I70" s="247"/>
+      <c r="P70" s="246"/>
+      <c r="Q70" s="246"/>
+      <c r="R70" s="209"/>
+      <c r="S70" s="209"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
         <v>86</v>
       </c>
-      <c r="H71" s="287">
+      <c r="H71" s="248">
         <v>11.78</v>
       </c>
-      <c r="I71" s="287"/>
-      <c r="P71" s="288"/>
-      <c r="Q71" s="288"/>
-      <c r="R71" s="289"/>
-      <c r="S71" s="289"/>
+      <c r="I71" s="248"/>
+      <c r="P71" s="246"/>
+      <c r="Q71" s="246"/>
+      <c r="R71" s="209"/>
+      <c r="S71" s="209"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
         <v>89</v>
       </c>
-      <c r="H72" s="287">
+      <c r="H72" s="248">
         <v>12.39</v>
       </c>
-      <c r="I72" s="287"/>
-      <c r="P72" s="288"/>
-      <c r="Q72" s="288"/>
-      <c r="R72" s="289"/>
-      <c r="S72" s="289"/>
+      <c r="I72" s="248"/>
+      <c r="P72" s="246"/>
+      <c r="Q72" s="246"/>
+      <c r="R72" s="209"/>
+      <c r="S72" s="209"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
-        <v>238</v>
-      </c>
-      <c r="H73" s="287">
+        <v>235</v>
+      </c>
+      <c r="H73" s="248">
         <v>11.21</v>
       </c>
-      <c r="I73" s="287"/>
+      <c r="I73" s="248"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="288"/>
-      <c r="Q73" s="288"/>
-      <c r="R73" s="289"/>
-      <c r="S73" s="289"/>
+      <c r="P73" s="246"/>
+      <c r="Q73" s="246"/>
+      <c r="R73" s="209"/>
+      <c r="S73" s="209"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
-        <v>239</v>
-      </c>
-      <c r="H74" s="290">
+        <v>236</v>
+      </c>
+      <c r="H74" s="249">
         <v>12.75</v>
       </c>
-      <c r="I74" s="290"/>
+      <c r="I74" s="249"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7750,28 +7720,28 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="288"/>
-      <c r="Q74" s="288"/>
-      <c r="R74" s="289"/>
-      <c r="S74" s="289"/>
+      <c r="P74" s="246"/>
+      <c r="Q74" s="246"/>
+      <c r="R74" s="209"/>
+      <c r="S74" s="209"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="277" t="s">
-        <v>240</v>
-      </c>
-      <c r="C75" s="278"/>
+      <c r="B75" s="216" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="217"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="279">
+      <c r="H75" s="260">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="280"/>
+      <c r="I75" s="261"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
@@ -7779,24 +7749,24 @@
       <c r="G76" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="H76" s="180" t="str">
+      <c r="H76" s="223" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="182"/>
+      <c r="I76" s="262"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="281" t="s">
-        <v>243</v>
-      </c>
-      <c r="B77" s="282"/>
-      <c r="C77" s="282"/>
-      <c r="D77" s="282"/>
-      <c r="E77" s="282"/>
-      <c r="F77" s="282"/>
-      <c r="G77" s="282"/>
-      <c r="H77" s="282"/>
-      <c r="I77" s="283"/>
+      <c r="A77" s="263" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" s="264"/>
+      <c r="C77" s="264"/>
+      <c r="D77" s="264"/>
+      <c r="E77" s="264"/>
+      <c r="F77" s="264"/>
+      <c r="G77" s="264"/>
+      <c r="H77" s="264"/>
+      <c r="I77" s="265"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7809,16 +7779,16 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="180" t="s">
-        <v>244</v>
-      </c>
-      <c r="B80" s="181"/>
-      <c r="C80" s="181"/>
+      <c r="A80" s="223" t="s">
+        <v>241</v>
+      </c>
+      <c r="B80" s="266"/>
+      <c r="C80" s="266"/>
       <c r="D80" s="47" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E80" s="48" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G80" s="88"/>
       <c r="H80" s="88"/>
@@ -7830,20 +7800,20 @@
       <c r="A81" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="B81" s="284" t="s">
+      <c r="B81" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="285"/>
+      <c r="C81" s="268"/>
       <c r="D81" s="102" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E81" s="103">
         <f t="array" ref="E81">INDEX($J$82:$J$84,MATCH(E80,$I$82:$I$84,0),0)</f>
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="286"/>
-      <c r="I81" s="286"/>
+      <c r="H81" s="269"/>
+      <c r="I81" s="269"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7851,18 +7821,18 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="268">
+      <c r="B82" s="250">
         <v>15</v>
       </c>
-      <c r="C82" s="268"/>
-      <c r="D82" s="269" t="s">
-        <v>248</v>
+      <c r="C82" s="250"/>
+      <c r="D82" s="251" t="s">
+        <v>245</v>
       </c>
       <c r="E82" s="106"/>
       <c r="G82" s="88"/>
       <c r="H82" s="107"/>
       <c r="I82" s="108" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J82" s="109">
         <v>0.42</v>
@@ -7871,15 +7841,15 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="B83" s="272" t="s">
-        <v>251</v>
-      </c>
-      <c r="C83" s="263"/>
-      <c r="D83" s="270"/>
+        <v>247</v>
+      </c>
+      <c r="B83" s="254" t="s">
+        <v>248</v>
+      </c>
+      <c r="C83" s="255"/>
+      <c r="D83" s="252"/>
       <c r="E83" s="46" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F83" s="110" t="s">
         <v>63</v>
@@ -7887,7 +7857,7 @@
       <c r="G83" s="88"/>
       <c r="H83" s="107"/>
       <c r="I83" s="108" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J83" s="109">
         <v>0.5</v>
@@ -7898,11 +7868,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="273">
+      <c r="B84" s="256">
         <v>2.8</v>
       </c>
-      <c r="C84" s="273"/>
-      <c r="D84" s="270"/>
+      <c r="C84" s="256"/>
+      <c r="D84" s="252"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7917,7 +7887,7 @@
       </c>
       <c r="H84" s="88"/>
       <c r="I84" s="112" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J84" s="109">
         <v>0.5</v>
@@ -7928,11 +7898,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="274">
+      <c r="B85" s="257">
         <v>5</v>
       </c>
-      <c r="C85" s="275"/>
-      <c r="D85" s="270"/>
+      <c r="C85" s="258"/>
+      <c r="D85" s="252"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -7954,11 +7924,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="276">
+      <c r="B86" s="259">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="276"/>
-      <c r="D86" s="271"/>
+      <c r="C86" s="259"/>
+      <c r="D86" s="253"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -7977,14 +7947,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="254" t="s">
-        <v>254</v>
-      </c>
-      <c r="B87" s="255"/>
-      <c r="C87" s="255"/>
-      <c r="D87" s="255"/>
-      <c r="E87" s="255"/>
-      <c r="F87" s="256"/>
+      <c r="A87" s="282" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" s="283"/>
+      <c r="C87" s="283"/>
+      <c r="D87" s="283"/>
+      <c r="E87" s="283"/>
+      <c r="F87" s="284"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -7992,12 +7962,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="257"/>
-      <c r="B88" s="258"/>
-      <c r="C88" s="258"/>
-      <c r="D88" s="258"/>
-      <c r="E88" s="258"/>
-      <c r="F88" s="259"/>
+      <c r="A88" s="285"/>
+      <c r="B88" s="286"/>
+      <c r="C88" s="286"/>
+      <c r="D88" s="286"/>
+      <c r="E88" s="286"/>
+      <c r="F88" s="287"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -8012,11 +7982,11 @@
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="181" t="s">
-        <v>255</v>
-      </c>
-      <c r="D90" s="181"/>
-      <c r="E90" s="182"/>
+      <c r="C90" s="266" t="s">
+        <v>252</v>
+      </c>
+      <c r="D90" s="266"/>
+      <c r="E90" s="262"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -8028,37 +7998,37 @@
       <c r="C91" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="D91" s="260">
+      <c r="D91" s="288">
         <v>107</v>
       </c>
-      <c r="E91" s="261"/>
+      <c r="E91" s="289"/>
       <c r="F91" s="120" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="262" t="s">
-        <v>256</v>
-      </c>
-      <c r="B92" s="263"/>
-      <c r="C92" s="264">
+      <c r="A92" s="290" t="s">
+        <v>253</v>
+      </c>
+      <c r="B92" s="255"/>
+      <c r="C92" s="291">
         <v>3</v>
       </c>
-      <c r="D92" s="264"/>
-      <c r="E92" s="264"/>
+      <c r="D92" s="291"/>
+      <c r="E92" s="291"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="265" t="s">
-        <v>257</v>
-      </c>
-      <c r="B93" s="266"/>
-      <c r="C93" s="266"/>
-      <c r="D93" s="266"/>
-      <c r="E93" s="267"/>
+      <c r="A93" s="292" t="s">
+        <v>254</v>
+      </c>
+      <c r="B93" s="293"/>
+      <c r="C93" s="293"/>
+      <c r="D93" s="293"/>
+      <c r="E93" s="294"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8074,11 +8044,11 @@
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="242" t="s">
-        <v>258</v>
-      </c>
-      <c r="D95" s="243"/>
-      <c r="E95" s="244"/>
+      <c r="C95" s="244" t="s">
+        <v>255</v>
+      </c>
+      <c r="D95" s="270"/>
+      <c r="E95" s="245"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8090,44 +8060,44 @@
       <c r="C96" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="D96" s="245">
+      <c r="D96" s="271">
         <v>3691</v>
       </c>
-      <c r="E96" s="246"/>
+      <c r="E96" s="272"/>
       <c r="F96" s="120" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="247" t="s">
-        <v>256</v>
-      </c>
-      <c r="B97" s="248"/>
-      <c r="C97" s="249">
+      <c r="A97" s="273" t="s">
+        <v>253</v>
+      </c>
+      <c r="B97" s="274"/>
+      <c r="C97" s="275">
         <v>6.25</v>
       </c>
-      <c r="D97" s="249"/>
-      <c r="E97" s="249"/>
+      <c r="D97" s="275"/>
+      <c r="E97" s="275"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="250" t="s">
-        <v>259</v>
-      </c>
-      <c r="B98" s="251"/>
-      <c r="C98" s="251"/>
-      <c r="D98" s="251"/>
-      <c r="E98" s="252"/>
+      <c r="A98" s="276" t="s">
+        <v>256</v>
+      </c>
+      <c r="B98" s="277"/>
+      <c r="C98" s="277"/>
+      <c r="D98" s="277"/>
+      <c r="E98" s="278"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="225"/>
-      <c r="B99" s="253"/>
-      <c r="C99" s="253"/>
-      <c r="D99" s="253"/>
-      <c r="E99" s="226"/>
+      <c r="A99" s="279"/>
+      <c r="B99" s="280"/>
+      <c r="C99" s="280"/>
+      <c r="D99" s="280"/>
+      <c r="E99" s="281"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8137,28 +8107,28 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="242" t="s">
-        <v>260</v>
-      </c>
-      <c r="B101" s="243"/>
-      <c r="C101" s="243"/>
-      <c r="D101" s="243"/>
-      <c r="E101" s="243"/>
-      <c r="F101" s="243"/>
-      <c r="G101" s="243"/>
-      <c r="H101" s="243"/>
-      <c r="I101" s="243"/>
-      <c r="J101" s="244"/>
+      <c r="A101" s="244" t="s">
+        <v>257</v>
+      </c>
+      <c r="B101" s="270"/>
+      <c r="C101" s="270"/>
+      <c r="D101" s="270"/>
+      <c r="E101" s="270"/>
+      <c r="F101" s="270"/>
+      <c r="G101" s="270"/>
+      <c r="H101" s="270"/>
+      <c r="I101" s="270"/>
+      <c r="J101" s="245"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B102" s="90" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C102" s="77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D102" s="84"/>
       <c r="E102" s="89" t="s">
@@ -8168,11 +8138,11 @@
         <v>500</v>
       </c>
       <c r="G102" s="129" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="219"/>
-      <c r="J102" s="220"/>
+      <c r="I102" s="300"/>
+      <c r="J102" s="301"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8184,92 +8154,92 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="221"/>
-      <c r="E103" s="222"/>
-      <c r="F103" s="222"/>
-      <c r="G103" s="223" t="s">
+      <c r="D103" s="302"/>
+      <c r="E103" s="178"/>
+      <c r="F103" s="178"/>
+      <c r="G103" s="303" t="s">
+        <v>261</v>
+      </c>
+      <c r="H103" s="304"/>
+      <c r="I103" s="305" t="s">
+        <v>262</v>
+      </c>
+      <c r="J103" s="306"/>
+      <c r="K103" s="307" t="s">
+        <v>63</v>
+      </c>
+      <c r="L103" s="308"/>
+    </row>
+    <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="311" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104" s="134" t="s">
+        <v>263</v>
+      </c>
+      <c r="C104" s="135" t="s">
         <v>264</v>
       </c>
-      <c r="H103" s="224"/>
-      <c r="I103" s="227" t="s">
+      <c r="D104" s="135" t="s">
         <v>265</v>
       </c>
-      <c r="J103" s="228"/>
-      <c r="K103" s="231" t="s">
-        <v>63</v>
-      </c>
-      <c r="L103" s="232"/>
-    </row>
-    <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="235" t="s">
-        <v>124</v>
-      </c>
-      <c r="B104" s="134" t="s">
+      <c r="E104" s="136" t="s">
         <v>266</v>
       </c>
-      <c r="C104" s="135" t="s">
+      <c r="F104" s="135" t="s">
         <v>267</v>
       </c>
-      <c r="D104" s="135" t="s">
-        <v>268</v>
-      </c>
-      <c r="E104" s="136" t="s">
-        <v>269</v>
-      </c>
-      <c r="F104" s="135" t="s">
-        <v>270</v>
-      </c>
-      <c r="G104" s="225"/>
-      <c r="H104" s="226"/>
-      <c r="I104" s="229"/>
+      <c r="G104" s="279"/>
+      <c r="H104" s="281"/>
+      <c r="I104" s="228"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="233"/>
-      <c r="L104" s="234"/>
+      <c r="K104" s="309"/>
+      <c r="L104" s="310"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="194"/>
+      <c r="A105" s="312"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>159</v>
-      </c>
-      <c r="G105" s="236">
+        <v>156</v>
+      </c>
+      <c r="G105" s="313">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="237"/>
-      <c r="I105" s="238">
+      <c r="H105" s="314"/>
+      <c r="I105" s="315">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="239"/>
-      <c r="K105" s="240" t="str">
+      <c r="J105" s="316"/>
+      <c r="K105" s="317" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="241"/>
+      <c r="L105" s="318"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="210" t="s">
-        <v>271</v>
-      </c>
-      <c r="B106" s="211"/>
-      <c r="C106" s="211"/>
-      <c r="D106" s="211"/>
-      <c r="E106" s="211"/>
-      <c r="F106" s="211"/>
-      <c r="G106" s="211"/>
-      <c r="H106" s="211"/>
-      <c r="I106" s="211"/>
-      <c r="J106" s="211"/>
-      <c r="K106" s="211"/>
-      <c r="L106" s="212"/>
+      <c r="A106" s="220" t="s">
+        <v>268</v>
+      </c>
+      <c r="B106" s="221"/>
+      <c r="C106" s="221"/>
+      <c r="D106" s="221"/>
+      <c r="E106" s="221"/>
+      <c r="F106" s="221"/>
+      <c r="G106" s="221"/>
+      <c r="H106" s="221"/>
+      <c r="I106" s="221"/>
+      <c r="J106" s="221"/>
+      <c r="K106" s="221"/>
+      <c r="L106" s="222"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -8281,10 +8251,10 @@
         <v>4</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8314,49 +8284,49 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="213" t="s">
+      <c r="A113" s="295" t="s">
         <v>115</v>
       </c>
-      <c r="B113" s="214"/>
-      <c r="C113" s="214"/>
-      <c r="D113" s="214"/>
-      <c r="E113" s="214" t="s">
+      <c r="B113" s="296"/>
+      <c r="C113" s="296"/>
+      <c r="D113" s="296"/>
+      <c r="E113" s="296" t="s">
+        <v>272</v>
+      </c>
+      <c r="F113" s="296"/>
+      <c r="G113" s="296" t="s">
+        <v>273</v>
+      </c>
+      <c r="H113" s="296" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113" s="298" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="297"/>
+      <c r="B114" s="188"/>
+      <c r="C114" s="188"/>
+      <c r="D114" s="188"/>
+      <c r="E114" s="188"/>
+      <c r="F114" s="188"/>
+      <c r="G114" s="188"/>
+      <c r="H114" s="188"/>
+      <c r="I114" s="299"/>
+    </row>
+    <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="326" t="s">
         <v>275</v>
       </c>
-      <c r="F113" s="214"/>
-      <c r="G113" s="214" t="s">
-        <v>276</v>
-      </c>
-      <c r="H113" s="214" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="217" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="215"/>
-      <c r="B114" s="216"/>
-      <c r="C114" s="216"/>
-      <c r="D114" s="216"/>
-      <c r="E114" s="216"/>
-      <c r="F114" s="216"/>
-      <c r="G114" s="216"/>
-      <c r="H114" s="216"/>
-      <c r="I114" s="218"/>
-    </row>
-    <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="205" t="s">
-        <v>278</v>
-      </c>
-      <c r="B115" s="206"/>
-      <c r="C115" s="206"/>
-      <c r="D115" s="206"/>
+      <c r="B115" s="327"/>
+      <c r="C115" s="327"/>
+      <c r="D115" s="327"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
       <c r="F115" s="145" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G115" s="146">
         <f>ROUND((E115*D111)/(60*B111),3)</f>
@@ -8366,22 +8336,22 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="207" t="s">
-        <v>279</v>
+      <c r="I115" s="328" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="201" t="s">
-        <v>280</v>
-      </c>
-      <c r="B116" s="202"/>
-      <c r="C116" s="202"/>
-      <c r="D116" s="202"/>
+      <c r="A116" s="322" t="s">
+        <v>277</v>
+      </c>
+      <c r="B116" s="323"/>
+      <c r="C116" s="323"/>
+      <c r="D116" s="323"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G116" s="45">
         <f>ROUND((E116*D111)/(60*B111),3)</f>
@@ -8391,20 +8361,20 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="208"/>
+      <c r="I116" s="329"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="201" t="s">
-        <v>281</v>
-      </c>
-      <c r="B117" s="202"/>
-      <c r="C117" s="202"/>
-      <c r="D117" s="202"/>
+      <c r="A117" s="322" t="s">
+        <v>278</v>
+      </c>
+      <c r="B117" s="323"/>
+      <c r="C117" s="323"/>
+      <c r="D117" s="323"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G117" s="45">
         <f>ROUND((E117*D111)/(60*B111),3)</f>
@@ -8414,20 +8384,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="208"/>
+      <c r="I117" s="329"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="201" t="s">
-        <v>282</v>
-      </c>
-      <c r="B118" s="202"/>
-      <c r="C118" s="202"/>
-      <c r="D118" s="202"/>
+      <c r="A118" s="322" t="s">
+        <v>279</v>
+      </c>
+      <c r="B118" s="323"/>
+      <c r="C118" s="323"/>
+      <c r="D118" s="323"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G118" s="45">
         <f>ROUND((E118*D111)/(60*B111),3)</f>
@@ -8437,20 +8407,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="208"/>
+      <c r="I118" s="329"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="203" t="s">
-        <v>283</v>
-      </c>
-      <c r="B119" s="204"/>
-      <c r="C119" s="204"/>
-      <c r="D119" s="204"/>
+      <c r="A119" s="324" t="s">
+        <v>280</v>
+      </c>
+      <c r="B119" s="325"/>
+      <c r="C119" s="325"/>
+      <c r="D119" s="325"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="F119" s="151" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G119" s="152">
         <f>ROUND((E119*D111)/(60*B111),3)</f>
@@ -8460,20 +8430,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="209"/>
+      <c r="I119" s="330"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="196" t="s">
-        <v>284</v>
-      </c>
-      <c r="B120" s="197"/>
-      <c r="C120" s="197"/>
-      <c r="D120" s="197"/>
+      <c r="A120" s="345" t="s">
+        <v>281</v>
+      </c>
+      <c r="B120" s="346"/>
+      <c r="C120" s="346"/>
+      <c r="D120" s="346"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
       <c r="F120" s="155" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G120" s="156">
         <f>ROUND((E120*D111)/(60*B111),3)</f>
@@ -8483,22 +8453,22 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="198" t="s">
-        <v>285</v>
+      <c r="I120" s="319" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="201" t="s">
-        <v>286</v>
-      </c>
-      <c r="B121" s="202"/>
-      <c r="C121" s="202"/>
-      <c r="D121" s="202"/>
+      <c r="A121" s="322" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" s="323"/>
+      <c r="C121" s="323"/>
+      <c r="D121" s="323"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G121" s="45">
         <f>ROUND((E121*D111)/(60*B111),3)</f>
@@ -8508,20 +8478,20 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="199"/>
+      <c r="I121" s="320"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="201" t="s">
-        <v>287</v>
-      </c>
-      <c r="B122" s="202"/>
-      <c r="C122" s="202"/>
-      <c r="D122" s="202"/>
+      <c r="A122" s="322" t="s">
+        <v>284</v>
+      </c>
+      <c r="B122" s="323"/>
+      <c r="C122" s="323"/>
+      <c r="D122" s="323"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G122" s="45">
         <f>ROUND((E122*D111)/(60*B111),3)</f>
@@ -8531,20 +8501,20 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="199"/>
+      <c r="I122" s="320"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="201" t="s">
-        <v>288</v>
-      </c>
-      <c r="B123" s="202"/>
-      <c r="C123" s="202"/>
-      <c r="D123" s="202"/>
+      <c r="A123" s="322" t="s">
+        <v>285</v>
+      </c>
+      <c r="B123" s="323"/>
+      <c r="C123" s="323"/>
+      <c r="D123" s="323"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G123" s="45">
         <f>ROUND((E123*D111)/(60*B111),3)</f>
@@ -8554,26 +8524,26 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="199"/>
+      <c r="I123" s="320"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="203" t="s">
-        <v>289</v>
-      </c>
-      <c r="B124" s="204"/>
-      <c r="C124" s="204"/>
-      <c r="D124" s="204"/>
+      <c r="A124" s="324" t="s">
+        <v>286</v>
+      </c>
+      <c r="B124" s="325"/>
+      <c r="C124" s="325"/>
+      <c r="D124" s="325"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G124" s="152" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H124" s="153" t="s">
-        <v>290</v>
-      </c>
-      <c r="I124" s="200"/>
+        <v>287</v>
+      </c>
+      <c r="I124" s="321"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8581,10 +8551,10 @@
     </row>
     <row r="126" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="158" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C126" s="159" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D126" s="160"/>
       <c r="E126" s="160"/>
@@ -8594,15 +8564,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="180" t="s">
-        <v>293</v>
-      </c>
-      <c r="B127" s="181"/>
-      <c r="C127" s="181"/>
-      <c r="D127" s="181"/>
-      <c r="E127" s="181"/>
-      <c r="F127" s="181"/>
-      <c r="G127" s="182"/>
+      <c r="A127" s="223" t="s">
+        <v>290</v>
+      </c>
+      <c r="B127" s="266"/>
+      <c r="C127" s="266"/>
+      <c r="D127" s="266"/>
+      <c r="E127" s="266"/>
+      <c r="F127" s="266"/>
+      <c r="G127" s="262"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8614,19 +8584,19 @@
     </row>
     <row r="128" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="99" t="s">
-        <v>294</v>
-      </c>
-      <c r="B128" s="183" t="s">
-        <v>295</v>
-      </c>
-      <c r="C128" s="184"/>
-      <c r="D128" s="184"/>
-      <c r="E128" s="185"/>
+        <v>291</v>
+      </c>
+      <c r="B128" s="194" t="s">
+        <v>292</v>
+      </c>
+      <c r="C128" s="195"/>
+      <c r="D128" s="195"/>
+      <c r="E128" s="196"/>
       <c r="F128" s="162" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G128" s="163" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H128" s="88"/>
       <c r="I128" s="88"/>
@@ -8642,11 +8612,11 @@
         <v>15</v>
       </c>
       <c r="B129" s="47" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C129" s="105"/>
       <c r="D129" s="164" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E129" s="105"/>
       <c r="F129" s="47" t="e">
@@ -8677,11 +8647,11 @@
         <v>15</v>
       </c>
       <c r="B130" s="102" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C130" s="114"/>
       <c r="D130" s="165" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E130" s="114"/>
       <c r="F130" s="102" t="e">
@@ -8708,15 +8678,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="186" t="s">
-        <v>301</v>
-      </c>
-      <c r="B131" s="176"/>
-      <c r="C131" s="176"/>
-      <c r="D131" s="176"/>
-      <c r="E131" s="176"/>
-      <c r="F131" s="176"/>
-      <c r="G131" s="177"/>
+      <c r="A131" s="336" t="s">
+        <v>298</v>
+      </c>
+      <c r="B131" s="332"/>
+      <c r="C131" s="332"/>
+      <c r="D131" s="332"/>
+      <c r="E131" s="332"/>
+      <c r="F131" s="332"/>
+      <c r="G131" s="333"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8727,15 +8697,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="187" t="s">
-        <v>302</v>
-      </c>
-      <c r="B132" s="188"/>
-      <c r="C132" s="188"/>
-      <c r="D132" s="188"/>
-      <c r="E132" s="188"/>
-      <c r="F132" s="188"/>
-      <c r="G132" s="189"/>
+      <c r="A132" s="337" t="s">
+        <v>299</v>
+      </c>
+      <c r="B132" s="338"/>
+      <c r="C132" s="338"/>
+      <c r="D132" s="338"/>
+      <c r="E132" s="338"/>
+      <c r="F132" s="338"/>
+      <c r="G132" s="339"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8746,13 +8716,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="190"/>
-      <c r="B133" s="191"/>
-      <c r="C133" s="191"/>
-      <c r="D133" s="191"/>
-      <c r="E133" s="191"/>
-      <c r="F133" s="191"/>
-      <c r="G133" s="192"/>
+      <c r="A133" s="340"/>
+      <c r="B133" s="341"/>
+      <c r="C133" s="341"/>
+      <c r="D133" s="341"/>
+      <c r="E133" s="341"/>
+      <c r="F133" s="341"/>
+      <c r="G133" s="342"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8774,7 +8744,7 @@
     </row>
     <row r="135" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="166" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B135" s="129"/>
       <c r="C135" s="129"/>
@@ -8782,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="168" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F135" s="169" t="str">
         <f>IF(D135&lt;=5,"Pass","Fail")</f>
@@ -8818,7 +8788,7 @@
     </row>
     <row r="138" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="44" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H138" s="98"/>
       <c r="I138" s="98"/>
@@ -8859,7 +8829,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="193" t="s">
+      <c r="A140" s="343" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8890,7 +8860,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="194"/>
+      <c r="A141" s="312"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8926,8 +8896,8 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="195" t="s">
-        <v>306</v>
+      <c r="B142" s="344" t="s">
+        <v>303</v>
       </c>
       <c r="C142" s="173">
         <f>C139-C141</f>
@@ -8960,7 +8930,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="195"/>
+      <c r="B143" s="344"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -8991,26 +8961,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="175" t="s">
-        <v>307</v>
-      </c>
-      <c r="B144" s="176"/>
-      <c r="C144" s="176"/>
-      <c r="D144" s="176"/>
-      <c r="E144" s="176"/>
-      <c r="F144" s="176"/>
-      <c r="G144" s="177"/>
+      <c r="A144" s="331" t="s">
+        <v>304</v>
+      </c>
+      <c r="B144" s="332"/>
+      <c r="C144" s="332"/>
+      <c r="D144" s="332"/>
+      <c r="E144" s="332"/>
+      <c r="F144" s="332"/>
+      <c r="G144" s="333"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="175" t="s">
-        <v>308</v>
-      </c>
-      <c r="B145" s="178"/>
-      <c r="C145" s="178"/>
-      <c r="D145" s="178"/>
-      <c r="E145" s="178"/>
-      <c r="F145" s="178"/>
-      <c r="G145" s="179"/>
+      <c r="A145" s="331" t="s">
+        <v>305</v>
+      </c>
+      <c r="B145" s="334"/>
+      <c r="C145" s="334"/>
+      <c r="D145" s="334"/>
+      <c r="E145" s="334"/>
+      <c r="F145" s="334"/>
+      <c r="G145" s="335"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9026,107 +8996,26 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9142,26 +9031,107 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <conditionalFormatting sqref="C142:G142">
     <cfRule type="cellIs" dxfId="40" priority="6" operator="greaterThan">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF25B65D-8DB7-42C1-9160-09DFAF1D835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4857E4A6-A2C7-46E8-BEA1-BEA25A8B5009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CT Scan Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="raw data" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="300">
   <si>
     <t>TEST: RADIATION PROFILE WIDTH FOR CT SCAN</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Set kV</t>
   </si>
   <si>
-    <t>@ mA 10</t>
-  </si>
-  <si>
     <t>@ mA 100</t>
   </si>
   <si>
@@ -200,12 +197,6 @@
     <t>Tolerance (%)</t>
   </si>
   <si>
-    <t>98.5</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
     <t>TEST: LINEARITY OF MAS LOADING</t>
   </si>
   <si>
@@ -320,9 +311,6 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>7.5</t>
-  </si>
-  <si>
     <t>TEST: Reproducibility of Radiation Output (Consistency Test)</t>
   </si>
   <si>
@@ -336,15 +324,6 @@
   </si>
   <si>
     <t>COV</t>
-  </si>
-  <si>
-    <t>100.5</t>
-  </si>
-  <si>
-    <t>100.6</t>
-  </si>
-  <si>
-    <t>100.4</t>
   </si>
   <si>
     <t>0.05</t>
@@ -1074,6 +1053,9 @@
   <si>
     <t>Note : Where I is + value &amp; S is - value &amp; vise versa if applicable</t>
   </si>
+  <si>
+    <t xml:space="preserve"> mA 10</t>
+  </si>
 </sst>
 </file>
 
@@ -1084,7 +1066,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1182,6 +1164,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2540,521 +2528,521 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3176,14 +3164,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3198,6 +3186,13 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3233,13 +3228,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3302,6 +3290,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -3317,13 +3312,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3748,7 +3736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="20.796875" customWidth="1"/>
@@ -3825,73 +3813,73 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="174">
+        <f>'raw data'!Q14</f>
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="174">
-        <f>Sheet2!Q14</f>
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>28</v>
-      </c>
-      <c r="I9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="174">
-        <f>Sheet2!Q15</f>
+        <f>'raw data'!Q15</f>
         <v>101.01</v>
       </c>
       <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
         <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3914,14 +3902,14 @@
         <v>6</v>
       </c>
       <c r="B11" s="174">
-        <f>Sheet2!Q16</f>
+        <f>'raw data'!Q16</f>
         <v>120.92</v>
       </c>
       <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
         <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3941,7 +3929,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -3949,119 +3937,119 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
         <v>35</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>36</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>40</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>41</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>42</v>
-      </c>
-      <c r="G15" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>45</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>46</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>50</v>
-      </c>
-      <c r="G17" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
         <v>52</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -4069,228 +4057,211 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
       </c>
       <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="D22" s="174" t="e">
+        <f>'raw data'!P22:Q22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E22" t="e">
+        <f>'raw data'!R22:S22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F22" t="e">
+        <f>'raw data'!P25:U25</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="D23" s="174" t="e">
+        <f>'raw data'!P23:Q23</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E23" t="e">
+        <f>'raw data'!R23:S23</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D24" s="174" t="e">
+        <f>'raw data'!P24:Q24</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E24" t="e">
+        <f>'raw data'!R24:S24</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
+      <c r="D25" s="174"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
         <v>10</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s">
-        <v>75</v>
-      </c>
-      <c r="J31" t="s">
-        <v>76</v>
-      </c>
-      <c r="K31" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>6</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
         <v>26</v>
       </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" t="s">
-        <v>80</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="G33" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s">
         <v>10</v>
-      </c>
-      <c r="J32" t="s">
-        <v>81</v>
-      </c>
-      <c r="K32" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H33" t="s">
-        <v>83</v>
-      </c>
-      <c r="I33" t="s">
-        <v>84</v>
       </c>
       <c r="J33" t="s">
         <v>78</v>
       </c>
       <c r="K33" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -4313,19 +4284,19 @@
         <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J34" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -4348,578 +4319,700 @@
         <v>10</v>
       </c>
       <c r="H35" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" t="s">
         <v>83</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
+        <v>84</v>
+      </c>
+      <c r="K35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>80</v>
+      </c>
+      <c r="I36" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" t="s">
+        <v>87</v>
+      </c>
+      <c r="K36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>89</v>
       </c>
-      <c r="J35" t="s">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>90</v>
       </c>
-      <c r="K35" t="s">
+      <c r="B39" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="C39" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="D39" t="s">
         <v>93</v>
       </c>
-      <c r="B38" t="s">
+      <c r="E39" t="s">
         <v>94</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f>'raw data'!Q44</f>
+        <v>140</v>
+      </c>
+      <c r="B40">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
         <v>95</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="174">
+        <f>'raw data'!R44</f>
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>96</v>
       </c>
-      <c r="E38" t="s">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="D43" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" t="s">
+        <v>98</v>
+      </c>
+      <c r="I43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J43" t="s">
+        <v>100</v>
+      </c>
+      <c r="K43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44">
+        <f>'raw data'!P37</f>
+        <v>80</v>
+      </c>
+      <c r="E44">
+        <f>'raw data'!Q37</f>
+        <v>5.2957999999999998</v>
+      </c>
+      <c r="F44">
+        <f>'raw data'!R37</f>
+        <v>5.2999000000000001</v>
+      </c>
+      <c r="G44">
+        <f>'raw data'!S37</f>
+        <v>5.3005000000000004</v>
+      </c>
+      <c r="H44">
+        <f>'raw data'!T37</f>
+        <v>5.3002000000000002</v>
+      </c>
+      <c r="I44">
+        <f>'raw data'!U37</f>
+        <v>5.2969999999999997</v>
+      </c>
+      <c r="J44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K44" t="e">
+        <f>'raw data'!P41:Y41</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <f>'raw data'!P38</f>
+        <v>100</v>
+      </c>
+      <c r="E45">
+        <f>'raw data'!Q38</f>
+        <v>9.4794</v>
+      </c>
+      <c r="F45">
+        <f>'raw data'!R38</f>
+        <v>9.4793000000000003</v>
+      </c>
+      <c r="G45">
+        <f>'raw data'!S38</f>
+        <v>9.4732000000000003</v>
+      </c>
+      <c r="H45">
+        <f>'raw data'!T38</f>
+        <v>9.4781999999999993</v>
+      </c>
+      <c r="I45">
+        <f>'raw data'!U38</f>
+        <v>9.4741999999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <f>'raw data'!P39</f>
+        <v>120</v>
+      </c>
+      <c r="E46">
+        <f>'raw data'!Q39</f>
+        <v>14.521599999999999</v>
+      </c>
+      <c r="F46">
+        <f>'raw data'!R39</f>
+        <v>14.5259</v>
+      </c>
+      <c r="G46">
+        <f>'raw data'!S39</f>
+        <v>14.532299999999999</v>
+      </c>
+      <c r="H46">
+        <f>'raw data'!T39</f>
+        <v>14.526</v>
+      </c>
+      <c r="I46">
+        <f>'raw data'!U38</f>
+        <v>9.4741999999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <f>'raw data'!P40</f>
+        <v>140</v>
+      </c>
+      <c r="E47">
+        <f>'raw data'!Q40</f>
+        <v>20.186800000000002</v>
+      </c>
+      <c r="F47">
+        <f>'raw data'!R40</f>
+        <v>20.193899999999999</v>
+      </c>
+      <c r="G47">
+        <f>'raw data'!S40</f>
+        <v>20.188400000000001</v>
+      </c>
+      <c r="H47">
+        <f>'raw data'!T40</f>
+        <v>20.187999999999999</v>
+      </c>
+      <c r="I47">
+        <f>'raw data'!U40</f>
+        <v>20.197600000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" t="s">
+        <v>107</v>
+      </c>
+      <c r="I51" t="s">
+        <v>108</v>
+      </c>
+      <c r="J51" t="s">
+        <v>109</v>
+      </c>
+      <c r="K51" t="s">
+        <v>110</v>
+      </c>
+      <c r="L51" t="s">
+        <v>111</v>
+      </c>
+      <c r="M51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>6</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H52" t="s">
+        <v>116</v>
+      </c>
+      <c r="I52" t="s">
+        <v>117</v>
+      </c>
+      <c r="J52" t="s">
+        <v>101</v>
+      </c>
+      <c r="K52" t="s">
+        <v>118</v>
+      </c>
+      <c r="L52" t="s">
+        <v>119</v>
+      </c>
+      <c r="M52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J53" t="s">
+        <v>122</v>
+      </c>
+      <c r="K53" t="s">
+        <v>122</v>
+      </c>
+      <c r="L53" t="s">
+        <v>118</v>
+      </c>
+      <c r="M53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
         <v>26</v>
       </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F57" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" t="s">
         <v>3</v>
       </c>
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" t="s">
-        <v>37</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="D60" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" t="s">
         <v>38</v>
       </c>
-      <c r="H42" t="s">
-        <v>102</v>
-      </c>
-      <c r="I42" t="s">
-        <v>103</v>
-      </c>
-      <c r="J42" t="s">
-        <v>104</v>
-      </c>
-      <c r="K42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
         <v>26</v>
       </c>
-      <c r="B43" t="s">
-        <v>27</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>105</v>
-      </c>
-      <c r="F43" t="s">
-        <v>31</v>
-      </c>
-      <c r="G43" t="s">
-        <v>106</v>
-      </c>
-      <c r="H43" t="s">
-        <v>107</v>
-      </c>
-      <c r="I43" t="s">
-        <v>105</v>
-      </c>
-      <c r="J43" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" t="s">
-        <v>113</v>
-      </c>
-      <c r="H46" t="s">
-        <v>114</v>
-      </c>
-      <c r="I46" t="s">
-        <v>115</v>
-      </c>
-      <c r="J46" t="s">
-        <v>116</v>
-      </c>
-      <c r="K46" t="s">
-        <v>117</v>
-      </c>
-      <c r="L46" t="s">
-        <v>118</v>
-      </c>
-      <c r="M46" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F47" t="s">
-        <v>98</v>
-      </c>
-      <c r="G47" t="s">
-        <v>122</v>
-      </c>
-      <c r="H47" t="s">
-        <v>123</v>
-      </c>
-      <c r="I47" t="s">
-        <v>124</v>
-      </c>
-      <c r="J47" t="s">
-        <v>108</v>
-      </c>
-      <c r="K47" t="s">
-        <v>125</v>
-      </c>
-      <c r="L47" t="s">
-        <v>126</v>
-      </c>
-      <c r="M47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" t="s">
-        <v>10</v>
-      </c>
-      <c r="H48" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="F61" t="s">
         <v>128</v>
-      </c>
-      <c r="J48" t="s">
-        <v>129</v>
-      </c>
-      <c r="K48" t="s">
-        <v>129</v>
-      </c>
-      <c r="L48" t="s">
-        <v>125</v>
-      </c>
-      <c r="M48" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" t="s">
-        <v>96</v>
-      </c>
-      <c r="F51" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C55" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" t="s">
-        <v>39</v>
-      </c>
-      <c r="C56" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>140</v>
-      </c>
-      <c r="B63" t="s">
-        <v>141</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" t="s">
-        <v>143</v>
-      </c>
-      <c r="F63" t="s">
-        <v>3</v>
-      </c>
-      <c r="G63" t="s">
-        <v>4</v>
-      </c>
-      <c r="H63" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" t="s">
-        <v>41</v>
-      </c>
-      <c r="D64" t="s">
-        <v>144</v>
-      </c>
-      <c r="E64" t="s">
-        <v>26</v>
-      </c>
-      <c r="F64" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" t="s">
-        <v>7</v>
-      </c>
-      <c r="H64" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" t="s">
-        <v>145</v>
-      </c>
-      <c r="D65" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" t="s">
-        <v>10</v>
-      </c>
-      <c r="H65" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" t="s">
+        <v>136</v>
+      </c>
+      <c r="F68" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>40</v>
+      </c>
+      <c r="D69" t="s">
+        <v>137</v>
+      </c>
+      <c r="E69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="C70" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" t="s">
-        <v>153</v>
-      </c>
-      <c r="C71" t="s">
-        <v>154</v>
+      <c r="D70" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>155</v>
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C74" t="s">
-        <v>157</v>
-      </c>
-      <c r="D74" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" t="s">
-        <v>159</v>
-      </c>
-      <c r="F74" t="s">
-        <v>4</v>
-      </c>
-      <c r="G74" t="s">
-        <v>65</v>
-      </c>
-      <c r="H74" t="s">
-        <v>95</v>
-      </c>
-      <c r="I74" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C75" t="s">
-        <v>161</v>
-      </c>
-      <c r="D75" t="s">
-        <v>162</v>
-      </c>
-      <c r="E75" t="s">
-        <v>163</v>
-      </c>
-      <c r="F75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" t="s">
-        <v>138</v>
-      </c>
-      <c r="I75" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="C76" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" t="s">
+        <v>150</v>
+      </c>
+      <c r="D79" t="s">
+        <v>151</v>
+      </c>
+      <c r="E79" t="s">
+        <v>152</v>
+      </c>
+      <c r="F79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G79" t="s">
+        <v>62</v>
+      </c>
+      <c r="H79" t="s">
+        <v>92</v>
+      </c>
+      <c r="I79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" t="s">
+        <v>154</v>
+      </c>
+      <c r="D80" t="s">
+        <v>155</v>
+      </c>
+      <c r="E80" t="s">
+        <v>156</v>
+      </c>
+      <c r="F80" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" t="s">
+        <v>131</v>
+      </c>
+      <c r="I80" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" t="s">
+        <v>154</v>
+      </c>
+      <c r="D81" t="s">
         <v>10</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E81" t="s">
         <v>10</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F81" t="s">
         <v>10</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G81" t="s">
         <v>10</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H81" t="s">
         <v>10</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I81" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M2 A5:M8 A4:H4 J4:M4 B3:M3 A12:M57 A9 C9:M9 A10 C10:M10 A11 C11:M11 A61:M76" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M2 A5:M7 A4:H4 J4:M4 B3:M3 A12:M21 A9 C9:M9 A10 C10:M10 A11 C11:M11 A66:M81 A8 C8:M8 A50:M62 A44:C44 J44 A45:C45 J45:M45 L44:M44 A41:M43 C40:D40 F40:M40 A26:M39 A22:C22 G22:M22 A23:C23 F23:M23 A24:C24 F24:M24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4949,40 +5042,40 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="175" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
+        <v>159</v>
+      </c>
+      <c r="B1" s="342" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
+      <c r="H1" s="342"/>
+      <c r="I1" s="342"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="175" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
+        <v>161</v>
+      </c>
+      <c r="B2" s="342" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -4992,16 +5085,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="175" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
+      <c r="B3" s="342" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
+      <c r="H3" s="342"/>
+      <c r="I3" s="342"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5011,16 +5104,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
+        <v>164</v>
+      </c>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5030,22 +5123,22 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="175" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
+        <v>165</v>
+      </c>
+      <c r="B5" s="342" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
       <c r="F5" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G5" s="176">
+        <v>167</v>
+      </c>
+      <c r="G5" s="345">
         <v>22.7</v>
       </c>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5055,22 +5148,22 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="175" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="175"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
+        <v>168</v>
+      </c>
+      <c r="B6" s="342" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="342"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="176">
+        <v>170</v>
+      </c>
+      <c r="G6" s="345">
         <v>50.2</v>
       </c>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5080,22 +5173,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="175" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
+        <v>171</v>
+      </c>
+      <c r="B7" s="342" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
       <c r="F7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="175" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+        <v>71</v>
+      </c>
+      <c r="G7" s="342" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5104,18 +5197,18 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="191">
+        <v>174</v>
+      </c>
+      <c r="B8" s="341">
         <v>46066</v>
       </c>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
+      <c r="C8" s="342"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="G8" s="342"/>
+      <c r="H8" s="342"/>
+      <c r="I8" s="342"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5124,14 +5217,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5140,18 +5233,18 @@
     </row>
     <row r="10" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="192" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="192"/>
-      <c r="H10" s="192"/>
-      <c r="I10" s="193"/>
+        <v>175</v>
+      </c>
+      <c r="B10" s="343" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="343"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="344"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5159,91 +5252,91 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="194" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="195"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="195" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="196"/>
+      <c r="A11" s="183" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="184"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="184" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="179" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q11" s="180"/>
-      <c r="R11" s="180"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="180"/>
-      <c r="U11" s="180"/>
-      <c r="V11" s="180"/>
-      <c r="W11" s="180"/>
-      <c r="X11" s="181"/>
+      <c r="P11" s="331" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
+      <c r="V11" s="332"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="P12" s="182" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q12" s="184" t="s">
-        <v>195</v>
-      </c>
-      <c r="R12" s="184"/>
-      <c r="S12" s="184"/>
-      <c r="T12" s="185" t="s">
-        <v>196</v>
-      </c>
-      <c r="U12" s="187" t="s">
-        <v>197</v>
-      </c>
-      <c r="V12" s="185"/>
+        <v>186</v>
+      </c>
+      <c r="P12" s="334" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q12" s="336" t="s">
+        <v>188</v>
+      </c>
+      <c r="R12" s="336"/>
+      <c r="S12" s="336"/>
+      <c r="T12" s="337" t="s">
+        <v>189</v>
+      </c>
+      <c r="U12" s="305" t="s">
+        <v>190</v>
+      </c>
+      <c r="V12" s="337"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="189" t="s">
-        <v>198</v>
+      <c r="X12" s="339" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -5282,7 +5375,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="183"/>
+      <c r="P13" s="335"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5295,11 +5388,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="186"/>
-      <c r="U13" s="188"/>
-      <c r="V13" s="186"/>
+      <c r="T13" s="338"/>
+      <c r="U13" s="216"/>
+      <c r="V13" s="338"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="190"/>
+      <c r="X13" s="340"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5367,7 +5460,7 @@
         <v>0.70999999999999375</v>
       </c>
       <c r="Y14" s="28" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29"/>
@@ -5468,7 +5561,7 @@
         <v>9.1636581420898438</v>
       </c>
       <c r="L16" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
@@ -5558,7 +5651,7 @@
         <v>141.59</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="T17" s="36">
         <f>ROUND(AVERAGE(Q17:S17),2)</f>
@@ -5611,15 +5704,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="206" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q18" s="207"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
-      <c r="T18" s="207"/>
-      <c r="U18" s="207"/>
-      <c r="V18" s="208"/>
+      <c r="P18" s="325" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q18" s="326"/>
+      <c r="R18" s="326"/>
+      <c r="S18" s="326"/>
+      <c r="T18" s="326"/>
+      <c r="U18" s="326"/>
+      <c r="V18" s="327"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5659,13 +5752,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="209"/>
-      <c r="Q19" s="209"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
+      <c r="P19" s="289"/>
+      <c r="Q19" s="289"/>
+      <c r="R19" s="289"/>
+      <c r="S19" s="289"/>
+      <c r="T19" s="289"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5703,14 +5796,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="210" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q20" s="211"/>
-      <c r="R20" s="211"/>
-      <c r="S20" s="211"/>
-      <c r="T20" s="211"/>
-      <c r="U20" s="212"/>
+      <c r="P20" s="310" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q20" s="311"/>
+      <c r="R20" s="311"/>
+      <c r="S20" s="311"/>
+      <c r="T20" s="311"/>
+      <c r="U20" s="313"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5748,19 +5841,19 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="213" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q21" s="214"/>
-      <c r="R21" s="215" t="s">
-        <v>205</v>
-      </c>
-      <c r="S21" s="214"/>
+      <c r="P21" s="328" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q21" s="329"/>
+      <c r="R21" s="330" t="s">
+        <v>198</v>
+      </c>
+      <c r="S21" s="329"/>
       <c r="T21" s="14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="U21" s="43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -5792,7 +5885,7 @@
         <v>9.1354408264160156</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
@@ -5802,16 +5895,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="197">
+      <c r="P22" s="316">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="198"/>
-      <c r="R22" s="199">
+      <c r="Q22" s="317"/>
+      <c r="R22" s="318">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="199"/>
+      <c r="S22" s="318"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5857,16 +5950,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="197">
+      <c r="P23" s="316">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="198"/>
-      <c r="R23" s="199">
+      <c r="Q23" s="317"/>
+      <c r="R23" s="318">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="199"/>
+      <c r="S23" s="318"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -5912,16 +6005,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="197">
+      <c r="P24" s="316">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="198"/>
-      <c r="R24" s="199">
+      <c r="Q24" s="317"/>
+      <c r="R24" s="318">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="199"/>
+      <c r="S24" s="318"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -5967,14 +6060,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="200" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q25" s="201"/>
-      <c r="R25" s="201"/>
-      <c r="S25" s="201"/>
-      <c r="T25" s="201"/>
-      <c r="U25" s="202"/>
+      <c r="P25" s="319" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q25" s="320"/>
+      <c r="R25" s="320"/>
+      <c r="S25" s="320"/>
+      <c r="T25" s="320"/>
+      <c r="U25" s="321"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6049,20 +6142,20 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="203" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q27" s="204"/>
-      <c r="R27" s="205"/>
+      <c r="P27" s="322" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q27" s="323"/>
+      <c r="R27" s="324"/>
       <c r="S27" s="47" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="T27" s="47">
         <f>A34</f>
         <v>120</v>
       </c>
       <c r="U27" s="47" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="V27" s="47"/>
       <c r="W27" s="47"/>
@@ -6108,23 +6201,23 @@
         <v>9.4741999999999997</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q28" s="187" t="s">
-        <v>212</v>
-      </c>
-      <c r="R28" s="187"/>
-      <c r="S28" s="187"/>
+        <v>204</v>
+      </c>
+      <c r="Q28" s="305" t="s">
+        <v>205</v>
+      </c>
+      <c r="R28" s="305"/>
+      <c r="S28" s="305"/>
       <c r="T28" s="14" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="U28" s="14" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
       <c r="X28" s="43" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -6156,7 +6249,7 @@
         <v>9.0879783630371094</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M29">
         <f t="shared" si="1"/>
@@ -6186,13 +6279,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="237">
+      <c r="U29" s="306">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="239" t="str">
+      <c r="X29" s="308" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6253,10 +6346,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="237"/>
+      <c r="U30" s="306"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="239"/>
+      <c r="X30" s="308"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6314,10 +6407,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="237"/>
+      <c r="U31" s="306"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="239"/>
+      <c r="X31" s="308"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6375,10 +6468,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="238"/>
+      <c r="U32" s="307"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="240"/>
+      <c r="X32" s="309"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6416,17 +6509,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="220" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q33" s="221"/>
-      <c r="R33" s="221"/>
-      <c r="S33" s="221"/>
-      <c r="T33" s="221"/>
-      <c r="U33" s="221"/>
-      <c r="V33" s="221"/>
-      <c r="W33" s="221"/>
-      <c r="X33" s="222"/>
+      <c r="P33" s="210" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q33" s="211"/>
+      <c r="R33" s="211"/>
+      <c r="S33" s="211"/>
+      <c r="T33" s="211"/>
+      <c r="U33" s="211"/>
+      <c r="V33" s="211"/>
+      <c r="W33" s="211"/>
+      <c r="X33" s="212"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6501,18 +6594,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="210" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
-      <c r="U35" s="211"/>
-      <c r="V35" s="241"/>
-      <c r="W35" s="241"/>
-      <c r="X35" s="241"/>
-      <c r="Y35" s="212"/>
+      <c r="P35" s="310" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q35" s="311"/>
+      <c r="R35" s="311"/>
+      <c r="S35" s="311"/>
+      <c r="T35" s="311"/>
+      <c r="U35" s="311"/>
+      <c r="V35" s="312"/>
+      <c r="W35" s="312"/>
+      <c r="X35" s="312"/>
+      <c r="Y35" s="313"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6551,26 +6644,26 @@
         <v>14.532299999999999</v>
       </c>
       <c r="P36" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q36" s="242" t="s">
-        <v>212</v>
-      </c>
-      <c r="R36" s="242"/>
-      <c r="S36" s="242"/>
-      <c r="T36" s="242"/>
-      <c r="U36" s="243"/>
+        <v>90</v>
+      </c>
+      <c r="Q36" s="314" t="s">
+        <v>205</v>
+      </c>
+      <c r="R36" s="314"/>
+      <c r="S36" s="314"/>
+      <c r="T36" s="314"/>
+      <c r="U36" s="315"/>
       <c r="V36" s="18" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="W36" s="18" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="X36" s="17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Y36" s="57" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6917,18 +7010,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="220" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q41" s="221"/>
-      <c r="R41" s="221"/>
-      <c r="S41" s="221"/>
-      <c r="T41" s="221"/>
-      <c r="U41" s="221"/>
-      <c r="V41" s="221"/>
-      <c r="W41" s="221"/>
-      <c r="X41" s="221"/>
-      <c r="Y41" s="222"/>
+      <c r="P41" s="210" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q41" s="211"/>
+      <c r="R41" s="211"/>
+      <c r="S41" s="211"/>
+      <c r="T41" s="211"/>
+      <c r="U41" s="211"/>
+      <c r="V41" s="211"/>
+      <c r="W41" s="211"/>
+      <c r="X41" s="211"/>
+      <c r="Y41" s="212"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -6959,7 +7052,7 @@
         <v>9.0919656753540039</v>
       </c>
       <c r="J42" s="44" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M42">
         <f t="shared" si="1"/>
@@ -7006,15 +7099,15 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="223" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q43" s="224"/>
+      <c r="P43" s="180" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q43" s="296"/>
       <c r="R43" s="72" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="S43" s="73" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -7054,7 +7147,7 @@
         <v>50.917000000000002</v>
       </c>
       <c r="P44" s="74" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="Q44" s="75">
         <f>A46</f>
@@ -7105,12 +7198,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="225" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q45" s="226"/>
-      <c r="R45" s="226"/>
-      <c r="S45" s="227"/>
+      <c r="P45" s="297" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q45" s="298"/>
+      <c r="R45" s="298"/>
+      <c r="S45" s="299"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7148,10 +7241,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="225"/>
-      <c r="Q46" s="226"/>
-      <c r="R46" s="226"/>
-      <c r="S46" s="227"/>
+      <c r="P46" s="297"/>
+      <c r="Q46" s="298"/>
+      <c r="R46" s="298"/>
+      <c r="S46" s="299"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7189,9 +7282,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="228"/>
-      <c r="Q47" s="229"/>
-      <c r="R47" s="229"/>
+      <c r="P47" s="229"/>
+      <c r="Q47" s="300"/>
+      <c r="R47" s="300"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7334,7 +7427,7 @@
         <v>9.3486919403076172</v>
       </c>
       <c r="J51" s="44" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M51">
         <f t="shared" si="1"/>
@@ -7406,62 +7499,62 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="231" t="s">
-        <v>222</v>
-      </c>
-      <c r="B57" s="232"/>
-      <c r="C57" s="232"/>
-      <c r="D57" s="232"/>
-      <c r="E57" s="232"/>
-      <c r="F57" s="232"/>
-      <c r="G57" s="232"/>
-      <c r="H57" s="232"/>
-      <c r="I57" s="233"/>
+      <c r="A57" s="301" t="s">
+        <v>215</v>
+      </c>
+      <c r="B57" s="302"/>
+      <c r="C57" s="302"/>
+      <c r="D57" s="302"/>
+      <c r="E57" s="302"/>
+      <c r="F57" s="302"/>
+      <c r="G57" s="302"/>
+      <c r="H57" s="302"/>
+      <c r="I57" s="303"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="82"/>
       <c r="B58" s="83" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C58" s="84"/>
       <c r="D58" s="84" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E58" s="84"/>
       <c r="F58" s="84"/>
       <c r="G58" s="84" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H58" s="84" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="I58" s="85"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="86"/>
       <c r="B59" s="87" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D59" s="87" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F59" s="87" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G59" s="87" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" s="234" t="s">
-        <v>233</v>
-      </c>
-      <c r="I59" s="235"/>
+        <v>225</v>
+      </c>
+      <c r="H59" s="291" t="s">
+        <v>226</v>
+      </c>
+      <c r="I59" s="292"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7472,79 +7565,79 @@
         <v>100</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H60" s="236">
+        <v>81</v>
+      </c>
+      <c r="H60" s="304">
         <v>18.12</v>
       </c>
-      <c r="I60" s="236"/>
+      <c r="I60" s="304"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
-        <v>86</v>
-      </c>
-      <c r="H61" s="248">
+        <v>83</v>
+      </c>
+      <c r="H61" s="287">
         <v>19.98</v>
       </c>
-      <c r="I61" s="248"/>
+      <c r="I61" s="287"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
-        <v>89</v>
-      </c>
-      <c r="H62" s="248">
+        <v>86</v>
+      </c>
+      <c r="H62" s="287">
         <v>18.7</v>
       </c>
-      <c r="I62" s="248"/>
+      <c r="I62" s="287"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="86"/>
       <c r="F63" t="s">
-        <v>235</v>
-      </c>
-      <c r="H63" s="248">
+        <v>228</v>
+      </c>
+      <c r="H63" s="287">
         <v>17.62</v>
       </c>
-      <c r="I63" s="248"/>
+      <c r="I63" s="287"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
     <row r="64" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="86"/>
       <c r="F64" t="s">
-        <v>236</v>
-      </c>
-      <c r="H64" s="249">
+        <v>229</v>
+      </c>
+      <c r="H64" s="290">
         <v>18.79</v>
       </c>
-      <c r="I64" s="249"/>
+      <c r="I64" s="290"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="216" t="s">
-        <v>237</v>
-      </c>
-      <c r="C65" s="217"/>
+      <c r="B65" s="277" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" s="278"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="218">
+      <c r="H65" s="294">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="219"/>
+      <c r="I65" s="295"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7557,13 +7650,13 @@
     <row r="66" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="86"/>
       <c r="G66" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H66" s="244" t="str">
+        <v>60</v>
+      </c>
+      <c r="H66" s="242" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="245"/>
+      <c r="I66" s="244"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7585,16 +7678,16 @@
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="86"/>
       <c r="B68" s="44" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D68" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G68" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H68" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="I68" s="94"/>
       <c r="J68" s="88"/>
@@ -7607,31 +7700,31 @@
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="86"/>
       <c r="B69" s="87" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C69" s="87" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D69" s="87" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E69" s="87" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F69" s="87" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G69" s="87" t="s">
-        <v>232</v>
-      </c>
-      <c r="H69" s="234" t="s">
-        <v>233</v>
-      </c>
-      <c r="I69" s="235"/>
-      <c r="P69" s="246"/>
-      <c r="Q69" s="246"/>
-      <c r="R69" s="209"/>
-      <c r="S69" s="209"/>
+        <v>225</v>
+      </c>
+      <c r="H69" s="291" t="s">
+        <v>226</v>
+      </c>
+      <c r="I69" s="292"/>
+      <c r="P69" s="288"/>
+      <c r="Q69" s="288"/>
+      <c r="R69" s="289"/>
+      <c r="S69" s="289"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7642,76 +7735,76 @@
         <v>100</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>84</v>
-      </c>
-      <c r="H70" s="247">
+        <v>81</v>
+      </c>
+      <c r="H70" s="293">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="247"/>
-      <c r="P70" s="246"/>
-      <c r="Q70" s="246"/>
-      <c r="R70" s="209"/>
-      <c r="S70" s="209"/>
+      <c r="I70" s="293"/>
+      <c r="P70" s="288"/>
+      <c r="Q70" s="288"/>
+      <c r="R70" s="289"/>
+      <c r="S70" s="289"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
-        <v>86</v>
-      </c>
-      <c r="H71" s="248">
+        <v>83</v>
+      </c>
+      <c r="H71" s="287">
         <v>11.78</v>
       </c>
-      <c r="I71" s="248"/>
-      <c r="P71" s="246"/>
-      <c r="Q71" s="246"/>
-      <c r="R71" s="209"/>
-      <c r="S71" s="209"/>
+      <c r="I71" s="287"/>
+      <c r="P71" s="288"/>
+      <c r="Q71" s="288"/>
+      <c r="R71" s="289"/>
+      <c r="S71" s="289"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
-        <v>89</v>
-      </c>
-      <c r="H72" s="248">
+        <v>86</v>
+      </c>
+      <c r="H72" s="287">
         <v>12.39</v>
       </c>
-      <c r="I72" s="248"/>
-      <c r="P72" s="246"/>
-      <c r="Q72" s="246"/>
-      <c r="R72" s="209"/>
-      <c r="S72" s="209"/>
+      <c r="I72" s="287"/>
+      <c r="P72" s="288"/>
+      <c r="Q72" s="288"/>
+      <c r="R72" s="289"/>
+      <c r="S72" s="289"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
-        <v>235</v>
-      </c>
-      <c r="H73" s="248">
+        <v>228</v>
+      </c>
+      <c r="H73" s="287">
         <v>11.21</v>
       </c>
-      <c r="I73" s="248"/>
+      <c r="I73" s="287"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="246"/>
-      <c r="Q73" s="246"/>
-      <c r="R73" s="209"/>
-      <c r="S73" s="209"/>
+      <c r="P73" s="288"/>
+      <c r="Q73" s="288"/>
+      <c r="R73" s="289"/>
+      <c r="S73" s="289"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
-        <v>236</v>
-      </c>
-      <c r="H74" s="249">
+        <v>229</v>
+      </c>
+      <c r="H74" s="290">
         <v>12.75</v>
       </c>
-      <c r="I74" s="249"/>
+      <c r="I74" s="290"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7720,53 +7813,53 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="246"/>
-      <c r="Q74" s="246"/>
-      <c r="R74" s="209"/>
-      <c r="S74" s="209"/>
+      <c r="P74" s="288"/>
+      <c r="Q74" s="288"/>
+      <c r="R74" s="289"/>
+      <c r="S74" s="289"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="216" t="s">
-        <v>237</v>
-      </c>
-      <c r="C75" s="217"/>
+      <c r="B75" s="277" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="278"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="260">
+      <c r="H75" s="279">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="261"/>
+      <c r="I75" s="280"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
     <row r="76" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="99" t="s">
-        <v>63</v>
-      </c>
-      <c r="H76" s="223" t="str">
+        <v>60</v>
+      </c>
+      <c r="H76" s="180" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="262"/>
+      <c r="I76" s="182"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="263" t="s">
-        <v>240</v>
-      </c>
-      <c r="B77" s="264"/>
-      <c r="C77" s="264"/>
-      <c r="D77" s="264"/>
-      <c r="E77" s="264"/>
-      <c r="F77" s="264"/>
-      <c r="G77" s="264"/>
-      <c r="H77" s="264"/>
-      <c r="I77" s="265"/>
+      <c r="A77" s="281" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" s="282"/>
+      <c r="C77" s="282"/>
+      <c r="D77" s="282"/>
+      <c r="E77" s="282"/>
+      <c r="F77" s="282"/>
+      <c r="G77" s="282"/>
+      <c r="H77" s="282"/>
+      <c r="I77" s="283"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7779,16 +7872,16 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="223" t="s">
-        <v>241</v>
-      </c>
-      <c r="B80" s="266"/>
-      <c r="C80" s="266"/>
+      <c r="A80" s="180" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" s="181"/>
+      <c r="C80" s="181"/>
       <c r="D80" s="47" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E80" s="48" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G80" s="88"/>
       <c r="H80" s="88"/>
@@ -7798,22 +7891,22 @@
     </row>
     <row r="81" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="267" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" s="284" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="268"/>
+      <c r="C81" s="285"/>
       <c r="D81" s="102" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E81" s="103">
         <f t="array" ref="E81">INDEX($J$82:$J$84,MATCH(E80,$I$82:$I$84,0),0)</f>
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="269"/>
-      <c r="I81" s="269"/>
+      <c r="H81" s="286"/>
+      <c r="I81" s="286"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7821,18 +7914,18 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="250">
+      <c r="B82" s="268">
         <v>15</v>
       </c>
-      <c r="C82" s="250"/>
-      <c r="D82" s="251" t="s">
-        <v>245</v>
+      <c r="C82" s="268"/>
+      <c r="D82" s="269" t="s">
+        <v>238</v>
       </c>
       <c r="E82" s="106"/>
       <c r="G82" s="88"/>
       <c r="H82" s="107"/>
       <c r="I82" s="108" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J82" s="109">
         <v>0.42</v>
@@ -7841,23 +7934,23 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="50" t="s">
-        <v>247</v>
-      </c>
-      <c r="B83" s="254" t="s">
-        <v>248</v>
-      </c>
-      <c r="C83" s="255"/>
-      <c r="D83" s="252"/>
+        <v>240</v>
+      </c>
+      <c r="B83" s="272" t="s">
+        <v>241</v>
+      </c>
+      <c r="C83" s="263"/>
+      <c r="D83" s="270"/>
       <c r="E83" s="46" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F83" s="110" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G83" s="88"/>
       <c r="H83" s="107"/>
       <c r="I83" s="108" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="J83" s="109">
         <v>0.5</v>
@@ -7868,11 +7961,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="256">
+      <c r="B84" s="273">
         <v>2.8</v>
       </c>
-      <c r="C84" s="256"/>
-      <c r="D84" s="252"/>
+      <c r="C84" s="273"/>
+      <c r="D84" s="270"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7887,7 +7980,7 @@
       </c>
       <c r="H84" s="88"/>
       <c r="I84" s="112" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="J84" s="109">
         <v>0.5</v>
@@ -7898,11 +7991,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="257">
+      <c r="B85" s="274">
         <v>5</v>
       </c>
-      <c r="C85" s="258"/>
-      <c r="D85" s="252"/>
+      <c r="C85" s="275"/>
+      <c r="D85" s="270"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -7924,11 +8017,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="259">
+      <c r="B86" s="276">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="259"/>
-      <c r="D86" s="253"/>
+      <c r="C86" s="276"/>
+      <c r="D86" s="271"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -7947,14 +8040,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="282" t="s">
-        <v>251</v>
-      </c>
-      <c r="B87" s="283"/>
-      <c r="C87" s="283"/>
-      <c r="D87" s="283"/>
-      <c r="E87" s="283"/>
-      <c r="F87" s="284"/>
+      <c r="A87" s="254" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" s="255"/>
+      <c r="C87" s="255"/>
+      <c r="D87" s="255"/>
+      <c r="E87" s="255"/>
+      <c r="F87" s="256"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -7962,12 +8055,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="285"/>
-      <c r="B88" s="286"/>
-      <c r="C88" s="286"/>
-      <c r="D88" s="286"/>
-      <c r="E88" s="286"/>
-      <c r="F88" s="287"/>
+      <c r="A88" s="257"/>
+      <c r="B88" s="258"/>
+      <c r="C88" s="258"/>
+      <c r="D88" s="258"/>
+      <c r="E88" s="258"/>
+      <c r="F88" s="259"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -7977,16 +8070,16 @@
     <row r="89" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="117" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="266" t="s">
-        <v>252</v>
-      </c>
-      <c r="D90" s="266"/>
-      <c r="E90" s="262"/>
+      <c r="C90" s="181" t="s">
+        <v>245</v>
+      </c>
+      <c r="D90" s="181"/>
+      <c r="E90" s="182"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -7996,39 +8089,39 @@
         <v>200</v>
       </c>
       <c r="C91" s="119" t="s">
-        <v>134</v>
-      </c>
-      <c r="D91" s="288">
+        <v>127</v>
+      </c>
+      <c r="D91" s="260">
         <v>107</v>
       </c>
-      <c r="E91" s="289"/>
+      <c r="E91" s="261"/>
       <c r="F91" s="120" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="290" t="s">
-        <v>253</v>
-      </c>
-      <c r="B92" s="255"/>
-      <c r="C92" s="291">
+      <c r="A92" s="262" t="s">
+        <v>246</v>
+      </c>
+      <c r="B92" s="263"/>
+      <c r="C92" s="264">
         <v>3</v>
       </c>
-      <c r="D92" s="291"/>
-      <c r="E92" s="291"/>
+      <c r="D92" s="264"/>
+      <c r="E92" s="264"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="292" t="s">
-        <v>254</v>
-      </c>
-      <c r="B93" s="293"/>
-      <c r="C93" s="293"/>
-      <c r="D93" s="293"/>
-      <c r="E93" s="294"/>
+      <c r="A93" s="265" t="s">
+        <v>247</v>
+      </c>
+      <c r="B93" s="266"/>
+      <c r="C93" s="266"/>
+      <c r="D93" s="266"/>
+      <c r="E93" s="267"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8039,16 +8132,16 @@
     </row>
     <row r="95" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="117" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="244" t="s">
-        <v>255</v>
-      </c>
-      <c r="D95" s="270"/>
-      <c r="E95" s="245"/>
+      <c r="C95" s="242" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" s="243"/>
+      <c r="E95" s="244"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8058,46 +8151,46 @@
         <v>65</v>
       </c>
       <c r="C96" s="127" t="s">
-        <v>134</v>
-      </c>
-      <c r="D96" s="271">
+        <v>127</v>
+      </c>
+      <c r="D96" s="245">
         <v>3691</v>
       </c>
-      <c r="E96" s="272"/>
+      <c r="E96" s="246"/>
       <c r="F96" s="120" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="273" t="s">
-        <v>253</v>
-      </c>
-      <c r="B97" s="274"/>
-      <c r="C97" s="275">
+      <c r="A97" s="247" t="s">
+        <v>246</v>
+      </c>
+      <c r="B97" s="248"/>
+      <c r="C97" s="249">
         <v>6.25</v>
       </c>
-      <c r="D97" s="275"/>
-      <c r="E97" s="275"/>
+      <c r="D97" s="249"/>
+      <c r="E97" s="249"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="276" t="s">
-        <v>256</v>
-      </c>
-      <c r="B98" s="277"/>
-      <c r="C98" s="277"/>
-      <c r="D98" s="277"/>
-      <c r="E98" s="278"/>
+      <c r="A98" s="250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B98" s="251"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
+      <c r="E98" s="252"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="279"/>
-      <c r="B99" s="280"/>
-      <c r="C99" s="280"/>
-      <c r="D99" s="280"/>
-      <c r="E99" s="281"/>
+      <c r="A99" s="225"/>
+      <c r="B99" s="253"/>
+      <c r="C99" s="253"/>
+      <c r="D99" s="253"/>
+      <c r="E99" s="226"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8107,42 +8200,42 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="244" t="s">
-        <v>257</v>
-      </c>
-      <c r="B101" s="270"/>
-      <c r="C101" s="270"/>
-      <c r="D101" s="270"/>
-      <c r="E101" s="270"/>
-      <c r="F101" s="270"/>
-      <c r="G101" s="270"/>
-      <c r="H101" s="270"/>
-      <c r="I101" s="270"/>
-      <c r="J101" s="245"/>
+      <c r="A101" s="242" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" s="243"/>
+      <c r="C101" s="243"/>
+      <c r="D101" s="243"/>
+      <c r="E101" s="243"/>
+      <c r="F101" s="243"/>
+      <c r="G101" s="243"/>
+      <c r="H101" s="243"/>
+      <c r="I101" s="243"/>
+      <c r="J101" s="244"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B102" s="90" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C102" s="77" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D102" s="84"/>
       <c r="E102" s="89" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F102" s="90">
         <v>500</v>
       </c>
       <c r="G102" s="129" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="300"/>
-      <c r="J102" s="301"/>
+      <c r="I102" s="219"/>
+      <c r="J102" s="220"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8154,107 +8247,107 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="302"/>
-      <c r="E103" s="178"/>
-      <c r="F103" s="178"/>
-      <c r="G103" s="303" t="s">
-        <v>261</v>
-      </c>
-      <c r="H103" s="304"/>
-      <c r="I103" s="305" t="s">
-        <v>262</v>
-      </c>
-      <c r="J103" s="306"/>
-      <c r="K103" s="307" t="s">
-        <v>63</v>
-      </c>
-      <c r="L103" s="308"/>
+      <c r="D103" s="221"/>
+      <c r="E103" s="222"/>
+      <c r="F103" s="222"/>
+      <c r="G103" s="223" t="s">
+        <v>254</v>
+      </c>
+      <c r="H103" s="224"/>
+      <c r="I103" s="227" t="s">
+        <v>255</v>
+      </c>
+      <c r="J103" s="228"/>
+      <c r="K103" s="231" t="s">
+        <v>60</v>
+      </c>
+      <c r="L103" s="232"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="311" t="s">
-        <v>124</v>
+      <c r="A104" s="235" t="s">
+        <v>117</v>
       </c>
       <c r="B104" s="134" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C104" s="135" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D104" s="135" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E104" s="136" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F104" s="135" t="s">
-        <v>267</v>
-      </c>
-      <c r="G104" s="279"/>
-      <c r="H104" s="281"/>
-      <c r="I104" s="228"/>
+        <v>260</v>
+      </c>
+      <c r="G104" s="225"/>
+      <c r="H104" s="226"/>
+      <c r="I104" s="229"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="309"/>
-      <c r="L104" s="310"/>
+      <c r="K104" s="233"/>
+      <c r="L104" s="234"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="312"/>
+      <c r="A105" s="194"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>156</v>
-      </c>
-      <c r="G105" s="313">
+        <v>149</v>
+      </c>
+      <c r="G105" s="236">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="314"/>
-      <c r="I105" s="315">
+      <c r="H105" s="237"/>
+      <c r="I105" s="238">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="316"/>
-      <c r="K105" s="317" t="str">
+      <c r="J105" s="239"/>
+      <c r="K105" s="240" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="318"/>
+      <c r="L105" s="241"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="220" t="s">
-        <v>268</v>
-      </c>
-      <c r="B106" s="221"/>
-      <c r="C106" s="221"/>
-      <c r="D106" s="221"/>
-      <c r="E106" s="221"/>
-      <c r="F106" s="221"/>
-      <c r="G106" s="221"/>
-      <c r="H106" s="221"/>
-      <c r="I106" s="221"/>
-      <c r="J106" s="221"/>
-      <c r="K106" s="221"/>
-      <c r="L106" s="222"/>
+      <c r="A106" s="210" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="211"/>
+      <c r="C106" s="211"/>
+      <c r="D106" s="211"/>
+      <c r="E106" s="211"/>
+      <c r="F106" s="211"/>
+      <c r="G106" s="211"/>
+      <c r="H106" s="211"/>
+      <c r="I106" s="211"/>
+      <c r="J106" s="211"/>
+      <c r="K106" s="211"/>
+      <c r="L106" s="212"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="117" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B110" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8284,49 +8377,49 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="295" t="s">
-        <v>115</v>
-      </c>
-      <c r="B113" s="296"/>
-      <c r="C113" s="296"/>
-      <c r="D113" s="296"/>
-      <c r="E113" s="296" t="s">
-        <v>272</v>
-      </c>
-      <c r="F113" s="296"/>
-      <c r="G113" s="296" t="s">
-        <v>273</v>
-      </c>
-      <c r="H113" s="296" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="298" t="s">
-        <v>274</v>
+      <c r="A113" s="213" t="s">
+        <v>108</v>
+      </c>
+      <c r="B113" s="214"/>
+      <c r="C113" s="214"/>
+      <c r="D113" s="214"/>
+      <c r="E113" s="214" t="s">
+        <v>265</v>
+      </c>
+      <c r="F113" s="214"/>
+      <c r="G113" s="214" t="s">
+        <v>266</v>
+      </c>
+      <c r="H113" s="214" t="s">
+        <v>60</v>
+      </c>
+      <c r="I113" s="217" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="297"/>
-      <c r="B114" s="188"/>
-      <c r="C114" s="188"/>
-      <c r="D114" s="188"/>
-      <c r="E114" s="188"/>
-      <c r="F114" s="188"/>
-      <c r="G114" s="188"/>
-      <c r="H114" s="188"/>
-      <c r="I114" s="299"/>
+      <c r="A114" s="215"/>
+      <c r="B114" s="216"/>
+      <c r="C114" s="216"/>
+      <c r="D114" s="216"/>
+      <c r="E114" s="216"/>
+      <c r="F114" s="216"/>
+      <c r="G114" s="216"/>
+      <c r="H114" s="216"/>
+      <c r="I114" s="218"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="326" t="s">
-        <v>275</v>
-      </c>
-      <c r="B115" s="327"/>
-      <c r="C115" s="327"/>
-      <c r="D115" s="327"/>
+      <c r="A115" s="205" t="s">
+        <v>268</v>
+      </c>
+      <c r="B115" s="206"/>
+      <c r="C115" s="206"/>
+      <c r="D115" s="206"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
       <c r="F115" s="145" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G115" s="146">
         <f>ROUND((E115*D111)/(60*B111),3)</f>
@@ -8336,22 +8429,22 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="328" t="s">
-        <v>276</v>
+      <c r="I115" s="207" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="322" t="s">
-        <v>277</v>
-      </c>
-      <c r="B116" s="323"/>
-      <c r="C116" s="323"/>
-      <c r="D116" s="323"/>
+      <c r="A116" s="201" t="s">
+        <v>270</v>
+      </c>
+      <c r="B116" s="202"/>
+      <c r="C116" s="202"/>
+      <c r="D116" s="202"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G116" s="45">
         <f>ROUND((E116*D111)/(60*B111),3)</f>
@@ -8361,20 +8454,20 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="329"/>
+      <c r="I116" s="208"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="322" t="s">
-        <v>278</v>
-      </c>
-      <c r="B117" s="323"/>
-      <c r="C117" s="323"/>
-      <c r="D117" s="323"/>
+      <c r="A117" s="201" t="s">
+        <v>271</v>
+      </c>
+      <c r="B117" s="202"/>
+      <c r="C117" s="202"/>
+      <c r="D117" s="202"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G117" s="45">
         <f>ROUND((E117*D111)/(60*B111),3)</f>
@@ -8384,20 +8477,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="329"/>
+      <c r="I117" s="208"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="322" t="s">
-        <v>279</v>
-      </c>
-      <c r="B118" s="323"/>
-      <c r="C118" s="323"/>
-      <c r="D118" s="323"/>
+      <c r="A118" s="201" t="s">
+        <v>272</v>
+      </c>
+      <c r="B118" s="202"/>
+      <c r="C118" s="202"/>
+      <c r="D118" s="202"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G118" s="45">
         <f>ROUND((E118*D111)/(60*B111),3)</f>
@@ -8407,20 +8500,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="329"/>
+      <c r="I118" s="208"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="324" t="s">
-        <v>280</v>
-      </c>
-      <c r="B119" s="325"/>
-      <c r="C119" s="325"/>
-      <c r="D119" s="325"/>
+      <c r="A119" s="203" t="s">
+        <v>273</v>
+      </c>
+      <c r="B119" s="204"/>
+      <c r="C119" s="204"/>
+      <c r="D119" s="204"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="F119" s="151" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G119" s="152">
         <f>ROUND((E119*D111)/(60*B111),3)</f>
@@ -8430,20 +8523,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="330"/>
+      <c r="I119" s="209"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="345" t="s">
-        <v>281</v>
-      </c>
-      <c r="B120" s="346"/>
-      <c r="C120" s="346"/>
-      <c r="D120" s="346"/>
+      <c r="A120" s="196" t="s">
+        <v>274</v>
+      </c>
+      <c r="B120" s="197"/>
+      <c r="C120" s="197"/>
+      <c r="D120" s="197"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
       <c r="F120" s="155" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G120" s="156">
         <f>ROUND((E120*D111)/(60*B111),3)</f>
@@ -8453,22 +8546,22 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="319" t="s">
-        <v>282</v>
+      <c r="I120" s="198" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="322" t="s">
-        <v>283</v>
-      </c>
-      <c r="B121" s="323"/>
-      <c r="C121" s="323"/>
-      <c r="D121" s="323"/>
+      <c r="A121" s="201" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" s="202"/>
+      <c r="C121" s="202"/>
+      <c r="D121" s="202"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G121" s="45">
         <f>ROUND((E121*D111)/(60*B111),3)</f>
@@ -8478,20 +8571,20 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="320"/>
+      <c r="I121" s="199"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="322" t="s">
-        <v>284</v>
-      </c>
-      <c r="B122" s="323"/>
-      <c r="C122" s="323"/>
-      <c r="D122" s="323"/>
+      <c r="A122" s="201" t="s">
+        <v>277</v>
+      </c>
+      <c r="B122" s="202"/>
+      <c r="C122" s="202"/>
+      <c r="D122" s="202"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G122" s="45">
         <f>ROUND((E122*D111)/(60*B111),3)</f>
@@ -8501,20 +8594,20 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="320"/>
+      <c r="I122" s="199"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="322" t="s">
-        <v>285</v>
-      </c>
-      <c r="B123" s="323"/>
-      <c r="C123" s="323"/>
-      <c r="D123" s="323"/>
+      <c r="A123" s="201" t="s">
+        <v>278</v>
+      </c>
+      <c r="B123" s="202"/>
+      <c r="C123" s="202"/>
+      <c r="D123" s="202"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G123" s="45">
         <f>ROUND((E123*D111)/(60*B111),3)</f>
@@ -8524,26 +8617,26 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="320"/>
+      <c r="I123" s="199"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="324" t="s">
-        <v>286</v>
-      </c>
-      <c r="B124" s="325"/>
-      <c r="C124" s="325"/>
-      <c r="D124" s="325"/>
+      <c r="A124" s="203" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+      <c r="D124" s="204"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G124" s="152" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="H124" s="153" t="s">
-        <v>287</v>
-      </c>
-      <c r="I124" s="321"/>
+        <v>280</v>
+      </c>
+      <c r="I124" s="200"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8551,10 +8644,10 @@
     </row>
     <row r="126" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="158" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C126" s="159" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D126" s="160"/>
       <c r="E126" s="160"/>
@@ -8564,15 +8657,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="223" t="s">
-        <v>290</v>
-      </c>
-      <c r="B127" s="266"/>
-      <c r="C127" s="266"/>
-      <c r="D127" s="266"/>
-      <c r="E127" s="266"/>
-      <c r="F127" s="266"/>
-      <c r="G127" s="262"/>
+      <c r="A127" s="180" t="s">
+        <v>283</v>
+      </c>
+      <c r="B127" s="181"/>
+      <c r="C127" s="181"/>
+      <c r="D127" s="181"/>
+      <c r="E127" s="181"/>
+      <c r="F127" s="181"/>
+      <c r="G127" s="182"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8584,19 +8677,19 @@
     </row>
     <row r="128" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="99" t="s">
-        <v>291</v>
-      </c>
-      <c r="B128" s="194" t="s">
-        <v>292</v>
-      </c>
-      <c r="C128" s="195"/>
-      <c r="D128" s="195"/>
-      <c r="E128" s="196"/>
+        <v>284</v>
+      </c>
+      <c r="B128" s="183" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="184"/>
+      <c r="D128" s="184"/>
+      <c r="E128" s="185"/>
       <c r="F128" s="162" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="G128" s="163" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H128" s="88"/>
       <c r="I128" s="88"/>
@@ -8612,11 +8705,11 @@
         <v>15</v>
       </c>
       <c r="B129" s="47" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C129" s="105"/>
       <c r="D129" s="164" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E129" s="105"/>
       <c r="F129" s="47" t="e">
@@ -8647,11 +8740,11 @@
         <v>15</v>
       </c>
       <c r="B130" s="102" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C130" s="114"/>
       <c r="D130" s="165" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E130" s="114"/>
       <c r="F130" s="102" t="e">
@@ -8678,15 +8771,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="336" t="s">
-        <v>298</v>
-      </c>
-      <c r="B131" s="332"/>
-      <c r="C131" s="332"/>
-      <c r="D131" s="332"/>
-      <c r="E131" s="332"/>
-      <c r="F131" s="332"/>
-      <c r="G131" s="333"/>
+      <c r="A131" s="186" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="176"/>
+      <c r="C131" s="176"/>
+      <c r="D131" s="176"/>
+      <c r="E131" s="176"/>
+      <c r="F131" s="176"/>
+      <c r="G131" s="177"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8697,15 +8790,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="337" t="s">
-        <v>299</v>
-      </c>
-      <c r="B132" s="338"/>
-      <c r="C132" s="338"/>
-      <c r="D132" s="338"/>
-      <c r="E132" s="338"/>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="A132" s="187" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="188"/>
+      <c r="C132" s="188"/>
+      <c r="D132" s="188"/>
+      <c r="E132" s="188"/>
+      <c r="F132" s="188"/>
+      <c r="G132" s="189"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8716,13 +8809,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="340"/>
-      <c r="B133" s="341"/>
-      <c r="C133" s="341"/>
-      <c r="D133" s="341"/>
-      <c r="E133" s="341"/>
-      <c r="F133" s="341"/>
-      <c r="G133" s="342"/>
+      <c r="A133" s="190"/>
+      <c r="B133" s="191"/>
+      <c r="C133" s="191"/>
+      <c r="D133" s="191"/>
+      <c r="E133" s="191"/>
+      <c r="F133" s="191"/>
+      <c r="G133" s="192"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8744,7 +8837,7 @@
     </row>
     <row r="135" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="166" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B135" s="129"/>
       <c r="C135" s="129"/>
@@ -8752,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="168" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F135" s="169" t="str">
         <f>IF(D135&lt;=5,"Pass","Fail")</f>
@@ -8788,7 +8881,7 @@
     </row>
     <row r="138" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="44" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="H138" s="98"/>
       <c r="I138" s="98"/>
@@ -8829,7 +8922,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="343" t="s">
+      <c r="A140" s="193" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8860,7 +8953,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="312"/>
+      <c r="A141" s="194"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8896,8 +8989,8 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="344" t="s">
-        <v>303</v>
+      <c r="B142" s="195" t="s">
+        <v>296</v>
       </c>
       <c r="C142" s="173">
         <f>C139-C141</f>
@@ -8930,7 +9023,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="344"/>
+      <c r="B143" s="195"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -8961,26 +9054,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="331" t="s">
-        <v>304</v>
-      </c>
-      <c r="B144" s="332"/>
-      <c r="C144" s="332"/>
-      <c r="D144" s="332"/>
-      <c r="E144" s="332"/>
-      <c r="F144" s="332"/>
-      <c r="G144" s="333"/>
+      <c r="A144" s="175" t="s">
+        <v>297</v>
+      </c>
+      <c r="B144" s="176"/>
+      <c r="C144" s="176"/>
+      <c r="D144" s="176"/>
+      <c r="E144" s="176"/>
+      <c r="F144" s="176"/>
+      <c r="G144" s="177"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="331" t="s">
-        <v>305</v>
-      </c>
-      <c r="B145" s="334"/>
-      <c r="C145" s="334"/>
-      <c r="D145" s="334"/>
-      <c r="E145" s="334"/>
-      <c r="F145" s="334"/>
-      <c r="G145" s="335"/>
+      <c r="A145" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="B145" s="178"/>
+      <c r="C145" s="178"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="179"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -8996,26 +9089,107 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9031,108 +9205,28 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C142:G142">
     <cfRule type="cellIs" dxfId="40" priority="6" operator="greaterThan">
       <formula>1</formula>
@@ -9147,19 +9241,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:F86">
-    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="37" priority="19" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",F84)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="20" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",F84)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="19" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
-    <cfRule type="containsText" dxfId="35" priority="18" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",F92)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",F92)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="17" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",F92)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
@@ -9197,11 +9291,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H66:I66">
-    <cfRule type="containsText" dxfId="25" priority="24" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",H66)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",H66)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="22" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",H66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H75:I75">
@@ -9210,11 +9304,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H76:I76 H78:I79">
-    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="22" priority="21" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",H76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",H76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",H76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105:J105">
@@ -9233,11 +9327,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L105">
-    <cfRule type="containsText" dxfId="17" priority="14" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",K105)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="14" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",K105)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",K105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q14:T14">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4857E4A6-A2C7-46E8-BEA1-BEA25A8B5009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142B24A8-CAB7-4527-88D4-6EE240A12013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CT Scan Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="279">
   <si>
     <t>TEST: RADIATION PROFILE WIDTH FOR CT SCAN</t>
   </si>
@@ -38,30 +38,18 @@
     <t>mA</t>
   </si>
   <si>
-    <t>0.62</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>1.27</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>3.05</t>
-  </si>
-  <si>
     <t>TEST: MEASUREMENT OF OPERATING POTENTIAL</t>
   </si>
   <si>
@@ -92,12 +80,6 @@
     <t>80</t>
   </si>
   <si>
-    <t>80.2</t>
-  </si>
-  <si>
-    <t>80.3</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -110,18 +92,6 @@
     <t>±</t>
   </si>
   <si>
-    <t>100.1</t>
-  </si>
-  <si>
-    <t>100.3</t>
-  </si>
-  <si>
-    <t>120.4</t>
-  </si>
-  <si>
-    <t>120.6</t>
-  </si>
-  <si>
     <t>TEST: MEASUREMENT OF MA LINEARITY</t>
   </si>
   <si>
@@ -146,43 +116,10 @@
     <t>10.1</t>
   </si>
   <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t>10.3</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
-    <t>20.2</t>
-  </si>
-  <si>
-    <t>20.1</t>
-  </si>
-  <si>
-    <t>20.3</t>
-  </si>
-  <si>
     <t>50</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>101.0</t>
-  </si>
-  <si>
-    <t>100.8</t>
-  </si>
-  <si>
-    <t>101.2</t>
   </si>
   <si>
     <t>TEST: TIMER ACCURACY</t>
@@ -2528,6 +2465,474 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2543,24 +2948,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2585,9 +2972,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2596,453 +2980,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3736,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="20.796875" customWidth="1"/>
@@ -3763,778 +3700,760 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.6</v>
-      </c>
-      <c r="B3" t="s">
+        <f>'raw data'!A84</f>
+        <v>1.25</v>
+      </c>
+      <c r="B3" s="174">
+        <f>'raw data'!B84:C84</f>
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <f>'raw data'!A82</f>
+        <v>140</v>
+      </c>
+      <c r="D3" t="e">
+        <f>'raw data'!B82:C82</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f>'raw data'!A85</f>
+        <v>2.5</v>
+      </c>
+      <c r="B4" s="174">
+        <f>'raw data'!B85:C85</f>
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
+      <c r="A5">
+        <f>'raw data'!A86</f>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <f>'raw data'!B86:C86</f>
+        <v>9.8000000000000007</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
+      <c r="A9">
+        <f>'raw data'!P14</f>
+        <v>80</v>
       </c>
       <c r="B9" s="174">
         <f>'raw data'!Q14</f>
         <v>78</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
+      <c r="C9" s="174">
+        <f>'raw data'!R14</f>
+        <v>80.06</v>
+      </c>
+      <c r="D9" s="174">
+        <f>'raw data'!S14</f>
+        <v>79.8</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>25</v>
+      <c r="A10">
+        <f>'raw data'!P15</f>
+        <v>100</v>
       </c>
       <c r="B10" s="174">
         <f>'raw data'!Q15</f>
         <v>101.01</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
+      <c r="C10" s="174">
+        <f>'raw data'!R15</f>
+        <v>101.08</v>
+      </c>
+      <c r="D10" s="174">
+        <f>'raw data'!S15</f>
+        <v>101.05</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
+      <c r="A11">
+        <f>'raw data'!P16</f>
+        <v>120</v>
       </c>
       <c r="B11" s="174">
         <f>'raw data'!Q16</f>
         <v>120.92</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
+      <c r="C11" s="174">
+        <f>'raw data'!R16</f>
+        <v>120.93</v>
+      </c>
+      <c r="D11" s="174">
+        <f>'raw data'!S16</f>
+        <v>121.31</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>33</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f>'raw data'!P17</f>
+        <v>140</v>
+      </c>
+      <c r="B12" s="174">
+        <f>'raw data'!Q17</f>
+        <v>141.65</v>
+      </c>
+      <c r="C12" s="174">
+        <f>'raw data'!R17</f>
+        <v>141.59</v>
+      </c>
+      <c r="D12" s="174" t="str">
+        <f>'raw data'!S17</f>
+        <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>22</v>
+      <c r="A16">
+        <f>'raw data'!T27</f>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <f>'raw data'!X27</f>
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <f>'raw data'!P29</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <f>'raw data'!Q29</f>
+        <v>7.2830000000000004</v>
+      </c>
+      <c r="F16">
+        <f>'raw data'!R29</f>
+        <v>7.2817999999999996</v>
+      </c>
+      <c r="G16">
+        <f>'raw data'!S29</f>
+        <v>7.2878999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f>'raw data'!P30</f>
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <f>'raw data'!Q30</f>
+        <v>14.521599999999999</v>
+      </c>
+      <c r="F17">
+        <f>'raw data'!R30</f>
+        <v>14.5259</v>
+      </c>
+      <c r="G17">
+        <f>'raw data'!S30</f>
+        <v>14.532299999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <f>'raw data'!P31</f>
+        <v>200</v>
+      </c>
+      <c r="E18">
+        <f>'raw data'!Q31</f>
+        <v>29.085699999999999</v>
+      </c>
+      <c r="F18">
+        <f>'raw data'!R31</f>
+        <v>29.1005</v>
+      </c>
+      <c r="G18">
+        <f>'raw data'!S31</f>
+        <v>29.098600000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f>'raw data'!P32</f>
+        <v>350</v>
+      </c>
+      <c r="E19">
+        <f>'raw data'!Q32</f>
+        <v>50.905500000000004</v>
+      </c>
+      <c r="F19">
+        <f>'raw data'!R32</f>
+        <v>50.876800000000003</v>
+      </c>
+      <c r="G19">
+        <f>'raw data'!S32</f>
+        <v>50.917000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>3</v>
       </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
         <v>4</v>
       </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="174" t="e">
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="174" t="e">
         <f>'raw data'!P22:Q22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E22" t="e">
+      <c r="E23" t="e">
         <f>'raw data'!R22:S22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F22" t="e">
+      <c r="F23" t="e">
         <f>'raw data'!P25:U25</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="174" t="e">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="174" t="e">
         <f>'raw data'!P23:Q23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E23" t="e">
+      <c r="E24" t="e">
         <f>'raw data'!R23:S23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D24" s="174" t="e">
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="174" t="e">
         <f>'raw data'!P24:Q24</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E24" t="e">
+      <c r="E25" t="e">
         <f>'raw data'!R24:S24</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D25" s="174"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="174"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" t="s">
-        <v>72</v>
-      </c>
-      <c r="J32" t="s">
-        <v>73</v>
-      </c>
-      <c r="K32" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I33" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K33" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H34" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="J34" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K34" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="I35" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J35" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="I36" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="J36" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="K36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>89</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>90</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41">
         <f>'raw data'!Q44</f>
         <v>140</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>100</v>
       </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="174">
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="174">
         <f>'raw data'!R44</f>
         <v>9.39</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" t="s">
-        <v>37</v>
-      </c>
-      <c r="H43" t="s">
-        <v>98</v>
-      </c>
-      <c r="I43" t="s">
-        <v>99</v>
-      </c>
-      <c r="J43" t="s">
-        <v>100</v>
-      </c>
-      <c r="K43" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" t="s">
         <v>25</v>
       </c>
-      <c r="B44" t="s">
+      <c r="F44" t="s">
         <v>26</v>
       </c>
-      <c r="C44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44">
+      <c r="G44" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s">
+        <v>79</v>
+      </c>
+      <c r="K44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45">
         <f>'raw data'!P37</f>
         <v>80</v>
       </c>
-      <c r="E44">
+      <c r="E45">
         <f>'raw data'!Q37</f>
         <v>5.2957999999999998</v>
       </c>
-      <c r="F44">
+      <c r="F45">
         <f>'raw data'!R37</f>
         <v>5.2999000000000001</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <f>'raw data'!S37</f>
         <v>5.3005000000000004</v>
       </c>
-      <c r="H44">
+      <c r="H45">
         <f>'raw data'!T37</f>
         <v>5.3002000000000002</v>
       </c>
-      <c r="I44">
+      <c r="I45">
         <f>'raw data'!U37</f>
         <v>5.2969999999999997</v>
       </c>
-      <c r="J44" t="s">
-        <v>10</v>
-      </c>
-      <c r="K44" t="e">
+      <c r="J45" t="s">
+        <v>7</v>
+      </c>
+      <c r="K45" t="e">
         <f>'raw data'!P41:Y41</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D46">
         <f>'raw data'!P38</f>
         <v>100</v>
       </c>
-      <c r="E45">
+      <c r="E46">
         <f>'raw data'!Q38</f>
         <v>9.4794</v>
       </c>
-      <c r="F45">
+      <c r="F46">
         <f>'raw data'!R38</f>
         <v>9.4793000000000003</v>
       </c>
-      <c r="G45">
+      <c r="G46">
         <f>'raw data'!S38</f>
         <v>9.4732000000000003</v>
       </c>
-      <c r="H45">
+      <c r="H46">
         <f>'raw data'!T38</f>
         <v>9.4781999999999993</v>
-      </c>
-      <c r="I45">
-        <f>'raw data'!U38</f>
-        <v>9.4741999999999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D46">
-        <f>'raw data'!P39</f>
-        <v>120</v>
-      </c>
-      <c r="E46">
-        <f>'raw data'!Q39</f>
-        <v>14.521599999999999</v>
-      </c>
-      <c r="F46">
-        <f>'raw data'!R39</f>
-        <v>14.5259</v>
-      </c>
-      <c r="G46">
-        <f>'raw data'!S39</f>
-        <v>14.532299999999999</v>
-      </c>
-      <c r="H46">
-        <f>'raw data'!T39</f>
-        <v>14.526</v>
       </c>
       <c r="I46">
         <f>'raw data'!U38</f>
@@ -4543,476 +4462,502 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D47">
+        <f>'raw data'!P39</f>
+        <v>120</v>
+      </c>
+      <c r="E47">
+        <f>'raw data'!Q39</f>
+        <v>14.521599999999999</v>
+      </c>
+      <c r="F47">
+        <f>'raw data'!R39</f>
+        <v>14.5259</v>
+      </c>
+      <c r="G47">
+        <f>'raw data'!S39</f>
+        <v>14.532299999999999</v>
+      </c>
+      <c r="H47">
+        <f>'raw data'!T39</f>
+        <v>14.526</v>
+      </c>
+      <c r="I47">
+        <f>'raw data'!U38</f>
+        <v>9.4741999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D48">
         <f>'raw data'!P40</f>
         <v>140</v>
       </c>
-      <c r="E47">
+      <c r="E48">
         <f>'raw data'!Q40</f>
         <v>20.186800000000002</v>
       </c>
-      <c r="F47">
+      <c r="F48">
         <f>'raw data'!R40</f>
         <v>20.193899999999999</v>
       </c>
-      <c r="G47">
+      <c r="G48">
         <f>'raw data'!S40</f>
         <v>20.188400000000001</v>
       </c>
-      <c r="H47">
+      <c r="H48">
         <f>'raw data'!T40</f>
         <v>20.187999999999999</v>
       </c>
-      <c r="I47">
+      <c r="I48">
         <f>'raw data'!U40</f>
         <v>20.197600000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>102</v>
-      </c>
-    </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" t="s">
-        <v>104</v>
-      </c>
-      <c r="E51" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" t="s">
-        <v>106</v>
-      </c>
-      <c r="H51" t="s">
-        <v>107</v>
-      </c>
-      <c r="I51" t="s">
-        <v>108</v>
-      </c>
-      <c r="J51" t="s">
-        <v>109</v>
-      </c>
-      <c r="K51" t="s">
-        <v>110</v>
-      </c>
-      <c r="L51" t="s">
-        <v>111</v>
-      </c>
-      <c r="M51" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="J52" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="L52" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="M52" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="J53" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="L53" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="M53" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>124</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
+        <v>100</v>
+      </c>
+      <c r="J54" t="s">
+        <v>101</v>
+      </c>
+      <c r="K54" t="s">
+        <v>101</v>
+      </c>
+      <c r="L54" t="s">
+        <v>97</v>
+      </c>
+      <c r="M54" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" t="s">
-        <v>93</v>
-      </c>
-      <c r="F56" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
         <v>6</v>
       </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>129</v>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" t="s">
-        <v>93</v>
-      </c>
-      <c r="F60" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>110</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
         <v>6</v>
       </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" t="s">
-        <v>26</v>
-      </c>
-      <c r="F61" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>132</v>
+      <c r="E62" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
-        <v>135</v>
-      </c>
-      <c r="E68" t="s">
-        <v>136</v>
-      </c>
-      <c r="F68" t="s">
-        <v>3</v>
-      </c>
-      <c r="G68" t="s">
-        <v>4</v>
-      </c>
-      <c r="H68" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F69" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H69" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G70" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>139</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>31</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" t="s">
-        <v>140</v>
-      </c>
-      <c r="C73" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>148</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>108</v>
-      </c>
-      <c r="B79" t="s">
-        <v>149</v>
-      </c>
-      <c r="C79" t="s">
-        <v>150</v>
-      </c>
-      <c r="D79" t="s">
-        <v>151</v>
-      </c>
-      <c r="E79" t="s">
-        <v>152</v>
-      </c>
-      <c r="F79" t="s">
-        <v>4</v>
-      </c>
-      <c r="G79" t="s">
-        <v>62</v>
-      </c>
-      <c r="H79" t="s">
-        <v>92</v>
-      </c>
-      <c r="I79" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E80" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G80" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="I80" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s">
         <v>101</v>
       </c>
       <c r="C81" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G81" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H81" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="I81" t="s">
-        <v>10</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>137</v>
+      </c>
+      <c r="B82" t="s">
+        <v>80</v>
+      </c>
+      <c r="C82" t="s">
+        <v>133</v>
+      </c>
+      <c r="D82" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82" t="s">
+        <v>7</v>
+      </c>
+      <c r="H82" t="s">
+        <v>7</v>
+      </c>
+      <c r="I82" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M2 A5:M7 A4:H4 J4:M4 B3:M3 A12:M21 A9 C9:M9 A10 C10:M10 A11 C11:M11 A66:M81 A8 C8:M8 A50:M62 A44:C44 J44 A45:C45 J45:M45 L44:M44 A41:M43 C40:D40 F40:M40 A26:M39 A22:C22 G22:M22 A23:C23 F23:M23 A24:C24 F24:M24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M2 A6:M7 C4:H4 J4:M4 E3:M3 A14:M15 A67:M82 A8 C8:M8 A51:M63 J45 A45:C46 J46:M46 L45:M45 A42:M44 C41:D41 F41:M41 A27:M40 G23:M23 A25:C25 F24:M25 E12:M12 E11:M11 E9:M9 E10:M10 A20:M22 H17:M17 H18:M18 H19:M19 B16 H16:M16 C5:M5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5042,40 +4987,40 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="342" t="s">
-        <v>160</v>
-      </c>
-      <c r="C1" s="342"/>
-      <c r="D1" s="342"/>
-      <c r="E1" s="342"/>
-      <c r="F1" s="342"/>
-      <c r="G1" s="342"/>
-      <c r="H1" s="342"/>
-      <c r="I1" s="342"/>
+        <v>138</v>
+      </c>
+      <c r="B1" s="175" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
+      <c r="K1" s="177"/>
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="342" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="342"/>
-      <c r="D2" s="342"/>
-      <c r="E2" s="342"/>
-      <c r="F2" s="342"/>
-      <c r="G2" s="342"/>
-      <c r="H2" s="342"/>
-      <c r="I2" s="342"/>
+        <v>140</v>
+      </c>
+      <c r="B2" s="175" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5085,16 +5030,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="342" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="342"/>
-      <c r="D3" s="342"/>
-      <c r="E3" s="342"/>
-      <c r="F3" s="342"/>
-      <c r="G3" s="342"/>
-      <c r="H3" s="342"/>
-      <c r="I3" s="342"/>
+      <c r="B3" s="175" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5104,16 +5049,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="342"/>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
+        <v>143</v>
+      </c>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5123,22 +5068,22 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="342" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="342"/>
-      <c r="D5" s="342"/>
-      <c r="E5" s="342"/>
+        <v>144</v>
+      </c>
+      <c r="B5" s="175" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="345">
+        <v>146</v>
+      </c>
+      <c r="G5" s="176">
         <v>22.7</v>
       </c>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5148,22 +5093,22 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="342" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="342"/>
-      <c r="D6" s="342"/>
-      <c r="E6" s="342"/>
+        <v>147</v>
+      </c>
+      <c r="B6" s="175" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="175"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
       <c r="F6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="G6" s="345">
+        <v>149</v>
+      </c>
+      <c r="G6" s="176">
         <v>50.2</v>
       </c>
-      <c r="H6" s="345"/>
-      <c r="I6" s="345"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5173,22 +5118,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="342" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
+        <v>150</v>
+      </c>
+      <c r="B7" s="175" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="175"/>
       <c r="F7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="342" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
+        <v>50</v>
+      </c>
+      <c r="G7" s="175" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="175"/>
+      <c r="I7" s="175"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5197,18 +5142,18 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8" s="341">
+        <v>153</v>
+      </c>
+      <c r="B8" s="191">
         <v>46066</v>
       </c>
-      <c r="C8" s="342"/>
-      <c r="D8" s="342"/>
-      <c r="E8" s="342"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="175"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="342"/>
-      <c r="H8" s="342"/>
-      <c r="I8" s="342"/>
+      <c r="G8" s="175"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5217,14 +5162,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5233,18 +5178,18 @@
     </row>
     <row r="10" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="343" t="s">
-        <v>176</v>
-      </c>
-      <c r="C10" s="343"/>
-      <c r="D10" s="343"/>
-      <c r="E10" s="343"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="343"/>
-      <c r="H10" s="343"/>
-      <c r="I10" s="344"/>
+        <v>154</v>
+      </c>
+      <c r="B10" s="192" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5252,91 +5197,91 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="183" t="s">
-        <v>177</v>
-      </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="184" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" s="184"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="185"/>
+      <c r="A11" s="194" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="195"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="195" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="196"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="331" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q11" s="332"/>
-      <c r="R11" s="332"/>
-      <c r="S11" s="332"/>
-      <c r="T11" s="332"/>
-      <c r="U11" s="332"/>
-      <c r="V11" s="332"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
+      <c r="P11" s="179" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q11" s="180"/>
+      <c r="R11" s="180"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="180"/>
+      <c r="U11" s="180"/>
+      <c r="V11" s="180"/>
+      <c r="W11" s="180"/>
+      <c r="X11" s="181"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P12" s="334" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q12" s="336" t="s">
-        <v>188</v>
-      </c>
-      <c r="R12" s="336"/>
-      <c r="S12" s="336"/>
-      <c r="T12" s="337" t="s">
-        <v>189</v>
-      </c>
-      <c r="U12" s="305" t="s">
-        <v>190</v>
-      </c>
-      <c r="V12" s="337"/>
+        <v>165</v>
+      </c>
+      <c r="P12" s="182" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q12" s="184" t="s">
+        <v>167</v>
+      </c>
+      <c r="R12" s="184"/>
+      <c r="S12" s="184"/>
+      <c r="T12" s="185" t="s">
+        <v>168</v>
+      </c>
+      <c r="U12" s="187" t="s">
+        <v>169</v>
+      </c>
+      <c r="V12" s="185"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="339" t="s">
-        <v>191</v>
+      <c r="X12" s="189" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -5375,7 +5320,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="335"/>
+      <c r="P13" s="183"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5388,11 +5333,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="338"/>
-      <c r="U13" s="216"/>
-      <c r="V13" s="338"/>
+      <c r="T13" s="186"/>
+      <c r="U13" s="188"/>
+      <c r="V13" s="186"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="340"/>
+      <c r="X13" s="190"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5460,7 +5405,7 @@
         <v>0.70999999999999375</v>
       </c>
       <c r="Y14" s="28" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29"/>
@@ -5561,7 +5506,7 @@
         <v>9.1636581420898438</v>
       </c>
       <c r="L16" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
@@ -5651,7 +5596,7 @@
         <v>141.59</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="T17" s="36">
         <f>ROUND(AVERAGE(Q17:S17),2)</f>
@@ -5704,15 +5649,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="325" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q18" s="326"/>
-      <c r="R18" s="326"/>
-      <c r="S18" s="326"/>
-      <c r="T18" s="326"/>
-      <c r="U18" s="326"/>
-      <c r="V18" s="327"/>
+      <c r="P18" s="206" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q18" s="207"/>
+      <c r="R18" s="207"/>
+      <c r="S18" s="207"/>
+      <c r="T18" s="207"/>
+      <c r="U18" s="207"/>
+      <c r="V18" s="208"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5752,13 +5697,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="289"/>
-      <c r="Q19" s="289"/>
-      <c r="R19" s="289"/>
-      <c r="S19" s="289"/>
-      <c r="T19" s="289"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
+      <c r="P19" s="209"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5796,14 +5741,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="310" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q20" s="311"/>
-      <c r="R20" s="311"/>
-      <c r="S20" s="311"/>
-      <c r="T20" s="311"/>
-      <c r="U20" s="313"/>
+      <c r="P20" s="210" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q20" s="211"/>
+      <c r="R20" s="211"/>
+      <c r="S20" s="211"/>
+      <c r="T20" s="211"/>
+      <c r="U20" s="212"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5841,19 +5786,19 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="328" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q21" s="329"/>
-      <c r="R21" s="330" t="s">
-        <v>198</v>
-      </c>
-      <c r="S21" s="329"/>
+      <c r="P21" s="213" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q21" s="214"/>
+      <c r="R21" s="215" t="s">
+        <v>177</v>
+      </c>
+      <c r="S21" s="214"/>
       <c r="T21" s="14" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="U21" s="43" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -5885,7 +5830,7 @@
         <v>9.1354408264160156</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
@@ -5895,16 +5840,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="316">
+      <c r="P22" s="197">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="317"/>
-      <c r="R22" s="318">
+      <c r="Q22" s="198"/>
+      <c r="R22" s="199">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="318"/>
+      <c r="S22" s="199"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5950,16 +5895,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="316">
+      <c r="P23" s="197">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="317"/>
-      <c r="R23" s="318">
+      <c r="Q23" s="198"/>
+      <c r="R23" s="199">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="318"/>
+      <c r="S23" s="199"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -6005,16 +5950,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="316">
+      <c r="P24" s="197">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="317"/>
-      <c r="R24" s="318">
+      <c r="Q24" s="198"/>
+      <c r="R24" s="199">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="318"/>
+      <c r="S24" s="199"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -6060,14 +6005,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="319" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q25" s="320"/>
-      <c r="R25" s="320"/>
-      <c r="S25" s="320"/>
-      <c r="T25" s="320"/>
-      <c r="U25" s="321"/>
+      <c r="P25" s="200" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q25" s="201"/>
+      <c r="R25" s="201"/>
+      <c r="S25" s="201"/>
+      <c r="T25" s="201"/>
+      <c r="U25" s="202"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6142,20 +6087,20 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="322" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q27" s="323"/>
-      <c r="R27" s="324"/>
+      <c r="P27" s="203" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q27" s="204"/>
+      <c r="R27" s="205"/>
       <c r="S27" s="47" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="T27" s="47">
         <f>A34</f>
         <v>120</v>
       </c>
       <c r="U27" s="47" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="V27" s="47"/>
       <c r="W27" s="47"/>
@@ -6201,23 +6146,23 @@
         <v>9.4741999999999997</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q28" s="305" t="s">
-        <v>205</v>
-      </c>
-      <c r="R28" s="305"/>
-      <c r="S28" s="305"/>
+        <v>183</v>
+      </c>
+      <c r="Q28" s="187" t="s">
+        <v>184</v>
+      </c>
+      <c r="R28" s="187"/>
+      <c r="S28" s="187"/>
       <c r="T28" s="14" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="U28" s="14" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
       <c r="X28" s="43" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -6249,7 +6194,7 @@
         <v>9.0879783630371094</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="M29">
         <f t="shared" si="1"/>
@@ -6279,13 +6224,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="306">
+      <c r="U29" s="237">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="308" t="str">
+      <c r="X29" s="239" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6346,10 +6291,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="306"/>
+      <c r="U30" s="237"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="308"/>
+      <c r="X30" s="239"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6407,10 +6352,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="306"/>
+      <c r="U31" s="237"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="308"/>
+      <c r="X31" s="239"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6468,10 +6413,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="307"/>
+      <c r="U32" s="238"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="309"/>
+      <c r="X32" s="240"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6509,17 +6454,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="210" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q33" s="211"/>
-      <c r="R33" s="211"/>
-      <c r="S33" s="211"/>
-      <c r="T33" s="211"/>
-      <c r="U33" s="211"/>
-      <c r="V33" s="211"/>
-      <c r="W33" s="211"/>
-      <c r="X33" s="212"/>
+      <c r="P33" s="220" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q33" s="221"/>
+      <c r="R33" s="221"/>
+      <c r="S33" s="221"/>
+      <c r="T33" s="221"/>
+      <c r="U33" s="221"/>
+      <c r="V33" s="221"/>
+      <c r="W33" s="221"/>
+      <c r="X33" s="222"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6594,18 +6539,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="310" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q35" s="311"/>
-      <c r="R35" s="311"/>
-      <c r="S35" s="311"/>
-      <c r="T35" s="311"/>
-      <c r="U35" s="311"/>
-      <c r="V35" s="312"/>
-      <c r="W35" s="312"/>
-      <c r="X35" s="312"/>
-      <c r="Y35" s="313"/>
+      <c r="P35" s="210" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q35" s="211"/>
+      <c r="R35" s="211"/>
+      <c r="S35" s="211"/>
+      <c r="T35" s="211"/>
+      <c r="U35" s="211"/>
+      <c r="V35" s="241"/>
+      <c r="W35" s="241"/>
+      <c r="X35" s="241"/>
+      <c r="Y35" s="212"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6644,26 +6589,26 @@
         <v>14.532299999999999</v>
       </c>
       <c r="P36" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q36" s="314" t="s">
-        <v>205</v>
-      </c>
-      <c r="R36" s="314"/>
-      <c r="S36" s="314"/>
-      <c r="T36" s="314"/>
-      <c r="U36" s="315"/>
+        <v>69</v>
+      </c>
+      <c r="Q36" s="242" t="s">
+        <v>184</v>
+      </c>
+      <c r="R36" s="242"/>
+      <c r="S36" s="242"/>
+      <c r="T36" s="242"/>
+      <c r="U36" s="243"/>
       <c r="V36" s="18" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="W36" s="18" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="X36" s="17" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="Y36" s="57" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -7010,18 +6955,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="210" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q41" s="211"/>
-      <c r="R41" s="211"/>
-      <c r="S41" s="211"/>
-      <c r="T41" s="211"/>
-      <c r="U41" s="211"/>
-      <c r="V41" s="211"/>
-      <c r="W41" s="211"/>
-      <c r="X41" s="211"/>
-      <c r="Y41" s="212"/>
+      <c r="P41" s="220" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q41" s="221"/>
+      <c r="R41" s="221"/>
+      <c r="S41" s="221"/>
+      <c r="T41" s="221"/>
+      <c r="U41" s="221"/>
+      <c r="V41" s="221"/>
+      <c r="W41" s="221"/>
+      <c r="X41" s="221"/>
+      <c r="Y41" s="222"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -7052,7 +6997,7 @@
         <v>9.0919656753540039</v>
       </c>
       <c r="J42" s="44" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="M42">
         <f t="shared" si="1"/>
@@ -7099,15 +7044,15 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="180" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q43" s="296"/>
+      <c r="P43" s="223" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q43" s="224"/>
       <c r="R43" s="72" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="S43" s="73" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -7147,7 +7092,7 @@
         <v>50.917000000000002</v>
       </c>
       <c r="P44" s="74" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="75">
         <f>A46</f>
@@ -7198,12 +7143,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="297" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q45" s="298"/>
-      <c r="R45" s="298"/>
-      <c r="S45" s="299"/>
+      <c r="P45" s="225" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q45" s="226"/>
+      <c r="R45" s="226"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7241,10 +7186,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="297"/>
-      <c r="Q46" s="298"/>
-      <c r="R46" s="298"/>
-      <c r="S46" s="299"/>
+      <c r="P46" s="225"/>
+      <c r="Q46" s="226"/>
+      <c r="R46" s="226"/>
+      <c r="S46" s="227"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7282,9 +7227,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="229"/>
-      <c r="Q47" s="300"/>
-      <c r="R47" s="300"/>
+      <c r="P47" s="228"/>
+      <c r="Q47" s="229"/>
+      <c r="R47" s="229"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7427,7 +7372,7 @@
         <v>9.3486919403076172</v>
       </c>
       <c r="J51" s="44" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="M51">
         <f t="shared" si="1"/>
@@ -7499,62 +7444,62 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="301" t="s">
-        <v>215</v>
-      </c>
-      <c r="B57" s="302"/>
-      <c r="C57" s="302"/>
-      <c r="D57" s="302"/>
-      <c r="E57" s="302"/>
-      <c r="F57" s="302"/>
-      <c r="G57" s="302"/>
-      <c r="H57" s="302"/>
-      <c r="I57" s="303"/>
+      <c r="A57" s="231" t="s">
+        <v>194</v>
+      </c>
+      <c r="B57" s="232"/>
+      <c r="C57" s="232"/>
+      <c r="D57" s="232"/>
+      <c r="E57" s="232"/>
+      <c r="F57" s="232"/>
+      <c r="G57" s="232"/>
+      <c r="H57" s="232"/>
+      <c r="I57" s="233"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="82"/>
       <c r="B58" s="83" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C58" s="84"/>
       <c r="D58" s="84" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="E58" s="84"/>
       <c r="F58" s="84"/>
       <c r="G58" s="84" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="H58" s="84" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="I58" s="85"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="86"/>
       <c r="B59" s="87" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="D59" s="87" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="F59" s="87" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G59" s="87" t="s">
-        <v>225</v>
-      </c>
-      <c r="H59" s="291" t="s">
-        <v>226</v>
-      </c>
-      <c r="I59" s="292"/>
+        <v>204</v>
+      </c>
+      <c r="H59" s="234" t="s">
+        <v>205</v>
+      </c>
+      <c r="I59" s="235"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7565,79 +7510,79 @@
         <v>100</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>81</v>
-      </c>
-      <c r="H60" s="304">
+        <v>60</v>
+      </c>
+      <c r="H60" s="236">
         <v>18.12</v>
       </c>
-      <c r="I60" s="304"/>
+      <c r="I60" s="236"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
-        <v>83</v>
-      </c>
-      <c r="H61" s="287">
+        <v>62</v>
+      </c>
+      <c r="H61" s="248">
         <v>19.98</v>
       </c>
-      <c r="I61" s="287"/>
+      <c r="I61" s="248"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
-        <v>86</v>
-      </c>
-      <c r="H62" s="287">
+        <v>65</v>
+      </c>
+      <c r="H62" s="248">
         <v>18.7</v>
       </c>
-      <c r="I62" s="287"/>
+      <c r="I62" s="248"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="86"/>
       <c r="F63" t="s">
-        <v>228</v>
-      </c>
-      <c r="H63" s="287">
+        <v>207</v>
+      </c>
+      <c r="H63" s="248">
         <v>17.62</v>
       </c>
-      <c r="I63" s="287"/>
+      <c r="I63" s="248"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
     <row r="64" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="86"/>
       <c r="F64" t="s">
-        <v>229</v>
-      </c>
-      <c r="H64" s="290">
+        <v>208</v>
+      </c>
+      <c r="H64" s="249">
         <v>18.79</v>
       </c>
-      <c r="I64" s="290"/>
+      <c r="I64" s="249"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="277" t="s">
-        <v>230</v>
-      </c>
-      <c r="C65" s="278"/>
+      <c r="B65" s="216" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" s="217"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="294">
+      <c r="H65" s="218">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="295"/>
+      <c r="I65" s="219"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7650,13 +7595,13 @@
     <row r="66" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="86"/>
       <c r="G66" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H66" s="242" t="str">
+        <v>39</v>
+      </c>
+      <c r="H66" s="244" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="244"/>
+      <c r="I66" s="245"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7678,16 +7623,16 @@
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="86"/>
       <c r="B68" s="44" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G68" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="H68" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="I68" s="94"/>
       <c r="J68" s="88"/>
@@ -7700,31 +7645,31 @@
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="86"/>
       <c r="B69" s="87" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C69" s="87" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="D69" s="87" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E69" s="87" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="F69" s="87" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G69" s="87" t="s">
-        <v>225</v>
-      </c>
-      <c r="H69" s="291" t="s">
-        <v>226</v>
-      </c>
-      <c r="I69" s="292"/>
-      <c r="P69" s="288"/>
-      <c r="Q69" s="288"/>
-      <c r="R69" s="289"/>
-      <c r="S69" s="289"/>
+        <v>204</v>
+      </c>
+      <c r="H69" s="234" t="s">
+        <v>205</v>
+      </c>
+      <c r="I69" s="235"/>
+      <c r="P69" s="246"/>
+      <c r="Q69" s="246"/>
+      <c r="R69" s="209"/>
+      <c r="S69" s="209"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7735,76 +7680,76 @@
         <v>100</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>81</v>
-      </c>
-      <c r="H70" s="293">
+        <v>60</v>
+      </c>
+      <c r="H70" s="247">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="293"/>
-      <c r="P70" s="288"/>
-      <c r="Q70" s="288"/>
-      <c r="R70" s="289"/>
-      <c r="S70" s="289"/>
+      <c r="I70" s="247"/>
+      <c r="P70" s="246"/>
+      <c r="Q70" s="246"/>
+      <c r="R70" s="209"/>
+      <c r="S70" s="209"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
-        <v>83</v>
-      </c>
-      <c r="H71" s="287">
+        <v>62</v>
+      </c>
+      <c r="H71" s="248">
         <v>11.78</v>
       </c>
-      <c r="I71" s="287"/>
-      <c r="P71" s="288"/>
-      <c r="Q71" s="288"/>
-      <c r="R71" s="289"/>
-      <c r="S71" s="289"/>
+      <c r="I71" s="248"/>
+      <c r="P71" s="246"/>
+      <c r="Q71" s="246"/>
+      <c r="R71" s="209"/>
+      <c r="S71" s="209"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
-        <v>86</v>
-      </c>
-      <c r="H72" s="287">
+        <v>65</v>
+      </c>
+      <c r="H72" s="248">
         <v>12.39</v>
       </c>
-      <c r="I72" s="287"/>
-      <c r="P72" s="288"/>
-      <c r="Q72" s="288"/>
-      <c r="R72" s="289"/>
-      <c r="S72" s="289"/>
+      <c r="I72" s="248"/>
+      <c r="P72" s="246"/>
+      <c r="Q72" s="246"/>
+      <c r="R72" s="209"/>
+      <c r="S72" s="209"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
-        <v>228</v>
-      </c>
-      <c r="H73" s="287">
+        <v>207</v>
+      </c>
+      <c r="H73" s="248">
         <v>11.21</v>
       </c>
-      <c r="I73" s="287"/>
+      <c r="I73" s="248"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="288"/>
-      <c r="Q73" s="288"/>
-      <c r="R73" s="289"/>
-      <c r="S73" s="289"/>
+      <c r="P73" s="246"/>
+      <c r="Q73" s="246"/>
+      <c r="R73" s="209"/>
+      <c r="S73" s="209"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
-        <v>229</v>
-      </c>
-      <c r="H74" s="290">
+        <v>208</v>
+      </c>
+      <c r="H74" s="249">
         <v>12.75</v>
       </c>
-      <c r="I74" s="290"/>
+      <c r="I74" s="249"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7813,53 +7758,53 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="288"/>
-      <c r="Q74" s="288"/>
-      <c r="R74" s="289"/>
-      <c r="S74" s="289"/>
+      <c r="P74" s="246"/>
+      <c r="Q74" s="246"/>
+      <c r="R74" s="209"/>
+      <c r="S74" s="209"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="277" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" s="278"/>
+      <c r="B75" s="216" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="217"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="279">
+      <c r="H75" s="260">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="280"/>
+      <c r="I75" s="261"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
     <row r="76" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="H76" s="180" t="str">
+        <v>39</v>
+      </c>
+      <c r="H76" s="223" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="182"/>
+      <c r="I76" s="262"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="281" t="s">
-        <v>233</v>
-      </c>
-      <c r="B77" s="282"/>
-      <c r="C77" s="282"/>
-      <c r="D77" s="282"/>
-      <c r="E77" s="282"/>
-      <c r="F77" s="282"/>
-      <c r="G77" s="282"/>
-      <c r="H77" s="282"/>
-      <c r="I77" s="283"/>
+      <c r="A77" s="263" t="s">
+        <v>212</v>
+      </c>
+      <c r="B77" s="264"/>
+      <c r="C77" s="264"/>
+      <c r="D77" s="264"/>
+      <c r="E77" s="264"/>
+      <c r="F77" s="264"/>
+      <c r="G77" s="264"/>
+      <c r="H77" s="264"/>
+      <c r="I77" s="265"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7872,16 +7817,16 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="180" t="s">
-        <v>234</v>
-      </c>
-      <c r="B80" s="181"/>
-      <c r="C80" s="181"/>
+      <c r="A80" s="223" t="s">
+        <v>213</v>
+      </c>
+      <c r="B80" s="266"/>
+      <c r="C80" s="266"/>
       <c r="D80" s="47" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="E80" s="48" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="G80" s="88"/>
       <c r="H80" s="88"/>
@@ -7891,22 +7836,22 @@
     </row>
     <row r="81" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="101" t="s">
-        <v>62</v>
-      </c>
-      <c r="B81" s="284" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="285"/>
+      <c r="C81" s="268"/>
       <c r="D81" s="102" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="E81" s="103">
         <f t="array" ref="E81">INDEX($J$82:$J$84,MATCH(E80,$I$82:$I$84,0),0)</f>
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="286"/>
-      <c r="I81" s="286"/>
+      <c r="H81" s="269"/>
+      <c r="I81" s="269"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7914,18 +7859,18 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="268">
+      <c r="B82" s="250">
         <v>15</v>
       </c>
-      <c r="C82" s="268"/>
-      <c r="D82" s="269" t="s">
-        <v>238</v>
+      <c r="C82" s="250"/>
+      <c r="D82" s="251" t="s">
+        <v>217</v>
       </c>
       <c r="E82" s="106"/>
       <c r="G82" s="88"/>
       <c r="H82" s="107"/>
       <c r="I82" s="108" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="J82" s="109">
         <v>0.42</v>
@@ -7934,23 +7879,23 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="B83" s="272" t="s">
-        <v>241</v>
-      </c>
-      <c r="C83" s="263"/>
-      <c r="D83" s="270"/>
+        <v>219</v>
+      </c>
+      <c r="B83" s="254" t="s">
+        <v>220</v>
+      </c>
+      <c r="C83" s="255"/>
+      <c r="D83" s="252"/>
       <c r="E83" s="46" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="F83" s="110" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G83" s="88"/>
       <c r="H83" s="107"/>
       <c r="I83" s="108" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="J83" s="109">
         <v>0.5</v>
@@ -7961,11 +7906,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="273">
+      <c r="B84" s="256">
         <v>2.8</v>
       </c>
-      <c r="C84" s="273"/>
-      <c r="D84" s="270"/>
+      <c r="C84" s="256"/>
+      <c r="D84" s="252"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7980,7 +7925,7 @@
       </c>
       <c r="H84" s="88"/>
       <c r="I84" s="112" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="J84" s="109">
         <v>0.5</v>
@@ -7991,11 +7936,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="274">
+      <c r="B85" s="257">
         <v>5</v>
       </c>
-      <c r="C85" s="275"/>
-      <c r="D85" s="270"/>
+      <c r="C85" s="258"/>
+      <c r="D85" s="252"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -8017,11 +7962,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="276">
+      <c r="B86" s="259">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="276"/>
-      <c r="D86" s="271"/>
+      <c r="C86" s="259"/>
+      <c r="D86" s="253"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -8040,14 +7985,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="254" t="s">
-        <v>244</v>
-      </c>
-      <c r="B87" s="255"/>
-      <c r="C87" s="255"/>
-      <c r="D87" s="255"/>
-      <c r="E87" s="255"/>
-      <c r="F87" s="256"/>
+      <c r="A87" s="282" t="s">
+        <v>223</v>
+      </c>
+      <c r="B87" s="283"/>
+      <c r="C87" s="283"/>
+      <c r="D87" s="283"/>
+      <c r="E87" s="283"/>
+      <c r="F87" s="284"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -8055,12 +8000,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="257"/>
-      <c r="B88" s="258"/>
-      <c r="C88" s="258"/>
-      <c r="D88" s="258"/>
-      <c r="E88" s="258"/>
-      <c r="F88" s="259"/>
+      <c r="A88" s="285"/>
+      <c r="B88" s="286"/>
+      <c r="C88" s="286"/>
+      <c r="D88" s="286"/>
+      <c r="E88" s="286"/>
+      <c r="F88" s="287"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -8070,16 +8015,16 @@
     <row r="89" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="117" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="181" t="s">
-        <v>245</v>
-      </c>
-      <c r="D90" s="181"/>
-      <c r="E90" s="182"/>
+      <c r="C90" s="266" t="s">
+        <v>224</v>
+      </c>
+      <c r="D90" s="266"/>
+      <c r="E90" s="262"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -8089,39 +8034,39 @@
         <v>200</v>
       </c>
       <c r="C91" s="119" t="s">
-        <v>127</v>
-      </c>
-      <c r="D91" s="260">
+        <v>106</v>
+      </c>
+      <c r="D91" s="288">
         <v>107</v>
       </c>
-      <c r="E91" s="261"/>
+      <c r="E91" s="289"/>
       <c r="F91" s="120" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="262" t="s">
-        <v>246</v>
-      </c>
-      <c r="B92" s="263"/>
-      <c r="C92" s="264">
+      <c r="A92" s="290" t="s">
+        <v>225</v>
+      </c>
+      <c r="B92" s="255"/>
+      <c r="C92" s="291">
         <v>3</v>
       </c>
-      <c r="D92" s="264"/>
-      <c r="E92" s="264"/>
+      <c r="D92" s="291"/>
+      <c r="E92" s="291"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="265" t="s">
-        <v>247</v>
-      </c>
-      <c r="B93" s="266"/>
-      <c r="C93" s="266"/>
-      <c r="D93" s="266"/>
-      <c r="E93" s="267"/>
+      <c r="A93" s="292" t="s">
+        <v>226</v>
+      </c>
+      <c r="B93" s="293"/>
+      <c r="C93" s="293"/>
+      <c r="D93" s="293"/>
+      <c r="E93" s="294"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8132,16 +8077,16 @@
     </row>
     <row r="95" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="117" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="242" t="s">
-        <v>248</v>
-      </c>
-      <c r="D95" s="243"/>
-      <c r="E95" s="244"/>
+      <c r="C95" s="244" t="s">
+        <v>227</v>
+      </c>
+      <c r="D95" s="270"/>
+      <c r="E95" s="245"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8151,46 +8096,46 @@
         <v>65</v>
       </c>
       <c r="C96" s="127" t="s">
-        <v>127</v>
-      </c>
-      <c r="D96" s="245">
+        <v>106</v>
+      </c>
+      <c r="D96" s="271">
         <v>3691</v>
       </c>
-      <c r="E96" s="246"/>
+      <c r="E96" s="272"/>
       <c r="F96" s="120" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="247" t="s">
-        <v>246</v>
-      </c>
-      <c r="B97" s="248"/>
-      <c r="C97" s="249">
+      <c r="A97" s="273" t="s">
+        <v>225</v>
+      </c>
+      <c r="B97" s="274"/>
+      <c r="C97" s="275">
         <v>6.25</v>
       </c>
-      <c r="D97" s="249"/>
-      <c r="E97" s="249"/>
+      <c r="D97" s="275"/>
+      <c r="E97" s="275"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="250" t="s">
-        <v>249</v>
-      </c>
-      <c r="B98" s="251"/>
-      <c r="C98" s="251"/>
-      <c r="D98" s="251"/>
-      <c r="E98" s="252"/>
+      <c r="A98" s="276" t="s">
+        <v>228</v>
+      </c>
+      <c r="B98" s="277"/>
+      <c r="C98" s="277"/>
+      <c r="D98" s="277"/>
+      <c r="E98" s="278"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="225"/>
-      <c r="B99" s="253"/>
-      <c r="C99" s="253"/>
-      <c r="D99" s="253"/>
-      <c r="E99" s="226"/>
+      <c r="A99" s="279"/>
+      <c r="B99" s="280"/>
+      <c r="C99" s="280"/>
+      <c r="D99" s="280"/>
+      <c r="E99" s="281"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8200,42 +8145,42 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="242" t="s">
-        <v>250</v>
-      </c>
-      <c r="B101" s="243"/>
-      <c r="C101" s="243"/>
-      <c r="D101" s="243"/>
-      <c r="E101" s="243"/>
-      <c r="F101" s="243"/>
-      <c r="G101" s="243"/>
-      <c r="H101" s="243"/>
-      <c r="I101" s="243"/>
-      <c r="J101" s="244"/>
+      <c r="A101" s="244" t="s">
+        <v>229</v>
+      </c>
+      <c r="B101" s="270"/>
+      <c r="C101" s="270"/>
+      <c r="D101" s="270"/>
+      <c r="E101" s="270"/>
+      <c r="F101" s="270"/>
+      <c r="G101" s="270"/>
+      <c r="H101" s="270"/>
+      <c r="I101" s="270"/>
+      <c r="J101" s="245"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B102" s="90" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="C102" s="77" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="D102" s="84"/>
       <c r="E102" s="89" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F102" s="90">
         <v>500</v>
       </c>
       <c r="G102" s="129" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="219"/>
-      <c r="J102" s="220"/>
+      <c r="I102" s="300"/>
+      <c r="J102" s="301"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8247,107 +8192,107 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="221"/>
-      <c r="E103" s="222"/>
-      <c r="F103" s="222"/>
-      <c r="G103" s="223" t="s">
-        <v>254</v>
-      </c>
-      <c r="H103" s="224"/>
-      <c r="I103" s="227" t="s">
-        <v>255</v>
-      </c>
-      <c r="J103" s="228"/>
-      <c r="K103" s="231" t="s">
-        <v>60</v>
-      </c>
-      <c r="L103" s="232"/>
+      <c r="D103" s="302"/>
+      <c r="E103" s="178"/>
+      <c r="F103" s="178"/>
+      <c r="G103" s="303" t="s">
+        <v>233</v>
+      </c>
+      <c r="H103" s="304"/>
+      <c r="I103" s="305" t="s">
+        <v>234</v>
+      </c>
+      <c r="J103" s="306"/>
+      <c r="K103" s="307" t="s">
+        <v>39</v>
+      </c>
+      <c r="L103" s="308"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="235" t="s">
-        <v>117</v>
+      <c r="A104" s="311" t="s">
+        <v>96</v>
       </c>
       <c r="B104" s="134" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C104" s="135" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="D104" s="135" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="E104" s="136" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="F104" s="135" t="s">
-        <v>260</v>
-      </c>
-      <c r="G104" s="225"/>
-      <c r="H104" s="226"/>
-      <c r="I104" s="229"/>
+        <v>239</v>
+      </c>
+      <c r="G104" s="279"/>
+      <c r="H104" s="281"/>
+      <c r="I104" s="228"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="233"/>
-      <c r="L104" s="234"/>
+      <c r="K104" s="309"/>
+      <c r="L104" s="310"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="194"/>
+      <c r="A105" s="312"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
       <c r="E105" s="140"/>
       <c r="F105" s="141" t="s">
-        <v>149</v>
-      </c>
-      <c r="G105" s="236">
+        <v>128</v>
+      </c>
+      <c r="G105" s="313">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="237"/>
-      <c r="I105" s="238">
+      <c r="H105" s="314"/>
+      <c r="I105" s="315">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="239"/>
-      <c r="K105" s="240" t="str">
+      <c r="J105" s="316"/>
+      <c r="K105" s="317" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="241"/>
+      <c r="L105" s="318"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="210" t="s">
-        <v>261</v>
-      </c>
-      <c r="B106" s="211"/>
-      <c r="C106" s="211"/>
-      <c r="D106" s="211"/>
-      <c r="E106" s="211"/>
-      <c r="F106" s="211"/>
-      <c r="G106" s="211"/>
-      <c r="H106" s="211"/>
-      <c r="I106" s="211"/>
-      <c r="J106" s="211"/>
-      <c r="K106" s="211"/>
-      <c r="L106" s="212"/>
+      <c r="A106" s="220" t="s">
+        <v>240</v>
+      </c>
+      <c r="B106" s="221"/>
+      <c r="C106" s="221"/>
+      <c r="D106" s="221"/>
+      <c r="E106" s="221"/>
+      <c r="F106" s="221"/>
+      <c r="G106" s="221"/>
+      <c r="H106" s="221"/>
+      <c r="I106" s="221"/>
+      <c r="J106" s="221"/>
+      <c r="K106" s="221"/>
+      <c r="L106" s="222"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="117" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B110" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8377,49 +8322,49 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="213" t="s">
-        <v>108</v>
-      </c>
-      <c r="B113" s="214"/>
-      <c r="C113" s="214"/>
-      <c r="D113" s="214"/>
-      <c r="E113" s="214" t="s">
-        <v>265</v>
-      </c>
-      <c r="F113" s="214"/>
-      <c r="G113" s="214" t="s">
-        <v>266</v>
-      </c>
-      <c r="H113" s="214" t="s">
-        <v>60</v>
-      </c>
-      <c r="I113" s="217" t="s">
-        <v>267</v>
+      <c r="A113" s="295" t="s">
+        <v>87</v>
+      </c>
+      <c r="B113" s="296"/>
+      <c r="C113" s="296"/>
+      <c r="D113" s="296"/>
+      <c r="E113" s="296" t="s">
+        <v>244</v>
+      </c>
+      <c r="F113" s="296"/>
+      <c r="G113" s="296" t="s">
+        <v>245</v>
+      </c>
+      <c r="H113" s="296" t="s">
+        <v>39</v>
+      </c>
+      <c r="I113" s="298" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="215"/>
-      <c r="B114" s="216"/>
-      <c r="C114" s="216"/>
-      <c r="D114" s="216"/>
-      <c r="E114" s="216"/>
-      <c r="F114" s="216"/>
-      <c r="G114" s="216"/>
-      <c r="H114" s="216"/>
-      <c r="I114" s="218"/>
+      <c r="A114" s="297"/>
+      <c r="B114" s="188"/>
+      <c r="C114" s="188"/>
+      <c r="D114" s="188"/>
+      <c r="E114" s="188"/>
+      <c r="F114" s="188"/>
+      <c r="G114" s="188"/>
+      <c r="H114" s="188"/>
+      <c r="I114" s="299"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="205" t="s">
-        <v>268</v>
-      </c>
-      <c r="B115" s="206"/>
-      <c r="C115" s="206"/>
-      <c r="D115" s="206"/>
+      <c r="A115" s="326" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="327"/>
+      <c r="C115" s="327"/>
+      <c r="D115" s="327"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
       <c r="F115" s="145" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G115" s="146">
         <f>ROUND((E115*D111)/(60*B111),3)</f>
@@ -8429,22 +8374,22 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="207" t="s">
-        <v>269</v>
+      <c r="I115" s="328" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="201" t="s">
-        <v>270</v>
-      </c>
-      <c r="B116" s="202"/>
-      <c r="C116" s="202"/>
-      <c r="D116" s="202"/>
+      <c r="A116" s="322" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" s="323"/>
+      <c r="C116" s="323"/>
+      <c r="D116" s="323"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G116" s="45">
         <f>ROUND((E116*D111)/(60*B111),3)</f>
@@ -8454,20 +8399,20 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="208"/>
+      <c r="I116" s="329"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="201" t="s">
-        <v>271</v>
-      </c>
-      <c r="B117" s="202"/>
-      <c r="C117" s="202"/>
-      <c r="D117" s="202"/>
+      <c r="A117" s="322" t="s">
+        <v>250</v>
+      </c>
+      <c r="B117" s="323"/>
+      <c r="C117" s="323"/>
+      <c r="D117" s="323"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G117" s="45">
         <f>ROUND((E117*D111)/(60*B111),3)</f>
@@ -8477,20 +8422,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="208"/>
+      <c r="I117" s="329"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="201" t="s">
-        <v>272</v>
-      </c>
-      <c r="B118" s="202"/>
-      <c r="C118" s="202"/>
-      <c r="D118" s="202"/>
+      <c r="A118" s="322" t="s">
+        <v>251</v>
+      </c>
+      <c r="B118" s="323"/>
+      <c r="C118" s="323"/>
+      <c r="D118" s="323"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G118" s="45">
         <f>ROUND((E118*D111)/(60*B111),3)</f>
@@ -8500,20 +8445,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="208"/>
+      <c r="I118" s="329"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="203" t="s">
-        <v>273</v>
-      </c>
-      <c r="B119" s="204"/>
-      <c r="C119" s="204"/>
-      <c r="D119" s="204"/>
+      <c r="A119" s="324" t="s">
+        <v>252</v>
+      </c>
+      <c r="B119" s="325"/>
+      <c r="C119" s="325"/>
+      <c r="D119" s="325"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="F119" s="151" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G119" s="152">
         <f>ROUND((E119*D111)/(60*B111),3)</f>
@@ -8523,20 +8468,20 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="209"/>
+      <c r="I119" s="330"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="196" t="s">
-        <v>274</v>
-      </c>
-      <c r="B120" s="197"/>
-      <c r="C120" s="197"/>
-      <c r="D120" s="197"/>
+      <c r="A120" s="345" t="s">
+        <v>253</v>
+      </c>
+      <c r="B120" s="346"/>
+      <c r="C120" s="346"/>
+      <c r="D120" s="346"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
       <c r="F120" s="155" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G120" s="156">
         <f>ROUND((E120*D111)/(60*B111),3)</f>
@@ -8546,22 +8491,22 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="198" t="s">
-        <v>275</v>
+      <c r="I120" s="319" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="201" t="s">
-        <v>276</v>
-      </c>
-      <c r="B121" s="202"/>
-      <c r="C121" s="202"/>
-      <c r="D121" s="202"/>
+      <c r="A121" s="322" t="s">
+        <v>255</v>
+      </c>
+      <c r="B121" s="323"/>
+      <c r="C121" s="323"/>
+      <c r="D121" s="323"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G121" s="45">
         <f>ROUND((E121*D111)/(60*B111),3)</f>
@@ -8571,20 +8516,20 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="199"/>
+      <c r="I121" s="320"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="201" t="s">
-        <v>277</v>
-      </c>
-      <c r="B122" s="202"/>
-      <c r="C122" s="202"/>
-      <c r="D122" s="202"/>
+      <c r="A122" s="322" t="s">
+        <v>256</v>
+      </c>
+      <c r="B122" s="323"/>
+      <c r="C122" s="323"/>
+      <c r="D122" s="323"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G122" s="45">
         <f>ROUND((E122*D111)/(60*B111),3)</f>
@@ -8594,20 +8539,20 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="199"/>
+      <c r="I122" s="320"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="201" t="s">
-        <v>278</v>
-      </c>
-      <c r="B123" s="202"/>
-      <c r="C123" s="202"/>
-      <c r="D123" s="202"/>
+      <c r="A123" s="322" t="s">
+        <v>257</v>
+      </c>
+      <c r="B123" s="323"/>
+      <c r="C123" s="323"/>
+      <c r="D123" s="323"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G123" s="45">
         <f>ROUND((E123*D111)/(60*B111),3)</f>
@@ -8617,26 +8562,26 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="199"/>
+      <c r="I123" s="320"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="203" t="s">
-        <v>279</v>
-      </c>
-      <c r="B124" s="204"/>
-      <c r="C124" s="204"/>
-      <c r="D124" s="204"/>
+      <c r="A124" s="324" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="325"/>
+      <c r="C124" s="325"/>
+      <c r="D124" s="325"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G124" s="152" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="H124" s="153" t="s">
-        <v>280</v>
-      </c>
-      <c r="I124" s="200"/>
+        <v>259</v>
+      </c>
+      <c r="I124" s="321"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8644,10 +8589,10 @@
     </row>
     <row r="126" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="158" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="C126" s="159" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="D126" s="160"/>
       <c r="E126" s="160"/>
@@ -8657,15 +8602,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="180" t="s">
-        <v>283</v>
-      </c>
-      <c r="B127" s="181"/>
-      <c r="C127" s="181"/>
-      <c r="D127" s="181"/>
-      <c r="E127" s="181"/>
-      <c r="F127" s="181"/>
-      <c r="G127" s="182"/>
+      <c r="A127" s="223" t="s">
+        <v>262</v>
+      </c>
+      <c r="B127" s="266"/>
+      <c r="C127" s="266"/>
+      <c r="D127" s="266"/>
+      <c r="E127" s="266"/>
+      <c r="F127" s="266"/>
+      <c r="G127" s="262"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8677,19 +8622,19 @@
     </row>
     <row r="128" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="99" t="s">
-        <v>284</v>
-      </c>
-      <c r="B128" s="183" t="s">
-        <v>285</v>
-      </c>
-      <c r="C128" s="184"/>
-      <c r="D128" s="184"/>
-      <c r="E128" s="185"/>
+        <v>263</v>
+      </c>
+      <c r="B128" s="194" t="s">
+        <v>264</v>
+      </c>
+      <c r="C128" s="195"/>
+      <c r="D128" s="195"/>
+      <c r="E128" s="196"/>
       <c r="F128" s="162" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="G128" s="163" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="H128" s="88"/>
       <c r="I128" s="88"/>
@@ -8705,11 +8650,11 @@
         <v>15</v>
       </c>
       <c r="B129" s="47" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="C129" s="105"/>
       <c r="D129" s="164" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="E129" s="105"/>
       <c r="F129" s="47" t="e">
@@ -8740,11 +8685,11 @@
         <v>15</v>
       </c>
       <c r="B130" s="102" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="C130" s="114"/>
       <c r="D130" s="165" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="E130" s="114"/>
       <c r="F130" s="102" t="e">
@@ -8771,15 +8716,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="186" t="s">
-        <v>291</v>
-      </c>
-      <c r="B131" s="176"/>
-      <c r="C131" s="176"/>
-      <c r="D131" s="176"/>
-      <c r="E131" s="176"/>
-      <c r="F131" s="176"/>
-      <c r="G131" s="177"/>
+      <c r="A131" s="336" t="s">
+        <v>270</v>
+      </c>
+      <c r="B131" s="332"/>
+      <c r="C131" s="332"/>
+      <c r="D131" s="332"/>
+      <c r="E131" s="332"/>
+      <c r="F131" s="332"/>
+      <c r="G131" s="333"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8790,15 +8735,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="187" t="s">
-        <v>292</v>
-      </c>
-      <c r="B132" s="188"/>
-      <c r="C132" s="188"/>
-      <c r="D132" s="188"/>
-      <c r="E132" s="188"/>
-      <c r="F132" s="188"/>
-      <c r="G132" s="189"/>
+      <c r="A132" s="337" t="s">
+        <v>271</v>
+      </c>
+      <c r="B132" s="338"/>
+      <c r="C132" s="338"/>
+      <c r="D132" s="338"/>
+      <c r="E132" s="338"/>
+      <c r="F132" s="338"/>
+      <c r="G132" s="339"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8809,13 +8754,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="190"/>
-      <c r="B133" s="191"/>
-      <c r="C133" s="191"/>
-      <c r="D133" s="191"/>
-      <c r="E133" s="191"/>
-      <c r="F133" s="191"/>
-      <c r="G133" s="192"/>
+      <c r="A133" s="340"/>
+      <c r="B133" s="341"/>
+      <c r="C133" s="341"/>
+      <c r="D133" s="341"/>
+      <c r="E133" s="341"/>
+      <c r="F133" s="341"/>
+      <c r="G133" s="342"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8837,7 +8782,7 @@
     </row>
     <row r="135" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="166" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B135" s="129"/>
       <c r="C135" s="129"/>
@@ -8845,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="168" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="F135" s="169" t="str">
         <f>IF(D135&lt;=5,"Pass","Fail")</f>
@@ -8881,7 +8826,7 @@
     </row>
     <row r="138" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="44" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="H138" s="98"/>
       <c r="I138" s="98"/>
@@ -8922,7 +8867,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="193" t="s">
+      <c r="A140" s="343" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8953,7 +8898,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="194"/>
+      <c r="A141" s="312"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8989,8 +8934,8 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="195" t="s">
-        <v>296</v>
+      <c r="B142" s="344" t="s">
+        <v>275</v>
       </c>
       <c r="C142" s="173">
         <f>C139-C141</f>
@@ -9023,7 +8968,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="195"/>
+      <c r="B143" s="344"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -9054,26 +8999,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="175" t="s">
-        <v>297</v>
-      </c>
-      <c r="B144" s="176"/>
-      <c r="C144" s="176"/>
-      <c r="D144" s="176"/>
-      <c r="E144" s="176"/>
-      <c r="F144" s="176"/>
-      <c r="G144" s="177"/>
+      <c r="A144" s="331" t="s">
+        <v>276</v>
+      </c>
+      <c r="B144" s="332"/>
+      <c r="C144" s="332"/>
+      <c r="D144" s="332"/>
+      <c r="E144" s="332"/>
+      <c r="F144" s="332"/>
+      <c r="G144" s="333"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="175" t="s">
-        <v>298</v>
-      </c>
-      <c r="B145" s="178"/>
-      <c r="C145" s="178"/>
-      <c r="D145" s="178"/>
-      <c r="E145" s="178"/>
-      <c r="F145" s="178"/>
-      <c r="G145" s="179"/>
+      <c r="A145" s="331" t="s">
+        <v>277</v>
+      </c>
+      <c r="B145" s="334"/>
+      <c r="C145" s="334"/>
+      <c r="D145" s="334"/>
+      <c r="E145" s="334"/>
+      <c r="F145" s="334"/>
+      <c r="G145" s="335"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9089,107 +9034,26 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9205,26 +9069,107 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C142:G142">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142B24A8-CAB7-4527-88D4-6EE240A12013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED6AA3-2B6F-4A58-87D1-12226F984847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2465,521 +2465,521 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3101,14 +3101,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3123,13 +3123,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3165,6 +3158,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3227,6 +3227,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -3242,13 +3249,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4957,7 +4957,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M2 A6:M7 C4:H4 J4:M4 E3:M3 A14:M15 A67:M82 A8 C8:M8 A51:M63 J45 A45:C46 J46:M46 L45:M45 A42:M44 C41:D41 F41:M41 A27:M40 G23:M23 A25:C25 F24:M25 E12:M12 E11:M11 E9:M9 E10:M10 A20:M22 H17:M17 H18:M18 H19:M19 B16 H16:M16 C5:M5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M2 A6:M7 C4:H4 J4:M4 E3:M3 A14:M15 A67:M80 A8 C8:M8 A51:M63 J45 A45:C46 J46:M46 L45:M45 A42:M44 C41:D41 F41:M41 A27:M40 G23:M23 A25:C25 F24:M25 E12:M12 E11:M11 E9:M9 E10:M10 A20:M22 H17:M17 H18:M18 H19:M19 B16 H16:M16 C5:M5 A82:M82 A81:B81 D81:M81" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4989,38 +4989,38 @@
       <c r="A1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="175" t="s">
+      <c r="B1" s="342" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
+      <c r="H1" s="342"/>
+      <c r="I1" s="342"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="342" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5030,16 +5030,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="175" t="s">
+      <c r="B3" s="342" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
+      <c r="H3" s="342"/>
+      <c r="I3" s="342"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5051,14 +5051,14 @@
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5070,20 +5070,20 @@
       <c r="A5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="175" t="s">
+      <c r="B5" s="342" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
       <c r="F5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="176">
+      <c r="G5" s="345">
         <v>22.7</v>
       </c>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5095,20 +5095,20 @@
       <c r="A6" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="342" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="175"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
+      <c r="C6" s="342"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
       <c r="F6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="176">
+      <c r="G6" s="345">
         <v>50.2</v>
       </c>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5120,20 +5120,20 @@
       <c r="A7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="175" t="s">
+      <c r="B7" s="342" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
       <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="175" t="s">
+      <c r="G7" s="342" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5144,16 +5144,16 @@
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="191">
+      <c r="B8" s="341">
         <v>46066</v>
       </c>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
+      <c r="C8" s="342"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="G8" s="342"/>
+      <c r="H8" s="342"/>
+      <c r="I8" s="342"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5162,14 +5162,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5180,16 +5180,16 @@
       <c r="A10" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="192" t="s">
+      <c r="B10" s="343" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="192"/>
-      <c r="H10" s="192"/>
-      <c r="I10" s="193"/>
+      <c r="C10" s="343"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="344"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5197,35 +5197,35 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="183" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="195"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="195" t="s">
+      <c r="B11" s="184"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="184" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="196"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="179" t="s">
+      <c r="P11" s="331" t="s">
         <v>158</v>
       </c>
-      <c r="Q11" s="180"/>
-      <c r="R11" s="180"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="180"/>
-      <c r="U11" s="180"/>
-      <c r="V11" s="180"/>
-      <c r="W11" s="180"/>
-      <c r="X11" s="181"/>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
+      <c r="V11" s="332"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
@@ -5264,23 +5264,23 @@
       <c r="N12" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P12" s="182" t="s">
+      <c r="P12" s="334" t="s">
         <v>166</v>
       </c>
-      <c r="Q12" s="184" t="s">
+      <c r="Q12" s="336" t="s">
         <v>167</v>
       </c>
-      <c r="R12" s="184"/>
-      <c r="S12" s="184"/>
-      <c r="T12" s="185" t="s">
+      <c r="R12" s="336"/>
+      <c r="S12" s="336"/>
+      <c r="T12" s="337" t="s">
         <v>168</v>
       </c>
-      <c r="U12" s="187" t="s">
+      <c r="U12" s="305" t="s">
         <v>169</v>
       </c>
-      <c r="V12" s="185"/>
+      <c r="V12" s="337"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="189" t="s">
+      <c r="X12" s="339" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="183"/>
+      <c r="P13" s="335"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5333,11 +5333,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="186"/>
-      <c r="U13" s="188"/>
-      <c r="V13" s="186"/>
+      <c r="T13" s="338"/>
+      <c r="U13" s="216"/>
+      <c r="V13" s="338"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="190"/>
+      <c r="X13" s="340"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5649,15 +5649,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="206" t="s">
+      <c r="P18" s="325" t="s">
         <v>174</v>
       </c>
-      <c r="Q18" s="207"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
-      <c r="T18" s="207"/>
-      <c r="U18" s="207"/>
-      <c r="V18" s="208"/>
+      <c r="Q18" s="326"/>
+      <c r="R18" s="326"/>
+      <c r="S18" s="326"/>
+      <c r="T18" s="326"/>
+      <c r="U18" s="326"/>
+      <c r="V18" s="327"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5697,13 +5697,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="209"/>
-      <c r="Q19" s="209"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
+      <c r="P19" s="289"/>
+      <c r="Q19" s="289"/>
+      <c r="R19" s="289"/>
+      <c r="S19" s="289"/>
+      <c r="T19" s="289"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5741,14 +5741,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="210" t="s">
+      <c r="P20" s="310" t="s">
         <v>175</v>
       </c>
-      <c r="Q20" s="211"/>
-      <c r="R20" s="211"/>
-      <c r="S20" s="211"/>
-      <c r="T20" s="211"/>
-      <c r="U20" s="212"/>
+      <c r="Q20" s="311"/>
+      <c r="R20" s="311"/>
+      <c r="S20" s="311"/>
+      <c r="T20" s="311"/>
+      <c r="U20" s="313"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5786,14 +5786,14 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="213" t="s">
+      <c r="P21" s="328" t="s">
         <v>176</v>
       </c>
-      <c r="Q21" s="214"/>
-      <c r="R21" s="215" t="s">
+      <c r="Q21" s="329"/>
+      <c r="R21" s="330" t="s">
         <v>177</v>
       </c>
-      <c r="S21" s="214"/>
+      <c r="S21" s="329"/>
       <c r="T21" s="14" t="s">
         <v>178</v>
       </c>
@@ -5840,16 +5840,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="197">
+      <c r="P22" s="316">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="198"/>
-      <c r="R22" s="199">
+      <c r="Q22" s="317"/>
+      <c r="R22" s="318">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="199"/>
+      <c r="S22" s="318"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5895,16 +5895,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="197">
+      <c r="P23" s="316">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="198"/>
-      <c r="R23" s="199">
+      <c r="Q23" s="317"/>
+      <c r="R23" s="318">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="199"/>
+      <c r="S23" s="318"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -5950,16 +5950,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="197">
+      <c r="P24" s="316">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="198"/>
-      <c r="R24" s="199">
+      <c r="Q24" s="317"/>
+      <c r="R24" s="318">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="199"/>
+      <c r="S24" s="318"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -6005,14 +6005,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="200" t="s">
+      <c r="P25" s="319" t="s">
         <v>180</v>
       </c>
-      <c r="Q25" s="201"/>
-      <c r="R25" s="201"/>
-      <c r="S25" s="201"/>
-      <c r="T25" s="201"/>
-      <c r="U25" s="202"/>
+      <c r="Q25" s="320"/>
+      <c r="R25" s="320"/>
+      <c r="S25" s="320"/>
+      <c r="T25" s="320"/>
+      <c r="U25" s="321"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6087,11 +6087,11 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="203" t="s">
+      <c r="P27" s="322" t="s">
         <v>181</v>
       </c>
-      <c r="Q27" s="204"/>
-      <c r="R27" s="205"/>
+      <c r="Q27" s="323"/>
+      <c r="R27" s="324"/>
       <c r="S27" s="47" t="s">
         <v>159</v>
       </c>
@@ -6148,11 +6148,11 @@
       <c r="P28" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="Q28" s="187" t="s">
+      <c r="Q28" s="305" t="s">
         <v>184</v>
       </c>
-      <c r="R28" s="187"/>
-      <c r="S28" s="187"/>
+      <c r="R28" s="305"/>
+      <c r="S28" s="305"/>
       <c r="T28" s="14" t="s">
         <v>185</v>
       </c>
@@ -6224,13 +6224,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="237">
+      <c r="U29" s="306">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="239" t="str">
+      <c r="X29" s="308" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6291,10 +6291,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="237"/>
+      <c r="U30" s="306"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="239"/>
+      <c r="X30" s="308"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6352,10 +6352,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="237"/>
+      <c r="U31" s="306"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="239"/>
+      <c r="X31" s="308"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6413,10 +6413,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="238"/>
+      <c r="U32" s="307"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="240"/>
+      <c r="X32" s="309"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6454,17 +6454,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="220" t="s">
+      <c r="P33" s="210" t="s">
         <v>187</v>
       </c>
-      <c r="Q33" s="221"/>
-      <c r="R33" s="221"/>
-      <c r="S33" s="221"/>
-      <c r="T33" s="221"/>
-      <c r="U33" s="221"/>
-      <c r="V33" s="221"/>
-      <c r="W33" s="221"/>
-      <c r="X33" s="222"/>
+      <c r="Q33" s="211"/>
+      <c r="R33" s="211"/>
+      <c r="S33" s="211"/>
+      <c r="T33" s="211"/>
+      <c r="U33" s="211"/>
+      <c r="V33" s="211"/>
+      <c r="W33" s="211"/>
+      <c r="X33" s="212"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6539,18 +6539,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="210" t="s">
+      <c r="P35" s="310" t="s">
         <v>188</v>
       </c>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
-      <c r="U35" s="211"/>
-      <c r="V35" s="241"/>
-      <c r="W35" s="241"/>
-      <c r="X35" s="241"/>
-      <c r="Y35" s="212"/>
+      <c r="Q35" s="311"/>
+      <c r="R35" s="311"/>
+      <c r="S35" s="311"/>
+      <c r="T35" s="311"/>
+      <c r="U35" s="311"/>
+      <c r="V35" s="312"/>
+      <c r="W35" s="312"/>
+      <c r="X35" s="312"/>
+      <c r="Y35" s="313"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6591,13 +6591,13 @@
       <c r="P36" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="Q36" s="242" t="s">
+      <c r="Q36" s="314" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="242"/>
-      <c r="S36" s="242"/>
-      <c r="T36" s="242"/>
-      <c r="U36" s="243"/>
+      <c r="R36" s="314"/>
+      <c r="S36" s="314"/>
+      <c r="T36" s="314"/>
+      <c r="U36" s="315"/>
       <c r="V36" s="18" t="s">
         <v>189</v>
       </c>
@@ -6955,18 +6955,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="220" t="s">
+      <c r="P41" s="210" t="s">
         <v>191</v>
       </c>
-      <c r="Q41" s="221"/>
-      <c r="R41" s="221"/>
-      <c r="S41" s="221"/>
-      <c r="T41" s="221"/>
-      <c r="U41" s="221"/>
-      <c r="V41" s="221"/>
-      <c r="W41" s="221"/>
-      <c r="X41" s="221"/>
-      <c r="Y41" s="222"/>
+      <c r="Q41" s="211"/>
+      <c r="R41" s="211"/>
+      <c r="S41" s="211"/>
+      <c r="T41" s="211"/>
+      <c r="U41" s="211"/>
+      <c r="V41" s="211"/>
+      <c r="W41" s="211"/>
+      <c r="X41" s="211"/>
+      <c r="Y41" s="212"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -7044,10 +7044,10 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="223" t="s">
+      <c r="P43" s="180" t="s">
         <v>192</v>
       </c>
-      <c r="Q43" s="224"/>
+      <c r="Q43" s="296"/>
       <c r="R43" s="72" t="s">
         <v>164</v>
       </c>
@@ -7143,12 +7143,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="225" t="s">
+      <c r="P45" s="297" t="s">
         <v>193</v>
       </c>
-      <c r="Q45" s="226"/>
-      <c r="R45" s="226"/>
-      <c r="S45" s="227"/>
+      <c r="Q45" s="298"/>
+      <c r="R45" s="298"/>
+      <c r="S45" s="299"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7186,10 +7186,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="225"/>
-      <c r="Q46" s="226"/>
-      <c r="R46" s="226"/>
-      <c r="S46" s="227"/>
+      <c r="P46" s="297"/>
+      <c r="Q46" s="298"/>
+      <c r="R46" s="298"/>
+      <c r="S46" s="299"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7227,9 +7227,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="228"/>
-      <c r="Q47" s="229"/>
-      <c r="R47" s="229"/>
+      <c r="P47" s="229"/>
+      <c r="Q47" s="300"/>
+      <c r="R47" s="300"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7444,17 +7444,17 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="231" t="s">
+      <c r="A57" s="301" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="232"/>
-      <c r="C57" s="232"/>
-      <c r="D57" s="232"/>
-      <c r="E57" s="232"/>
-      <c r="F57" s="232"/>
-      <c r="G57" s="232"/>
-      <c r="H57" s="232"/>
-      <c r="I57" s="233"/>
+      <c r="B57" s="302"/>
+      <c r="C57" s="302"/>
+      <c r="D57" s="302"/>
+      <c r="E57" s="302"/>
+      <c r="F57" s="302"/>
+      <c r="G57" s="302"/>
+      <c r="H57" s="302"/>
+      <c r="I57" s="303"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -7496,10 +7496,10 @@
       <c r="G59" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H59" s="234" t="s">
+      <c r="H59" s="291" t="s">
         <v>205</v>
       </c>
-      <c r="I59" s="235"/>
+      <c r="I59" s="292"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7518,30 +7518,30 @@
       <c r="F60" t="s">
         <v>60</v>
       </c>
-      <c r="H60" s="236">
+      <c r="H60" s="304">
         <v>18.12</v>
       </c>
-      <c r="I60" s="236"/>
+      <c r="I60" s="304"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
         <v>62</v>
       </c>
-      <c r="H61" s="248">
+      <c r="H61" s="287">
         <v>19.98</v>
       </c>
-      <c r="I61" s="248"/>
+      <c r="I61" s="287"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
         <v>65</v>
       </c>
-      <c r="H62" s="248">
+      <c r="H62" s="287">
         <v>18.7</v>
       </c>
-      <c r="I62" s="248"/>
+      <c r="I62" s="287"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
@@ -7550,10 +7550,10 @@
       <c r="F63" t="s">
         <v>207</v>
       </c>
-      <c r="H63" s="248">
+      <c r="H63" s="287">
         <v>17.62</v>
       </c>
-      <c r="I63" s="248"/>
+      <c r="I63" s="287"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
@@ -7562,27 +7562,27 @@
       <c r="F64" t="s">
         <v>208</v>
       </c>
-      <c r="H64" s="249">
+      <c r="H64" s="290">
         <v>18.79</v>
       </c>
-      <c r="I64" s="249"/>
+      <c r="I64" s="290"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="216" t="s">
+      <c r="B65" s="277" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="217"/>
+      <c r="C65" s="278"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="218">
+      <c r="H65" s="294">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="219"/>
+      <c r="I65" s="295"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7597,11 +7597,11 @@
       <c r="G66" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="244" t="str">
+      <c r="H66" s="242" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="245"/>
+      <c r="I66" s="244"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7662,14 +7662,14 @@
       <c r="G69" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H69" s="234" t="s">
+      <c r="H69" s="291" t="s">
         <v>205</v>
       </c>
-      <c r="I69" s="235"/>
-      <c r="P69" s="246"/>
-      <c r="Q69" s="246"/>
-      <c r="R69" s="209"/>
-      <c r="S69" s="209"/>
+      <c r="I69" s="292"/>
+      <c r="P69" s="288"/>
+      <c r="Q69" s="288"/>
+      <c r="R69" s="289"/>
+      <c r="S69" s="289"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7688,68 +7688,68 @@
       <c r="F70" t="s">
         <v>60</v>
       </c>
-      <c r="H70" s="247">
+      <c r="H70" s="293">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="247"/>
-      <c r="P70" s="246"/>
-      <c r="Q70" s="246"/>
-      <c r="R70" s="209"/>
-      <c r="S70" s="209"/>
+      <c r="I70" s="293"/>
+      <c r="P70" s="288"/>
+      <c r="Q70" s="288"/>
+      <c r="R70" s="289"/>
+      <c r="S70" s="289"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" s="248">
+      <c r="H71" s="287">
         <v>11.78</v>
       </c>
-      <c r="I71" s="248"/>
-      <c r="P71" s="246"/>
-      <c r="Q71" s="246"/>
-      <c r="R71" s="209"/>
-      <c r="S71" s="209"/>
+      <c r="I71" s="287"/>
+      <c r="P71" s="288"/>
+      <c r="Q71" s="288"/>
+      <c r="R71" s="289"/>
+      <c r="S71" s="289"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
         <v>65</v>
       </c>
-      <c r="H72" s="248">
+      <c r="H72" s="287">
         <v>12.39</v>
       </c>
-      <c r="I72" s="248"/>
-      <c r="P72" s="246"/>
-      <c r="Q72" s="246"/>
-      <c r="R72" s="209"/>
-      <c r="S72" s="209"/>
+      <c r="I72" s="287"/>
+      <c r="P72" s="288"/>
+      <c r="Q72" s="288"/>
+      <c r="R72" s="289"/>
+      <c r="S72" s="289"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
         <v>207</v>
       </c>
-      <c r="H73" s="248">
+      <c r="H73" s="287">
         <v>11.21</v>
       </c>
-      <c r="I73" s="248"/>
+      <c r="I73" s="287"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="246"/>
-      <c r="Q73" s="246"/>
-      <c r="R73" s="209"/>
-      <c r="S73" s="209"/>
+      <c r="P73" s="288"/>
+      <c r="Q73" s="288"/>
+      <c r="R73" s="289"/>
+      <c r="S73" s="289"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
         <v>208</v>
       </c>
-      <c r="H74" s="249">
+      <c r="H74" s="290">
         <v>12.75</v>
       </c>
-      <c r="I74" s="249"/>
+      <c r="I74" s="290"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7758,28 +7758,28 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="246"/>
-      <c r="Q74" s="246"/>
-      <c r="R74" s="209"/>
-      <c r="S74" s="209"/>
+      <c r="P74" s="288"/>
+      <c r="Q74" s="288"/>
+      <c r="R74" s="289"/>
+      <c r="S74" s="289"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="216" t="s">
+      <c r="B75" s="277" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="217"/>
+      <c r="C75" s="278"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="260">
+      <c r="H75" s="279">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="261"/>
+      <c r="I75" s="280"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
@@ -7787,24 +7787,24 @@
       <c r="G76" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H76" s="223" t="str">
+      <c r="H76" s="180" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="262"/>
+      <c r="I76" s="182"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="263" t="s">
+      <c r="A77" s="281" t="s">
         <v>212</v>
       </c>
-      <c r="B77" s="264"/>
-      <c r="C77" s="264"/>
-      <c r="D77" s="264"/>
-      <c r="E77" s="264"/>
-      <c r="F77" s="264"/>
-      <c r="G77" s="264"/>
-      <c r="H77" s="264"/>
-      <c r="I77" s="265"/>
+      <c r="B77" s="282"/>
+      <c r="C77" s="282"/>
+      <c r="D77" s="282"/>
+      <c r="E77" s="282"/>
+      <c r="F77" s="282"/>
+      <c r="G77" s="282"/>
+      <c r="H77" s="282"/>
+      <c r="I77" s="283"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7817,11 +7817,11 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="223" t="s">
+      <c r="A80" s="180" t="s">
         <v>213</v>
       </c>
-      <c r="B80" s="266"/>
-      <c r="C80" s="266"/>
+      <c r="B80" s="181"/>
+      <c r="C80" s="181"/>
       <c r="D80" s="47" t="s">
         <v>214</v>
       </c>
@@ -7838,10 +7838,10 @@
       <c r="A81" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="267" t="s">
+      <c r="B81" s="284" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="268"/>
+      <c r="C81" s="285"/>
       <c r="D81" s="102" t="s">
         <v>216</v>
       </c>
@@ -7850,8 +7850,8 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="269"/>
-      <c r="I81" s="269"/>
+      <c r="H81" s="286"/>
+      <c r="I81" s="286"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7859,11 +7859,11 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="250">
+      <c r="B82" s="268">
         <v>15</v>
       </c>
-      <c r="C82" s="250"/>
-      <c r="D82" s="251" t="s">
+      <c r="C82" s="268"/>
+      <c r="D82" s="269" t="s">
         <v>217</v>
       </c>
       <c r="E82" s="106"/>
@@ -7881,11 +7881,11 @@
       <c r="A83" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="B83" s="254" t="s">
+      <c r="B83" s="272" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="255"/>
-      <c r="D83" s="252"/>
+      <c r="C83" s="263"/>
+      <c r="D83" s="270"/>
       <c r="E83" s="46" t="s">
         <v>221</v>
       </c>
@@ -7906,11 +7906,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="256">
+      <c r="B84" s="273">
         <v>2.8</v>
       </c>
-      <c r="C84" s="256"/>
-      <c r="D84" s="252"/>
+      <c r="C84" s="273"/>
+      <c r="D84" s="270"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7936,11 +7936,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="257">
+      <c r="B85" s="274">
         <v>5</v>
       </c>
-      <c r="C85" s="258"/>
-      <c r="D85" s="252"/>
+      <c r="C85" s="275"/>
+      <c r="D85" s="270"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -7962,11 +7962,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="259">
+      <c r="B86" s="276">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="259"/>
-      <c r="D86" s="253"/>
+      <c r="C86" s="276"/>
+      <c r="D86" s="271"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -7985,14 +7985,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="282" t="s">
+      <c r="A87" s="254" t="s">
         <v>223</v>
       </c>
-      <c r="B87" s="283"/>
-      <c r="C87" s="283"/>
-      <c r="D87" s="283"/>
-      <c r="E87" s="283"/>
-      <c r="F87" s="284"/>
+      <c r="B87" s="255"/>
+      <c r="C87" s="255"/>
+      <c r="D87" s="255"/>
+      <c r="E87" s="255"/>
+      <c r="F87" s="256"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -8000,12 +8000,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="285"/>
-      <c r="B88" s="286"/>
-      <c r="C88" s="286"/>
-      <c r="D88" s="286"/>
-      <c r="E88" s="286"/>
-      <c r="F88" s="287"/>
+      <c r="A88" s="257"/>
+      <c r="B88" s="258"/>
+      <c r="C88" s="258"/>
+      <c r="D88" s="258"/>
+      <c r="E88" s="258"/>
+      <c r="F88" s="259"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -8020,11 +8020,11 @@
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="266" t="s">
+      <c r="C90" s="181" t="s">
         <v>224</v>
       </c>
-      <c r="D90" s="266"/>
-      <c r="E90" s="262"/>
+      <c r="D90" s="181"/>
+      <c r="E90" s="182"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -8036,37 +8036,37 @@
       <c r="C91" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="D91" s="288">
+      <c r="D91" s="260">
         <v>107</v>
       </c>
-      <c r="E91" s="289"/>
+      <c r="E91" s="261"/>
       <c r="F91" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="290" t="s">
+      <c r="A92" s="262" t="s">
         <v>225</v>
       </c>
-      <c r="B92" s="255"/>
-      <c r="C92" s="291">
+      <c r="B92" s="263"/>
+      <c r="C92" s="264">
         <v>3</v>
       </c>
-      <c r="D92" s="291"/>
-      <c r="E92" s="291"/>
+      <c r="D92" s="264"/>
+      <c r="E92" s="264"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="292" t="s">
+      <c r="A93" s="265" t="s">
         <v>226</v>
       </c>
-      <c r="B93" s="293"/>
-      <c r="C93" s="293"/>
-      <c r="D93" s="293"/>
-      <c r="E93" s="294"/>
+      <c r="B93" s="266"/>
+      <c r="C93" s="266"/>
+      <c r="D93" s="266"/>
+      <c r="E93" s="267"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8082,11 +8082,11 @@
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="244" t="s">
+      <c r="C95" s="242" t="s">
         <v>227</v>
       </c>
-      <c r="D95" s="270"/>
-      <c r="E95" s="245"/>
+      <c r="D95" s="243"/>
+      <c r="E95" s="244"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8098,44 +8098,44 @@
       <c r="C96" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="D96" s="271">
+      <c r="D96" s="245">
         <v>3691</v>
       </c>
-      <c r="E96" s="272"/>
+      <c r="E96" s="246"/>
       <c r="F96" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="273" t="s">
+      <c r="A97" s="247" t="s">
         <v>225</v>
       </c>
-      <c r="B97" s="274"/>
-      <c r="C97" s="275">
+      <c r="B97" s="248"/>
+      <c r="C97" s="249">
         <v>6.25</v>
       </c>
-      <c r="D97" s="275"/>
-      <c r="E97" s="275"/>
+      <c r="D97" s="249"/>
+      <c r="E97" s="249"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="276" t="s">
+      <c r="A98" s="250" t="s">
         <v>228</v>
       </c>
-      <c r="B98" s="277"/>
-      <c r="C98" s="277"/>
-      <c r="D98" s="277"/>
-      <c r="E98" s="278"/>
+      <c r="B98" s="251"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
+      <c r="E98" s="252"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="279"/>
-      <c r="B99" s="280"/>
-      <c r="C99" s="280"/>
-      <c r="D99" s="280"/>
-      <c r="E99" s="281"/>
+      <c r="A99" s="225"/>
+      <c r="B99" s="253"/>
+      <c r="C99" s="253"/>
+      <c r="D99" s="253"/>
+      <c r="E99" s="226"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8145,18 +8145,18 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="244" t="s">
+      <c r="A101" s="242" t="s">
         <v>229</v>
       </c>
-      <c r="B101" s="270"/>
-      <c r="C101" s="270"/>
-      <c r="D101" s="270"/>
-      <c r="E101" s="270"/>
-      <c r="F101" s="270"/>
-      <c r="G101" s="270"/>
-      <c r="H101" s="270"/>
-      <c r="I101" s="270"/>
-      <c r="J101" s="245"/>
+      <c r="B101" s="243"/>
+      <c r="C101" s="243"/>
+      <c r="D101" s="243"/>
+      <c r="E101" s="243"/>
+      <c r="F101" s="243"/>
+      <c r="G101" s="243"/>
+      <c r="H101" s="243"/>
+      <c r="I101" s="243"/>
+      <c r="J101" s="244"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
@@ -8179,8 +8179,8 @@
         <v>232</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="300"/>
-      <c r="J102" s="301"/>
+      <c r="I102" s="219"/>
+      <c r="J102" s="220"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8192,24 +8192,24 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="302"/>
-      <c r="E103" s="178"/>
-      <c r="F103" s="178"/>
-      <c r="G103" s="303" t="s">
+      <c r="D103" s="221"/>
+      <c r="E103" s="222"/>
+      <c r="F103" s="222"/>
+      <c r="G103" s="223" t="s">
         <v>233</v>
       </c>
-      <c r="H103" s="304"/>
-      <c r="I103" s="305" t="s">
+      <c r="H103" s="224"/>
+      <c r="I103" s="227" t="s">
         <v>234</v>
       </c>
-      <c r="J103" s="306"/>
-      <c r="K103" s="307" t="s">
+      <c r="J103" s="228"/>
+      <c r="K103" s="231" t="s">
         <v>39</v>
       </c>
-      <c r="L103" s="308"/>
+      <c r="L103" s="232"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="311" t="s">
+      <c r="A104" s="235" t="s">
         <v>96</v>
       </c>
       <c r="B104" s="134" t="s">
@@ -8227,15 +8227,15 @@
       <c r="F104" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="G104" s="279"/>
-      <c r="H104" s="281"/>
-      <c r="I104" s="228"/>
+      <c r="G104" s="225"/>
+      <c r="H104" s="226"/>
+      <c r="I104" s="229"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="309"/>
-      <c r="L104" s="310"/>
+      <c r="K104" s="233"/>
+      <c r="L104" s="234"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="312"/>
+      <c r="A105" s="194"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
@@ -8243,37 +8243,37 @@
       <c r="F105" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="G105" s="313">
+      <c r="G105" s="236">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="314"/>
-      <c r="I105" s="315">
+      <c r="H105" s="237"/>
+      <c r="I105" s="238">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="316"/>
-      <c r="K105" s="317" t="str">
+      <c r="J105" s="239"/>
+      <c r="K105" s="240" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="318"/>
+      <c r="L105" s="241"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="220" t="s">
+      <c r="A106" s="210" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="221"/>
-      <c r="C106" s="221"/>
-      <c r="D106" s="221"/>
-      <c r="E106" s="221"/>
-      <c r="F106" s="221"/>
-      <c r="G106" s="221"/>
-      <c r="H106" s="221"/>
-      <c r="I106" s="221"/>
-      <c r="J106" s="221"/>
-      <c r="K106" s="221"/>
-      <c r="L106" s="222"/>
+      <c r="B106" s="211"/>
+      <c r="C106" s="211"/>
+      <c r="D106" s="211"/>
+      <c r="E106" s="211"/>
+      <c r="F106" s="211"/>
+      <c r="G106" s="211"/>
+      <c r="H106" s="211"/>
+      <c r="I106" s="211"/>
+      <c r="J106" s="211"/>
+      <c r="K106" s="211"/>
+      <c r="L106" s="212"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -8322,44 +8322,44 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="295" t="s">
+      <c r="A113" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="B113" s="296"/>
-      <c r="C113" s="296"/>
-      <c r="D113" s="296"/>
-      <c r="E113" s="296" t="s">
+      <c r="B113" s="214"/>
+      <c r="C113" s="214"/>
+      <c r="D113" s="214"/>
+      <c r="E113" s="214" t="s">
         <v>244</v>
       </c>
-      <c r="F113" s="296"/>
-      <c r="G113" s="296" t="s">
+      <c r="F113" s="214"/>
+      <c r="G113" s="214" t="s">
         <v>245</v>
       </c>
-      <c r="H113" s="296" t="s">
+      <c r="H113" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="I113" s="298" t="s">
+      <c r="I113" s="217" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="297"/>
-      <c r="B114" s="188"/>
-      <c r="C114" s="188"/>
-      <c r="D114" s="188"/>
-      <c r="E114" s="188"/>
-      <c r="F114" s="188"/>
-      <c r="G114" s="188"/>
-      <c r="H114" s="188"/>
-      <c r="I114" s="299"/>
+      <c r="A114" s="215"/>
+      <c r="B114" s="216"/>
+      <c r="C114" s="216"/>
+      <c r="D114" s="216"/>
+      <c r="E114" s="216"/>
+      <c r="F114" s="216"/>
+      <c r="G114" s="216"/>
+      <c r="H114" s="216"/>
+      <c r="I114" s="218"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="326" t="s">
+      <c r="A115" s="205" t="s">
         <v>247</v>
       </c>
-      <c r="B115" s="327"/>
-      <c r="C115" s="327"/>
-      <c r="D115" s="327"/>
+      <c r="B115" s="206"/>
+      <c r="C115" s="206"/>
+      <c r="D115" s="206"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
@@ -8374,17 +8374,17 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="328" t="s">
+      <c r="I115" s="207" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="322" t="s">
+      <c r="A116" s="201" t="s">
         <v>249</v>
       </c>
-      <c r="B116" s="323"/>
-      <c r="C116" s="323"/>
-      <c r="D116" s="323"/>
+      <c r="B116" s="202"/>
+      <c r="C116" s="202"/>
+      <c r="D116" s="202"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
@@ -8399,15 +8399,15 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="329"/>
+      <c r="I116" s="208"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="322" t="s">
+      <c r="A117" s="201" t="s">
         <v>250</v>
       </c>
-      <c r="B117" s="323"/>
-      <c r="C117" s="323"/>
-      <c r="D117" s="323"/>
+      <c r="B117" s="202"/>
+      <c r="C117" s="202"/>
+      <c r="D117" s="202"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -8422,15 +8422,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="329"/>
+      <c r="I117" s="208"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="322" t="s">
+      <c r="A118" s="201" t="s">
         <v>251</v>
       </c>
-      <c r="B118" s="323"/>
-      <c r="C118" s="323"/>
-      <c r="D118" s="323"/>
+      <c r="B118" s="202"/>
+      <c r="C118" s="202"/>
+      <c r="D118" s="202"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
@@ -8445,15 +8445,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="329"/>
+      <c r="I118" s="208"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="324" t="s">
+      <c r="A119" s="203" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="325"/>
-      <c r="C119" s="325"/>
-      <c r="D119" s="325"/>
+      <c r="B119" s="204"/>
+      <c r="C119" s="204"/>
+      <c r="D119" s="204"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -8468,15 +8468,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="330"/>
+      <c r="I119" s="209"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="345" t="s">
+      <c r="A120" s="196" t="s">
         <v>253</v>
       </c>
-      <c r="B120" s="346"/>
-      <c r="C120" s="346"/>
-      <c r="D120" s="346"/>
+      <c r="B120" s="197"/>
+      <c r="C120" s="197"/>
+      <c r="D120" s="197"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
@@ -8491,17 +8491,17 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="319" t="s">
+      <c r="I120" s="198" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="322" t="s">
+      <c r="A121" s="201" t="s">
         <v>255</v>
       </c>
-      <c r="B121" s="323"/>
-      <c r="C121" s="323"/>
-      <c r="D121" s="323"/>
+      <c r="B121" s="202"/>
+      <c r="C121" s="202"/>
+      <c r="D121" s="202"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -8516,15 +8516,15 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="320"/>
+      <c r="I121" s="199"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="322" t="s">
+      <c r="A122" s="201" t="s">
         <v>256</v>
       </c>
-      <c r="B122" s="323"/>
-      <c r="C122" s="323"/>
-      <c r="D122" s="323"/>
+      <c r="B122" s="202"/>
+      <c r="C122" s="202"/>
+      <c r="D122" s="202"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -8539,15 +8539,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="320"/>
+      <c r="I122" s="199"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="322" t="s">
+      <c r="A123" s="201" t="s">
         <v>257</v>
       </c>
-      <c r="B123" s="323"/>
-      <c r="C123" s="323"/>
-      <c r="D123" s="323"/>
+      <c r="B123" s="202"/>
+      <c r="C123" s="202"/>
+      <c r="D123" s="202"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
@@ -8562,15 +8562,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="320"/>
+      <c r="I123" s="199"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="324" t="s">
+      <c r="A124" s="203" t="s">
         <v>258</v>
       </c>
-      <c r="B124" s="325"/>
-      <c r="C124" s="325"/>
-      <c r="D124" s="325"/>
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+      <c r="D124" s="204"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
         <v>128</v>
@@ -8581,7 +8581,7 @@
       <c r="H124" s="153" t="s">
         <v>259</v>
       </c>
-      <c r="I124" s="321"/>
+      <c r="I124" s="200"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8602,15 +8602,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="223" t="s">
+      <c r="A127" s="180" t="s">
         <v>262</v>
       </c>
-      <c r="B127" s="266"/>
-      <c r="C127" s="266"/>
-      <c r="D127" s="266"/>
-      <c r="E127" s="266"/>
-      <c r="F127" s="266"/>
-      <c r="G127" s="262"/>
+      <c r="B127" s="181"/>
+      <c r="C127" s="181"/>
+      <c r="D127" s="181"/>
+      <c r="E127" s="181"/>
+      <c r="F127" s="181"/>
+      <c r="G127" s="182"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8624,12 +8624,12 @@
       <c r="A128" s="99" t="s">
         <v>263</v>
       </c>
-      <c r="B128" s="194" t="s">
+      <c r="B128" s="183" t="s">
         <v>264</v>
       </c>
-      <c r="C128" s="195"/>
-      <c r="D128" s="195"/>
-      <c r="E128" s="196"/>
+      <c r="C128" s="184"/>
+      <c r="D128" s="184"/>
+      <c r="E128" s="185"/>
       <c r="F128" s="162" t="s">
         <v>265</v>
       </c>
@@ -8716,15 +8716,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="336" t="s">
+      <c r="A131" s="186" t="s">
         <v>270</v>
       </c>
-      <c r="B131" s="332"/>
-      <c r="C131" s="332"/>
-      <c r="D131" s="332"/>
-      <c r="E131" s="332"/>
-      <c r="F131" s="332"/>
-      <c r="G131" s="333"/>
+      <c r="B131" s="176"/>
+      <c r="C131" s="176"/>
+      <c r="D131" s="176"/>
+      <c r="E131" s="176"/>
+      <c r="F131" s="176"/>
+      <c r="G131" s="177"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8735,15 +8735,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="337" t="s">
+      <c r="A132" s="187" t="s">
         <v>271</v>
       </c>
-      <c r="B132" s="338"/>
-      <c r="C132" s="338"/>
-      <c r="D132" s="338"/>
-      <c r="E132" s="338"/>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="B132" s="188"/>
+      <c r="C132" s="188"/>
+      <c r="D132" s="188"/>
+      <c r="E132" s="188"/>
+      <c r="F132" s="188"/>
+      <c r="G132" s="189"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8754,13 +8754,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="340"/>
-      <c r="B133" s="341"/>
-      <c r="C133" s="341"/>
-      <c r="D133" s="341"/>
-      <c r="E133" s="341"/>
-      <c r="F133" s="341"/>
-      <c r="G133" s="342"/>
+      <c r="A133" s="190"/>
+      <c r="B133" s="191"/>
+      <c r="C133" s="191"/>
+      <c r="D133" s="191"/>
+      <c r="E133" s="191"/>
+      <c r="F133" s="191"/>
+      <c r="G133" s="192"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8867,7 +8867,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="343" t="s">
+      <c r="A140" s="193" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8898,7 +8898,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="312"/>
+      <c r="A141" s="194"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="344" t="s">
+      <c r="B142" s="195" t="s">
         <v>275</v>
       </c>
       <c r="C142" s="173">
@@ -8968,7 +8968,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="344"/>
+      <c r="B143" s="195"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -8999,26 +8999,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="331" t="s">
+      <c r="A144" s="175" t="s">
         <v>276</v>
       </c>
-      <c r="B144" s="332"/>
-      <c r="C144" s="332"/>
-      <c r="D144" s="332"/>
-      <c r="E144" s="332"/>
-      <c r="F144" s="332"/>
-      <c r="G144" s="333"/>
+      <c r="B144" s="176"/>
+      <c r="C144" s="176"/>
+      <c r="D144" s="176"/>
+      <c r="E144" s="176"/>
+      <c r="F144" s="176"/>
+      <c r="G144" s="177"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="331" t="s">
+      <c r="A145" s="175" t="s">
         <v>277</v>
       </c>
-      <c r="B145" s="334"/>
-      <c r="C145" s="334"/>
-      <c r="D145" s="334"/>
-      <c r="E145" s="334"/>
-      <c r="F145" s="334"/>
-      <c r="G145" s="335"/>
+      <c r="B145" s="178"/>
+      <c r="C145" s="178"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="179"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9034,26 +9034,107 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9069,107 +9150,26 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C142:G142">
@@ -9186,19 +9186,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:F86">
-    <cfRule type="containsText" dxfId="37" priority="19" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",F84)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="19" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",F84)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="20" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F92">
-    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="35" priority="18" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",F92)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="17" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",F92)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",F92)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
@@ -9236,11 +9236,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H66:I66">
-    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="25" priority="24" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",H66)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="22" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",H66)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",H66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H75:I75">
@@ -9249,11 +9249,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H76:I76 H78:I79">
-    <cfRule type="containsText" dxfId="22" priority="21" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",H76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",H76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",H76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105:J105">
@@ -9272,11 +9272,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L105">
-    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="17" priority="14" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K105)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",K105)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",K105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q14:T14">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRAJWALA\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED6AA3-2B6F-4A58-87D1-12226F984847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72E0679-3BF4-4202-8C44-14D26C8B090E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,17 @@
     <sheet name="raw data" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -991,7 +1002,7 @@
     <t>Note : Where I is + value &amp; S is - value &amp; vise versa if applicable</t>
   </si>
   <si>
-    <t xml:space="preserve"> mA 10</t>
+    <t xml:space="preserve"> @mA 10</t>
   </si>
 </sst>
 </file>
@@ -2465,6 +2476,474 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2480,24 +2959,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2522,9 +2983,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2533,453 +2991,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4989,38 +5000,38 @@
       <c r="A1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="342" t="s">
+      <c r="B1" s="175" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="342"/>
-      <c r="D1" s="342"/>
-      <c r="E1" s="342"/>
-      <c r="F1" s="342"/>
-      <c r="G1" s="342"/>
-      <c r="H1" s="342"/>
-      <c r="I1" s="342"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
+      <c r="K1" s="177"/>
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="342" t="s">
+      <c r="B2" s="175" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="342"/>
-      <c r="D2" s="342"/>
-      <c r="E2" s="342"/>
-      <c r="F2" s="342"/>
-      <c r="G2" s="342"/>
-      <c r="H2" s="342"/>
-      <c r="I2" s="342"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5030,16 +5041,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="342" t="s">
+      <c r="B3" s="175" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="342"/>
-      <c r="D3" s="342"/>
-      <c r="E3" s="342"/>
-      <c r="F3" s="342"/>
-      <c r="G3" s="342"/>
-      <c r="H3" s="342"/>
-      <c r="I3" s="342"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5051,14 +5062,14 @@
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="342"/>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5070,20 +5081,20 @@
       <c r="A5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="342" t="s">
+      <c r="B5" s="175" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="342"/>
-      <c r="D5" s="342"/>
-      <c r="E5" s="342"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="345">
+      <c r="G5" s="176">
         <v>22.7</v>
       </c>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5095,20 +5106,20 @@
       <c r="A6" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="342" t="s">
+      <c r="B6" s="175" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="342"/>
-      <c r="D6" s="342"/>
-      <c r="E6" s="342"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
       <c r="F6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="345">
+      <c r="G6" s="176">
         <v>50.2</v>
       </c>
-      <c r="H6" s="345"/>
-      <c r="I6" s="345"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5120,20 +5131,20 @@
       <c r="A7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="342" t="s">
+      <c r="B7" s="175" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="175"/>
       <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="342" t="s">
+      <c r="G7" s="175" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
+      <c r="H7" s="175"/>
+      <c r="I7" s="175"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5144,16 +5155,16 @@
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="341">
+      <c r="B8" s="191">
         <v>46066</v>
       </c>
-      <c r="C8" s="342"/>
-      <c r="D8" s="342"/>
-      <c r="E8" s="342"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="175"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="342"/>
-      <c r="H8" s="342"/>
-      <c r="I8" s="342"/>
+      <c r="G8" s="175"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5162,14 +5173,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5180,16 +5191,16 @@
       <c r="A10" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="343" t="s">
+      <c r="B10" s="192" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="343"/>
-      <c r="D10" s="343"/>
-      <c r="E10" s="343"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="343"/>
-      <c r="H10" s="343"/>
-      <c r="I10" s="344"/>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5197,35 +5208,35 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="183" t="s">
+      <c r="A11" s="194" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="184" t="s">
+      <c r="B11" s="195"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="195" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="184"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="185"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="196"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="331" t="s">
+      <c r="P11" s="179" t="s">
         <v>158</v>
       </c>
-      <c r="Q11" s="332"/>
-      <c r="R11" s="332"/>
-      <c r="S11" s="332"/>
-      <c r="T11" s="332"/>
-      <c r="U11" s="332"/>
-      <c r="V11" s="332"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
+      <c r="Q11" s="180"/>
+      <c r="R11" s="180"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="180"/>
+      <c r="U11" s="180"/>
+      <c r="V11" s="180"/>
+      <c r="W11" s="180"/>
+      <c r="X11" s="181"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
@@ -5264,23 +5275,23 @@
       <c r="N12" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P12" s="334" t="s">
+      <c r="P12" s="182" t="s">
         <v>166</v>
       </c>
-      <c r="Q12" s="336" t="s">
+      <c r="Q12" s="184" t="s">
         <v>167</v>
       </c>
-      <c r="R12" s="336"/>
-      <c r="S12" s="336"/>
-      <c r="T12" s="337" t="s">
+      <c r="R12" s="184"/>
+      <c r="S12" s="184"/>
+      <c r="T12" s="185" t="s">
         <v>168</v>
       </c>
-      <c r="U12" s="305" t="s">
+      <c r="U12" s="187" t="s">
         <v>169</v>
       </c>
-      <c r="V12" s="337"/>
+      <c r="V12" s="185"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="339" t="s">
+      <c r="X12" s="189" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5320,7 +5331,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="335"/>
+      <c r="P13" s="183"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5333,11 +5344,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="338"/>
-      <c r="U13" s="216"/>
-      <c r="V13" s="338"/>
+      <c r="T13" s="186"/>
+      <c r="U13" s="188"/>
+      <c r="V13" s="186"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="340"/>
+      <c r="X13" s="190"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5649,15 +5660,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="325" t="s">
+      <c r="P18" s="206" t="s">
         <v>174</v>
       </c>
-      <c r="Q18" s="326"/>
-      <c r="R18" s="326"/>
-      <c r="S18" s="326"/>
-      <c r="T18" s="326"/>
-      <c r="U18" s="326"/>
-      <c r="V18" s="327"/>
+      <c r="Q18" s="207"/>
+      <c r="R18" s="207"/>
+      <c r="S18" s="207"/>
+      <c r="T18" s="207"/>
+      <c r="U18" s="207"/>
+      <c r="V18" s="208"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5697,13 +5708,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="289"/>
-      <c r="Q19" s="289"/>
-      <c r="R19" s="289"/>
-      <c r="S19" s="289"/>
-      <c r="T19" s="289"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
+      <c r="P19" s="209"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5741,14 +5752,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="310" t="s">
+      <c r="P20" s="210" t="s">
         <v>175</v>
       </c>
-      <c r="Q20" s="311"/>
-      <c r="R20" s="311"/>
-      <c r="S20" s="311"/>
-      <c r="T20" s="311"/>
-      <c r="U20" s="313"/>
+      <c r="Q20" s="211"/>
+      <c r="R20" s="211"/>
+      <c r="S20" s="211"/>
+      <c r="T20" s="211"/>
+      <c r="U20" s="212"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5786,14 +5797,14 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="328" t="s">
+      <c r="P21" s="213" t="s">
         <v>176</v>
       </c>
-      <c r="Q21" s="329"/>
-      <c r="R21" s="330" t="s">
+      <c r="Q21" s="214"/>
+      <c r="R21" s="215" t="s">
         <v>177</v>
       </c>
-      <c r="S21" s="329"/>
+      <c r="S21" s="214"/>
       <c r="T21" s="14" t="s">
         <v>178</v>
       </c>
@@ -5840,16 +5851,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="316">
+      <c r="P22" s="197">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="317"/>
-      <c r="R22" s="318">
+      <c r="Q22" s="198"/>
+      <c r="R22" s="199">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="318"/>
+      <c r="S22" s="199"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5895,16 +5906,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="316">
+      <c r="P23" s="197">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="317"/>
-      <c r="R23" s="318">
+      <c r="Q23" s="198"/>
+      <c r="R23" s="199">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="318"/>
+      <c r="S23" s="199"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -5950,16 +5961,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="316">
+      <c r="P24" s="197">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="317"/>
-      <c r="R24" s="318">
+      <c r="Q24" s="198"/>
+      <c r="R24" s="199">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="318"/>
+      <c r="S24" s="199"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -6005,14 +6016,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="319" t="s">
+      <c r="P25" s="200" t="s">
         <v>180</v>
       </c>
-      <c r="Q25" s="320"/>
-      <c r="R25" s="320"/>
-      <c r="S25" s="320"/>
-      <c r="T25" s="320"/>
-      <c r="U25" s="321"/>
+      <c r="Q25" s="201"/>
+      <c r="R25" s="201"/>
+      <c r="S25" s="201"/>
+      <c r="T25" s="201"/>
+      <c r="U25" s="202"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6087,11 +6098,11 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="322" t="s">
+      <c r="P27" s="203" t="s">
         <v>181</v>
       </c>
-      <c r="Q27" s="323"/>
-      <c r="R27" s="324"/>
+      <c r="Q27" s="204"/>
+      <c r="R27" s="205"/>
       <c r="S27" s="47" t="s">
         <v>159</v>
       </c>
@@ -6148,11 +6159,11 @@
       <c r="P28" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="Q28" s="305" t="s">
+      <c r="Q28" s="187" t="s">
         <v>184</v>
       </c>
-      <c r="R28" s="305"/>
-      <c r="S28" s="305"/>
+      <c r="R28" s="187"/>
+      <c r="S28" s="187"/>
       <c r="T28" s="14" t="s">
         <v>185</v>
       </c>
@@ -6224,13 +6235,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="306">
+      <c r="U29" s="237">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="308" t="str">
+      <c r="X29" s="239" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6291,10 +6302,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="306"/>
+      <c r="U30" s="237"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="308"/>
+      <c r="X30" s="239"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6352,10 +6363,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="306"/>
+      <c r="U31" s="237"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="308"/>
+      <c r="X31" s="239"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6413,10 +6424,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="307"/>
+      <c r="U32" s="238"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="309"/>
+      <c r="X32" s="240"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6454,17 +6465,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="210" t="s">
+      <c r="P33" s="220" t="s">
         <v>187</v>
       </c>
-      <c r="Q33" s="211"/>
-      <c r="R33" s="211"/>
-      <c r="S33" s="211"/>
-      <c r="T33" s="211"/>
-      <c r="U33" s="211"/>
-      <c r="V33" s="211"/>
-      <c r="W33" s="211"/>
-      <c r="X33" s="212"/>
+      <c r="Q33" s="221"/>
+      <c r="R33" s="221"/>
+      <c r="S33" s="221"/>
+      <c r="T33" s="221"/>
+      <c r="U33" s="221"/>
+      <c r="V33" s="221"/>
+      <c r="W33" s="221"/>
+      <c r="X33" s="222"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6539,18 +6550,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="310" t="s">
+      <c r="P35" s="210" t="s">
         <v>188</v>
       </c>
-      <c r="Q35" s="311"/>
-      <c r="R35" s="311"/>
-      <c r="S35" s="311"/>
-      <c r="T35" s="311"/>
-      <c r="U35" s="311"/>
-      <c r="V35" s="312"/>
-      <c r="W35" s="312"/>
-      <c r="X35" s="312"/>
-      <c r="Y35" s="313"/>
+      <c r="Q35" s="211"/>
+      <c r="R35" s="211"/>
+      <c r="S35" s="211"/>
+      <c r="T35" s="211"/>
+      <c r="U35" s="211"/>
+      <c r="V35" s="241"/>
+      <c r="W35" s="241"/>
+      <c r="X35" s="241"/>
+      <c r="Y35" s="212"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6591,13 +6602,13 @@
       <c r="P36" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="Q36" s="314" t="s">
+      <c r="Q36" s="242" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="314"/>
-      <c r="S36" s="314"/>
-      <c r="T36" s="314"/>
-      <c r="U36" s="315"/>
+      <c r="R36" s="242"/>
+      <c r="S36" s="242"/>
+      <c r="T36" s="242"/>
+      <c r="U36" s="243"/>
       <c r="V36" s="18" t="s">
         <v>189</v>
       </c>
@@ -6955,18 +6966,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="210" t="s">
+      <c r="P41" s="220" t="s">
         <v>191</v>
       </c>
-      <c r="Q41" s="211"/>
-      <c r="R41" s="211"/>
-      <c r="S41" s="211"/>
-      <c r="T41" s="211"/>
-      <c r="U41" s="211"/>
-      <c r="V41" s="211"/>
-      <c r="W41" s="211"/>
-      <c r="X41" s="211"/>
-      <c r="Y41" s="212"/>
+      <c r="Q41" s="221"/>
+      <c r="R41" s="221"/>
+      <c r="S41" s="221"/>
+      <c r="T41" s="221"/>
+      <c r="U41" s="221"/>
+      <c r="V41" s="221"/>
+      <c r="W41" s="221"/>
+      <c r="X41" s="221"/>
+      <c r="Y41" s="222"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -7044,10 +7055,10 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="180" t="s">
+      <c r="P43" s="223" t="s">
         <v>192</v>
       </c>
-      <c r="Q43" s="296"/>
+      <c r="Q43" s="224"/>
       <c r="R43" s="72" t="s">
         <v>164</v>
       </c>
@@ -7143,12 +7154,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="297" t="s">
+      <c r="P45" s="225" t="s">
         <v>193</v>
       </c>
-      <c r="Q45" s="298"/>
-      <c r="R45" s="298"/>
-      <c r="S45" s="299"/>
+      <c r="Q45" s="226"/>
+      <c r="R45" s="226"/>
+      <c r="S45" s="227"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7186,10 +7197,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="297"/>
-      <c r="Q46" s="298"/>
-      <c r="R46" s="298"/>
-      <c r="S46" s="299"/>
+      <c r="P46" s="225"/>
+      <c r="Q46" s="226"/>
+      <c r="R46" s="226"/>
+      <c r="S46" s="227"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7227,9 +7238,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="229"/>
-      <c r="Q47" s="300"/>
-      <c r="R47" s="300"/>
+      <c r="P47" s="228"/>
+      <c r="Q47" s="229"/>
+      <c r="R47" s="229"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7444,17 +7455,17 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="301" t="s">
+      <c r="A57" s="231" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="302"/>
-      <c r="C57" s="302"/>
-      <c r="D57" s="302"/>
-      <c r="E57" s="302"/>
-      <c r="F57" s="302"/>
-      <c r="G57" s="302"/>
-      <c r="H57" s="302"/>
-      <c r="I57" s="303"/>
+      <c r="B57" s="232"/>
+      <c r="C57" s="232"/>
+      <c r="D57" s="232"/>
+      <c r="E57" s="232"/>
+      <c r="F57" s="232"/>
+      <c r="G57" s="232"/>
+      <c r="H57" s="232"/>
+      <c r="I57" s="233"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -7496,10 +7507,10 @@
       <c r="G59" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H59" s="291" t="s">
+      <c r="H59" s="234" t="s">
         <v>205</v>
       </c>
-      <c r="I59" s="292"/>
+      <c r="I59" s="235"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7518,30 +7529,30 @@
       <c r="F60" t="s">
         <v>60</v>
       </c>
-      <c r="H60" s="304">
+      <c r="H60" s="236">
         <v>18.12</v>
       </c>
-      <c r="I60" s="304"/>
+      <c r="I60" s="236"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
         <v>62</v>
       </c>
-      <c r="H61" s="287">
+      <c r="H61" s="248">
         <v>19.98</v>
       </c>
-      <c r="I61" s="287"/>
+      <c r="I61" s="248"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
         <v>65</v>
       </c>
-      <c r="H62" s="287">
+      <c r="H62" s="248">
         <v>18.7</v>
       </c>
-      <c r="I62" s="287"/>
+      <c r="I62" s="248"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
@@ -7550,10 +7561,10 @@
       <c r="F63" t="s">
         <v>207</v>
       </c>
-      <c r="H63" s="287">
+      <c r="H63" s="248">
         <v>17.62</v>
       </c>
-      <c r="I63" s="287"/>
+      <c r="I63" s="248"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
@@ -7562,27 +7573,27 @@
       <c r="F64" t="s">
         <v>208</v>
       </c>
-      <c r="H64" s="290">
+      <c r="H64" s="249">
         <v>18.79</v>
       </c>
-      <c r="I64" s="290"/>
+      <c r="I64" s="249"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="277" t="s">
+      <c r="B65" s="216" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="278"/>
+      <c r="C65" s="217"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="294">
+      <c r="H65" s="218">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="295"/>
+      <c r="I65" s="219"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7597,11 +7608,11 @@
       <c r="G66" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="242" t="str">
+      <c r="H66" s="244" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="244"/>
+      <c r="I66" s="245"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7662,14 +7673,14 @@
       <c r="G69" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H69" s="291" t="s">
+      <c r="H69" s="234" t="s">
         <v>205</v>
       </c>
-      <c r="I69" s="292"/>
-      <c r="P69" s="288"/>
-      <c r="Q69" s="288"/>
-      <c r="R69" s="289"/>
-      <c r="S69" s="289"/>
+      <c r="I69" s="235"/>
+      <c r="P69" s="246"/>
+      <c r="Q69" s="246"/>
+      <c r="R69" s="209"/>
+      <c r="S69" s="209"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7688,68 +7699,68 @@
       <c r="F70" t="s">
         <v>60</v>
       </c>
-      <c r="H70" s="293">
+      <c r="H70" s="247">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="293"/>
-      <c r="P70" s="288"/>
-      <c r="Q70" s="288"/>
-      <c r="R70" s="289"/>
-      <c r="S70" s="289"/>
+      <c r="I70" s="247"/>
+      <c r="P70" s="246"/>
+      <c r="Q70" s="246"/>
+      <c r="R70" s="209"/>
+      <c r="S70" s="209"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" s="287">
+      <c r="H71" s="248">
         <v>11.78</v>
       </c>
-      <c r="I71" s="287"/>
-      <c r="P71" s="288"/>
-      <c r="Q71" s="288"/>
-      <c r="R71" s="289"/>
-      <c r="S71" s="289"/>
+      <c r="I71" s="248"/>
+      <c r="P71" s="246"/>
+      <c r="Q71" s="246"/>
+      <c r="R71" s="209"/>
+      <c r="S71" s="209"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
         <v>65</v>
       </c>
-      <c r="H72" s="287">
+      <c r="H72" s="248">
         <v>12.39</v>
       </c>
-      <c r="I72" s="287"/>
-      <c r="P72" s="288"/>
-      <c r="Q72" s="288"/>
-      <c r="R72" s="289"/>
-      <c r="S72" s="289"/>
+      <c r="I72" s="248"/>
+      <c r="P72" s="246"/>
+      <c r="Q72" s="246"/>
+      <c r="R72" s="209"/>
+      <c r="S72" s="209"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
         <v>207</v>
       </c>
-      <c r="H73" s="287">
+      <c r="H73" s="248">
         <v>11.21</v>
       </c>
-      <c r="I73" s="287"/>
+      <c r="I73" s="248"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="288"/>
-      <c r="Q73" s="288"/>
-      <c r="R73" s="289"/>
-      <c r="S73" s="289"/>
+      <c r="P73" s="246"/>
+      <c r="Q73" s="246"/>
+      <c r="R73" s="209"/>
+      <c r="S73" s="209"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
         <v>208</v>
       </c>
-      <c r="H74" s="290">
+      <c r="H74" s="249">
         <v>12.75</v>
       </c>
-      <c r="I74" s="290"/>
+      <c r="I74" s="249"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7758,28 +7769,28 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="288"/>
-      <c r="Q74" s="288"/>
-      <c r="R74" s="289"/>
-      <c r="S74" s="289"/>
+      <c r="P74" s="246"/>
+      <c r="Q74" s="246"/>
+      <c r="R74" s="209"/>
+      <c r="S74" s="209"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="277" t="s">
+      <c r="B75" s="216" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="278"/>
+      <c r="C75" s="217"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="279">
+      <c r="H75" s="260">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="280"/>
+      <c r="I75" s="261"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
@@ -7787,24 +7798,24 @@
       <c r="G76" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H76" s="180" t="str">
+      <c r="H76" s="223" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="182"/>
+      <c r="I76" s="262"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="281" t="s">
+      <c r="A77" s="263" t="s">
         <v>212</v>
       </c>
-      <c r="B77" s="282"/>
-      <c r="C77" s="282"/>
-      <c r="D77" s="282"/>
-      <c r="E77" s="282"/>
-      <c r="F77" s="282"/>
-      <c r="G77" s="282"/>
-      <c r="H77" s="282"/>
-      <c r="I77" s="283"/>
+      <c r="B77" s="264"/>
+      <c r="C77" s="264"/>
+      <c r="D77" s="264"/>
+      <c r="E77" s="264"/>
+      <c r="F77" s="264"/>
+      <c r="G77" s="264"/>
+      <c r="H77" s="264"/>
+      <c r="I77" s="265"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7817,11 +7828,11 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="180" t="s">
+      <c r="A80" s="223" t="s">
         <v>213</v>
       </c>
-      <c r="B80" s="181"/>
-      <c r="C80" s="181"/>
+      <c r="B80" s="266"/>
+      <c r="C80" s="266"/>
       <c r="D80" s="47" t="s">
         <v>214</v>
       </c>
@@ -7838,10 +7849,10 @@
       <c r="A81" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="284" t="s">
+      <c r="B81" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="285"/>
+      <c r="C81" s="268"/>
       <c r="D81" s="102" t="s">
         <v>216</v>
       </c>
@@ -7850,8 +7861,8 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="286"/>
-      <c r="I81" s="286"/>
+      <c r="H81" s="269"/>
+      <c r="I81" s="269"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7859,11 +7870,11 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="268">
+      <c r="B82" s="250">
         <v>15</v>
       </c>
-      <c r="C82" s="268"/>
-      <c r="D82" s="269" t="s">
+      <c r="C82" s="250"/>
+      <c r="D82" s="251" t="s">
         <v>217</v>
       </c>
       <c r="E82" s="106"/>
@@ -7881,11 +7892,11 @@
       <c r="A83" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="B83" s="272" t="s">
+      <c r="B83" s="254" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="263"/>
-      <c r="D83" s="270"/>
+      <c r="C83" s="255"/>
+      <c r="D83" s="252"/>
       <c r="E83" s="46" t="s">
         <v>221</v>
       </c>
@@ -7906,11 +7917,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="273">
+      <c r="B84" s="256">
         <v>2.8</v>
       </c>
-      <c r="C84" s="273"/>
-      <c r="D84" s="270"/>
+      <c r="C84" s="256"/>
+      <c r="D84" s="252"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7936,11 +7947,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="274">
+      <c r="B85" s="257">
         <v>5</v>
       </c>
-      <c r="C85" s="275"/>
-      <c r="D85" s="270"/>
+      <c r="C85" s="258"/>
+      <c r="D85" s="252"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -7962,11 +7973,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="276">
+      <c r="B86" s="259">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="276"/>
-      <c r="D86" s="271"/>
+      <c r="C86" s="259"/>
+      <c r="D86" s="253"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -7985,14 +7996,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="254" t="s">
+      <c r="A87" s="282" t="s">
         <v>223</v>
       </c>
-      <c r="B87" s="255"/>
-      <c r="C87" s="255"/>
-      <c r="D87" s="255"/>
-      <c r="E87" s="255"/>
-      <c r="F87" s="256"/>
+      <c r="B87" s="283"/>
+      <c r="C87" s="283"/>
+      <c r="D87" s="283"/>
+      <c r="E87" s="283"/>
+      <c r="F87" s="284"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -8000,12 +8011,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="257"/>
-      <c r="B88" s="258"/>
-      <c r="C88" s="258"/>
-      <c r="D88" s="258"/>
-      <c r="E88" s="258"/>
-      <c r="F88" s="259"/>
+      <c r="A88" s="285"/>
+      <c r="B88" s="286"/>
+      <c r="C88" s="286"/>
+      <c r="D88" s="286"/>
+      <c r="E88" s="286"/>
+      <c r="F88" s="287"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -8020,11 +8031,11 @@
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="181" t="s">
+      <c r="C90" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="D90" s="181"/>
-      <c r="E90" s="182"/>
+      <c r="D90" s="266"/>
+      <c r="E90" s="262"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -8036,37 +8047,37 @@
       <c r="C91" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="D91" s="260">
+      <c r="D91" s="288">
         <v>107</v>
       </c>
-      <c r="E91" s="261"/>
+      <c r="E91" s="289"/>
       <c r="F91" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="262" t="s">
+      <c r="A92" s="290" t="s">
         <v>225</v>
       </c>
-      <c r="B92" s="263"/>
-      <c r="C92" s="264">
+      <c r="B92" s="255"/>
+      <c r="C92" s="291">
         <v>3</v>
       </c>
-      <c r="D92" s="264"/>
-      <c r="E92" s="264"/>
+      <c r="D92" s="291"/>
+      <c r="E92" s="291"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="265" t="s">
+      <c r="A93" s="292" t="s">
         <v>226</v>
       </c>
-      <c r="B93" s="266"/>
-      <c r="C93" s="266"/>
-      <c r="D93" s="266"/>
-      <c r="E93" s="267"/>
+      <c r="B93" s="293"/>
+      <c r="C93" s="293"/>
+      <c r="D93" s="293"/>
+      <c r="E93" s="294"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8082,11 +8093,11 @@
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="242" t="s">
+      <c r="C95" s="244" t="s">
         <v>227</v>
       </c>
-      <c r="D95" s="243"/>
-      <c r="E95" s="244"/>
+      <c r="D95" s="270"/>
+      <c r="E95" s="245"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8098,44 +8109,44 @@
       <c r="C96" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="D96" s="245">
+      <c r="D96" s="271">
         <v>3691</v>
       </c>
-      <c r="E96" s="246"/>
+      <c r="E96" s="272"/>
       <c r="F96" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="247" t="s">
+      <c r="A97" s="273" t="s">
         <v>225</v>
       </c>
-      <c r="B97" s="248"/>
-      <c r="C97" s="249">
+      <c r="B97" s="274"/>
+      <c r="C97" s="275">
         <v>6.25</v>
       </c>
-      <c r="D97" s="249"/>
-      <c r="E97" s="249"/>
+      <c r="D97" s="275"/>
+      <c r="E97" s="275"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="250" t="s">
+      <c r="A98" s="276" t="s">
         <v>228</v>
       </c>
-      <c r="B98" s="251"/>
-      <c r="C98" s="251"/>
-      <c r="D98" s="251"/>
-      <c r="E98" s="252"/>
+      <c r="B98" s="277"/>
+      <c r="C98" s="277"/>
+      <c r="D98" s="277"/>
+      <c r="E98" s="278"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="225"/>
-      <c r="B99" s="253"/>
-      <c r="C99" s="253"/>
-      <c r="D99" s="253"/>
-      <c r="E99" s="226"/>
+      <c r="A99" s="279"/>
+      <c r="B99" s="280"/>
+      <c r="C99" s="280"/>
+      <c r="D99" s="280"/>
+      <c r="E99" s="281"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8145,18 +8156,18 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="242" t="s">
+      <c r="A101" s="244" t="s">
         <v>229</v>
       </c>
-      <c r="B101" s="243"/>
-      <c r="C101" s="243"/>
-      <c r="D101" s="243"/>
-      <c r="E101" s="243"/>
-      <c r="F101" s="243"/>
-      <c r="G101" s="243"/>
-      <c r="H101" s="243"/>
-      <c r="I101" s="243"/>
-      <c r="J101" s="244"/>
+      <c r="B101" s="270"/>
+      <c r="C101" s="270"/>
+      <c r="D101" s="270"/>
+      <c r="E101" s="270"/>
+      <c r="F101" s="270"/>
+      <c r="G101" s="270"/>
+      <c r="H101" s="270"/>
+      <c r="I101" s="270"/>
+      <c r="J101" s="245"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
@@ -8179,8 +8190,8 @@
         <v>232</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="219"/>
-      <c r="J102" s="220"/>
+      <c r="I102" s="300"/>
+      <c r="J102" s="301"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8192,24 +8203,24 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="221"/>
-      <c r="E103" s="222"/>
-      <c r="F103" s="222"/>
-      <c r="G103" s="223" t="s">
+      <c r="D103" s="302"/>
+      <c r="E103" s="178"/>
+      <c r="F103" s="178"/>
+      <c r="G103" s="303" t="s">
         <v>233</v>
       </c>
-      <c r="H103" s="224"/>
-      <c r="I103" s="227" t="s">
+      <c r="H103" s="304"/>
+      <c r="I103" s="305" t="s">
         <v>234</v>
       </c>
-      <c r="J103" s="228"/>
-      <c r="K103" s="231" t="s">
+      <c r="J103" s="306"/>
+      <c r="K103" s="307" t="s">
         <v>39</v>
       </c>
-      <c r="L103" s="232"/>
+      <c r="L103" s="308"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="235" t="s">
+      <c r="A104" s="311" t="s">
         <v>96</v>
       </c>
       <c r="B104" s="134" t="s">
@@ -8227,15 +8238,15 @@
       <c r="F104" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="G104" s="225"/>
-      <c r="H104" s="226"/>
-      <c r="I104" s="229"/>
+      <c r="G104" s="279"/>
+      <c r="H104" s="281"/>
+      <c r="I104" s="228"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="233"/>
-      <c r="L104" s="234"/>
+      <c r="K104" s="309"/>
+      <c r="L104" s="310"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="194"/>
+      <c r="A105" s="312"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
@@ -8243,37 +8254,37 @@
       <c r="F105" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="G105" s="236">
+      <c r="G105" s="313">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="237"/>
-      <c r="I105" s="238">
+      <c r="H105" s="314"/>
+      <c r="I105" s="315">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="239"/>
-      <c r="K105" s="240" t="str">
+      <c r="J105" s="316"/>
+      <c r="K105" s="317" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="241"/>
+      <c r="L105" s="318"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="210" t="s">
+      <c r="A106" s="220" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="211"/>
-      <c r="C106" s="211"/>
-      <c r="D106" s="211"/>
-      <c r="E106" s="211"/>
-      <c r="F106" s="211"/>
-      <c r="G106" s="211"/>
-      <c r="H106" s="211"/>
-      <c r="I106" s="211"/>
-      <c r="J106" s="211"/>
-      <c r="K106" s="211"/>
-      <c r="L106" s="212"/>
+      <c r="B106" s="221"/>
+      <c r="C106" s="221"/>
+      <c r="D106" s="221"/>
+      <c r="E106" s="221"/>
+      <c r="F106" s="221"/>
+      <c r="G106" s="221"/>
+      <c r="H106" s="221"/>
+      <c r="I106" s="221"/>
+      <c r="J106" s="221"/>
+      <c r="K106" s="221"/>
+      <c r="L106" s="222"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -8322,44 +8333,44 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="213" t="s">
+      <c r="A113" s="295" t="s">
         <v>87</v>
       </c>
-      <c r="B113" s="214"/>
-      <c r="C113" s="214"/>
-      <c r="D113" s="214"/>
-      <c r="E113" s="214" t="s">
+      <c r="B113" s="296"/>
+      <c r="C113" s="296"/>
+      <c r="D113" s="296"/>
+      <c r="E113" s="296" t="s">
         <v>244</v>
       </c>
-      <c r="F113" s="214"/>
-      <c r="G113" s="214" t="s">
+      <c r="F113" s="296"/>
+      <c r="G113" s="296" t="s">
         <v>245</v>
       </c>
-      <c r="H113" s="214" t="s">
+      <c r="H113" s="296" t="s">
         <v>39</v>
       </c>
-      <c r="I113" s="217" t="s">
+      <c r="I113" s="298" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="215"/>
-      <c r="B114" s="216"/>
-      <c r="C114" s="216"/>
-      <c r="D114" s="216"/>
-      <c r="E114" s="216"/>
-      <c r="F114" s="216"/>
-      <c r="G114" s="216"/>
-      <c r="H114" s="216"/>
-      <c r="I114" s="218"/>
+      <c r="A114" s="297"/>
+      <c r="B114" s="188"/>
+      <c r="C114" s="188"/>
+      <c r="D114" s="188"/>
+      <c r="E114" s="188"/>
+      <c r="F114" s="188"/>
+      <c r="G114" s="188"/>
+      <c r="H114" s="188"/>
+      <c r="I114" s="299"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="205" t="s">
+      <c r="A115" s="326" t="s">
         <v>247</v>
       </c>
-      <c r="B115" s="206"/>
-      <c r="C115" s="206"/>
-      <c r="D115" s="206"/>
+      <c r="B115" s="327"/>
+      <c r="C115" s="327"/>
+      <c r="D115" s="327"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
@@ -8374,17 +8385,17 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="207" t="s">
+      <c r="I115" s="328" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="201" t="s">
+      <c r="A116" s="322" t="s">
         <v>249</v>
       </c>
-      <c r="B116" s="202"/>
-      <c r="C116" s="202"/>
-      <c r="D116" s="202"/>
+      <c r="B116" s="323"/>
+      <c r="C116" s="323"/>
+      <c r="D116" s="323"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
@@ -8399,15 +8410,15 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="208"/>
+      <c r="I116" s="329"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="201" t="s">
+      <c r="A117" s="322" t="s">
         <v>250</v>
       </c>
-      <c r="B117" s="202"/>
-      <c r="C117" s="202"/>
-      <c r="D117" s="202"/>
+      <c r="B117" s="323"/>
+      <c r="C117" s="323"/>
+      <c r="D117" s="323"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -8422,15 +8433,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="208"/>
+      <c r="I117" s="329"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="201" t="s">
+      <c r="A118" s="322" t="s">
         <v>251</v>
       </c>
-      <c r="B118" s="202"/>
-      <c r="C118" s="202"/>
-      <c r="D118" s="202"/>
+      <c r="B118" s="323"/>
+      <c r="C118" s="323"/>
+      <c r="D118" s="323"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
@@ -8445,15 +8456,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="208"/>
+      <c r="I118" s="329"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="203" t="s">
+      <c r="A119" s="324" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="204"/>
-      <c r="C119" s="204"/>
-      <c r="D119" s="204"/>
+      <c r="B119" s="325"/>
+      <c r="C119" s="325"/>
+      <c r="D119" s="325"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -8468,15 +8479,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="209"/>
+      <c r="I119" s="330"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="196" t="s">
+      <c r="A120" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="B120" s="197"/>
-      <c r="C120" s="197"/>
-      <c r="D120" s="197"/>
+      <c r="B120" s="346"/>
+      <c r="C120" s="346"/>
+      <c r="D120" s="346"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
@@ -8491,17 +8502,17 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="198" t="s">
+      <c r="I120" s="319" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="201" t="s">
+      <c r="A121" s="322" t="s">
         <v>255</v>
       </c>
-      <c r="B121" s="202"/>
-      <c r="C121" s="202"/>
-      <c r="D121" s="202"/>
+      <c r="B121" s="323"/>
+      <c r="C121" s="323"/>
+      <c r="D121" s="323"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -8516,15 +8527,15 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="199"/>
+      <c r="I121" s="320"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="201" t="s">
+      <c r="A122" s="322" t="s">
         <v>256</v>
       </c>
-      <c r="B122" s="202"/>
-      <c r="C122" s="202"/>
-      <c r="D122" s="202"/>
+      <c r="B122" s="323"/>
+      <c r="C122" s="323"/>
+      <c r="D122" s="323"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -8539,15 +8550,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="199"/>
+      <c r="I122" s="320"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="201" t="s">
+      <c r="A123" s="322" t="s">
         <v>257</v>
       </c>
-      <c r="B123" s="202"/>
-      <c r="C123" s="202"/>
-      <c r="D123" s="202"/>
+      <c r="B123" s="323"/>
+      <c r="C123" s="323"/>
+      <c r="D123" s="323"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
@@ -8562,15 +8573,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="199"/>
+      <c r="I123" s="320"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="203" t="s">
+      <c r="A124" s="324" t="s">
         <v>258</v>
       </c>
-      <c r="B124" s="204"/>
-      <c r="C124" s="204"/>
-      <c r="D124" s="204"/>
+      <c r="B124" s="325"/>
+      <c r="C124" s="325"/>
+      <c r="D124" s="325"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
         <v>128</v>
@@ -8581,7 +8592,7 @@
       <c r="H124" s="153" t="s">
         <v>259</v>
       </c>
-      <c r="I124" s="200"/>
+      <c r="I124" s="321"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8602,15 +8613,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="180" t="s">
+      <c r="A127" s="223" t="s">
         <v>262</v>
       </c>
-      <c r="B127" s="181"/>
-      <c r="C127" s="181"/>
-      <c r="D127" s="181"/>
-      <c r="E127" s="181"/>
-      <c r="F127" s="181"/>
-      <c r="G127" s="182"/>
+      <c r="B127" s="266"/>
+      <c r="C127" s="266"/>
+      <c r="D127" s="266"/>
+      <c r="E127" s="266"/>
+      <c r="F127" s="266"/>
+      <c r="G127" s="262"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8624,12 +8635,12 @@
       <c r="A128" s="99" t="s">
         <v>263</v>
       </c>
-      <c r="B128" s="183" t="s">
+      <c r="B128" s="194" t="s">
         <v>264</v>
       </c>
-      <c r="C128" s="184"/>
-      <c r="D128" s="184"/>
-      <c r="E128" s="185"/>
+      <c r="C128" s="195"/>
+      <c r="D128" s="195"/>
+      <c r="E128" s="196"/>
       <c r="F128" s="162" t="s">
         <v>265</v>
       </c>
@@ -8716,15 +8727,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="186" t="s">
+      <c r="A131" s="336" t="s">
         <v>270</v>
       </c>
-      <c r="B131" s="176"/>
-      <c r="C131" s="176"/>
-      <c r="D131" s="176"/>
-      <c r="E131" s="176"/>
-      <c r="F131" s="176"/>
-      <c r="G131" s="177"/>
+      <c r="B131" s="332"/>
+      <c r="C131" s="332"/>
+      <c r="D131" s="332"/>
+      <c r="E131" s="332"/>
+      <c r="F131" s="332"/>
+      <c r="G131" s="333"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8735,15 +8746,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="187" t="s">
+      <c r="A132" s="337" t="s">
         <v>271</v>
       </c>
-      <c r="B132" s="188"/>
-      <c r="C132" s="188"/>
-      <c r="D132" s="188"/>
-      <c r="E132" s="188"/>
-      <c r="F132" s="188"/>
-      <c r="G132" s="189"/>
+      <c r="B132" s="338"/>
+      <c r="C132" s="338"/>
+      <c r="D132" s="338"/>
+      <c r="E132" s="338"/>
+      <c r="F132" s="338"/>
+      <c r="G132" s="339"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8754,13 +8765,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="190"/>
-      <c r="B133" s="191"/>
-      <c r="C133" s="191"/>
-      <c r="D133" s="191"/>
-      <c r="E133" s="191"/>
-      <c r="F133" s="191"/>
-      <c r="G133" s="192"/>
+      <c r="A133" s="340"/>
+      <c r="B133" s="341"/>
+      <c r="C133" s="341"/>
+      <c r="D133" s="341"/>
+      <c r="E133" s="341"/>
+      <c r="F133" s="341"/>
+      <c r="G133" s="342"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8867,7 +8878,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="193" t="s">
+      <c r="A140" s="343" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8898,7 +8909,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="194"/>
+      <c r="A141" s="312"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8934,7 +8945,7 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="195" t="s">
+      <c r="B142" s="344" t="s">
         <v>275</v>
       </c>
       <c r="C142" s="173">
@@ -8968,7 +8979,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="195"/>
+      <c r="B143" s="344"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -8999,26 +9010,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="175" t="s">
+      <c r="A144" s="331" t="s">
         <v>276</v>
       </c>
-      <c r="B144" s="176"/>
-      <c r="C144" s="176"/>
-      <c r="D144" s="176"/>
-      <c r="E144" s="176"/>
-      <c r="F144" s="176"/>
-      <c r="G144" s="177"/>
+      <c r="B144" s="332"/>
+      <c r="C144" s="332"/>
+      <c r="D144" s="332"/>
+      <c r="E144" s="332"/>
+      <c r="F144" s="332"/>
+      <c r="G144" s="333"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="175" t="s">
+      <c r="A145" s="331" t="s">
         <v>277</v>
       </c>
-      <c r="B145" s="178"/>
-      <c r="C145" s="178"/>
-      <c r="D145" s="178"/>
-      <c r="E145" s="178"/>
-      <c r="F145" s="178"/>
-      <c r="G145" s="179"/>
+      <c r="B145" s="334"/>
+      <c r="C145" s="334"/>
+      <c r="D145" s="334"/>
+      <c r="E145" s="334"/>
+      <c r="F145" s="334"/>
+      <c r="G145" s="335"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9034,107 +9045,26 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9150,26 +9080,107 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C142:G142">

--- a/public/templates/CTScan_SingleTube_Sample.xlsx
+++ b/public/templates/CTScan_SingleTube_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRAJWALA\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72E0679-3BF4-4202-8C44-14D26C8B090E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40988541-9E1C-4B85-B615-388F313B85F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
     <t>Note : Where I is + value &amp; S is - value &amp; vise versa if applicable</t>
   </si>
   <si>
-    <t xml:space="preserve"> @mA 10</t>
+    <t xml:space="preserve"> @mA 30</t>
   </si>
 </sst>
 </file>
@@ -2476,521 +2476,521 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3687,7 +3687,17 @@
   <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="10" width="20.796875" customWidth="1"/>
+    <col min="1" max="1" width="52.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -5000,38 +5010,38 @@
       <c r="A1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="175" t="s">
+      <c r="B1" s="342" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
+      <c r="H1" s="342"/>
+      <c r="I1" s="342"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="342" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5041,16 +5051,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="175" t="s">
+      <c r="B3" s="342" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
+      <c r="H3" s="342"/>
+      <c r="I3" s="342"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5062,14 +5072,14 @@
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -5081,20 +5091,20 @@
       <c r="A5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="175" t="s">
+      <c r="B5" s="342" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
       <c r="F5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="176">
+      <c r="G5" s="345">
         <v>22.7</v>
       </c>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5106,20 +5116,20 @@
       <c r="A6" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="342" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="175"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
+      <c r="C6" s="342"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
       <c r="F6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="176">
+      <c r="G6" s="345">
         <v>50.2</v>
       </c>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -5131,20 +5141,20 @@
       <c r="A7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="175" t="s">
+      <c r="B7" s="342" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
       <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="175" t="s">
+      <c r="G7" s="342" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -5155,16 +5165,16 @@
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="191">
+      <c r="B8" s="341">
         <v>46066</v>
       </c>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
+      <c r="C8" s="342"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="G8" s="342"/>
+      <c r="H8" s="342"/>
+      <c r="I8" s="342"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -5173,14 +5183,14 @@
     </row>
     <row r="9" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5191,16 +5201,16 @@
       <c r="A10" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="192" t="s">
+      <c r="B10" s="343" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="192"/>
-      <c r="H10" s="192"/>
-      <c r="I10" s="193"/>
+      <c r="C10" s="343"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="344"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5208,35 +5218,35 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="183" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="195"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="195" t="s">
+      <c r="B11" s="184"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="184" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="196"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="179" t="s">
+      <c r="P11" s="331" t="s">
         <v>158</v>
       </c>
-      <c r="Q11" s="180"/>
-      <c r="R11" s="180"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="180"/>
-      <c r="U11" s="180"/>
-      <c r="V11" s="180"/>
-      <c r="W11" s="180"/>
-      <c r="X11" s="181"/>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
+      <c r="V11" s="332"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
     </row>
     <row r="12" spans="1:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
@@ -5275,23 +5285,23 @@
       <c r="N12" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P12" s="182" t="s">
+      <c r="P12" s="334" t="s">
         <v>166</v>
       </c>
-      <c r="Q12" s="184" t="s">
+      <c r="Q12" s="336" t="s">
         <v>167</v>
       </c>
-      <c r="R12" s="184"/>
-      <c r="S12" s="184"/>
-      <c r="T12" s="185" t="s">
+      <c r="R12" s="336"/>
+      <c r="S12" s="336"/>
+      <c r="T12" s="337" t="s">
         <v>168</v>
       </c>
-      <c r="U12" s="187" t="s">
+      <c r="U12" s="305" t="s">
         <v>169</v>
       </c>
-      <c r="V12" s="185"/>
+      <c r="V12" s="337"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="189" t="s">
+      <c r="X12" s="339" t="s">
         <v>170</v>
       </c>
     </row>
@@ -5331,7 +5341,7 @@
         <f>ROUND(F13,4)</f>
         <v>0.53200000000000003</v>
       </c>
-      <c r="P13" s="183"/>
+      <c r="P13" s="335"/>
       <c r="Q13" s="17">
         <f>B14</f>
         <v>10</v>
@@ -5344,11 +5354,11 @@
         <f>B22</f>
         <v>350</v>
       </c>
-      <c r="T13" s="186"/>
-      <c r="U13" s="188"/>
-      <c r="V13" s="186"/>
+      <c r="T13" s="338"/>
+      <c r="U13" s="216"/>
+      <c r="V13" s="338"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="190"/>
+      <c r="X13" s="340"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -5660,15 +5670,15 @@
         <f t="shared" si="0"/>
         <v>5.2999000000000001</v>
       </c>
-      <c r="P18" s="206" t="s">
+      <c r="P18" s="325" t="s">
         <v>174</v>
       </c>
-      <c r="Q18" s="207"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
-      <c r="T18" s="207"/>
-      <c r="U18" s="207"/>
-      <c r="V18" s="208"/>
+      <c r="Q18" s="326"/>
+      <c r="R18" s="326"/>
+      <c r="S18" s="326"/>
+      <c r="T18" s="326"/>
+      <c r="U18" s="326"/>
+      <c r="V18" s="327"/>
       <c r="W18" s="40"/>
       <c r="X18" s="41"/>
     </row>
@@ -5708,13 +5718,13 @@
         <f t="shared" si="0"/>
         <v>5.3005000000000004</v>
       </c>
-      <c r="P19" s="209"/>
-      <c r="Q19" s="209"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
+      <c r="P19" s="289"/>
+      <c r="Q19" s="289"/>
+      <c r="R19" s="289"/>
+      <c r="S19" s="289"/>
+      <c r="T19" s="289"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -5752,14 +5762,14 @@
         <f t="shared" si="0"/>
         <v>5.3002000000000002</v>
       </c>
-      <c r="P20" s="210" t="s">
+      <c r="P20" s="310" t="s">
         <v>175</v>
       </c>
-      <c r="Q20" s="211"/>
-      <c r="R20" s="211"/>
-      <c r="S20" s="211"/>
-      <c r="T20" s="211"/>
-      <c r="U20" s="212"/>
+      <c r="Q20" s="311"/>
+      <c r="R20" s="311"/>
+      <c r="S20" s="311"/>
+      <c r="T20" s="311"/>
+      <c r="U20" s="313"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -5797,14 +5807,14 @@
         <f t="shared" si="0"/>
         <v>5.2969999999999997</v>
       </c>
-      <c r="P21" s="213" t="s">
+      <c r="P21" s="328" t="s">
         <v>176</v>
       </c>
-      <c r="Q21" s="214"/>
-      <c r="R21" s="215" t="s">
+      <c r="Q21" s="329"/>
+      <c r="R21" s="330" t="s">
         <v>177</v>
       </c>
-      <c r="S21" s="214"/>
+      <c r="S21" s="329"/>
       <c r="T21" s="14" t="s">
         <v>178</v>
       </c>
@@ -5851,16 +5861,16 @@
         <f t="shared" si="0"/>
         <v>18.497399999999999</v>
       </c>
-      <c r="P22" s="197">
+      <c r="P22" s="316">
         <f>C14</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="198"/>
-      <c r="R22" s="199">
+      <c r="Q22" s="317"/>
+      <c r="R22" s="318">
         <f>ROUND(E14/1000,4)</f>
         <v>1.0092000000000001</v>
       </c>
-      <c r="S22" s="199"/>
+      <c r="S22" s="318"/>
       <c r="T22" s="45">
         <f>ROUND(ABS(((R22-P22)/P22*100)),2)</f>
         <v>0.92</v>
@@ -5906,16 +5916,16 @@
         <f t="shared" si="0"/>
         <v>0.94920000000000004</v>
       </c>
-      <c r="P23" s="197">
+      <c r="P23" s="316">
         <f>C15</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="198"/>
-      <c r="R23" s="199">
+      <c r="Q23" s="317"/>
+      <c r="R23" s="318">
         <f>ROUND(E15/1000,4)</f>
         <v>2.0093999999999999</v>
       </c>
-      <c r="S23" s="199"/>
+      <c r="S23" s="318"/>
       <c r="T23" s="45">
         <f>ROUND(ABS(((R23-P23)/P23*100)),2)</f>
         <v>0.47</v>
@@ -5961,16 +5971,16 @@
         <f t="shared" si="0"/>
         <v>9.4794</v>
       </c>
-      <c r="P24" s="197">
+      <c r="P24" s="316">
         <f>C16</f>
         <v>3</v>
       </c>
-      <c r="Q24" s="198"/>
-      <c r="R24" s="199">
+      <c r="Q24" s="317"/>
+      <c r="R24" s="318">
         <f>ROUND(E16/1000,4)</f>
         <v>3.0081000000000002</v>
       </c>
-      <c r="S24" s="199"/>
+      <c r="S24" s="318"/>
       <c r="T24" s="45">
         <f>ROUND(ABS(((R24-P24)/P24*100)),2)</f>
         <v>0.27</v>
@@ -6016,14 +6026,14 @@
         <f t="shared" si="0"/>
         <v>9.4793000000000003</v>
       </c>
-      <c r="P25" s="200" t="s">
+      <c r="P25" s="319" t="s">
         <v>180</v>
       </c>
-      <c r="Q25" s="201"/>
-      <c r="R25" s="201"/>
-      <c r="S25" s="201"/>
-      <c r="T25" s="201"/>
-      <c r="U25" s="202"/>
+      <c r="Q25" s="320"/>
+      <c r="R25" s="320"/>
+      <c r="S25" s="320"/>
+      <c r="T25" s="320"/>
+      <c r="U25" s="321"/>
     </row>
     <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
@@ -6098,11 +6108,11 @@
         <f t="shared" si="0"/>
         <v>9.4781999999999993</v>
       </c>
-      <c r="P27" s="203" t="s">
+      <c r="P27" s="322" t="s">
         <v>181</v>
       </c>
-      <c r="Q27" s="204"/>
-      <c r="R27" s="205"/>
+      <c r="Q27" s="323"/>
+      <c r="R27" s="324"/>
       <c r="S27" s="47" t="s">
         <v>159</v>
       </c>
@@ -6159,11 +6169,11 @@
       <c r="P28" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="Q28" s="187" t="s">
+      <c r="Q28" s="305" t="s">
         <v>184</v>
       </c>
-      <c r="R28" s="187"/>
-      <c r="S28" s="187"/>
+      <c r="R28" s="305"/>
+      <c r="S28" s="305"/>
       <c r="T28" s="14" t="s">
         <v>185</v>
       </c>
@@ -6235,13 +6245,13 @@
         <f>ROUND((AVERAGE(Q29:S29)/(P29*X27)),4)</f>
         <v>0.1457</v>
       </c>
-      <c r="U29" s="237">
+      <c r="U29" s="306">
         <f>ROUND((MAX(T29:T32)-MIN(T29:T32))/(MAX(T29:T32)+MIN(T29:T32)),4)</f>
         <v>1.4E-3</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="5"/>
-      <c r="X29" s="239" t="str">
+      <c r="X29" s="308" t="str">
         <f>IF(U29&lt;0.1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
@@ -6302,10 +6312,10 @@
         <f>ROUND((AVERAGE(Q30:S30)/(P30*X27)),4)</f>
         <v>0.14530000000000001</v>
       </c>
-      <c r="U30" s="237"/>
+      <c r="U30" s="306"/>
       <c r="V30" s="13"/>
       <c r="W30" s="5"/>
-      <c r="X30" s="239"/>
+      <c r="X30" s="308"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
@@ -6363,10 +6373,10 @@
         <f>ROUND((AVERAGE(Q31:S31)/(P31*X27)),4)</f>
         <v>0.14549999999999999</v>
       </c>
-      <c r="U31" s="237"/>
+      <c r="U31" s="306"/>
       <c r="V31" s="13"/>
       <c r="W31" s="5"/>
-      <c r="X31" s="239"/>
+      <c r="X31" s="308"/>
     </row>
     <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
@@ -6424,10 +6434,10 @@
         <f>ROUND((AVERAGE(Q32:S32)/(P32*X27)),4)</f>
         <v>0.1454</v>
       </c>
-      <c r="U32" s="238"/>
+      <c r="U32" s="307"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="240"/>
+      <c r="X32" s="309"/>
     </row>
     <row r="33" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
@@ -6465,17 +6475,17 @@
         <f t="shared" si="0"/>
         <v>7.2878999999999996</v>
       </c>
-      <c r="P33" s="220" t="s">
+      <c r="P33" s="210" t="s">
         <v>187</v>
       </c>
-      <c r="Q33" s="221"/>
-      <c r="R33" s="221"/>
-      <c r="S33" s="221"/>
-      <c r="T33" s="221"/>
-      <c r="U33" s="221"/>
-      <c r="V33" s="221"/>
-      <c r="W33" s="221"/>
-      <c r="X33" s="222"/>
+      <c r="Q33" s="211"/>
+      <c r="R33" s="211"/>
+      <c r="S33" s="211"/>
+      <c r="T33" s="211"/>
+      <c r="U33" s="211"/>
+      <c r="V33" s="211"/>
+      <c r="W33" s="211"/>
+      <c r="X33" s="212"/>
     </row>
     <row r="34" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
@@ -6550,18 +6560,18 @@
         <f t="shared" si="0"/>
         <v>14.5259</v>
       </c>
-      <c r="P35" s="210" t="s">
+      <c r="P35" s="310" t="s">
         <v>188</v>
       </c>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
-      <c r="U35" s="211"/>
-      <c r="V35" s="241"/>
-      <c r="W35" s="241"/>
-      <c r="X35" s="241"/>
-      <c r="Y35" s="212"/>
+      <c r="Q35" s="311"/>
+      <c r="R35" s="311"/>
+      <c r="S35" s="311"/>
+      <c r="T35" s="311"/>
+      <c r="U35" s="311"/>
+      <c r="V35" s="312"/>
+      <c r="W35" s="312"/>
+      <c r="X35" s="312"/>
+      <c r="Y35" s="313"/>
     </row>
     <row r="36" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
@@ -6602,13 +6612,13 @@
       <c r="P36" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="Q36" s="242" t="s">
+      <c r="Q36" s="314" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="242"/>
-      <c r="S36" s="242"/>
-      <c r="T36" s="242"/>
-      <c r="U36" s="243"/>
+      <c r="R36" s="314"/>
+      <c r="S36" s="314"/>
+      <c r="T36" s="314"/>
+      <c r="U36" s="315"/>
       <c r="V36" s="18" t="s">
         <v>189</v>
       </c>
@@ -6966,18 +6976,18 @@
         <f t="shared" si="0"/>
         <v>29.098600000000001</v>
       </c>
-      <c r="P41" s="220" t="s">
+      <c r="P41" s="210" t="s">
         <v>191</v>
       </c>
-      <c r="Q41" s="221"/>
-      <c r="R41" s="221"/>
-      <c r="S41" s="221"/>
-      <c r="T41" s="221"/>
-      <c r="U41" s="221"/>
-      <c r="V41" s="221"/>
-      <c r="W41" s="221"/>
-      <c r="X41" s="221"/>
-      <c r="Y41" s="222"/>
+      <c r="Q41" s="211"/>
+      <c r="R41" s="211"/>
+      <c r="S41" s="211"/>
+      <c r="T41" s="211"/>
+      <c r="U41" s="211"/>
+      <c r="V41" s="211"/>
+      <c r="W41" s="211"/>
+      <c r="X41" s="211"/>
+      <c r="Y41" s="212"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
@@ -7055,10 +7065,10 @@
         <f t="shared" si="0"/>
         <v>50.876800000000003</v>
       </c>
-      <c r="P43" s="223" t="s">
+      <c r="P43" s="180" t="s">
         <v>192</v>
       </c>
-      <c r="Q43" s="224"/>
+      <c r="Q43" s="296"/>
       <c r="R43" s="72" t="s">
         <v>164</v>
       </c>
@@ -7154,12 +7164,12 @@
         <f t="shared" si="0"/>
         <v>2.0246</v>
       </c>
-      <c r="P45" s="225" t="s">
+      <c r="P45" s="297" t="s">
         <v>193</v>
       </c>
-      <c r="Q45" s="226"/>
-      <c r="R45" s="226"/>
-      <c r="S45" s="227"/>
+      <c r="Q45" s="298"/>
+      <c r="R45" s="298"/>
+      <c r="S45" s="299"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
@@ -7197,10 +7207,10 @@
         <f t="shared" si="0"/>
         <v>20.186800000000002</v>
       </c>
-      <c r="P46" s="225"/>
-      <c r="Q46" s="226"/>
-      <c r="R46" s="226"/>
-      <c r="S46" s="227"/>
+      <c r="P46" s="297"/>
+      <c r="Q46" s="298"/>
+      <c r="R46" s="298"/>
+      <c r="S46" s="299"/>
     </row>
     <row r="47" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
@@ -7238,9 +7248,9 @@
         <f t="shared" si="0"/>
         <v>20.193899999999999</v>
       </c>
-      <c r="P47" s="228"/>
-      <c r="Q47" s="229"/>
-      <c r="R47" s="229"/>
+      <c r="P47" s="229"/>
+      <c r="Q47" s="300"/>
+      <c r="R47" s="300"/>
       <c r="S47" s="230"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -7455,17 +7465,17 @@
       <c r="J56" s="80"/>
     </row>
     <row r="57" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="231" t="s">
+      <c r="A57" s="301" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="232"/>
-      <c r="C57" s="232"/>
-      <c r="D57" s="232"/>
-      <c r="E57" s="232"/>
-      <c r="F57" s="232"/>
-      <c r="G57" s="232"/>
-      <c r="H57" s="232"/>
-      <c r="I57" s="233"/>
+      <c r="B57" s="302"/>
+      <c r="C57" s="302"/>
+      <c r="D57" s="302"/>
+      <c r="E57" s="302"/>
+      <c r="F57" s="302"/>
+      <c r="G57" s="302"/>
+      <c r="H57" s="302"/>
+      <c r="I57" s="303"/>
       <c r="J57" s="80"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -7507,10 +7517,10 @@
       <c r="G59" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H59" s="234" t="s">
+      <c r="H59" s="291" t="s">
         <v>205</v>
       </c>
-      <c r="I59" s="235"/>
+      <c r="I59" s="292"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="86"/>
@@ -7529,30 +7539,30 @@
       <c r="F60" t="s">
         <v>60</v>
       </c>
-      <c r="H60" s="236">
+      <c r="H60" s="304">
         <v>18.12</v>
       </c>
-      <c r="I60" s="236"/>
+      <c r="I60" s="304"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="F61" t="s">
         <v>62</v>
       </c>
-      <c r="H61" s="248">
+      <c r="H61" s="287">
         <v>19.98</v>
       </c>
-      <c r="I61" s="248"/>
+      <c r="I61" s="287"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="F62" t="s">
         <v>65</v>
       </c>
-      <c r="H62" s="248">
+      <c r="H62" s="287">
         <v>18.7</v>
       </c>
-      <c r="I62" s="248"/>
+      <c r="I62" s="287"/>
       <c r="J62" s="88"/>
       <c r="K62" s="88"/>
     </row>
@@ -7561,10 +7571,10 @@
       <c r="F63" t="s">
         <v>207</v>
       </c>
-      <c r="H63" s="248">
+      <c r="H63" s="287">
         <v>17.62</v>
       </c>
-      <c r="I63" s="248"/>
+      <c r="I63" s="287"/>
       <c r="J63" s="88"/>
       <c r="K63" s="88"/>
     </row>
@@ -7573,27 +7583,27 @@
       <c r="F64" t="s">
         <v>208</v>
       </c>
-      <c r="H64" s="249">
+      <c r="H64" s="290">
         <v>18.79</v>
       </c>
-      <c r="I64" s="249"/>
+      <c r="I64" s="290"/>
       <c r="J64" s="88"/>
       <c r="K64" s="88"/>
     </row>
     <row r="65" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="86"/>
-      <c r="B65" s="216" t="s">
+      <c r="B65" s="277" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="217"/>
+      <c r="C65" s="278"/>
       <c r="D65" s="91">
         <v>18.05</v>
       </c>
-      <c r="H65" s="218">
+      <c r="H65" s="294">
         <f>(H60/3)+(2/3*J65)</f>
         <v>18.555</v>
       </c>
-      <c r="I65" s="219"/>
+      <c r="I65" s="295"/>
       <c r="J65" s="92">
         <f>AVERAGE(H61:I64)</f>
         <v>18.772500000000001</v>
@@ -7608,11 +7618,11 @@
       <c r="G66" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="244" t="str">
+      <c r="H66" s="242" t="str">
         <f>IF(K65&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I66" s="245"/>
+      <c r="I66" s="244"/>
       <c r="J66" s="88"/>
       <c r="K66" s="88"/>
       <c r="P66" s="2"/>
@@ -7673,14 +7683,14 @@
       <c r="G69" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="H69" s="234" t="s">
+      <c r="H69" s="291" t="s">
         <v>205</v>
       </c>
-      <c r="I69" s="235"/>
-      <c r="P69" s="246"/>
-      <c r="Q69" s="246"/>
-      <c r="R69" s="209"/>
-      <c r="S69" s="209"/>
+      <c r="I69" s="292"/>
+      <c r="P69" s="288"/>
+      <c r="Q69" s="288"/>
+      <c r="R69" s="289"/>
+      <c r="S69" s="289"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="86"/>
@@ -7699,68 +7709,68 @@
       <c r="F70" t="s">
         <v>60</v>
       </c>
-      <c r="H70" s="247">
+      <c r="H70" s="293">
         <v>5.5410000000000004</v>
       </c>
-      <c r="I70" s="247"/>
-      <c r="P70" s="246"/>
-      <c r="Q70" s="246"/>
-      <c r="R70" s="209"/>
-      <c r="S70" s="209"/>
+      <c r="I70" s="293"/>
+      <c r="P70" s="288"/>
+      <c r="Q70" s="288"/>
+      <c r="R70" s="289"/>
+      <c r="S70" s="289"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="86"/>
       <c r="F71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" s="248">
+      <c r="H71" s="287">
         <v>11.78</v>
       </c>
-      <c r="I71" s="248"/>
-      <c r="P71" s="246"/>
-      <c r="Q71" s="246"/>
-      <c r="R71" s="209"/>
-      <c r="S71" s="209"/>
+      <c r="I71" s="287"/>
+      <c r="P71" s="288"/>
+      <c r="Q71" s="288"/>
+      <c r="R71" s="289"/>
+      <c r="S71" s="289"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="86"/>
       <c r="F72" t="s">
         <v>65</v>
       </c>
-      <c r="H72" s="248">
+      <c r="H72" s="287">
         <v>12.39</v>
       </c>
-      <c r="I72" s="248"/>
-      <c r="P72" s="246"/>
-      <c r="Q72" s="246"/>
-      <c r="R72" s="209"/>
-      <c r="S72" s="209"/>
+      <c r="I72" s="287"/>
+      <c r="P72" s="288"/>
+      <c r="Q72" s="288"/>
+      <c r="R72" s="289"/>
+      <c r="S72" s="289"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="86"/>
       <c r="F73" t="s">
         <v>207</v>
       </c>
-      <c r="H73" s="248">
+      <c r="H73" s="287">
         <v>11.21</v>
       </c>
-      <c r="I73" s="248"/>
+      <c r="I73" s="287"/>
       <c r="J73" s="88"/>
       <c r="K73" s="88"/>
-      <c r="P73" s="246"/>
-      <c r="Q73" s="246"/>
-      <c r="R73" s="209"/>
-      <c r="S73" s="209"/>
+      <c r="P73" s="288"/>
+      <c r="Q73" s="288"/>
+      <c r="R73" s="289"/>
+      <c r="S73" s="289"/>
     </row>
     <row r="74" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="86"/>
       <c r="F74" t="s">
         <v>208</v>
       </c>
-      <c r="H74" s="249">
+      <c r="H74" s="290">
         <v>12.75</v>
       </c>
-      <c r="I74" s="249"/>
+      <c r="I74" s="290"/>
       <c r="J74" s="95">
         <f>AVERAGE(H71:I74)</f>
         <v>12.032500000000001</v>
@@ -7769,28 +7779,28 @@
         <f>ABS(H75-D75)/D75*100</f>
         <v>4.2097852868708063</v>
       </c>
-      <c r="P74" s="246"/>
-      <c r="Q74" s="246"/>
-      <c r="R74" s="209"/>
-      <c r="S74" s="209"/>
+      <c r="P74" s="288"/>
+      <c r="Q74" s="288"/>
+      <c r="R74" s="289"/>
+      <c r="S74" s="289"/>
     </row>
     <row r="75" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96"/>
-      <c r="B75" s="216" t="s">
+      <c r="B75" s="277" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="217"/>
+      <c r="C75" s="278"/>
       <c r="D75" s="91">
         <v>9.4700000000000006</v>
       </c>
       <c r="E75" s="97"/>
       <c r="F75" s="97"/>
       <c r="G75" s="97"/>
-      <c r="H75" s="260">
+      <c r="H75" s="279">
         <f>(H70/3)+(2/3*J74)</f>
         <v>9.868666666666666</v>
       </c>
-      <c r="I75" s="261"/>
+      <c r="I75" s="280"/>
       <c r="J75" s="98"/>
       <c r="K75" s="98"/>
     </row>
@@ -7798,24 +7808,24 @@
       <c r="G76" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H76" s="223" t="str">
+      <c r="H76" s="180" t="str">
         <f>IF(K74&lt;20,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I76" s="262"/>
+      <c r="I76" s="182"/>
     </row>
     <row r="77" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="263" t="s">
+      <c r="A77" s="281" t="s">
         <v>212</v>
       </c>
-      <c r="B77" s="264"/>
-      <c r="C77" s="264"/>
-      <c r="D77" s="264"/>
-      <c r="E77" s="264"/>
-      <c r="F77" s="264"/>
-      <c r="G77" s="264"/>
-      <c r="H77" s="264"/>
-      <c r="I77" s="265"/>
+      <c r="B77" s="282"/>
+      <c r="C77" s="282"/>
+      <c r="D77" s="282"/>
+      <c r="E77" s="282"/>
+      <c r="F77" s="282"/>
+      <c r="G77" s="282"/>
+      <c r="H77" s="282"/>
+      <c r="I77" s="283"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
@@ -7828,11 +7838,11 @@
       <c r="I79" s="100"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="223" t="s">
+      <c r="A80" s="180" t="s">
         <v>213</v>
       </c>
-      <c r="B80" s="266"/>
-      <c r="C80" s="266"/>
+      <c r="B80" s="181"/>
+      <c r="C80" s="181"/>
       <c r="D80" s="47" t="s">
         <v>214</v>
       </c>
@@ -7849,10 +7859,10 @@
       <c r="A81" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="267" t="s">
+      <c r="B81" s="284" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="268"/>
+      <c r="C81" s="285"/>
       <c r="D81" s="102" t="s">
         <v>216</v>
       </c>
@@ -7861,8 +7871,8 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="88"/>
-      <c r="H81" s="269"/>
-      <c r="I81" s="269"/>
+      <c r="H81" s="286"/>
+      <c r="I81" s="286"/>
       <c r="J81" s="88"/>
       <c r="K81" s="88"/>
     </row>
@@ -7870,11 +7880,11 @@
       <c r="A82" s="104">
         <v>140</v>
       </c>
-      <c r="B82" s="250">
+      <c r="B82" s="268">
         <v>15</v>
       </c>
-      <c r="C82" s="250"/>
-      <c r="D82" s="251" t="s">
+      <c r="C82" s="268"/>
+      <c r="D82" s="269" t="s">
         <v>217</v>
       </c>
       <c r="E82" s="106"/>
@@ -7892,11 +7902,11 @@
       <c r="A83" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="B83" s="254" t="s">
+      <c r="B83" s="272" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="255"/>
-      <c r="D83" s="252"/>
+      <c r="C83" s="263"/>
+      <c r="D83" s="270"/>
       <c r="E83" s="46" t="s">
         <v>221</v>
       </c>
@@ -7917,11 +7927,11 @@
       <c r="A84" s="50">
         <v>1.25</v>
       </c>
-      <c r="B84" s="256">
+      <c r="B84" s="273">
         <v>2.8</v>
       </c>
-      <c r="C84" s="256"/>
-      <c r="D84" s="252"/>
+      <c r="C84" s="273"/>
+      <c r="D84" s="270"/>
       <c r="E84" s="111">
         <f>B84*E81</f>
         <v>1.4</v>
@@ -7947,11 +7957,11 @@
       <c r="A85" s="50">
         <v>2.5</v>
       </c>
-      <c r="B85" s="257">
+      <c r="B85" s="274">
         <v>5</v>
       </c>
-      <c r="C85" s="258"/>
-      <c r="D85" s="252"/>
+      <c r="C85" s="275"/>
+      <c r="D85" s="270"/>
       <c r="E85" s="111">
         <f>B85*E81</f>
         <v>2.5</v>
@@ -7973,11 +7983,11 @@
       <c r="A86" s="113">
         <v>5</v>
       </c>
-      <c r="B86" s="259">
+      <c r="B86" s="276">
         <v>9.8000000000000007</v>
       </c>
-      <c r="C86" s="259"/>
-      <c r="D86" s="253"/>
+      <c r="C86" s="276"/>
+      <c r="D86" s="271"/>
       <c r="E86" s="115">
         <f>B86*E81</f>
         <v>4.9000000000000004</v>
@@ -7996,14 +8006,14 @@
       <c r="K86" s="88"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="282" t="s">
+      <c r="A87" s="254" t="s">
         <v>223</v>
       </c>
-      <c r="B87" s="283"/>
-      <c r="C87" s="283"/>
-      <c r="D87" s="283"/>
-      <c r="E87" s="283"/>
-      <c r="F87" s="284"/>
+      <c r="B87" s="255"/>
+      <c r="C87" s="255"/>
+      <c r="D87" s="255"/>
+      <c r="E87" s="255"/>
+      <c r="F87" s="256"/>
       <c r="G87" s="88"/>
       <c r="H87" s="88"/>
       <c r="I87" s="88"/>
@@ -8011,12 +8021,12 @@
       <c r="K87" s="88"/>
     </row>
     <row r="88" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="285"/>
-      <c r="B88" s="286"/>
-      <c r="C88" s="286"/>
-      <c r="D88" s="286"/>
-      <c r="E88" s="286"/>
-      <c r="F88" s="287"/>
+      <c r="A88" s="257"/>
+      <c r="B88" s="258"/>
+      <c r="C88" s="258"/>
+      <c r="D88" s="258"/>
+      <c r="E88" s="258"/>
+      <c r="F88" s="259"/>
       <c r="G88" s="88"/>
       <c r="H88" s="88"/>
       <c r="I88" s="88"/>
@@ -8031,11 +8041,11 @@
       <c r="B90" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C90" s="266" t="s">
+      <c r="C90" s="181" t="s">
         <v>224</v>
       </c>
-      <c r="D90" s="266"/>
-      <c r="E90" s="262"/>
+      <c r="D90" s="181"/>
+      <c r="E90" s="182"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="118">
@@ -8047,37 +8057,37 @@
       <c r="C91" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="D91" s="288">
+      <c r="D91" s="260">
         <v>107</v>
       </c>
-      <c r="E91" s="289"/>
+      <c r="E91" s="261"/>
       <c r="F91" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="290" t="s">
+      <c r="A92" s="262" t="s">
         <v>225</v>
       </c>
-      <c r="B92" s="255"/>
-      <c r="C92" s="291">
+      <c r="B92" s="263"/>
+      <c r="C92" s="264">
         <v>3</v>
       </c>
-      <c r="D92" s="291"/>
-      <c r="E92" s="291"/>
+      <c r="D92" s="264"/>
+      <c r="E92" s="264"/>
       <c r="F92" s="121" t="str">
         <f>IF(C92&lt;=5,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="292" t="s">
+      <c r="A93" s="265" t="s">
         <v>226</v>
       </c>
-      <c r="B93" s="293"/>
-      <c r="C93" s="293"/>
-      <c r="D93" s="293"/>
-      <c r="E93" s="294"/>
+      <c r="B93" s="266"/>
+      <c r="C93" s="266"/>
+      <c r="D93" s="266"/>
+      <c r="E93" s="267"/>
     </row>
     <row r="94" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="122"/>
@@ -8093,11 +8103,11 @@
       <c r="B95" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="244" t="s">
+      <c r="C95" s="242" t="s">
         <v>227</v>
       </c>
-      <c r="D95" s="270"/>
-      <c r="E95" s="245"/>
+      <c r="D95" s="243"/>
+      <c r="E95" s="244"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="118">
@@ -8109,44 +8119,44 @@
       <c r="C96" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="D96" s="271">
+      <c r="D96" s="245">
         <v>3691</v>
       </c>
-      <c r="E96" s="272"/>
+      <c r="E96" s="246"/>
       <c r="F96" s="120" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="273" t="s">
+      <c r="A97" s="247" t="s">
         <v>225</v>
       </c>
-      <c r="B97" s="274"/>
-      <c r="C97" s="275">
+      <c r="B97" s="248"/>
+      <c r="C97" s="249">
         <v>6.25</v>
       </c>
-      <c r="D97" s="275"/>
-      <c r="E97" s="275"/>
+      <c r="D97" s="249"/>
+      <c r="E97" s="249"/>
       <c r="F97" s="121" t="str">
         <f>IF(C97&gt;=3.12,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="276" t="s">
+      <c r="A98" s="250" t="s">
         <v>228</v>
       </c>
-      <c r="B98" s="277"/>
-      <c r="C98" s="277"/>
-      <c r="D98" s="277"/>
-      <c r="E98" s="278"/>
+      <c r="B98" s="251"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
+      <c r="E98" s="252"/>
     </row>
     <row r="99" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="279"/>
-      <c r="B99" s="280"/>
-      <c r="C99" s="280"/>
-      <c r="D99" s="280"/>
-      <c r="E99" s="281"/>
+      <c r="A99" s="225"/>
+      <c r="B99" s="253"/>
+      <c r="C99" s="253"/>
+      <c r="D99" s="253"/>
+      <c r="E99" s="226"/>
     </row>
     <row r="100" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="128"/>
@@ -8156,18 +8166,18 @@
       <c r="E100" s="128"/>
     </row>
     <row r="101" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="244" t="s">
+      <c r="A101" s="242" t="s">
         <v>229</v>
       </c>
-      <c r="B101" s="270"/>
-      <c r="C101" s="270"/>
-      <c r="D101" s="270"/>
-      <c r="E101" s="270"/>
-      <c r="F101" s="270"/>
-      <c r="G101" s="270"/>
-      <c r="H101" s="270"/>
-      <c r="I101" s="270"/>
-      <c r="J101" s="245"/>
+      <c r="B101" s="243"/>
+      <c r="C101" s="243"/>
+      <c r="D101" s="243"/>
+      <c r="E101" s="243"/>
+      <c r="F101" s="243"/>
+      <c r="G101" s="243"/>
+      <c r="H101" s="243"/>
+      <c r="I101" s="243"/>
+      <c r="J101" s="244"/>
     </row>
     <row r="102" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
@@ -8190,8 +8200,8 @@
         <v>232</v>
       </c>
       <c r="H102" s="130"/>
-      <c r="I102" s="300"/>
-      <c r="J102" s="301"/>
+      <c r="I102" s="219"/>
+      <c r="J102" s="220"/>
     </row>
     <row r="103" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="131">
@@ -8203,24 +8213,24 @@
       <c r="C103" s="133">
         <v>1</v>
       </c>
-      <c r="D103" s="302"/>
-      <c r="E103" s="178"/>
-      <c r="F103" s="178"/>
-      <c r="G103" s="303" t="s">
+      <c r="D103" s="221"/>
+      <c r="E103" s="222"/>
+      <c r="F103" s="222"/>
+      <c r="G103" s="223" t="s">
         <v>233</v>
       </c>
-      <c r="H103" s="304"/>
-      <c r="I103" s="305" t="s">
+      <c r="H103" s="224"/>
+      <c r="I103" s="227" t="s">
         <v>234</v>
       </c>
-      <c r="J103" s="306"/>
-      <c r="K103" s="307" t="s">
+      <c r="J103" s="228"/>
+      <c r="K103" s="231" t="s">
         <v>39</v>
       </c>
-      <c r="L103" s="308"/>
+      <c r="L103" s="232"/>
     </row>
     <row r="104" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="311" t="s">
+      <c r="A104" s="235" t="s">
         <v>96</v>
       </c>
       <c r="B104" s="134" t="s">
@@ -8238,15 +8248,15 @@
       <c r="F104" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="G104" s="279"/>
-      <c r="H104" s="281"/>
-      <c r="I104" s="228"/>
+      <c r="G104" s="225"/>
+      <c r="H104" s="226"/>
+      <c r="I104" s="229"/>
       <c r="J104" s="230"/>
-      <c r="K104" s="309"/>
-      <c r="L104" s="310"/>
+      <c r="K104" s="233"/>
+      <c r="L104" s="234"/>
     </row>
     <row r="105" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="312"/>
+      <c r="A105" s="194"/>
       <c r="B105" s="138"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
@@ -8254,37 +8264,37 @@
       <c r="F105" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="G105" s="313">
+      <c r="G105" s="236">
         <f>ROUND(F102*MAX(B105:E105)/(60*B103),3)</f>
         <v>0</v>
       </c>
-      <c r="H105" s="314"/>
-      <c r="I105" s="315">
+      <c r="H105" s="237"/>
+      <c r="I105" s="238">
         <f>ROUND(8.33*MAX(B105:F105)/(B103*114),3)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="316"/>
-      <c r="K105" s="317" t="str">
+      <c r="J105" s="239"/>
+      <c r="K105" s="240" t="str">
         <f>IF(I105&lt;=1,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="L105" s="318"/>
+      <c r="L105" s="241"/>
     </row>
     <row r="106" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="220" t="s">
+      <c r="A106" s="210" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="221"/>
-      <c r="C106" s="221"/>
-      <c r="D106" s="221"/>
-      <c r="E106" s="221"/>
-      <c r="F106" s="221"/>
-      <c r="G106" s="221"/>
-      <c r="H106" s="221"/>
-      <c r="I106" s="221"/>
-      <c r="J106" s="221"/>
-      <c r="K106" s="221"/>
-      <c r="L106" s="222"/>
+      <c r="B106" s="211"/>
+      <c r="C106" s="211"/>
+      <c r="D106" s="211"/>
+      <c r="E106" s="211"/>
+      <c r="F106" s="211"/>
+      <c r="G106" s="211"/>
+      <c r="H106" s="211"/>
+      <c r="I106" s="211"/>
+      <c r="J106" s="211"/>
+      <c r="K106" s="211"/>
+      <c r="L106" s="212"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -8333,44 +8343,44 @@
       <c r="I112" s="88"/>
     </row>
     <row r="113" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="295" t="s">
+      <c r="A113" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="B113" s="296"/>
-      <c r="C113" s="296"/>
-      <c r="D113" s="296"/>
-      <c r="E113" s="296" t="s">
+      <c r="B113" s="214"/>
+      <c r="C113" s="214"/>
+      <c r="D113" s="214"/>
+      <c r="E113" s="214" t="s">
         <v>244</v>
       </c>
-      <c r="F113" s="296"/>
-      <c r="G113" s="296" t="s">
+      <c r="F113" s="214"/>
+      <c r="G113" s="214" t="s">
         <v>245</v>
       </c>
-      <c r="H113" s="296" t="s">
+      <c r="H113" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="I113" s="298" t="s">
+      <c r="I113" s="217" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="297"/>
-      <c r="B114" s="188"/>
-      <c r="C114" s="188"/>
-      <c r="D114" s="188"/>
-      <c r="E114" s="188"/>
-      <c r="F114" s="188"/>
-      <c r="G114" s="188"/>
-      <c r="H114" s="188"/>
-      <c r="I114" s="299"/>
+      <c r="A114" s="215"/>
+      <c r="B114" s="216"/>
+      <c r="C114" s="216"/>
+      <c r="D114" s="216"/>
+      <c r="E114" s="216"/>
+      <c r="F114" s="216"/>
+      <c r="G114" s="216"/>
+      <c r="H114" s="216"/>
+      <c r="I114" s="218"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="326" t="s">
+      <c r="A115" s="205" t="s">
         <v>247</v>
       </c>
-      <c r="B115" s="327"/>
-      <c r="C115" s="327"/>
-      <c r="D115" s="327"/>
+      <c r="B115" s="206"/>
+      <c r="C115" s="206"/>
+      <c r="D115" s="206"/>
       <c r="E115" s="144">
         <v>2.7E-2</v>
       </c>
@@ -8385,17 +8395,17 @@
         <f>IF(E115&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I115" s="328" t="s">
+      <c r="I115" s="207" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="322" t="s">
+      <c r="A116" s="201" t="s">
         <v>249</v>
       </c>
-      <c r="B116" s="323"/>
-      <c r="C116" s="323"/>
-      <c r="D116" s="323"/>
+      <c r="B116" s="202"/>
+      <c r="C116" s="202"/>
+      <c r="D116" s="202"/>
       <c r="E116" s="148">
         <v>4.3999999999999997E-2</v>
       </c>
@@ -8410,15 +8420,15 @@
         <f t="shared" ref="H116:H119" si="11">IF(E116&lt;=2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I116" s="329"/>
+      <c r="I116" s="208"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="322" t="s">
+      <c r="A117" s="201" t="s">
         <v>250</v>
       </c>
-      <c r="B117" s="323"/>
-      <c r="C117" s="323"/>
-      <c r="D117" s="323"/>
+      <c r="B117" s="202"/>
+      <c r="C117" s="202"/>
+      <c r="D117" s="202"/>
       <c r="E117" s="148">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -8433,15 +8443,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I117" s="329"/>
+      <c r="I117" s="208"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="322" t="s">
+      <c r="A118" s="201" t="s">
         <v>251</v>
       </c>
-      <c r="B118" s="323"/>
-      <c r="C118" s="323"/>
-      <c r="D118" s="323"/>
+      <c r="B118" s="202"/>
+      <c r="C118" s="202"/>
+      <c r="D118" s="202"/>
       <c r="E118" s="148">
         <v>0.04</v>
       </c>
@@ -8456,15 +8466,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I118" s="329"/>
+      <c r="I118" s="208"/>
     </row>
     <row r="119" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="324" t="s">
+      <c r="A119" s="203" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="325"/>
-      <c r="C119" s="325"/>
-      <c r="D119" s="325"/>
+      <c r="B119" s="204"/>
+      <c r="C119" s="204"/>
+      <c r="D119" s="204"/>
       <c r="E119" s="150">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -8479,15 +8489,15 @@
         <f t="shared" si="11"/>
         <v>Pass</v>
       </c>
-      <c r="I119" s="330"/>
+      <c r="I119" s="209"/>
     </row>
     <row r="120" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="345" t="s">
+      <c r="A120" s="196" t="s">
         <v>253</v>
       </c>
-      <c r="B120" s="346"/>
-      <c r="C120" s="346"/>
-      <c r="D120" s="346"/>
+      <c r="B120" s="197"/>
+      <c r="C120" s="197"/>
+      <c r="D120" s="197"/>
       <c r="E120" s="154">
         <v>0.106</v>
       </c>
@@ -8502,17 +8512,17 @@
         <f>IF(E120&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I120" s="319" t="s">
+      <c r="I120" s="198" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="322" t="s">
+      <c r="A121" s="201" t="s">
         <v>255</v>
       </c>
-      <c r="B121" s="323"/>
-      <c r="C121" s="323"/>
-      <c r="D121" s="323"/>
+      <c r="B121" s="202"/>
+      <c r="C121" s="202"/>
+      <c r="D121" s="202"/>
       <c r="E121" s="148">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -8527,15 +8537,15 @@
         <f t="shared" ref="H121:H123" si="12">IF(E121&lt;=0.2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="I121" s="320"/>
+      <c r="I121" s="199"/>
     </row>
     <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="322" t="s">
+      <c r="A122" s="201" t="s">
         <v>256</v>
       </c>
-      <c r="B122" s="323"/>
-      <c r="C122" s="323"/>
-      <c r="D122" s="323"/>
+      <c r="B122" s="202"/>
+      <c r="C122" s="202"/>
+      <c r="D122" s="202"/>
       <c r="E122" s="148">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -8550,15 +8560,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I122" s="320"/>
+      <c r="I122" s="199"/>
     </row>
     <row r="123" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="322" t="s">
+      <c r="A123" s="201" t="s">
         <v>257</v>
       </c>
-      <c r="B123" s="323"/>
-      <c r="C123" s="323"/>
-      <c r="D123" s="323"/>
+      <c r="B123" s="202"/>
+      <c r="C123" s="202"/>
+      <c r="D123" s="202"/>
       <c r="E123" s="148">
         <v>2.4E-2</v>
       </c>
@@ -8573,15 +8583,15 @@
         <f t="shared" si="12"/>
         <v>Pass</v>
       </c>
-      <c r="I123" s="320"/>
+      <c r="I123" s="199"/>
     </row>
     <row r="124" spans="1:15" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="324" t="s">
+      <c r="A124" s="203" t="s">
         <v>258</v>
       </c>
-      <c r="B124" s="325"/>
-      <c r="C124" s="325"/>
-      <c r="D124" s="325"/>
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+      <c r="D124" s="204"/>
       <c r="E124" s="150"/>
       <c r="F124" s="151" t="s">
         <v>128</v>
@@ -8592,7 +8602,7 @@
       <c r="H124" s="153" t="s">
         <v>259</v>
       </c>
-      <c r="I124" s="321"/>
+      <c r="I124" s="200"/>
     </row>
     <row r="125" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H125" s="88"/>
@@ -8613,15 +8623,15 @@
       <c r="I126" s="88"/>
     </row>
     <row r="127" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="223" t="s">
+      <c r="A127" s="180" t="s">
         <v>262</v>
       </c>
-      <c r="B127" s="266"/>
-      <c r="C127" s="266"/>
-      <c r="D127" s="266"/>
-      <c r="E127" s="266"/>
-      <c r="F127" s="266"/>
-      <c r="G127" s="262"/>
+      <c r="B127" s="181"/>
+      <c r="C127" s="181"/>
+      <c r="D127" s="181"/>
+      <c r="E127" s="181"/>
+      <c r="F127" s="181"/>
+      <c r="G127" s="182"/>
       <c r="H127" s="98"/>
       <c r="I127" s="98"/>
       <c r="J127" s="98"/>
@@ -8635,12 +8645,12 @@
       <c r="A128" s="99" t="s">
         <v>263</v>
       </c>
-      <c r="B128" s="194" t="s">
+      <c r="B128" s="183" t="s">
         <v>264</v>
       </c>
-      <c r="C128" s="195"/>
-      <c r="D128" s="195"/>
-      <c r="E128" s="196"/>
+      <c r="C128" s="184"/>
+      <c r="D128" s="184"/>
+      <c r="E128" s="185"/>
       <c r="F128" s="162" t="s">
         <v>265</v>
       </c>
@@ -8727,15 +8737,15 @@
       <c r="O130" s="98"/>
     </row>
     <row r="131" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="336" t="s">
+      <c r="A131" s="186" t="s">
         <v>270</v>
       </c>
-      <c r="B131" s="332"/>
-      <c r="C131" s="332"/>
-      <c r="D131" s="332"/>
-      <c r="E131" s="332"/>
-      <c r="F131" s="332"/>
-      <c r="G131" s="333"/>
+      <c r="B131" s="176"/>
+      <c r="C131" s="176"/>
+      <c r="D131" s="176"/>
+      <c r="E131" s="176"/>
+      <c r="F131" s="176"/>
+      <c r="G131" s="177"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
       <c r="J131" s="88"/>
@@ -8746,15 +8756,15 @@
       <c r="O131" s="98"/>
     </row>
     <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="337" t="s">
+      <c r="A132" s="187" t="s">
         <v>271</v>
       </c>
-      <c r="B132" s="338"/>
-      <c r="C132" s="338"/>
-      <c r="D132" s="338"/>
-      <c r="E132" s="338"/>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="B132" s="188"/>
+      <c r="C132" s="188"/>
+      <c r="D132" s="188"/>
+      <c r="E132" s="188"/>
+      <c r="F132" s="188"/>
+      <c r="G132" s="189"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
       <c r="J132" s="88"/>
@@ -8765,13 +8775,13 @@
       <c r="O132" s="98"/>
     </row>
     <row r="133" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="340"/>
-      <c r="B133" s="341"/>
-      <c r="C133" s="341"/>
-      <c r="D133" s="341"/>
-      <c r="E133" s="341"/>
-      <c r="F133" s="341"/>
-      <c r="G133" s="342"/>
+      <c r="A133" s="190"/>
+      <c r="B133" s="191"/>
+      <c r="C133" s="191"/>
+      <c r="D133" s="191"/>
+      <c r="E133" s="191"/>
+      <c r="F133" s="191"/>
+      <c r="G133" s="192"/>
       <c r="H133" s="98"/>
       <c r="I133" s="98"/>
       <c r="J133" s="98"/>
@@ -8878,7 +8888,7 @@
       <c r="O139" s="98"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="343" t="s">
+      <c r="A140" s="193" t="s">
         <v>2</v>
       </c>
       <c r="B140" s="20">
@@ -8909,7 +8919,7 @@
       <c r="O140" s="98"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="312"/>
+      <c r="A141" s="194"/>
       <c r="B141" s="20">
         <f>B140-B140</f>
         <v>0</v>
@@ -8945,7 +8955,7 @@
     </row>
     <row r="142" spans="1:15" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="96"/>
-      <c r="B142" s="344" t="s">
+      <c r="B142" s="195" t="s">
         <v>275</v>
       </c>
       <c r="C142" s="173">
@@ -8979,7 +8989,7 @@
     </row>
     <row r="143" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="96"/>
-      <c r="B143" s="344"/>
+      <c r="B143" s="195"/>
       <c r="C143" s="20" t="str">
         <f t="shared" ref="C143:E143" si="14">IF(C142&gt;1,"Fail","Pass")</f>
         <v>Pass</v>
@@ -9010,26 +9020,26 @@
       <c r="O143" s="98"/>
     </row>
     <row r="144" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="331" t="s">
+      <c r="A144" s="175" t="s">
         <v>276</v>
       </c>
-      <c r="B144" s="332"/>
-      <c r="C144" s="332"/>
-      <c r="D144" s="332"/>
-      <c r="E144" s="332"/>
-      <c r="F144" s="332"/>
-      <c r="G144" s="333"/>
+      <c r="B144" s="176"/>
+      <c r="C144" s="176"/>
+      <c r="D144" s="176"/>
+      <c r="E144" s="176"/>
+      <c r="F144" s="176"/>
+      <c r="G144" s="177"/>
     </row>
     <row r="145" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="331" t="s">
+      <c r="A145" s="175" t="s">
         <v>277</v>
       </c>
-      <c r="B145" s="334"/>
-      <c r="C145" s="334"/>
-      <c r="D145" s="334"/>
-      <c r="E145" s="334"/>
-      <c r="F145" s="334"/>
-      <c r="G145" s="335"/>
+      <c r="B145" s="178"/>
+      <c r="C145" s="178"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="179"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9045,26 +9055,107 @@
     <protectedRange sqref="A126" name="Range10"/>
   </protectedRanges>
   <mergeCells count="136">
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A145:G145"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A132:G133"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="I120:I124"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="P25:U25"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="P41:Y41"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P45:S47"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="U29:U32"/>
+    <mergeCell ref="X29:X32"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P35:Y35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:E99"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A87:F88"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A113:D114"/>
     <mergeCell ref="E113:F114"/>
@@ -9080,107 +9171,26 @@
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="K105:L105"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A98:E99"/>
-    <mergeCell ref="A101:J101"/>
-    <mergeCell ref="A87:F88"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="P41:Y41"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P45:S47"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="U29:U32"/>
-    <mergeCell ref="X29:X32"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P35:Y35"/>
-    <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="P25:U25"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="I120:I124"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A132:G133"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A120:D120"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C142:G142">
